--- a/gstdatabase/GSTR-3B-2024-2025.xlsx
+++ b/gstdatabase/GSTR-3B-2024-2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Feb-26\GST Statistics Downloads 28th Feb 26\Downloads\GSTR 3B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\May-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 3B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CAE2BC2-1D16-45B9-BE5D-8A06DB4F0DD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C43DF8B-1BF7-4E56-BD14-C6E4CE357A6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -185,10 +185,10 @@
     <t>FINANCIAL YEAR 2024-2025</t>
   </si>
   <si>
-    <t>Data Considered upto 28th Feb 2026</t>
+    <t>Data Considered upto 31st May 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 28th Feb 2026</t>
+    <t>Filing %age as on 31st May 2026</t>
   </si>
 </sst>
 </file>
@@ -415,15 +415,6 @@
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="17" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -435,6 +426,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
@@ -865,10 +865,10 @@
       <c r="BJ2" s="2"/>
     </row>
     <row r="3" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="29"/>
+      <c r="B3" s="26"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -1189,100 +1189,100 @@
       <c r="BJ7" s="1"/>
     </row>
     <row r="8" spans="1:62" s="15" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="23">
         <v>45383</v>
       </c>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="26">
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="23">
         <v>45413</v>
       </c>
-      <c r="I8" s="27"/>
-      <c r="J8" s="27"/>
-      <c r="K8" s="27"/>
-      <c r="L8" s="28"/>
-      <c r="M8" s="26">
+      <c r="I8" s="24"/>
+      <c r="J8" s="24"/>
+      <c r="K8" s="24"/>
+      <c r="L8" s="25"/>
+      <c r="M8" s="23">
         <v>45444</v>
       </c>
-      <c r="N8" s="27"/>
-      <c r="O8" s="27"/>
-      <c r="P8" s="27"/>
-      <c r="Q8" s="28"/>
-      <c r="R8" s="26">
+      <c r="N8" s="24"/>
+      <c r="O8" s="24"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="25"/>
+      <c r="R8" s="23">
         <v>45474</v>
       </c>
-      <c r="S8" s="27"/>
-      <c r="T8" s="27"/>
-      <c r="U8" s="27"/>
-      <c r="V8" s="28"/>
-      <c r="W8" s="26">
+      <c r="S8" s="24"/>
+      <c r="T8" s="24"/>
+      <c r="U8" s="24"/>
+      <c r="V8" s="25"/>
+      <c r="W8" s="23">
         <v>45505</v>
       </c>
-      <c r="X8" s="27"/>
-      <c r="Y8" s="27"/>
-      <c r="Z8" s="27"/>
-      <c r="AA8" s="28"/>
-      <c r="AB8" s="26">
+      <c r="X8" s="24"/>
+      <c r="Y8" s="24"/>
+      <c r="Z8" s="24"/>
+      <c r="AA8" s="25"/>
+      <c r="AB8" s="23">
         <v>45536</v>
       </c>
-      <c r="AC8" s="27"/>
-      <c r="AD8" s="27"/>
-      <c r="AE8" s="27"/>
-      <c r="AF8" s="28"/>
-      <c r="AG8" s="26">
+      <c r="AC8" s="24"/>
+      <c r="AD8" s="24"/>
+      <c r="AE8" s="24"/>
+      <c r="AF8" s="25"/>
+      <c r="AG8" s="23">
         <v>45566</v>
       </c>
-      <c r="AH8" s="27"/>
-      <c r="AI8" s="27"/>
-      <c r="AJ8" s="27"/>
-      <c r="AK8" s="28"/>
-      <c r="AL8" s="26">
+      <c r="AH8" s="24"/>
+      <c r="AI8" s="24"/>
+      <c r="AJ8" s="24"/>
+      <c r="AK8" s="25"/>
+      <c r="AL8" s="23">
         <v>45597</v>
       </c>
-      <c r="AM8" s="27"/>
-      <c r="AN8" s="27"/>
-      <c r="AO8" s="27"/>
-      <c r="AP8" s="28"/>
-      <c r="AQ8" s="26">
+      <c r="AM8" s="24"/>
+      <c r="AN8" s="24"/>
+      <c r="AO8" s="24"/>
+      <c r="AP8" s="25"/>
+      <c r="AQ8" s="23">
         <v>45627</v>
       </c>
-      <c r="AR8" s="27"/>
-      <c r="AS8" s="27"/>
-      <c r="AT8" s="27"/>
-      <c r="AU8" s="28"/>
-      <c r="AV8" s="26">
+      <c r="AR8" s="24"/>
+      <c r="AS8" s="24"/>
+      <c r="AT8" s="24"/>
+      <c r="AU8" s="25"/>
+      <c r="AV8" s="23">
         <v>45658</v>
       </c>
-      <c r="AW8" s="27"/>
-      <c r="AX8" s="27"/>
-      <c r="AY8" s="27"/>
-      <c r="AZ8" s="28"/>
-      <c r="BA8" s="26">
+      <c r="AW8" s="24"/>
+      <c r="AX8" s="24"/>
+      <c r="AY8" s="24"/>
+      <c r="AZ8" s="25"/>
+      <c r="BA8" s="23">
         <v>45689</v>
       </c>
-      <c r="BB8" s="27"/>
-      <c r="BC8" s="27"/>
-      <c r="BD8" s="27"/>
-      <c r="BE8" s="28"/>
-      <c r="BF8" s="26">
+      <c r="BB8" s="24"/>
+      <c r="BC8" s="24"/>
+      <c r="BD8" s="24"/>
+      <c r="BE8" s="25"/>
+      <c r="BF8" s="23">
         <v>45717</v>
       </c>
-      <c r="BG8" s="27"/>
-      <c r="BH8" s="27"/>
-      <c r="BI8" s="27"/>
-      <c r="BJ8" s="28"/>
+      <c r="BG8" s="24"/>
+      <c r="BH8" s="24"/>
+      <c r="BI8" s="24"/>
+      <c r="BJ8" s="25"/>
     </row>
     <row r="9" spans="1:62" s="15" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="24"/>
-      <c r="B9" s="25"/>
+      <c r="A9" s="28"/>
+      <c r="B9" s="29"/>
       <c r="C9" s="16" t="s">
         <v>2</v>
       </c>
@@ -1479,14 +1479,14 @@
       </c>
       <c r="E10" s="4">
         <f>F10-D10</f>
-        <v>15628</v>
+        <v>15640</v>
       </c>
       <c r="F10" s="13">
-        <v>73018</v>
+        <v>73030</v>
       </c>
       <c r="G10" s="5">
         <f>F10/C10</f>
-        <v>1.0014812782883007</v>
+        <v>1.0016458647647786</v>
       </c>
       <c r="H10" s="7">
         <v>74548</v>
@@ -1496,14 +1496,14 @@
       </c>
       <c r="J10" s="4">
         <f>K10-I10</f>
-        <v>15533</v>
+        <v>15550</v>
       </c>
       <c r="K10" s="13">
-        <v>74089</v>
+        <v>74106</v>
       </c>
       <c r="L10" s="5">
         <f>K10/H10</f>
-        <v>0.99384289316950158</v>
+        <v>0.99407093416322367</v>
       </c>
       <c r="M10" s="7">
         <v>129395</v>
@@ -1513,14 +1513,14 @@
       </c>
       <c r="O10" s="4">
         <f>P10-N10</f>
-        <v>25045</v>
+        <v>25075</v>
       </c>
       <c r="P10" s="6">
-        <v>129022</v>
+        <v>129052</v>
       </c>
       <c r="Q10" s="5">
         <f>P10/M10</f>
-        <v>0.99711735383902</v>
+        <v>0.99734920205572086</v>
       </c>
       <c r="R10" s="7">
         <v>72583</v>
@@ -1530,14 +1530,14 @@
       </c>
       <c r="T10" s="4">
         <f>U10-S10</f>
-        <v>14213</v>
+        <v>14230</v>
       </c>
       <c r="U10" s="13">
-        <v>73041</v>
+        <v>73058</v>
       </c>
       <c r="V10" s="5">
         <f>U10/R10</f>
-        <v>1.0063100174972102</v>
+        <v>1.006544232120469</v>
       </c>
       <c r="W10" s="7">
         <v>74384</v>
@@ -1547,14 +1547,14 @@
       </c>
       <c r="Y10" s="4">
         <f>Z10-X10</f>
-        <v>15672</v>
+        <v>15701</v>
       </c>
       <c r="Z10" s="13">
-        <v>73629</v>
+        <v>73658</v>
       </c>
       <c r="AA10" s="5">
         <f>Z10/W10</f>
-        <v>0.98984996773499678</v>
+        <v>0.99023983652398362</v>
       </c>
       <c r="AB10" s="7">
         <v>130621</v>
@@ -1564,14 +1564,14 @@
       </c>
       <c r="AD10" s="4">
         <f>AE10-AC10</f>
-        <v>26301</v>
+        <v>26355</v>
       </c>
       <c r="AE10" s="6">
-        <v>129854</v>
+        <v>129908</v>
       </c>
       <c r="AF10" s="5">
         <f>AE10/AB10</f>
-        <v>0.99412804985415826</v>
+        <v>0.99454145964278329</v>
       </c>
       <c r="AG10" s="7">
         <v>72721</v>
@@ -1581,14 +1581,14 @@
       </c>
       <c r="AI10" s="4">
         <f>AJ10-AH10</f>
-        <v>14451</v>
+        <v>14485</v>
       </c>
       <c r="AJ10" s="6">
-        <v>72665</v>
+        <v>72699</v>
       </c>
       <c r="AK10" s="5">
         <f>AJ10/AG10</f>
-        <v>0.99922993358177148</v>
+        <v>0.99969747390712449</v>
       </c>
       <c r="AL10" s="7">
         <v>74187</v>
@@ -1598,14 +1598,14 @@
       </c>
       <c r="AN10" s="4">
         <f>AO10-AM10</f>
-        <v>13027</v>
+        <v>13063</v>
       </c>
       <c r="AO10" s="6">
-        <v>73712</v>
+        <v>73748</v>
       </c>
       <c r="AP10" s="5">
         <f>AO10/AL10</f>
-        <v>0.9935972609756426</v>
+        <v>0.99408252119643603</v>
       </c>
       <c r="AQ10" s="7">
         <v>132270</v>
@@ -1615,14 +1615,14 @@
       </c>
       <c r="AS10" s="4">
         <f>AT10-AR10</f>
-        <v>21450</v>
+        <v>21531</v>
       </c>
       <c r="AT10" s="6">
-        <v>131930</v>
+        <v>132011</v>
       </c>
       <c r="AU10" s="5">
         <f>AT10/AQ10</f>
-        <v>0.9974295002646103</v>
+        <v>0.99804188402510019</v>
       </c>
       <c r="AV10" s="7">
         <v>73561</v>
@@ -1632,14 +1632,14 @@
       </c>
       <c r="AX10" s="4">
         <f>AY10-AW10</f>
-        <v>12782</v>
+        <v>12826</v>
       </c>
       <c r="AY10" s="6">
-        <v>73531</v>
+        <v>73575</v>
       </c>
       <c r="AZ10" s="5">
         <f>AY10/AV10</f>
-        <v>0.99959217520153343</v>
+        <v>1.0001903182392844</v>
       </c>
       <c r="BA10" s="7">
         <v>75582</v>
@@ -1649,14 +1649,14 @@
       </c>
       <c r="BC10" s="4">
         <f>BD10-BB10</f>
-        <v>12446</v>
+        <v>12511</v>
       </c>
       <c r="BD10" s="6">
-        <v>74411</v>
+        <v>74476</v>
       </c>
       <c r="BE10" s="5">
         <f>BD10/BA10</f>
-        <v>0.98450689317562379</v>
+        <v>0.98536688629567881</v>
       </c>
       <c r="BF10" s="7">
         <v>134150</v>
@@ -1666,14 +1666,14 @@
       </c>
       <c r="BH10" s="4">
         <f>BI10-BG10</f>
-        <v>32879</v>
+        <v>33039</v>
       </c>
       <c r="BI10" s="6">
-        <v>133346</v>
+        <v>133506</v>
       </c>
       <c r="BJ10" s="5">
         <f>BI10/BF10</f>
-        <v>0.99400670890793885</v>
+        <v>0.9951994036526276</v>
       </c>
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.3">
@@ -1691,14 +1691,14 @@
       </c>
       <c r="E11" s="4">
         <f t="shared" ref="E11:E33" si="0">F11-D11</f>
-        <v>8226</v>
+        <v>8247</v>
       </c>
       <c r="F11" s="13">
-        <v>46464</v>
+        <v>46485</v>
       </c>
       <c r="G11" s="5">
         <f t="shared" ref="G11:G33" si="1">F11/C11</f>
-        <v>0.99834554478846604</v>
+        <v>0.99879675984615712</v>
       </c>
       <c r="H11" s="7">
         <v>47616</v>
@@ -1708,14 +1708,14 @@
       </c>
       <c r="J11" s="4">
         <f t="shared" ref="J11:J33" si="2">K11-I11</f>
-        <v>8123</v>
+        <v>8141</v>
       </c>
       <c r="K11" s="13">
-        <v>47120</v>
+        <v>47138</v>
       </c>
       <c r="L11" s="5">
         <f t="shared" ref="L11:L33" si="3">K11/H11</f>
-        <v>0.98958333333333337</v>
+        <v>0.98996135752688175</v>
       </c>
       <c r="M11" s="7">
         <v>108402</v>
@@ -1725,14 +1725,14 @@
       </c>
       <c r="O11" s="4">
         <f t="shared" ref="O11:O33" si="4">P11-N11</f>
-        <v>16770</v>
+        <v>16815</v>
       </c>
       <c r="P11" s="6">
-        <v>107728</v>
+        <v>107773</v>
       </c>
       <c r="Q11" s="5">
         <f t="shared" ref="Q11:Q33" si="5">P11/M11</f>
-        <v>0.99378240253869854</v>
+        <v>0.99419752403092199</v>
       </c>
       <c r="R11" s="7">
         <v>46539</v>
@@ -1742,14 +1742,14 @@
       </c>
       <c r="T11" s="4">
         <f t="shared" ref="T11:T33" si="6">U11-S11</f>
-        <v>8170</v>
+        <v>8192</v>
       </c>
       <c r="U11" s="13">
-        <v>46438</v>
+        <v>46460</v>
       </c>
       <c r="V11" s="5">
         <f t="shared" ref="V11:V33" si="7">U11/R11</f>
-        <v>0.99782977717613186</v>
+        <v>0.99830249897935064</v>
       </c>
       <c r="W11" s="7">
         <v>48300</v>
@@ -1759,14 +1759,14 @@
       </c>
       <c r="Y11" s="4">
         <f t="shared" ref="Y11:Y33" si="8">Z11-X11</f>
-        <v>8344</v>
+        <v>8368</v>
       </c>
       <c r="Z11" s="13">
-        <v>47049</v>
+        <v>47073</v>
       </c>
       <c r="AA11" s="5">
         <f t="shared" ref="AA11:AA33" si="9">Z11/W11</f>
-        <v>0.97409937888198761</v>
+        <v>0.97459627329192544</v>
       </c>
       <c r="AB11" s="7">
         <v>109219</v>
@@ -1776,14 +1776,14 @@
       </c>
       <c r="AD11" s="4">
         <f t="shared" ref="AD11:AD33" si="10">AE11-AC11</f>
-        <v>18070</v>
+        <v>18132</v>
       </c>
       <c r="AE11" s="6">
-        <v>108352</v>
+        <v>108414</v>
       </c>
       <c r="AF11" s="5">
         <f t="shared" ref="AF11:AF33" si="11">AE11/AB11</f>
-        <v>0.99206182074547467</v>
+        <v>0.9926294875433761</v>
       </c>
       <c r="AG11" s="7">
         <v>46763</v>
@@ -1793,14 +1793,14 @@
       </c>
       <c r="AI11" s="4">
         <f t="shared" ref="AI11:AI47" si="12">AJ11-AH11</f>
-        <v>8283</v>
+        <v>8315</v>
       </c>
       <c r="AJ11" s="6">
-        <v>46652</v>
+        <v>46684</v>
       </c>
       <c r="AK11" s="5">
         <f t="shared" ref="AK11:AK33" si="13">AJ11/AG11</f>
-        <v>0.99762632850758082</v>
+        <v>0.99831063019908906</v>
       </c>
       <c r="AL11" s="7">
         <v>48206</v>
@@ -1810,14 +1810,14 @@
       </c>
       <c r="AN11" s="4">
         <f t="shared" ref="AN11:AN33" si="14">AO11-AM11</f>
-        <v>7491</v>
+        <v>7523</v>
       </c>
       <c r="AO11" s="6">
-        <v>47180</v>
+        <v>47212</v>
       </c>
       <c r="AP11" s="5">
         <f t="shared" ref="AP11:AP33" si="15">AO11/AL11</f>
-        <v>0.97871634236402105</v>
+        <v>0.9793801601460399</v>
       </c>
       <c r="AQ11" s="7">
         <v>110196</v>
@@ -1827,14 +1827,14 @@
       </c>
       <c r="AS11" s="4">
         <f t="shared" ref="AS11:AS33" si="16">AT11-AR11</f>
-        <v>15014</v>
+        <v>15088</v>
       </c>
       <c r="AT11" s="6">
-        <v>109567</v>
+        <v>109641</v>
       </c>
       <c r="AU11" s="5">
         <f t="shared" ref="AU11:AU33" si="17">AT11/AQ11</f>
-        <v>0.99429198881992087</v>
+        <v>0.99496351954698903</v>
       </c>
       <c r="AV11" s="7">
         <v>47206</v>
@@ -1844,14 +1844,14 @@
       </c>
       <c r="AX11" s="4">
         <f t="shared" ref="AX11:AX33" si="18">AY11-AW11</f>
-        <v>7527</v>
+        <v>7568</v>
       </c>
       <c r="AY11" s="6">
-        <v>46983</v>
+        <v>47024</v>
       </c>
       <c r="AZ11" s="5">
         <f t="shared" ref="AZ11:AZ33" si="19">AY11/AV11</f>
-        <v>0.99527602423420747</v>
+        <v>0.99614455789518286</v>
       </c>
       <c r="BA11" s="7">
         <v>48813</v>
@@ -1861,14 +1861,14 @@
       </c>
       <c r="BC11" s="4">
         <f t="shared" ref="BC11:BC33" si="20">BD11-BB11</f>
-        <v>7380</v>
+        <v>7427</v>
       </c>
       <c r="BD11" s="6">
-        <v>47503</v>
+        <v>47550</v>
       </c>
       <c r="BE11" s="5">
         <f t="shared" ref="BE11:BE33" si="21">BD11/BA11</f>
-        <v>0.97316288693585729</v>
+        <v>0.97412574519083028</v>
       </c>
       <c r="BF11" s="7">
         <v>111276</v>
@@ -1878,14 +1878,14 @@
       </c>
       <c r="BH11" s="4">
         <f t="shared" ref="BH11:BH33" si="22">BI11-BG11</f>
-        <v>20924</v>
+        <v>21067</v>
       </c>
       <c r="BI11" s="6">
-        <v>110473</v>
+        <v>110616</v>
       </c>
       <c r="BJ11" s="5">
         <f t="shared" ref="BJ11:BJ33" si="23">BI11/BF11</f>
-        <v>0.99278370897587975</v>
+        <v>0.99406880189798341</v>
       </c>
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.3">
@@ -1903,14 +1903,14 @@
       </c>
       <c r="E12" s="4">
         <f t="shared" si="0"/>
-        <v>27422</v>
+        <v>27449</v>
       </c>
       <c r="F12" s="13">
-        <v>175747</v>
+        <v>175774</v>
       </c>
       <c r="G12" s="5">
         <f t="shared" si="1"/>
-        <v>0.9924106815140239</v>
+        <v>0.99256314550146529</v>
       </c>
       <c r="H12" s="7">
         <v>181172</v>
@@ -1920,14 +1920,14 @@
       </c>
       <c r="J12" s="4">
         <f t="shared" si="2"/>
-        <v>25281</v>
+        <v>25308</v>
       </c>
       <c r="K12" s="13">
-        <v>178107</v>
+        <v>178134</v>
       </c>
       <c r="L12" s="5">
         <f t="shared" si="3"/>
-        <v>0.98308237475989668</v>
+        <v>0.98323140441127765</v>
       </c>
       <c r="M12" s="7">
         <v>363483</v>
@@ -1937,14 +1937,14 @@
       </c>
       <c r="O12" s="4">
         <f t="shared" si="4"/>
-        <v>56125</v>
+        <v>56194</v>
       </c>
       <c r="P12" s="6">
-        <v>360359</v>
+        <v>360428</v>
       </c>
       <c r="Q12" s="5">
         <f t="shared" si="5"/>
-        <v>0.99140537521699779</v>
+        <v>0.99159520527782596</v>
       </c>
       <c r="R12" s="7">
         <v>177513</v>
@@ -1954,14 +1954,14 @@
       </c>
       <c r="T12" s="4">
         <f t="shared" si="6"/>
-        <v>27008</v>
+        <v>27044</v>
       </c>
       <c r="U12" s="13">
-        <v>177128</v>
+        <v>177164</v>
       </c>
       <c r="V12" s="5">
         <f t="shared" si="7"/>
-        <v>0.99783114476122881</v>
+        <v>0.99803394680952939</v>
       </c>
       <c r="W12" s="7">
         <v>182324</v>
@@ -1971,14 +1971,14 @@
       </c>
       <c r="Y12" s="4">
         <f t="shared" si="8"/>
-        <v>28672</v>
+        <v>28713</v>
       </c>
       <c r="Z12" s="13">
-        <v>178744</v>
+        <v>178785</v>
       </c>
       <c r="AA12" s="5">
         <f t="shared" si="9"/>
-        <v>0.98036462561154869</v>
+        <v>0.98058950001096945</v>
       </c>
       <c r="AB12" s="7">
         <v>365690</v>
@@ -1988,14 +1988,14 @@
       </c>
       <c r="AD12" s="4">
         <f t="shared" si="10"/>
-        <v>60724</v>
+        <v>60833</v>
       </c>
       <c r="AE12" s="6">
-        <v>362287</v>
+        <v>362396</v>
       </c>
       <c r="AF12" s="5">
         <f t="shared" si="11"/>
-        <v>0.99069430391861957</v>
+        <v>0.99099237058710932</v>
       </c>
       <c r="AG12" s="7">
         <v>180670</v>
@@ -2005,14 +2005,14 @@
       </c>
       <c r="AI12" s="4">
         <f t="shared" si="12"/>
-        <v>29969</v>
+        <v>30031</v>
       </c>
       <c r="AJ12" s="6">
-        <v>178346</v>
+        <v>178408</v>
       </c>
       <c r="AK12" s="5">
         <f t="shared" si="13"/>
-        <v>0.98713676869430456</v>
+        <v>0.98747993579454252</v>
       </c>
       <c r="AL12" s="7">
         <v>181581</v>
@@ -2022,14 +2022,14 @@
       </c>
       <c r="AN12" s="4">
         <f t="shared" si="14"/>
-        <v>25631</v>
+        <v>25702</v>
       </c>
       <c r="AO12" s="6">
-        <v>178494</v>
+        <v>178565</v>
       </c>
       <c r="AP12" s="5">
         <f t="shared" si="15"/>
-        <v>0.98299932261635303</v>
+        <v>0.98339033268899279</v>
       </c>
       <c r="AQ12" s="7">
         <v>363376</v>
@@ -2039,14 +2039,14 @@
       </c>
       <c r="AS12" s="4">
         <f t="shared" si="16"/>
-        <v>53997</v>
+        <v>54160</v>
       </c>
       <c r="AT12" s="6">
-        <v>361877</v>
+        <v>362040</v>
       </c>
       <c r="AU12" s="5">
         <f t="shared" si="17"/>
-        <v>0.99587479635418963</v>
+        <v>0.99632336753115236</v>
       </c>
       <c r="AV12" s="7">
         <v>179534</v>
@@ -2056,14 +2056,14 @@
       </c>
       <c r="AX12" s="4">
         <f t="shared" si="18"/>
-        <v>25999</v>
+        <v>26101</v>
       </c>
       <c r="AY12" s="6">
-        <v>178719</v>
+        <v>178821</v>
       </c>
       <c r="AZ12" s="5">
         <f t="shared" si="19"/>
-        <v>0.99546046988314196</v>
+        <v>0.99602860739469956</v>
       </c>
       <c r="BA12" s="7">
         <v>184469</v>
@@ -2073,14 +2073,14 @@
       </c>
       <c r="BC12" s="4">
         <f t="shared" si="20"/>
-        <v>26182</v>
+        <v>26293</v>
       </c>
       <c r="BD12" s="6">
-        <v>181759</v>
+        <v>181870</v>
       </c>
       <c r="BE12" s="5">
         <f t="shared" si="21"/>
-        <v>0.98530918474106766</v>
+        <v>0.98591091186052937</v>
       </c>
       <c r="BF12" s="7">
         <v>368393</v>
@@ -2090,14 +2090,14 @@
       </c>
       <c r="BH12" s="4">
         <f t="shared" si="22"/>
-        <v>76778</v>
+        <v>77069</v>
       </c>
       <c r="BI12" s="6">
-        <v>366741</v>
+        <v>367032</v>
       </c>
       <c r="BJ12" s="5">
         <f t="shared" si="23"/>
-        <v>0.99551565854942958</v>
+        <v>0.99630557583884605</v>
       </c>
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.3">
@@ -2132,14 +2132,14 @@
       </c>
       <c r="J13" s="4">
         <f t="shared" si="2"/>
-        <v>2405</v>
+        <v>2406</v>
       </c>
       <c r="K13" s="13">
-        <v>17676</v>
+        <v>17677</v>
       </c>
       <c r="L13" s="5">
         <f t="shared" si="3"/>
-        <v>9.7564745104099973E-2</v>
+        <v>9.7570264720817784E-2</v>
       </c>
       <c r="M13" s="7">
         <v>28677</v>
@@ -2149,14 +2149,14 @@
       </c>
       <c r="O13" s="4">
         <f t="shared" si="4"/>
-        <v>4346</v>
+        <v>4348</v>
       </c>
       <c r="P13" s="6">
-        <v>28635</v>
+        <v>28637</v>
       </c>
       <c r="Q13" s="5">
         <f t="shared" si="5"/>
-        <v>0.99853541165393866</v>
+        <v>0.99860515395613214</v>
       </c>
       <c r="R13" s="7">
         <v>17606</v>
@@ -2166,14 +2166,14 @@
       </c>
       <c r="T13" s="4">
         <f t="shared" si="6"/>
-        <v>2518</v>
+        <v>2519</v>
       </c>
       <c r="U13" s="13">
-        <v>17618</v>
+        <v>17619</v>
       </c>
       <c r="V13" s="5">
         <f t="shared" si="7"/>
-        <v>1.0006815858230149</v>
+        <v>1.0007383846415994</v>
       </c>
       <c r="W13" s="7">
         <v>17849</v>
@@ -2183,14 +2183,14 @@
       </c>
       <c r="Y13" s="4">
         <f t="shared" si="8"/>
-        <v>2585</v>
+        <v>2586</v>
       </c>
       <c r="Z13" s="13">
-        <v>17747</v>
+        <v>17748</v>
       </c>
       <c r="AA13" s="5">
         <f t="shared" si="9"/>
-        <v>0.99428539413972772</v>
+        <v>0.99434141968737744</v>
       </c>
       <c r="AB13" s="7">
         <v>28890</v>
@@ -2200,14 +2200,14 @@
       </c>
       <c r="AD13" s="4">
         <f t="shared" si="10"/>
-        <v>4664</v>
+        <v>4669</v>
       </c>
       <c r="AE13" s="6">
-        <v>28817</v>
+        <v>28822</v>
       </c>
       <c r="AF13" s="5">
         <f t="shared" si="11"/>
-        <v>0.99747317410868808</v>
+        <v>0.99764624437521632</v>
       </c>
       <c r="AG13" s="7">
         <v>17747</v>
@@ -2217,14 +2217,14 @@
       </c>
       <c r="AI13" s="4">
         <f t="shared" si="12"/>
-        <v>2750</v>
+        <v>2751</v>
       </c>
       <c r="AJ13" s="6">
-        <v>17837</v>
+        <v>17838</v>
       </c>
       <c r="AK13" s="5">
         <f t="shared" si="13"/>
-        <v>1.0050712796528991</v>
+        <v>1.0051276272045979</v>
       </c>
       <c r="AL13" s="7">
         <v>17937</v>
@@ -2234,14 +2234,14 @@
       </c>
       <c r="AN13" s="4">
         <f t="shared" si="14"/>
-        <v>2557</v>
+        <v>2561</v>
       </c>
       <c r="AO13" s="6">
-        <v>17864</v>
+        <v>17868</v>
       </c>
       <c r="AP13" s="5">
         <f t="shared" si="15"/>
-        <v>0.99593020014495182</v>
+        <v>0.99615320287673526</v>
       </c>
       <c r="AQ13" s="7">
         <v>28933</v>
@@ -2251,14 +2251,14 @@
       </c>
       <c r="AS13" s="4">
         <f t="shared" si="16"/>
-        <v>4301</v>
+        <v>4309</v>
       </c>
       <c r="AT13" s="6">
-        <v>28948</v>
+        <v>28956</v>
       </c>
       <c r="AU13" s="5">
         <f t="shared" si="17"/>
-        <v>1.0005184391525248</v>
+        <v>1.0007949400338714</v>
       </c>
       <c r="AV13" s="7">
         <v>17858</v>
@@ -2268,14 +2268,14 @@
       </c>
       <c r="AX13" s="4">
         <f t="shared" si="18"/>
-        <v>2395</v>
+        <v>2398</v>
       </c>
       <c r="AY13" s="6">
-        <v>17904</v>
+        <v>17907</v>
       </c>
       <c r="AZ13" s="5">
         <f t="shared" si="19"/>
-        <v>1.0025758763579349</v>
+        <v>1.0027438682943219</v>
       </c>
       <c r="BA13" s="7">
         <v>18026</v>
@@ -2285,14 +2285,14 @@
       </c>
       <c r="BC13" s="4">
         <f t="shared" si="20"/>
-        <v>2457</v>
+        <v>2466</v>
       </c>
       <c r="BD13" s="6">
-        <v>17919</v>
+        <v>17928</v>
       </c>
       <c r="BE13" s="5">
         <f t="shared" si="21"/>
-        <v>0.99406412959059132</v>
+        <v>0.99456340841007429</v>
       </c>
       <c r="BF13" s="7">
         <v>29023</v>
@@ -2302,14 +2302,14 @@
       </c>
       <c r="BH13" s="4">
         <f t="shared" si="22"/>
-        <v>5631</v>
+        <v>5654</v>
       </c>
       <c r="BI13" s="6">
-        <v>29052</v>
+        <v>29075</v>
       </c>
       <c r="BJ13" s="5">
         <f t="shared" si="23"/>
-        <v>1.0009992075250664</v>
+        <v>1.0017916824587396</v>
       </c>
     </row>
     <row r="14" spans="1:62" x14ac:dyDescent="0.3">
@@ -2327,14 +2327,14 @@
       </c>
       <c r="E14" s="4">
         <f t="shared" si="0"/>
-        <v>18589</v>
+        <v>18620</v>
       </c>
       <c r="F14" s="13">
-        <v>89899</v>
+        <v>89930</v>
       </c>
       <c r="G14" s="5">
         <f t="shared" si="1"/>
-        <v>0.99371048326480083</v>
+        <v>0.99405314586373084</v>
       </c>
       <c r="H14" s="7">
         <v>94129</v>
@@ -2344,14 +2344,14 @@
       </c>
       <c r="J14" s="4">
         <f t="shared" si="2"/>
-        <v>17728</v>
+        <v>17764</v>
       </c>
       <c r="K14" s="13">
-        <v>91347</v>
+        <v>91383</v>
       </c>
       <c r="L14" s="5">
         <f t="shared" si="3"/>
-        <v>0.97044481509417924</v>
+        <v>0.97082726896068161</v>
       </c>
       <c r="M14" s="7">
         <v>164995</v>
@@ -2361,14 +2361,14 @@
       </c>
       <c r="O14" s="4">
         <f t="shared" si="4"/>
-        <v>31625</v>
+        <v>31686</v>
       </c>
       <c r="P14" s="6">
-        <v>163590</v>
+        <v>163651</v>
       </c>
       <c r="Q14" s="5">
         <f t="shared" si="5"/>
-        <v>0.99148459044213466</v>
+        <v>0.99185429861510954</v>
       </c>
       <c r="R14" s="7">
         <v>91074</v>
@@ -2378,14 +2378,14 @@
       </c>
       <c r="T14" s="4">
         <f t="shared" si="6"/>
-        <v>18878</v>
+        <v>18916</v>
       </c>
       <c r="U14" s="13">
-        <v>90816</v>
+        <v>90854</v>
       </c>
       <c r="V14" s="5">
         <f t="shared" si="7"/>
-        <v>0.99716713881019825</v>
+        <v>0.99758438193117682</v>
       </c>
       <c r="W14" s="7">
         <v>93800</v>
@@ -2395,14 +2395,14 @@
       </c>
       <c r="Y14" s="4">
         <f t="shared" si="8"/>
-        <v>18527</v>
+        <v>18575</v>
       </c>
       <c r="Z14" s="13">
-        <v>91310</v>
+        <v>91358</v>
       </c>
       <c r="AA14" s="5">
         <f t="shared" si="9"/>
-        <v>0.97345415778251598</v>
+        <v>0.97396588486140723</v>
       </c>
       <c r="AB14" s="7">
         <v>166352</v>
@@ -2412,14 +2412,14 @@
       </c>
       <c r="AD14" s="4">
         <f t="shared" si="10"/>
-        <v>34869</v>
+        <v>34966</v>
       </c>
       <c r="AE14" s="6">
-        <v>164312</v>
+        <v>164409</v>
       </c>
       <c r="AF14" s="5">
         <f t="shared" si="11"/>
-        <v>0.98773684716745214</v>
+        <v>0.9883199480619409</v>
       </c>
       <c r="AG14" s="7">
         <v>92175</v>
@@ -2429,14 +2429,14 @@
       </c>
       <c r="AI14" s="4">
         <f t="shared" si="12"/>
-        <v>19078</v>
+        <v>19132</v>
       </c>
       <c r="AJ14" s="6">
-        <v>91525</v>
+        <v>91579</v>
       </c>
       <c r="AK14" s="5">
         <f t="shared" si="13"/>
-        <v>0.99294819636560894</v>
+        <v>0.99353403851369682</v>
       </c>
       <c r="AL14" s="7">
         <v>94655</v>
@@ -2446,14 +2446,14 @@
       </c>
       <c r="AN14" s="4">
         <f t="shared" si="14"/>
-        <v>17359</v>
+        <v>17420</v>
       </c>
       <c r="AO14" s="6">
-        <v>92942</v>
+        <v>93003</v>
       </c>
       <c r="AP14" s="5">
         <f t="shared" si="15"/>
-        <v>0.98190269927631924</v>
+        <v>0.98254714489461725</v>
       </c>
       <c r="AQ14" s="7">
         <v>168400</v>
@@ -2463,14 +2463,14 @@
       </c>
       <c r="AS14" s="4">
         <f t="shared" si="16"/>
-        <v>31211</v>
+        <v>31338</v>
       </c>
       <c r="AT14" s="6">
-        <v>167253</v>
+        <v>167380</v>
       </c>
       <c r="AU14" s="5">
         <f t="shared" si="17"/>
-        <v>0.99318883610451303</v>
+        <v>0.99394299287410925</v>
       </c>
       <c r="AV14" s="7">
         <v>94024</v>
@@ -2480,14 +2480,14 @@
       </c>
       <c r="AX14" s="4">
         <f t="shared" si="18"/>
-        <v>16881</v>
+        <v>16953</v>
       </c>
       <c r="AY14" s="6">
-        <v>93469</v>
+        <v>93541</v>
       </c>
       <c r="AZ14" s="5">
         <f t="shared" si="19"/>
-        <v>0.99409725176550667</v>
+        <v>0.99486301369863017</v>
       </c>
       <c r="BA14" s="7">
         <v>96514</v>
@@ -2497,14 +2497,14 @@
       </c>
       <c r="BC14" s="4">
         <f t="shared" si="20"/>
-        <v>16622</v>
+        <v>16711</v>
       </c>
       <c r="BD14" s="6">
-        <v>94850</v>
+        <v>94939</v>
       </c>
       <c r="BE14" s="5">
         <f t="shared" si="21"/>
-        <v>0.98275897797210765</v>
+        <v>0.98368112398201302</v>
       </c>
       <c r="BF14" s="7">
         <v>171502</v>
@@ -2514,14 +2514,14 @@
       </c>
       <c r="BH14" s="4">
         <f t="shared" si="22"/>
-        <v>39570</v>
+        <v>39787</v>
       </c>
       <c r="BI14" s="6">
-        <v>170371</v>
+        <v>170588</v>
       </c>
       <c r="BJ14" s="5">
         <f t="shared" si="23"/>
-        <v>0.99340532471924525</v>
+        <v>0.99467061608610974</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.3">
@@ -2539,14 +2539,14 @@
       </c>
       <c r="E15" s="4">
         <f t="shared" si="0"/>
-        <v>50754</v>
+        <v>50766</v>
       </c>
       <c r="F15" s="13">
-        <v>301900</v>
+        <v>301912</v>
       </c>
       <c r="G15" s="5">
         <f t="shared" si="1"/>
-        <v>0.99129538238258941</v>
+        <v>0.99133478465018998</v>
       </c>
       <c r="H15" s="7">
         <v>309950</v>
@@ -2556,14 +2556,14 @@
       </c>
       <c r="J15" s="4">
         <f t="shared" si="2"/>
-        <v>47809</v>
+        <v>47821</v>
       </c>
       <c r="K15" s="13">
-        <v>306442</v>
+        <v>306454</v>
       </c>
       <c r="L15" s="5">
         <f t="shared" si="3"/>
-        <v>0.98868204549120831</v>
+        <v>0.98872076141313114</v>
       </c>
       <c r="M15" s="7">
         <v>517862</v>
@@ -2573,14 +2573,14 @@
       </c>
       <c r="O15" s="4">
         <f t="shared" si="4"/>
-        <v>81156</v>
+        <v>81188</v>
       </c>
       <c r="P15" s="6">
-        <v>512905</v>
+        <v>512937</v>
       </c>
       <c r="Q15" s="5">
         <f t="shared" si="5"/>
-        <v>0.99042795184817578</v>
+        <v>0.99048974437205284</v>
       </c>
       <c r="R15" s="7">
         <v>307768</v>
@@ -2590,14 +2590,14 @@
       </c>
       <c r="T15" s="4">
         <f t="shared" si="6"/>
-        <v>52532</v>
+        <v>52551</v>
       </c>
       <c r="U15" s="13">
-        <v>306384</v>
+        <v>306403</v>
       </c>
       <c r="V15" s="5">
         <f t="shared" si="7"/>
-        <v>0.99550310623586602</v>
+        <v>0.99556484104910192</v>
       </c>
       <c r="W15" s="7">
         <v>314114</v>
@@ -2607,14 +2607,14 @@
       </c>
       <c r="Y15" s="4">
         <f t="shared" si="8"/>
-        <v>50962</v>
+        <v>50987</v>
       </c>
       <c r="Z15" s="13">
-        <v>308523</v>
+        <v>308548</v>
       </c>
       <c r="AA15" s="5">
         <f t="shared" si="9"/>
-        <v>0.98220072967139316</v>
+        <v>0.98228031861044085</v>
       </c>
       <c r="AB15" s="7">
         <v>523203</v>
@@ -2624,14 +2624,14 @@
       </c>
       <c r="AD15" s="4">
         <f t="shared" si="10"/>
-        <v>91335</v>
+        <v>91398</v>
       </c>
       <c r="AE15" s="6">
-        <v>519112</v>
+        <v>519175</v>
       </c>
       <c r="AF15" s="5">
         <f t="shared" si="11"/>
-        <v>0.9921808552320992</v>
+        <v>0.99230126738569924</v>
       </c>
       <c r="AG15" s="7">
         <v>312916</v>
@@ -2641,14 +2641,14 @@
       </c>
       <c r="AI15" s="4">
         <f t="shared" si="12"/>
-        <v>54234</v>
+        <v>54270</v>
       </c>
       <c r="AJ15" s="6">
-        <v>310774</v>
+        <v>310810</v>
       </c>
       <c r="AK15" s="5">
         <f t="shared" si="13"/>
-        <v>0.99315471244679088</v>
+        <v>0.99326975929642458</v>
       </c>
       <c r="AL15" s="7">
         <v>318942</v>
@@ -2658,14 +2658,14 @@
       </c>
       <c r="AN15" s="4">
         <f t="shared" si="14"/>
-        <v>48539</v>
+        <v>48585</v>
       </c>
       <c r="AO15" s="6">
-        <v>313852</v>
+        <v>313898</v>
       </c>
       <c r="AP15" s="5">
         <f t="shared" si="15"/>
-        <v>0.98404098550833696</v>
+        <v>0.98418521235835987</v>
       </c>
       <c r="AQ15" s="7">
         <v>530087</v>
@@ -2675,14 +2675,14 @@
       </c>
       <c r="AS15" s="4">
         <f t="shared" si="16"/>
-        <v>77377</v>
+        <v>77495</v>
       </c>
       <c r="AT15" s="6">
-        <v>526416</v>
+        <v>526534</v>
       </c>
       <c r="AU15" s="5">
         <f t="shared" si="17"/>
-        <v>0.99307472169662714</v>
+        <v>0.99329732666524551</v>
       </c>
       <c r="AV15" s="7">
         <v>317508</v>
@@ -2692,14 +2692,14 @@
       </c>
       <c r="AX15" s="4">
         <f t="shared" si="18"/>
-        <v>49691</v>
+        <v>49763</v>
       </c>
       <c r="AY15" s="6">
-        <v>316702</v>
+        <v>316774</v>
       </c>
       <c r="AZ15" s="5">
         <f t="shared" si="19"/>
-        <v>0.99746148128551093</v>
+        <v>0.99768824722526672</v>
       </c>
       <c r="BA15" s="7">
         <v>324414</v>
@@ -2709,14 +2709,14 @@
       </c>
       <c r="BC15" s="4">
         <f t="shared" si="20"/>
-        <v>49158</v>
+        <v>49260</v>
       </c>
       <c r="BD15" s="6">
-        <v>320534</v>
+        <v>320636</v>
       </c>
       <c r="BE15" s="5">
         <f t="shared" si="21"/>
-        <v>0.98803997361396245</v>
+        <v>0.98835438667874997</v>
       </c>
       <c r="BF15" s="7">
         <v>538701</v>
@@ -2726,14 +2726,14 @@
       </c>
       <c r="BH15" s="4">
         <f t="shared" si="22"/>
-        <v>107531</v>
+        <v>107817</v>
       </c>
       <c r="BI15" s="6">
-        <v>535814</v>
+        <v>536100</v>
       </c>
       <c r="BJ15" s="5">
         <f t="shared" si="23"/>
-        <v>0.99464081187894582</v>
+        <v>0.99517171863427023</v>
       </c>
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.3">
@@ -2751,14 +2751,14 @@
       </c>
       <c r="E16" s="4">
         <f t="shared" si="0"/>
-        <v>75447</v>
+        <v>75555</v>
       </c>
       <c r="F16" s="13">
-        <v>440362</v>
+        <v>440470</v>
       </c>
       <c r="G16" s="5">
         <f t="shared" si="1"/>
-        <v>0.98807210587015737</v>
+        <v>0.98831443329040247</v>
       </c>
       <c r="H16" s="7">
         <v>453561</v>
@@ -2768,14 +2768,14 @@
       </c>
       <c r="J16" s="4">
         <f t="shared" si="2"/>
-        <v>72191</v>
+        <v>72315</v>
       </c>
       <c r="K16" s="13">
-        <v>444414</v>
+        <v>444538</v>
       </c>
       <c r="L16" s="5">
         <f t="shared" si="3"/>
-        <v>0.97983292214277684</v>
+        <v>0.98010631425541439</v>
       </c>
       <c r="M16" s="7">
         <v>776551</v>
@@ -2785,14 +2785,14 @@
       </c>
       <c r="O16" s="4">
         <f t="shared" si="4"/>
-        <v>126303</v>
+        <v>126555</v>
       </c>
       <c r="P16" s="6">
-        <v>768287</v>
+        <v>768539</v>
       </c>
       <c r="Q16" s="5">
         <f t="shared" si="5"/>
-        <v>0.9893580717815057</v>
+        <v>0.98968258362940742</v>
       </c>
       <c r="R16" s="7">
         <v>446959</v>
@@ -2802,14 +2802,14 @@
       </c>
       <c r="T16" s="4">
         <f t="shared" si="6"/>
-        <v>79064</v>
+        <v>79211</v>
       </c>
       <c r="U16" s="13">
-        <v>443549</v>
+        <v>443696</v>
       </c>
       <c r="V16" s="5">
         <f t="shared" si="7"/>
-        <v>0.99237066487082704</v>
+        <v>0.99269955409780319</v>
       </c>
       <c r="W16" s="7">
         <v>453618</v>
@@ -2819,14 +2819,14 @@
       </c>
       <c r="Y16" s="4">
         <f t="shared" si="8"/>
-        <v>73555</v>
+        <v>73718</v>
       </c>
       <c r="Z16" s="13">
-        <v>442902</v>
+        <v>443065</v>
       </c>
       <c r="AA16" s="5">
         <f t="shared" si="9"/>
-        <v>0.9763765988122165</v>
+        <v>0.9767359319956439</v>
       </c>
       <c r="AB16" s="7">
         <v>775718</v>
@@ -2836,14 +2836,14 @@
       </c>
       <c r="AD16" s="4">
         <f t="shared" si="10"/>
-        <v>135252</v>
+        <v>135603</v>
       </c>
       <c r="AE16" s="6">
-        <v>766940</v>
+        <v>767291</v>
       </c>
       <c r="AF16" s="5">
         <f t="shared" si="11"/>
-        <v>0.98868403208382427</v>
+        <v>0.98913651610507947</v>
       </c>
       <c r="AG16" s="7">
         <v>444751</v>
@@ -2853,14 +2853,14 @@
       </c>
       <c r="AI16" s="4">
         <f t="shared" si="12"/>
-        <v>79243</v>
+        <v>79449</v>
       </c>
       <c r="AJ16" s="6">
-        <v>439281</v>
+        <v>439487</v>
       </c>
       <c r="AK16" s="5">
         <f t="shared" si="13"/>
-        <v>0.98770098324680555</v>
+        <v>0.98816416376804095</v>
       </c>
       <c r="AL16" s="7">
         <v>448369</v>
@@ -2870,14 +2870,14 @@
       </c>
       <c r="AN16" s="4">
         <f t="shared" si="14"/>
-        <v>70393</v>
+        <v>70631</v>
       </c>
       <c r="AO16" s="6">
-        <v>439800</v>
+        <v>440038</v>
       </c>
       <c r="AP16" s="5">
         <f t="shared" si="15"/>
-        <v>0.98088850924127224</v>
+        <v>0.98141932203163018</v>
       </c>
       <c r="AQ16" s="7">
         <v>770483</v>
@@ -2887,14 +2887,14 @@
       </c>
       <c r="AS16" s="4">
         <f t="shared" si="16"/>
-        <v>116014</v>
+        <v>116511</v>
       </c>
       <c r="AT16" s="6">
-        <v>766353</v>
+        <v>766850</v>
       </c>
       <c r="AU16" s="5">
         <f t="shared" si="17"/>
-        <v>0.99463972599006079</v>
+        <v>0.99528477591329079</v>
       </c>
       <c r="AV16" s="7">
         <v>444563</v>
@@ -2904,14 +2904,14 @@
       </c>
       <c r="AX16" s="4">
         <f t="shared" si="18"/>
-        <v>71878</v>
+        <v>72174</v>
       </c>
       <c r="AY16" s="6">
-        <v>443940</v>
+        <v>444236</v>
       </c>
       <c r="AZ16" s="5">
         <f t="shared" si="19"/>
-        <v>0.99859862381709674</v>
+        <v>0.99926444620897381</v>
       </c>
       <c r="BA16" s="7">
         <v>453397</v>
@@ -2921,14 +2921,14 @@
       </c>
       <c r="BC16" s="4">
         <f t="shared" si="20"/>
-        <v>71065</v>
+        <v>71401</v>
       </c>
       <c r="BD16" s="6">
-        <v>447522</v>
+        <v>447858</v>
       </c>
       <c r="BE16" s="5">
         <f t="shared" si="21"/>
-        <v>0.98704226097658343</v>
+        <v>0.98778333337009283</v>
       </c>
       <c r="BF16" s="7">
         <v>780218</v>
@@ -2938,14 +2938,14 @@
       </c>
       <c r="BH16" s="4">
         <f t="shared" si="22"/>
-        <v>150043</v>
+        <v>150801</v>
       </c>
       <c r="BI16" s="6">
-        <v>776021</v>
+        <v>776779</v>
       </c>
       <c r="BJ16" s="5">
         <f t="shared" si="23"/>
-        <v>0.99462073420505548</v>
+        <v>0.99559225754853131</v>
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.3">
@@ -2963,14 +2963,14 @@
       </c>
       <c r="E17" s="4">
         <f t="shared" si="0"/>
-        <v>54434</v>
+        <v>54505</v>
       </c>
       <c r="F17" s="13">
-        <v>322788</v>
+        <v>322859</v>
       </c>
       <c r="G17" s="5">
         <f t="shared" si="1"/>
-        <v>0.99636689148519131</v>
+        <v>0.99658605096229536</v>
       </c>
       <c r="H17" s="7">
         <v>333085</v>
@@ -2980,14 +2980,14 @@
       </c>
       <c r="J17" s="4">
         <f t="shared" si="2"/>
-        <v>50141</v>
+        <v>50219</v>
       </c>
       <c r="K17" s="13">
-        <v>329370</v>
+        <v>329448</v>
       </c>
       <c r="L17" s="5">
         <f t="shared" si="3"/>
-        <v>0.98884669078463461</v>
+        <v>0.98908086524460725</v>
       </c>
       <c r="M17" s="7">
         <v>731481</v>
@@ -2997,14 +2997,14 @@
       </c>
       <c r="O17" s="4">
         <f t="shared" si="4"/>
-        <v>121010</v>
+        <v>121218</v>
       </c>
       <c r="P17" s="6">
-        <v>726691</v>
+        <v>726899</v>
       </c>
       <c r="Q17" s="5">
         <f t="shared" si="5"/>
-        <v>0.99345164125930818</v>
+        <v>0.99373599587685801</v>
       </c>
       <c r="R17" s="7">
         <v>324758</v>
@@ -3014,14 +3014,14 @@
       </c>
       <c r="T17" s="4">
         <f t="shared" si="6"/>
-        <v>57728</v>
+        <v>57822</v>
       </c>
       <c r="U17" s="13">
-        <v>324839</v>
+        <v>324933</v>
       </c>
       <c r="V17" s="5">
         <f t="shared" si="7"/>
-        <v>1.0002494164885853</v>
+        <v>1.0005388627839806</v>
       </c>
       <c r="W17" s="7">
         <v>336053</v>
@@ -3031,14 +3031,14 @@
       </c>
       <c r="Y17" s="4">
         <f t="shared" si="8"/>
-        <v>56953</v>
+        <v>57060</v>
       </c>
       <c r="Z17" s="13">
-        <v>327839</v>
+        <v>327946</v>
       </c>
       <c r="AA17" s="5">
         <f t="shared" si="9"/>
-        <v>0.97555742695348646</v>
+        <v>0.97587582911028914</v>
       </c>
       <c r="AB17" s="7">
         <v>736224</v>
@@ -3048,14 +3048,14 @@
       </c>
       <c r="AD17" s="4">
         <f t="shared" si="10"/>
-        <v>130574</v>
+        <v>130883</v>
       </c>
       <c r="AE17" s="6">
-        <v>728357</v>
+        <v>728666</v>
       </c>
       <c r="AF17" s="5">
         <f t="shared" si="11"/>
-        <v>0.98931439344547312</v>
+        <v>0.98973410266440653</v>
       </c>
       <c r="AG17" s="7">
         <v>328692</v>
@@ -3065,14 +3065,14 @@
       </c>
       <c r="AI17" s="4">
         <f t="shared" si="12"/>
-        <v>57596</v>
+        <v>57722</v>
       </c>
       <c r="AJ17" s="6">
-        <v>327342</v>
+        <v>327468</v>
       </c>
       <c r="AK17" s="5">
         <f t="shared" si="13"/>
-        <v>0.99589281150742948</v>
+        <v>0.99627614910006934</v>
       </c>
       <c r="AL17" s="7">
         <v>339621</v>
@@ -3082,14 +3082,14 @@
       </c>
       <c r="AN17" s="4">
         <f t="shared" si="14"/>
-        <v>51445</v>
+        <v>51605</v>
       </c>
       <c r="AO17" s="6">
-        <v>333051</v>
+        <v>333211</v>
       </c>
       <c r="AP17" s="5">
         <f t="shared" si="15"/>
-        <v>0.98065490649871478</v>
+        <v>0.98112601988687387</v>
       </c>
       <c r="AQ17" s="7">
         <v>745574</v>
@@ -3099,14 +3099,14 @@
       </c>
       <c r="AS17" s="4">
         <f t="shared" si="16"/>
-        <v>113809</v>
+        <v>114267</v>
       </c>
       <c r="AT17" s="6">
-        <v>739604</v>
+        <v>740062</v>
       </c>
       <c r="AU17" s="5">
         <f t="shared" si="17"/>
-        <v>0.99199274652817826</v>
+        <v>0.9926070383355643</v>
       </c>
       <c r="AV17" s="7">
         <v>334329</v>
@@ -3116,14 +3116,14 @@
       </c>
       <c r="AX17" s="4">
         <f t="shared" si="18"/>
-        <v>53466</v>
+        <v>53655</v>
       </c>
       <c r="AY17" s="6">
-        <v>333556</v>
+        <v>333745</v>
       </c>
       <c r="AZ17" s="5">
         <f t="shared" si="19"/>
-        <v>0.99768790622410863</v>
+        <v>0.99825321763891262</v>
       </c>
       <c r="BA17" s="7">
         <v>348862</v>
@@ -3133,14 +3133,14 @@
       </c>
       <c r="BC17" s="4">
         <f t="shared" si="20"/>
-        <v>52313</v>
+        <v>52573</v>
       </c>
       <c r="BD17" s="6">
-        <v>340298</v>
+        <v>340558</v>
       </c>
       <c r="BE17" s="5">
         <f t="shared" si="21"/>
-        <v>0.97545161123882795</v>
+        <v>0.97619689160756973</v>
       </c>
       <c r="BF17" s="7">
         <v>757181</v>
@@ -3150,14 +3150,14 @@
       </c>
       <c r="BH17" s="4">
         <f t="shared" si="22"/>
-        <v>156399</v>
+        <v>157226</v>
       </c>
       <c r="BI17" s="6">
-        <v>752813</v>
+        <v>753640</v>
       </c>
       <c r="BJ17" s="5">
         <f t="shared" si="23"/>
-        <v>0.99423123401141866</v>
+        <v>0.9953234431397513</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -3175,14 +3175,14 @@
       </c>
       <c r="E18" s="4">
         <f t="shared" si="0"/>
-        <v>183953</v>
+        <v>184117</v>
       </c>
       <c r="F18" s="13">
-        <v>989364</v>
+        <v>989528</v>
       </c>
       <c r="G18" s="5">
         <f t="shared" si="1"/>
-        <v>0.99089790996462523</v>
+        <v>0.99106216423022842</v>
       </c>
       <c r="H18" s="7">
         <v>1018686</v>
@@ -3192,14 +3192,14 @@
       </c>
       <c r="J18" s="4">
         <f t="shared" si="2"/>
-        <v>172212</v>
+        <v>172390</v>
       </c>
       <c r="K18" s="13">
-        <v>1002189</v>
+        <v>1002367</v>
       </c>
       <c r="L18" s="5">
         <f t="shared" si="3"/>
-        <v>0.98380560840141118</v>
+        <v>0.98398034330500272</v>
       </c>
       <c r="M18" s="7">
         <v>1536859</v>
@@ -3209,14 +3209,14 @@
       </c>
       <c r="O18" s="4">
         <f t="shared" si="4"/>
-        <v>261696</v>
+        <v>262017</v>
       </c>
       <c r="P18" s="6">
-        <v>1520665</v>
+        <v>1520986</v>
       </c>
       <c r="Q18" s="5">
         <f t="shared" si="5"/>
-        <v>0.98946292405484171</v>
+        <v>0.98967179162174279</v>
       </c>
       <c r="R18" s="7">
         <v>1011292</v>
@@ -3226,14 +3226,14 @@
       </c>
       <c r="T18" s="4">
         <f t="shared" si="6"/>
-        <v>185562</v>
+        <v>185781</v>
       </c>
       <c r="U18" s="13">
-        <v>1003904</v>
+        <v>1004123</v>
       </c>
       <c r="V18" s="5">
         <f t="shared" si="7"/>
-        <v>0.99269449377627828</v>
+        <v>0.9929110484410042</v>
       </c>
       <c r="W18" s="7">
         <v>1030498</v>
@@ -3243,14 +3243,14 @@
       </c>
       <c r="Y18" s="4">
         <f t="shared" si="8"/>
-        <v>182638</v>
+        <v>182905</v>
       </c>
       <c r="Z18" s="13">
-        <v>1008956</v>
+        <v>1009223</v>
       </c>
       <c r="AA18" s="5">
         <f t="shared" si="9"/>
-        <v>0.9790955440961554</v>
+        <v>0.97935464212448742</v>
       </c>
       <c r="AB18" s="7">
         <v>1557879</v>
@@ -3260,14 +3260,14 @@
       </c>
       <c r="AD18" s="4">
         <f t="shared" si="10"/>
-        <v>284584</v>
+        <v>285050</v>
       </c>
       <c r="AE18" s="6">
-        <v>1537014</v>
+        <v>1537480</v>
       </c>
       <c r="AF18" s="5">
         <f t="shared" si="11"/>
-        <v>0.98660679038615962</v>
+        <v>0.98690591502934444</v>
       </c>
       <c r="AG18" s="7">
         <v>1025067</v>
@@ -3277,14 +3277,14 @@
       </c>
       <c r="AI18" s="4">
         <f t="shared" si="12"/>
-        <v>194899</v>
+        <v>195237</v>
       </c>
       <c r="AJ18" s="6">
-        <v>1018553</v>
+        <v>1018891</v>
       </c>
       <c r="AK18" s="5">
         <f t="shared" si="13"/>
-        <v>0.99364529342960017</v>
+        <v>0.99397502797378123</v>
       </c>
       <c r="AL18" s="7">
         <v>1045736</v>
@@ -3294,14 +3294,14 @@
       </c>
       <c r="AN18" s="4">
         <f t="shared" si="14"/>
-        <v>168256</v>
+        <v>168662</v>
       </c>
       <c r="AO18" s="6">
-        <v>1031687</v>
+        <v>1032093</v>
       </c>
       <c r="AP18" s="5">
         <f t="shared" si="15"/>
-        <v>0.98656544290337145</v>
+        <v>0.98695368620760882</v>
       </c>
       <c r="AQ18" s="7">
         <v>1584961</v>
@@ -3311,14 +3311,14 @@
       </c>
       <c r="AS18" s="4">
         <f t="shared" si="16"/>
-        <v>239658</v>
+        <v>240397</v>
       </c>
       <c r="AT18" s="6">
-        <v>1570067</v>
+        <v>1570806</v>
       </c>
       <c r="AU18" s="5">
         <f t="shared" si="17"/>
-        <v>0.99060292335268818</v>
+        <v>0.9910691808820532</v>
       </c>
       <c r="AV18" s="7">
         <v>1051416</v>
@@ -3328,14 +3328,14 @@
       </c>
       <c r="AX18" s="4">
         <f t="shared" si="18"/>
-        <v>176410</v>
+        <v>176949</v>
       </c>
       <c r="AY18" s="6">
-        <v>1045940</v>
+        <v>1046479</v>
       </c>
       <c r="AZ18" s="5">
         <f t="shared" si="19"/>
-        <v>0.99479178555395775</v>
+        <v>0.99530442755293813</v>
       </c>
       <c r="BA18" s="7">
         <v>1075670</v>
@@ -3345,14 +3345,14 @@
       </c>
       <c r="BC18" s="4">
         <f t="shared" si="20"/>
-        <v>178755</v>
+        <v>179423</v>
       </c>
       <c r="BD18" s="6">
-        <v>1060031</v>
+        <v>1060699</v>
       </c>
       <c r="BE18" s="5">
         <f t="shared" si="21"/>
-        <v>0.9854611544432772</v>
+        <v>0.98608216274507976</v>
       </c>
       <c r="BF18" s="7">
         <v>1620029</v>
@@ -3362,14 +3362,14 @@
       </c>
       <c r="BH18" s="4">
         <f t="shared" si="22"/>
-        <v>347847</v>
+        <v>349376</v>
       </c>
       <c r="BI18" s="6">
-        <v>1603375</v>
+        <v>1604904</v>
       </c>
       <c r="BJ18" s="5">
         <f t="shared" si="23"/>
-        <v>0.98971993711223682</v>
+        <v>0.99066374737736174</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -3387,14 +3387,14 @@
       </c>
       <c r="E19" s="4">
         <f t="shared" si="0"/>
-        <v>63330</v>
+        <v>63421</v>
       </c>
       <c r="F19" s="13">
-        <v>284904</v>
+        <v>284995</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" si="1"/>
-        <v>0.97782506478128806</v>
+        <v>0.97813738781253756</v>
       </c>
       <c r="H19" s="7">
         <v>301141</v>
@@ -3404,14 +3404,14 @@
       </c>
       <c r="J19" s="4">
         <f t="shared" si="2"/>
-        <v>54029</v>
+        <v>54134</v>
       </c>
       <c r="K19" s="13">
-        <v>289034</v>
+        <v>289139</v>
       </c>
       <c r="L19" s="5">
         <f t="shared" si="3"/>
-        <v>0.95979624162767607</v>
+        <v>0.96014491550469716</v>
       </c>
       <c r="M19" s="7">
         <v>505864</v>
@@ -3421,14 +3421,14 @@
       </c>
       <c r="O19" s="4">
         <f t="shared" si="4"/>
-        <v>88192</v>
+        <v>88392</v>
       </c>
       <c r="P19" s="6">
-        <v>496013</v>
+        <v>496213</v>
       </c>
       <c r="Q19" s="5">
         <f t="shared" si="5"/>
-        <v>0.98052638653867441</v>
+        <v>0.98092174971929214</v>
       </c>
       <c r="R19" s="7">
         <v>293000</v>
@@ -3438,14 +3438,14 @@
       </c>
       <c r="T19" s="4">
         <f t="shared" si="6"/>
-        <v>53933</v>
+        <v>54055</v>
       </c>
       <c r="U19" s="13">
-        <v>286665</v>
+        <v>286787</v>
       </c>
       <c r="V19" s="5">
         <f t="shared" si="7"/>
-        <v>0.97837883959044369</v>
+        <v>0.97879522184300338</v>
       </c>
       <c r="W19" s="7">
         <v>302979</v>
@@ -3455,14 +3455,14 @@
       </c>
       <c r="Y19" s="4">
         <f t="shared" si="8"/>
-        <v>59482</v>
+        <v>59645</v>
       </c>
       <c r="Z19" s="13">
-        <v>287542</v>
+        <v>287705</v>
       </c>
       <c r="AA19" s="5">
         <f t="shared" si="9"/>
-        <v>0.94904927404209538</v>
+        <v>0.9495872651239855</v>
       </c>
       <c r="AB19" s="7">
         <v>514622</v>
@@ -3472,14 +3472,14 @@
       </c>
       <c r="AD19" s="4">
         <f t="shared" si="10"/>
-        <v>103175</v>
+        <v>103484</v>
       </c>
       <c r="AE19" s="6">
-        <v>496808</v>
+        <v>497117</v>
       </c>
       <c r="AF19" s="5">
         <f t="shared" si="11"/>
-        <v>0.96538430148730525</v>
+        <v>0.96598474219912867</v>
       </c>
       <c r="AG19" s="7">
         <v>295766</v>
@@ -3489,14 +3489,14 @@
       </c>
       <c r="AI19" s="4">
         <f t="shared" si="12"/>
-        <v>61428</v>
+        <v>61630</v>
       </c>
       <c r="AJ19" s="6">
-        <v>287272</v>
+        <v>287474</v>
       </c>
       <c r="AK19" s="5">
         <f t="shared" si="13"/>
-        <v>0.97128135079759004</v>
+        <v>0.97196432314735293</v>
       </c>
       <c r="AL19" s="7">
         <v>302797</v>
@@ -3506,14 +3506,14 @@
       </c>
       <c r="AN19" s="4">
         <f t="shared" si="14"/>
-        <v>54325</v>
+        <v>54563</v>
       </c>
       <c r="AO19" s="6">
-        <v>290900</v>
+        <v>291138</v>
       </c>
       <c r="AP19" s="5">
         <f t="shared" si="15"/>
-        <v>0.96070965035981204</v>
+        <v>0.96149565550517346</v>
       </c>
       <c r="AQ19" s="7">
         <v>519490</v>
@@ -3523,14 +3523,14 @@
       </c>
       <c r="AS19" s="4">
         <f t="shared" si="16"/>
-        <v>87796</v>
+        <v>88300</v>
       </c>
       <c r="AT19" s="6">
-        <v>505468</v>
+        <v>505972</v>
       </c>
       <c r="AU19" s="5">
         <f t="shared" si="17"/>
-        <v>0.97300814260139756</v>
+        <v>0.97397832489557068</v>
       </c>
       <c r="AV19" s="7">
         <v>299668</v>
@@ -3540,14 +3540,14 @@
       </c>
       <c r="AX19" s="4">
         <f t="shared" si="18"/>
-        <v>55520</v>
+        <v>55852</v>
       </c>
       <c r="AY19" s="6">
-        <v>294470</v>
+        <v>294802</v>
       </c>
       <c r="AZ19" s="5">
         <f t="shared" si="19"/>
-        <v>0.982654137245218</v>
+        <v>0.98376202997984441</v>
       </c>
       <c r="BA19" s="7">
         <v>313772</v>
@@ -3557,14 +3557,14 @@
       </c>
       <c r="BC19" s="4">
         <f t="shared" si="20"/>
-        <v>57364</v>
+        <v>57753</v>
       </c>
       <c r="BD19" s="6">
-        <v>299020</v>
+        <v>299409</v>
       </c>
       <c r="BE19" s="5">
         <f t="shared" si="21"/>
-        <v>0.9529849699782007</v>
+        <v>0.95422472368471378</v>
       </c>
       <c r="BF19" s="7">
         <v>528004</v>
@@ -3574,14 +3574,14 @@
       </c>
       <c r="BH19" s="4">
         <f t="shared" si="22"/>
-        <v>132163</v>
+        <v>133136</v>
       </c>
       <c r="BI19" s="6">
-        <v>515570</v>
+        <v>516543</v>
       </c>
       <c r="BJ19" s="5">
         <f t="shared" si="23"/>
-        <v>0.97645093597775778</v>
+        <v>0.97829372504753753</v>
       </c>
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.3">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="E20" s="4">
         <f t="shared" si="0"/>
-        <v>1824</v>
+        <v>1833</v>
       </c>
       <c r="F20" s="13">
-        <v>6411</v>
+        <v>6420</v>
       </c>
       <c r="G20" s="5">
         <f t="shared" si="1"/>
-        <v>0.99210770659238623</v>
+        <v>0.99350046425255334</v>
       </c>
       <c r="H20" s="7">
         <v>6957</v>
@@ -3616,14 +3616,14 @@
       </c>
       <c r="J20" s="4">
         <f t="shared" si="2"/>
-        <v>1645</v>
+        <v>1657</v>
       </c>
       <c r="K20" s="13">
-        <v>6459</v>
+        <v>6471</v>
       </c>
       <c r="L20" s="5">
         <f t="shared" si="3"/>
-        <v>0.92841742130228544</v>
+        <v>0.93014230271668819</v>
       </c>
       <c r="M20" s="7">
         <v>9947</v>
@@ -3633,14 +3633,14 @@
       </c>
       <c r="O20" s="4">
         <f t="shared" si="4"/>
-        <v>2276</v>
+        <v>2290</v>
       </c>
       <c r="P20" s="6">
-        <v>9819</v>
+        <v>9833</v>
       </c>
       <c r="Q20" s="5">
         <f t="shared" si="5"/>
-        <v>0.98713179853222077</v>
+        <v>0.98853925806775911</v>
       </c>
       <c r="R20" s="7">
         <v>6587</v>
@@ -3650,14 +3650,14 @@
       </c>
       <c r="T20" s="4">
         <f t="shared" si="6"/>
-        <v>1603</v>
+        <v>1616</v>
       </c>
       <c r="U20" s="13">
-        <v>6504</v>
+        <v>6517</v>
       </c>
       <c r="V20" s="5">
         <f t="shared" si="7"/>
-        <v>0.98739942310611806</v>
+        <v>0.98937300743889478</v>
       </c>
       <c r="W20" s="7">
         <v>6643</v>
@@ -3667,14 +3667,14 @@
       </c>
       <c r="Y20" s="4">
         <f t="shared" si="8"/>
-        <v>1705</v>
+        <v>1720</v>
       </c>
       <c r="Z20" s="13">
-        <v>6498</v>
+        <v>6513</v>
       </c>
       <c r="AA20" s="5">
         <f t="shared" si="9"/>
-        <v>0.97817251241908776</v>
+        <v>0.98043052837573386</v>
       </c>
       <c r="AB20" s="7">
         <v>9927</v>
@@ -3684,14 +3684,14 @@
       </c>
       <c r="AD20" s="4">
         <f t="shared" si="10"/>
-        <v>2669</v>
+        <v>2694</v>
       </c>
       <c r="AE20" s="6">
-        <v>9852</v>
+        <v>9877</v>
       </c>
       <c r="AF20" s="5">
         <f t="shared" si="11"/>
-        <v>0.99244484738591721</v>
+        <v>0.99496323159061151</v>
       </c>
       <c r="AG20" s="7">
         <v>6546</v>
@@ -3701,14 +3701,14 @@
       </c>
       <c r="AI20" s="4">
         <f t="shared" si="12"/>
-        <v>1781</v>
+        <v>1801</v>
       </c>
       <c r="AJ20" s="6">
-        <v>6466</v>
+        <v>6486</v>
       </c>
       <c r="AK20" s="5">
         <f t="shared" si="13"/>
-        <v>0.98777879621142683</v>
+        <v>0.99083409715857007</v>
       </c>
       <c r="AL20" s="7">
         <v>6627</v>
@@ -3718,14 +3718,14 @@
       </c>
       <c r="AN20" s="4">
         <f t="shared" si="14"/>
-        <v>1611</v>
+        <v>1630</v>
       </c>
       <c r="AO20" s="6">
-        <v>6533</v>
+        <v>6552</v>
       </c>
       <c r="AP20" s="5">
         <f t="shared" si="15"/>
-        <v>0.98581560283687941</v>
+        <v>0.98868266183793574</v>
       </c>
       <c r="AQ20" s="7">
         <v>9949</v>
@@ -3735,14 +3735,14 @@
       </c>
       <c r="AS20" s="4">
         <f t="shared" si="16"/>
-        <v>2338</v>
+        <v>2367</v>
       </c>
       <c r="AT20" s="6">
-        <v>9938</v>
+        <v>9967</v>
       </c>
       <c r="AU20" s="5">
         <f t="shared" si="17"/>
-        <v>0.99889436124233588</v>
+        <v>1.0018092270579957</v>
       </c>
       <c r="AV20" s="7">
         <v>6437</v>
@@ -3752,14 +3752,14 @@
       </c>
       <c r="AX20" s="4">
         <f t="shared" si="18"/>
-        <v>1545</v>
+        <v>1569</v>
       </c>
       <c r="AY20" s="6">
-        <v>6416</v>
+        <v>6440</v>
       </c>
       <c r="AZ20" s="5">
         <f t="shared" si="19"/>
-        <v>0.99673761068820876</v>
+        <v>1.0004660556159701</v>
       </c>
       <c r="BA20" s="7">
         <v>6564</v>
@@ -3769,14 +3769,14 @@
       </c>
       <c r="BC20" s="4">
         <f t="shared" si="20"/>
-        <v>1575</v>
+        <v>1603</v>
       </c>
       <c r="BD20" s="6">
-        <v>6488</v>
+        <v>6516</v>
       </c>
       <c r="BE20" s="5">
         <f t="shared" si="21"/>
-        <v>0.98842169408897018</v>
+        <v>0.99268738574040216</v>
       </c>
       <c r="BF20" s="7">
         <v>10109</v>
@@ -3786,14 +3786,14 @@
       </c>
       <c r="BH20" s="4">
         <f t="shared" si="22"/>
-        <v>2986</v>
+        <v>3036</v>
       </c>
       <c r="BI20" s="6">
-        <v>10010</v>
+        <v>10060</v>
       </c>
       <c r="BJ20" s="5">
         <f t="shared" si="23"/>
-        <v>0.99020674646354734</v>
+        <v>0.99515283410822042</v>
       </c>
     </row>
     <row r="21" spans="1:62" x14ac:dyDescent="0.3">
@@ -3811,14 +3811,14 @@
       </c>
       <c r="E21" s="4">
         <f t="shared" si="0"/>
-        <v>4173</v>
+        <v>4197</v>
       </c>
       <c r="F21" s="13">
-        <v>10886</v>
+        <v>10910</v>
       </c>
       <c r="G21" s="5">
         <f t="shared" si="1"/>
-        <v>0.99080731773914621</v>
+        <v>0.9929917174842996</v>
       </c>
       <c r="H21" s="7">
         <v>10970</v>
@@ -3828,14 +3828,14 @@
       </c>
       <c r="J21" s="4">
         <f t="shared" si="2"/>
-        <v>3454</v>
+        <v>3477</v>
       </c>
       <c r="K21" s="13">
-        <v>10931</v>
+        <v>10954</v>
       </c>
       <c r="L21" s="5">
         <f t="shared" si="3"/>
-        <v>0.99644484958979029</v>
+        <v>0.99854147675478577</v>
       </c>
       <c r="M21" s="7">
         <v>14288</v>
@@ -3845,14 +3845,14 @@
       </c>
       <c r="O21" s="4">
         <f t="shared" si="4"/>
-        <v>4614</v>
+        <v>4644</v>
       </c>
       <c r="P21" s="6">
-        <v>14496</v>
+        <v>14526</v>
       </c>
       <c r="Q21" s="5">
         <f t="shared" si="5"/>
-        <v>1.0145576707726764</v>
+        <v>1.0166573348264278</v>
       </c>
       <c r="R21" s="7">
         <v>10910</v>
@@ -3862,14 +3862,14 @@
       </c>
       <c r="T21" s="4">
         <f t="shared" si="6"/>
-        <v>3662</v>
+        <v>3687</v>
       </c>
       <c r="U21" s="13">
-        <v>11160</v>
+        <v>11185</v>
       </c>
       <c r="V21" s="5">
         <f t="shared" si="7"/>
-        <v>1.0229147571035746</v>
+        <v>1.0252062328139322</v>
       </c>
       <c r="W21" s="7">
         <v>11256</v>
@@ -3879,14 +3879,14 @@
       </c>
       <c r="Y21" s="4">
         <f t="shared" si="8"/>
-        <v>3640</v>
+        <v>3668</v>
       </c>
       <c r="Z21" s="13">
-        <v>11279</v>
+        <v>11307</v>
       </c>
       <c r="AA21" s="5">
         <f t="shared" si="9"/>
-        <v>1.0020433546552949</v>
+        <v>1.0045309168443497</v>
       </c>
       <c r="AB21" s="7">
         <v>14831</v>
@@ -3896,14 +3896,14 @@
       </c>
       <c r="AD21" s="4">
         <f t="shared" si="10"/>
-        <v>4842</v>
+        <v>4884</v>
       </c>
       <c r="AE21" s="6">
-        <v>14931</v>
+        <v>14973</v>
       </c>
       <c r="AF21" s="5">
         <f t="shared" si="11"/>
-        <v>1.0067426336727126</v>
+        <v>1.0095745398152518</v>
       </c>
       <c r="AG21" s="7">
         <v>11222</v>
@@ -3913,14 +3913,14 @@
       </c>
       <c r="AI21" s="4">
         <f t="shared" si="12"/>
-        <v>3671</v>
+        <v>3705</v>
       </c>
       <c r="AJ21" s="6">
-        <v>11314</v>
+        <v>11348</v>
       </c>
       <c r="AK21" s="5">
         <f t="shared" si="13"/>
-        <v>1.0081981821422206</v>
+        <v>1.0112279451078239</v>
       </c>
       <c r="AL21" s="7">
         <v>11337</v>
@@ -3930,14 +3930,14 @@
       </c>
       <c r="AN21" s="4">
         <f t="shared" si="14"/>
-        <v>3443</v>
+        <v>3485</v>
       </c>
       <c r="AO21" s="6">
-        <v>11468</v>
+        <v>11510</v>
       </c>
       <c r="AP21" s="5">
         <f t="shared" si="15"/>
-        <v>1.0115550851195201</v>
+        <v>1.0152597688982976</v>
       </c>
       <c r="AQ21" s="7">
         <v>15149</v>
@@ -3947,14 +3947,14 @@
       </c>
       <c r="AS21" s="4">
         <f t="shared" si="16"/>
-        <v>4501</v>
+        <v>4564</v>
       </c>
       <c r="AT21" s="6">
-        <v>15315</v>
+        <v>15378</v>
       </c>
       <c r="AU21" s="5">
         <f t="shared" si="17"/>
-        <v>1.0109578189979536</v>
+        <v>1.0151165093405505</v>
       </c>
       <c r="AV21" s="7">
         <v>11422</v>
@@ -3964,14 +3964,14 @@
       </c>
       <c r="AX21" s="4">
         <f t="shared" si="18"/>
-        <v>3557</v>
+        <v>3620</v>
       </c>
       <c r="AY21" s="6">
-        <v>11631</v>
+        <v>11694</v>
       </c>
       <c r="AZ21" s="5">
         <f t="shared" si="19"/>
-        <v>1.0182980213622834</v>
+        <v>1.0238136928734023</v>
       </c>
       <c r="BA21" s="7">
         <v>11689</v>
@@ -3981,14 +3981,14 @@
       </c>
       <c r="BC21" s="4">
         <f t="shared" si="20"/>
-        <v>3422</v>
+        <v>3497</v>
       </c>
       <c r="BD21" s="6">
-        <v>11744</v>
+        <v>11819</v>
       </c>
       <c r="BE21" s="5">
         <f t="shared" si="21"/>
-        <v>1.0047052784669348</v>
+        <v>1.0111215672854821</v>
       </c>
       <c r="BF21" s="7">
         <v>15725</v>
@@ -3998,14 +3998,14 @@
       </c>
       <c r="BH21" s="4">
         <f t="shared" si="22"/>
-        <v>6193</v>
+        <v>6330</v>
       </c>
       <c r="BI21" s="6">
-        <v>15638</v>
+        <v>15775</v>
       </c>
       <c r="BJ21" s="5">
         <f t="shared" si="23"/>
-        <v>0.99446740858505567</v>
+        <v>1.0031796502384738</v>
       </c>
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.3">
@@ -4023,14 +4023,14 @@
       </c>
       <c r="E22" s="4">
         <f t="shared" si="0"/>
-        <v>1793</v>
+        <v>1809</v>
       </c>
       <c r="F22" s="13">
-        <v>6664</v>
+        <v>6680</v>
       </c>
       <c r="G22" s="5">
         <f t="shared" si="1"/>
-        <v>0.98638247483718178</v>
+        <v>0.98875074008288932</v>
       </c>
       <c r="H22" s="7">
         <v>6770</v>
@@ -4040,14 +4040,14 @@
       </c>
       <c r="J22" s="4">
         <f t="shared" si="2"/>
-        <v>1656</v>
+        <v>1673</v>
       </c>
       <c r="K22" s="13">
-        <v>6748</v>
+        <v>6765</v>
       </c>
       <c r="L22" s="5">
         <f t="shared" si="3"/>
-        <v>0.99675036927621863</v>
+        <v>0.99926144756277691</v>
       </c>
       <c r="M22" s="7">
         <v>8074</v>
@@ -4057,14 +4057,14 @@
       </c>
       <c r="O22" s="4">
         <f t="shared" si="4"/>
-        <v>1970</v>
+        <v>1990</v>
       </c>
       <c r="P22" s="6">
-        <v>8057</v>
+        <v>8077</v>
       </c>
       <c r="Q22" s="5">
         <f t="shared" si="5"/>
-        <v>0.99789447609611093</v>
+        <v>1.0003715630418628</v>
       </c>
       <c r="R22" s="7">
         <v>6748</v>
@@ -4074,14 +4074,14 @@
       </c>
       <c r="T22" s="4">
         <f t="shared" si="6"/>
-        <v>1735</v>
+        <v>1755</v>
       </c>
       <c r="U22" s="13">
-        <v>6770</v>
+        <v>6790</v>
       </c>
       <c r="V22" s="5">
         <f t="shared" si="7"/>
-        <v>1.0032602252519265</v>
+        <v>1.0062240663900415</v>
       </c>
       <c r="W22" s="7">
         <v>6876</v>
@@ -4091,14 +4091,14 @@
       </c>
       <c r="Y22" s="4">
         <f t="shared" si="8"/>
-        <v>1665</v>
+        <v>1685</v>
       </c>
       <c r="Z22" s="13">
-        <v>6831</v>
+        <v>6851</v>
       </c>
       <c r="AA22" s="5">
         <f t="shared" si="9"/>
-        <v>0.99345549738219896</v>
+        <v>0.99636416521233273</v>
       </c>
       <c r="AB22" s="7">
         <v>8219</v>
@@ -4108,14 +4108,14 @@
       </c>
       <c r="AD22" s="4">
         <f t="shared" si="10"/>
-        <v>2224</v>
+        <v>2247</v>
       </c>
       <c r="AE22" s="6">
-        <v>8209</v>
+        <v>8232</v>
       </c>
       <c r="AF22" s="5">
         <f t="shared" si="11"/>
-        <v>0.99878330697165107</v>
+        <v>1.0015817009368537</v>
       </c>
       <c r="AG22" s="7">
         <v>6901</v>
@@ -4125,14 +4125,14 @@
       </c>
       <c r="AI22" s="4">
         <f t="shared" si="12"/>
-        <v>1702</v>
+        <v>1725</v>
       </c>
       <c r="AJ22" s="6">
-        <v>6884</v>
+        <v>6907</v>
       </c>
       <c r="AK22" s="5">
         <f t="shared" si="13"/>
-        <v>0.99753658890015939</v>
+        <v>1.0008694392117083</v>
       </c>
       <c r="AL22" s="7">
         <v>6948</v>
@@ -4142,14 +4142,14 @@
       </c>
       <c r="AN22" s="4">
         <f t="shared" si="14"/>
-        <v>1685</v>
+        <v>1712</v>
       </c>
       <c r="AO22" s="6">
-        <v>6914</v>
+        <v>6941</v>
       </c>
       <c r="AP22" s="5">
         <f t="shared" si="15"/>
-        <v>0.99510650546919976</v>
+        <v>0.99899251583189408</v>
       </c>
       <c r="AQ22" s="7">
         <v>8297</v>
@@ -4159,14 +4159,14 @@
       </c>
       <c r="AS22" s="4">
         <f t="shared" si="16"/>
-        <v>2093</v>
+        <v>2126</v>
       </c>
       <c r="AT22" s="6">
-        <v>8268</v>
+        <v>8301</v>
       </c>
       <c r="AU22" s="5">
         <f t="shared" si="17"/>
-        <v>0.99650476075690009</v>
+        <v>1.0004821019645656</v>
       </c>
       <c r="AV22" s="7">
         <v>6958</v>
@@ -4176,14 +4176,14 @@
       </c>
       <c r="AX22" s="4">
         <f t="shared" si="18"/>
-        <v>1829</v>
+        <v>1857</v>
       </c>
       <c r="AY22" s="6">
-        <v>6955</v>
+        <v>6983</v>
       </c>
       <c r="AZ22" s="5">
         <f t="shared" si="19"/>
-        <v>0.99956884162115556</v>
+        <v>1.0035929864903708</v>
       </c>
       <c r="BA22" s="7">
         <v>7049</v>
@@ -4193,14 +4193,14 @@
       </c>
       <c r="BC22" s="4">
         <f t="shared" si="20"/>
-        <v>1704</v>
+        <v>1737</v>
       </c>
       <c r="BD22" s="6">
-        <v>7010</v>
+        <v>7043</v>
       </c>
       <c r="BE22" s="5">
         <f t="shared" si="21"/>
-        <v>0.99446730032628738</v>
+        <v>0.99914881543481349</v>
       </c>
       <c r="BF22" s="7">
         <v>8436</v>
@@ -4210,14 +4210,14 @@
       </c>
       <c r="BH22" s="4">
         <f t="shared" si="22"/>
-        <v>2622</v>
+        <v>2666</v>
       </c>
       <c r="BI22" s="6">
-        <v>8361</v>
+        <v>8405</v>
       </c>
       <c r="BJ22" s="5">
         <f t="shared" si="23"/>
-        <v>0.99110953058321483</v>
+        <v>0.99632527264106208</v>
       </c>
     </row>
     <row r="23" spans="1:62" x14ac:dyDescent="0.3">
@@ -4235,14 +4235,14 @@
       </c>
       <c r="E23" s="4">
         <f t="shared" si="0"/>
-        <v>3035</v>
+        <v>3052</v>
       </c>
       <c r="F23" s="13">
-        <v>8660</v>
+        <v>8677</v>
       </c>
       <c r="G23" s="5">
         <f t="shared" si="1"/>
-        <v>0.98319709355131701</v>
+        <v>0.98512715712988197</v>
       </c>
       <c r="H23" s="7">
         <v>8878</v>
@@ -4252,14 +4252,14 @@
       </c>
       <c r="J23" s="4">
         <f t="shared" si="2"/>
-        <v>2864</v>
+        <v>2883</v>
       </c>
       <c r="K23" s="13">
-        <v>8771</v>
+        <v>8790</v>
       </c>
       <c r="L23" s="5">
         <f t="shared" si="3"/>
-        <v>0.98794773597657126</v>
+        <v>0.99008785762559137</v>
       </c>
       <c r="M23" s="7">
         <v>11255</v>
@@ -4269,14 +4269,14 @@
       </c>
       <c r="O23" s="4">
         <f t="shared" si="4"/>
-        <v>3380</v>
+        <v>3404</v>
       </c>
       <c r="P23" s="6">
-        <v>11186</v>
+        <v>11210</v>
       </c>
       <c r="Q23" s="5">
         <f t="shared" si="5"/>
-        <v>0.99386939138160812</v>
+        <v>0.99600177698800529</v>
       </c>
       <c r="R23" s="7">
         <v>8944</v>
@@ -4286,14 +4286,14 @@
       </c>
       <c r="T23" s="4">
         <f t="shared" si="6"/>
-        <v>2633</v>
+        <v>2658</v>
       </c>
       <c r="U23" s="13">
-        <v>8891</v>
+        <v>8916</v>
       </c>
       <c r="V23" s="5">
         <f t="shared" si="7"/>
-        <v>0.99407423971377462</v>
+        <v>0.99686940966010729</v>
       </c>
       <c r="W23" s="7">
         <v>10422</v>
@@ -4303,14 +4303,14 @@
       </c>
       <c r="Y23" s="4">
         <f t="shared" si="8"/>
-        <v>2917</v>
+        <v>2948</v>
       </c>
       <c r="Z23" s="13">
-        <v>8994</v>
+        <v>9025</v>
       </c>
       <c r="AA23" s="5">
         <f t="shared" si="9"/>
-        <v>0.86298215313759352</v>
+        <v>0.86595663020533487</v>
       </c>
       <c r="AB23" s="7">
         <v>11673</v>
@@ -4320,14 +4320,14 @@
       </c>
       <c r="AD23" s="4">
         <f t="shared" si="10"/>
-        <v>3687</v>
+        <v>3724</v>
       </c>
       <c r="AE23" s="6">
-        <v>11359</v>
+        <v>11396</v>
       </c>
       <c r="AF23" s="5">
         <f t="shared" si="11"/>
-        <v>0.97310031697078725</v>
+        <v>0.97627002484365633</v>
       </c>
       <c r="AG23" s="7">
         <v>9370</v>
@@ -4337,14 +4337,14 @@
       </c>
       <c r="AI23" s="4">
         <f t="shared" si="12"/>
-        <v>4379</v>
+        <v>4409</v>
       </c>
       <c r="AJ23" s="6">
-        <v>8965</v>
+        <v>8995</v>
       </c>
       <c r="AK23" s="5">
         <f t="shared" si="13"/>
-        <v>0.95677694770544286</v>
+        <v>0.95997865528281745</v>
       </c>
       <c r="AL23" s="7">
         <v>9238</v>
@@ -4354,14 +4354,14 @@
       </c>
       <c r="AN23" s="4">
         <f t="shared" si="14"/>
-        <v>2599</v>
+        <v>2629</v>
       </c>
       <c r="AO23" s="6">
-        <v>9002</v>
+        <v>9032</v>
       </c>
       <c r="AP23" s="5">
         <f t="shared" si="15"/>
-        <v>0.97445334487984414</v>
+        <v>0.977700801039186</v>
       </c>
       <c r="AQ23" s="7">
         <v>11727</v>
@@ -4371,14 +4371,14 @@
       </c>
       <c r="AS23" s="4">
         <f t="shared" si="16"/>
-        <v>3069</v>
+        <v>3109</v>
       </c>
       <c r="AT23" s="6">
-        <v>11481</v>
+        <v>11521</v>
       </c>
       <c r="AU23" s="5">
         <f t="shared" si="17"/>
-        <v>0.97902276797134813</v>
+        <v>0.98243370000852737</v>
       </c>
       <c r="AV23" s="7">
         <v>9359</v>
@@ -4388,14 +4388,14 @@
       </c>
       <c r="AX23" s="4">
         <f t="shared" si="18"/>
-        <v>2733</v>
+        <v>2768</v>
       </c>
       <c r="AY23" s="6">
-        <v>9116</v>
+        <v>9151</v>
       </c>
       <c r="AZ23" s="5">
         <f t="shared" si="19"/>
-        <v>0.97403568757345871</v>
+        <v>0.9777754033550593</v>
       </c>
       <c r="BA23" s="7">
         <v>9570</v>
@@ -4405,14 +4405,14 @@
       </c>
       <c r="BC23" s="4">
         <f t="shared" si="20"/>
-        <v>2858</v>
+        <v>2897</v>
       </c>
       <c r="BD23" s="6">
-        <v>9167</v>
+        <v>9206</v>
       </c>
       <c r="BE23" s="5">
         <f t="shared" si="21"/>
-        <v>0.95788923719958208</v>
+        <v>0.96196447230929993</v>
       </c>
       <c r="BF23" s="7">
         <v>11968</v>
@@ -4422,14 +4422,14 @@
       </c>
       <c r="BH23" s="4">
         <f t="shared" si="22"/>
-        <v>4248</v>
+        <v>4305</v>
       </c>
       <c r="BI23" s="6">
-        <v>11648</v>
+        <v>11705</v>
       </c>
       <c r="BJ23" s="5">
         <f t="shared" si="23"/>
-        <v>0.9732620320855615</v>
+        <v>0.97802473262032086</v>
       </c>
     </row>
     <row r="24" spans="1:62" x14ac:dyDescent="0.3">
@@ -4447,14 +4447,14 @@
       </c>
       <c r="E24" s="4">
         <f t="shared" si="0"/>
-        <v>1281</v>
+        <v>1289</v>
       </c>
       <c r="F24" s="13">
-        <v>6175</v>
+        <v>6183</v>
       </c>
       <c r="G24" s="5">
         <f t="shared" si="1"/>
-        <v>0.98799999999999999</v>
+        <v>0.98928000000000005</v>
       </c>
       <c r="H24" s="7">
         <v>6322</v>
@@ -4464,14 +4464,14 @@
       </c>
       <c r="J24" s="4">
         <f t="shared" si="2"/>
-        <v>1198</v>
+        <v>1206</v>
       </c>
       <c r="K24" s="13">
-        <v>6226</v>
+        <v>6234</v>
       </c>
       <c r="L24" s="5">
         <f t="shared" si="3"/>
-        <v>0.98481493198354952</v>
+        <v>0.98608035431825369</v>
       </c>
       <c r="M24" s="7">
         <v>7266</v>
@@ -4481,14 +4481,14 @@
       </c>
       <c r="O24" s="4">
         <f t="shared" si="4"/>
-        <v>1415</v>
+        <v>1423</v>
       </c>
       <c r="P24" s="6">
-        <v>7145</v>
+        <v>7153</v>
       </c>
       <c r="Q24" s="5">
         <f t="shared" si="5"/>
-        <v>0.98334709606385906</v>
+        <v>0.98444811450591796</v>
       </c>
       <c r="R24" s="7">
         <v>6403</v>
@@ -4498,14 +4498,14 @@
       </c>
       <c r="T24" s="4">
         <f t="shared" si="6"/>
-        <v>1246</v>
+        <v>1254</v>
       </c>
       <c r="U24" s="13">
-        <v>6290</v>
+        <v>6298</v>
       </c>
       <c r="V24" s="5">
         <f t="shared" si="7"/>
-        <v>0.98235202248945808</v>
+        <v>0.9836014368264876</v>
       </c>
       <c r="W24" s="7">
         <v>6540</v>
@@ -4515,14 +4515,14 @@
       </c>
       <c r="Y24" s="4">
         <f t="shared" si="8"/>
-        <v>1286</v>
+        <v>1296</v>
       </c>
       <c r="Z24" s="13">
-        <v>6393</v>
+        <v>6403</v>
       </c>
       <c r="AA24" s="5">
         <f t="shared" si="9"/>
-        <v>0.97752293577981653</v>
+        <v>0.97905198776758406</v>
       </c>
       <c r="AB24" s="7">
         <v>7473</v>
@@ -4532,14 +4532,14 @@
       </c>
       <c r="AD24" s="4">
         <f t="shared" si="10"/>
-        <v>1715</v>
+        <v>1728</v>
       </c>
       <c r="AE24" s="6">
-        <v>7359</v>
+        <v>7372</v>
       </c>
       <c r="AF24" s="5">
         <f t="shared" si="11"/>
-        <v>0.98474508229626656</v>
+        <v>0.98648467817476249</v>
       </c>
       <c r="AG24" s="7">
         <v>6660</v>
@@ -4549,14 +4549,14 @@
       </c>
       <c r="AI24" s="4">
         <f t="shared" si="12"/>
-        <v>1420</v>
+        <v>1430</v>
       </c>
       <c r="AJ24" s="6">
-        <v>6574</v>
+        <v>6584</v>
       </c>
       <c r="AK24" s="5">
         <f t="shared" si="13"/>
-        <v>0.98708708708708703</v>
+        <v>0.98858858858858856</v>
       </c>
       <c r="AL24" s="7">
         <v>6723</v>
@@ -4566,14 +4566,14 @@
       </c>
       <c r="AN24" s="4">
         <f t="shared" si="14"/>
-        <v>1357</v>
+        <v>1368</v>
       </c>
       <c r="AO24" s="6">
-        <v>6620</v>
+        <v>6631</v>
       </c>
       <c r="AP24" s="5">
         <f t="shared" si="15"/>
-        <v>0.98467945857504091</v>
+        <v>0.98631563290197832</v>
       </c>
       <c r="AQ24" s="7">
         <v>7657</v>
@@ -4583,14 +4583,14 @@
       </c>
       <c r="AS24" s="4">
         <f t="shared" si="16"/>
-        <v>1554</v>
+        <v>1571</v>
       </c>
       <c r="AT24" s="6">
-        <v>7537</v>
+        <v>7554</v>
       </c>
       <c r="AU24" s="5">
         <f t="shared" si="17"/>
-        <v>0.98432806582212351</v>
+        <v>0.9865482564973227</v>
       </c>
       <c r="AV24" s="7">
         <v>6786</v>
@@ -4600,14 +4600,14 @@
       </c>
       <c r="AX24" s="4">
         <f t="shared" si="18"/>
-        <v>1422</v>
+        <v>1435</v>
       </c>
       <c r="AY24" s="6">
-        <v>6725</v>
+        <v>6738</v>
       </c>
       <c r="AZ24" s="5">
         <f t="shared" si="19"/>
-        <v>0.99101090480400822</v>
+        <v>0.99292661361626877</v>
       </c>
       <c r="BA24" s="7">
         <v>7025</v>
@@ -4617,14 +4617,14 @@
       </c>
       <c r="BC24" s="4">
         <f t="shared" si="20"/>
-        <v>1273</v>
+        <v>1288</v>
       </c>
       <c r="BD24" s="6">
-        <v>6783</v>
+        <v>6798</v>
       </c>
       <c r="BE24" s="5">
         <f t="shared" si="21"/>
-        <v>0.9655516014234875</v>
+        <v>0.9676868327402135</v>
       </c>
       <c r="BF24" s="7">
         <v>7878</v>
@@ -4634,14 +4634,14 @@
       </c>
       <c r="BH24" s="4">
         <f t="shared" si="22"/>
-        <v>1952</v>
+        <v>1968</v>
       </c>
       <c r="BI24" s="6">
-        <v>7722</v>
+        <v>7738</v>
       </c>
       <c r="BJ24" s="5">
         <f t="shared" si="23"/>
-        <v>0.98019801980198018</v>
+        <v>0.98222899212998227</v>
       </c>
     </row>
     <row r="25" spans="1:62" x14ac:dyDescent="0.3">
@@ -4659,14 +4659,14 @@
       </c>
       <c r="E25" s="4">
         <f t="shared" si="0"/>
-        <v>4270</v>
+        <v>4284</v>
       </c>
       <c r="F25" s="13">
-        <v>20214</v>
+        <v>20228</v>
       </c>
       <c r="G25" s="5">
         <f t="shared" si="1"/>
-        <v>0.96588302752293576</v>
+        <v>0.96655198776758411</v>
       </c>
       <c r="H25" s="7">
         <v>20519</v>
@@ -4676,14 +4676,14 @@
       </c>
       <c r="J25" s="4">
         <f t="shared" si="2"/>
-        <v>3822</v>
+        <v>3842</v>
       </c>
       <c r="K25" s="13">
-        <v>20309</v>
+        <v>20329</v>
       </c>
       <c r="L25" s="5">
         <f t="shared" si="3"/>
-        <v>0.98976558311808571</v>
+        <v>0.9907402894877918</v>
       </c>
       <c r="M25" s="7">
         <v>27924</v>
@@ -4693,14 +4693,14 @@
       </c>
       <c r="O25" s="4">
         <f t="shared" si="4"/>
-        <v>5518</v>
+        <v>5548</v>
       </c>
       <c r="P25" s="6">
-        <v>27850</v>
+        <v>27880</v>
       </c>
       <c r="Q25" s="5">
         <f t="shared" si="5"/>
-        <v>0.99734994986391634</v>
+        <v>0.99842429451367998</v>
       </c>
       <c r="R25" s="7">
         <v>20481</v>
@@ -4710,14 +4710,14 @@
       </c>
       <c r="T25" s="4">
         <f t="shared" si="6"/>
-        <v>4471</v>
+        <v>4497</v>
       </c>
       <c r="U25" s="13">
-        <v>20492</v>
+        <v>20518</v>
       </c>
       <c r="V25" s="5">
         <f t="shared" si="7"/>
-        <v>1.0005370831502367</v>
+        <v>1.0018065524144328</v>
       </c>
       <c r="W25" s="7">
         <v>20934</v>
@@ -4727,14 +4727,14 @@
       </c>
       <c r="Y25" s="4">
         <f t="shared" si="8"/>
-        <v>4197</v>
+        <v>4221</v>
       </c>
       <c r="Z25" s="13">
-        <v>20596</v>
+        <v>20620</v>
       </c>
       <c r="AA25" s="5">
         <f t="shared" si="9"/>
-        <v>0.98385401738798128</v>
+        <v>0.98500047769179322</v>
       </c>
       <c r="AB25" s="7">
         <v>28211</v>
@@ -4744,14 +4744,14 @@
       </c>
       <c r="AD25" s="4">
         <f t="shared" si="10"/>
-        <v>6189</v>
+        <v>6226</v>
       </c>
       <c r="AE25" s="6">
-        <v>28148</v>
+        <v>28185</v>
       </c>
       <c r="AF25" s="5">
         <f t="shared" si="11"/>
-        <v>0.99776682854205812</v>
+        <v>0.99907837368402397</v>
       </c>
       <c r="AG25" s="7">
         <v>20778</v>
@@ -4761,14 +4761,14 @@
       </c>
       <c r="AI25" s="4">
         <f t="shared" si="12"/>
-        <v>4127</v>
+        <v>4154</v>
       </c>
       <c r="AJ25" s="6">
-        <v>20692</v>
+        <v>20719</v>
       </c>
       <c r="AK25" s="5">
         <f t="shared" si="13"/>
-        <v>0.99586100683415146</v>
+        <v>0.9971604581769179</v>
       </c>
       <c r="AL25" s="7">
         <v>21081</v>
@@ -4778,14 +4778,14 @@
       </c>
       <c r="AN25" s="4">
         <f t="shared" si="14"/>
-        <v>4069</v>
+        <v>4095</v>
       </c>
       <c r="AO25" s="6">
-        <v>20864</v>
+        <v>20890</v>
       </c>
       <c r="AP25" s="5">
         <f t="shared" si="15"/>
-        <v>0.98970637066552825</v>
+        <v>0.9909397087424695</v>
       </c>
       <c r="AQ25" s="7">
         <v>28478</v>
@@ -4795,14 +4795,14 @@
       </c>
       <c r="AS25" s="4">
         <f t="shared" si="16"/>
-        <v>5069</v>
+        <v>5120</v>
       </c>
       <c r="AT25" s="6">
-        <v>28394</v>
+        <v>28445</v>
       </c>
       <c r="AU25" s="5">
         <f t="shared" si="17"/>
-        <v>0.99705035465973735</v>
+        <v>0.99884121075918253</v>
       </c>
       <c r="AV25" s="7">
         <v>21086</v>
@@ -4812,14 +4812,14 @@
       </c>
       <c r="AX25" s="4">
         <f t="shared" si="18"/>
-        <v>4283</v>
+        <v>4323</v>
       </c>
       <c r="AY25" s="6">
-        <v>21015</v>
+        <v>21055</v>
       </c>
       <c r="AZ25" s="5">
         <f t="shared" si="19"/>
-        <v>0.99663283695342886</v>
+        <v>0.99852983021910269</v>
       </c>
       <c r="BA25" s="7">
         <v>21405</v>
@@ -4829,14 +4829,14 @@
       </c>
       <c r="BC25" s="4">
         <f t="shared" si="20"/>
-        <v>4349</v>
+        <v>4394</v>
       </c>
       <c r="BD25" s="6">
-        <v>21181</v>
+        <v>21226</v>
       </c>
       <c r="BE25" s="5">
         <f t="shared" si="21"/>
-        <v>0.989535155337538</v>
+        <v>0.99163746788133611</v>
       </c>
       <c r="BF25" s="7">
         <v>28924</v>
@@ -4846,14 +4846,14 @@
       </c>
       <c r="BH25" s="4">
         <f t="shared" si="22"/>
-        <v>7907</v>
+        <v>7988</v>
       </c>
       <c r="BI25" s="6">
-        <v>28721</v>
+        <v>28802</v>
       </c>
       <c r="BJ25" s="5">
         <f t="shared" si="23"/>
-        <v>0.99298160696999027</v>
+        <v>0.99578204950905824</v>
       </c>
     </row>
     <row r="26" spans="1:62" x14ac:dyDescent="0.3">
@@ -4871,14 +4871,14 @@
       </c>
       <c r="E26" s="4">
         <f t="shared" si="0"/>
-        <v>3345</v>
+        <v>3352</v>
       </c>
       <c r="F26" s="13">
-        <v>14061</v>
+        <v>14068</v>
       </c>
       <c r="G26" s="5">
         <f t="shared" si="1"/>
-        <v>0.99850873455475075</v>
+        <v>0.99900582303650054</v>
       </c>
       <c r="H26" s="7">
         <v>14494</v>
@@ -4888,14 +4888,14 @@
       </c>
       <c r="J26" s="4">
         <f t="shared" si="2"/>
-        <v>3054</v>
+        <v>3064</v>
       </c>
       <c r="K26" s="13">
-        <v>14321</v>
+        <v>14331</v>
       </c>
       <c r="L26" s="5">
         <f t="shared" si="3"/>
-        <v>0.98806402649372149</v>
+        <v>0.98875396715882435</v>
       </c>
       <c r="M26" s="7">
         <v>27473</v>
@@ -4905,14 +4905,14 @@
       </c>
       <c r="O26" s="4">
         <f t="shared" si="4"/>
-        <v>5242</v>
+        <v>5272</v>
       </c>
       <c r="P26" s="6">
-        <v>27357</v>
+        <v>27387</v>
       </c>
       <c r="Q26" s="5">
         <f t="shared" si="5"/>
-        <v>0.99577767262403083</v>
+        <v>0.99686965384195392</v>
       </c>
       <c r="R26" s="7">
         <v>14274</v>
@@ -4922,14 +4922,14 @@
       </c>
       <c r="T26" s="4">
         <f t="shared" si="6"/>
-        <v>3374</v>
+        <v>3383</v>
       </c>
       <c r="U26" s="13">
-        <v>14276</v>
+        <v>14285</v>
       </c>
       <c r="V26" s="5">
         <f t="shared" si="7"/>
-        <v>1.0001401148942133</v>
+        <v>1.0007706319181728</v>
       </c>
       <c r="W26" s="7">
         <v>14651</v>
@@ -4939,14 +4939,14 @@
       </c>
       <c r="Y26" s="4">
         <f t="shared" si="8"/>
-        <v>3113</v>
+        <v>3121</v>
       </c>
       <c r="Z26" s="13">
-        <v>14426</v>
+        <v>14434</v>
       </c>
       <c r="AA26" s="5">
         <f t="shared" si="9"/>
-        <v>0.98464268650604059</v>
+        <v>0.98518872431915905</v>
       </c>
       <c r="AB26" s="7">
         <v>28023</v>
@@ -4956,14 +4956,14 @@
       </c>
       <c r="AD26" s="4">
         <f t="shared" si="10"/>
-        <v>5716</v>
+        <v>5756</v>
       </c>
       <c r="AE26" s="6">
-        <v>27605</v>
+        <v>27645</v>
       </c>
       <c r="AF26" s="5">
         <f t="shared" si="11"/>
-        <v>0.98508368126182067</v>
+        <v>0.98651108018413447</v>
       </c>
       <c r="AG26" s="7">
         <v>14346</v>
@@ -4973,14 +4973,14 @@
       </c>
       <c r="AI26" s="4">
         <f t="shared" si="12"/>
-        <v>3056</v>
+        <v>3072</v>
       </c>
       <c r="AJ26" s="6">
-        <v>14287</v>
+        <v>14303</v>
       </c>
       <c r="AK26" s="5">
         <f t="shared" si="13"/>
-        <v>0.9958873553603792</v>
+        <v>0.99700264882197132</v>
       </c>
       <c r="AL26" s="7">
         <v>14687</v>
@@ -4990,14 +4990,14 @@
       </c>
       <c r="AN26" s="4">
         <f t="shared" si="14"/>
-        <v>2969</v>
+        <v>2988</v>
       </c>
       <c r="AO26" s="6">
-        <v>14412</v>
+        <v>14431</v>
       </c>
       <c r="AP26" s="5">
         <f t="shared" si="15"/>
-        <v>0.98127595833049641</v>
+        <v>0.98256961939129839</v>
       </c>
       <c r="AQ26" s="7">
         <v>27948</v>
@@ -5007,14 +5007,14 @@
       </c>
       <c r="AS26" s="4">
         <f t="shared" si="16"/>
-        <v>5253</v>
+        <v>5304</v>
       </c>
       <c r="AT26" s="6">
-        <v>27726</v>
+        <v>27777</v>
       </c>
       <c r="AU26" s="5">
         <f t="shared" si="17"/>
-        <v>0.99205667668527264</v>
+        <v>0.99388149420352079</v>
       </c>
       <c r="AV26" s="7">
         <v>14478</v>
@@ -5024,14 +5024,14 @@
       </c>
       <c r="AX26" s="4">
         <f t="shared" si="18"/>
-        <v>3150</v>
+        <v>3173</v>
       </c>
       <c r="AY26" s="6">
-        <v>14407</v>
+        <v>14430</v>
       </c>
       <c r="AZ26" s="5">
         <f t="shared" si="19"/>
-        <v>0.99509600773587514</v>
+        <v>0.99668462494819732</v>
       </c>
       <c r="BA26" s="7">
         <v>14902</v>
@@ -5041,14 +5041,14 @@
       </c>
       <c r="BC26" s="4">
         <f t="shared" si="20"/>
-        <v>3046</v>
+        <v>3076</v>
       </c>
       <c r="BD26" s="6">
-        <v>14512</v>
+        <v>14542</v>
       </c>
       <c r="BE26" s="5">
         <f t="shared" si="21"/>
-        <v>0.97382901623943097</v>
+        <v>0.97584216883639785</v>
       </c>
       <c r="BF26" s="7">
         <v>28105</v>
@@ -5058,14 +5058,14 @@
       </c>
       <c r="BH26" s="4">
         <f t="shared" si="22"/>
-        <v>6467</v>
+        <v>6548</v>
       </c>
       <c r="BI26" s="6">
-        <v>27806</v>
+        <v>27887</v>
       </c>
       <c r="BJ26" s="5">
         <f t="shared" si="23"/>
-        <v>0.98936132360789897</v>
+        <v>0.99224337306529087</v>
       </c>
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
@@ -5083,14 +5083,14 @@
       </c>
       <c r="E27" s="4">
         <f t="shared" si="0"/>
-        <v>36608</v>
+        <v>36714</v>
       </c>
       <c r="F27" s="13">
-        <v>125142</v>
+        <v>125248</v>
       </c>
       <c r="G27" s="5">
         <f t="shared" si="1"/>
-        <v>0.96906386240968889</v>
+        <v>0.96988469609794248</v>
       </c>
       <c r="H27" s="7">
         <v>129298</v>
@@ -5100,14 +5100,14 @@
       </c>
       <c r="J27" s="4">
         <f t="shared" si="2"/>
-        <v>32317</v>
+        <v>32431</v>
       </c>
       <c r="K27" s="13">
-        <v>125982</v>
+        <v>126096</v>
       </c>
       <c r="L27" s="5">
         <f t="shared" si="3"/>
-        <v>0.97435381831118806</v>
+        <v>0.97523550248263702</v>
       </c>
       <c r="M27" s="7">
         <v>186733</v>
@@ -5117,14 +5117,14 @@
       </c>
       <c r="O27" s="4">
         <f t="shared" si="4"/>
-        <v>47547</v>
+        <v>47741</v>
       </c>
       <c r="P27" s="6">
-        <v>185095</v>
+        <v>185289</v>
       </c>
       <c r="Q27" s="5">
         <f t="shared" si="5"/>
-        <v>0.99122811715122661</v>
+        <v>0.99226703367910329</v>
       </c>
       <c r="R27" s="7">
         <v>126872</v>
@@ -5134,14 +5134,14 @@
       </c>
       <c r="T27" s="4">
         <f t="shared" si="6"/>
-        <v>32393</v>
+        <v>32538</v>
       </c>
       <c r="U27" s="13">
-        <v>125616</v>
+        <v>125761</v>
       </c>
       <c r="V27" s="5">
         <f t="shared" si="7"/>
-        <v>0.99010025852828043</v>
+        <v>0.99124314269499969</v>
       </c>
       <c r="W27" s="7">
         <v>129739</v>
@@ -5151,14 +5151,14 @@
       </c>
       <c r="Y27" s="4">
         <f t="shared" si="8"/>
-        <v>33624</v>
+        <v>33775</v>
       </c>
       <c r="Z27" s="13">
-        <v>126485</v>
+        <v>126636</v>
       </c>
       <c r="AA27" s="5">
         <f t="shared" si="9"/>
-        <v>0.97491887558868184</v>
+        <v>0.97608275075343576</v>
       </c>
       <c r="AB27" s="7">
         <v>188270</v>
@@ -5168,14 +5168,14 @@
       </c>
       <c r="AD27" s="4">
         <f t="shared" si="10"/>
-        <v>52150</v>
+        <v>52399</v>
       </c>
       <c r="AE27" s="6">
-        <v>186481</v>
+        <v>186730</v>
       </c>
       <c r="AF27" s="5">
         <f t="shared" si="11"/>
-        <v>0.99049768948850059</v>
+        <v>0.99182025813990549</v>
       </c>
       <c r="AG27" s="7">
         <v>127800</v>
@@ -5185,14 +5185,14 @@
       </c>
       <c r="AI27" s="4">
         <f t="shared" si="12"/>
-        <v>33970</v>
+        <v>34157</v>
       </c>
       <c r="AJ27" s="6">
-        <v>126656</v>
+        <v>126843</v>
       </c>
       <c r="AK27" s="5">
         <f t="shared" si="13"/>
-        <v>0.99104851330203447</v>
+        <v>0.99251173708920193</v>
       </c>
       <c r="AL27" s="7">
         <v>130262</v>
@@ -5202,14 +5202,14 @@
       </c>
       <c r="AN27" s="4">
         <f t="shared" si="14"/>
-        <v>30716</v>
+        <v>30926</v>
       </c>
       <c r="AO27" s="6">
-        <v>127550</v>
+        <v>127760</v>
       </c>
       <c r="AP27" s="5">
         <f t="shared" si="15"/>
-        <v>0.97918042099768154</v>
+        <v>0.9807925565398965</v>
       </c>
       <c r="AQ27" s="7">
         <v>189830</v>
@@ -5219,14 +5219,14 @@
       </c>
       <c r="AS27" s="4">
         <f t="shared" si="16"/>
-        <v>44593</v>
+        <v>44945</v>
       </c>
       <c r="AT27" s="6">
-        <v>188407</v>
+        <v>188759</v>
       </c>
       <c r="AU27" s="5">
         <f t="shared" si="17"/>
-        <v>0.99250381920665864</v>
+        <v>0.99435810988779438</v>
       </c>
       <c r="AV27" s="7">
         <v>128733</v>
@@ -5236,14 +5236,14 @@
       </c>
       <c r="AX27" s="4">
         <f t="shared" si="18"/>
-        <v>30559</v>
+        <v>30809</v>
       </c>
       <c r="AY27" s="6">
-        <v>128300</v>
+        <v>128550</v>
       </c>
       <c r="AZ27" s="5">
         <f t="shared" si="19"/>
-        <v>0.9966364490845393</v>
+        <v>0.99857845307729953</v>
       </c>
       <c r="BA27" s="7">
         <v>132099</v>
@@ -5253,14 +5253,14 @@
       </c>
       <c r="BC27" s="4">
         <f t="shared" si="20"/>
-        <v>30992</v>
+        <v>31283</v>
       </c>
       <c r="BD27" s="6">
-        <v>129668</v>
+        <v>129959</v>
       </c>
       <c r="BE27" s="5">
         <f t="shared" si="21"/>
-        <v>0.98159713548172201</v>
+        <v>0.98380002876630401</v>
       </c>
       <c r="BF27" s="7">
         <v>192460</v>
@@ -5270,14 +5270,14 @@
       </c>
       <c r="BH27" s="4">
         <f t="shared" si="22"/>
-        <v>64237</v>
+        <v>64826</v>
       </c>
       <c r="BI27" s="6">
-        <v>190643</v>
+        <v>191232</v>
       </c>
       <c r="BJ27" s="5">
         <f t="shared" si="23"/>
-        <v>0.99055907721084901</v>
+        <v>0.9936194533929128</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -5295,14 +5295,14 @@
       </c>
       <c r="E28" s="4">
         <f t="shared" si="0"/>
-        <v>69779</v>
+        <v>69854</v>
       </c>
       <c r="F28" s="13">
-        <v>409624</v>
+        <v>409699</v>
       </c>
       <c r="G28" s="5">
         <f t="shared" si="1"/>
-        <v>0.99100502731394347</v>
+        <v>0.99118647512229585</v>
       </c>
       <c r="H28" s="7">
         <v>423216</v>
@@ -5312,14 +5312,14 @@
       </c>
       <c r="J28" s="4">
         <f t="shared" si="2"/>
-        <v>63800</v>
+        <v>63900</v>
       </c>
       <c r="K28" s="13">
-        <v>413853</v>
+        <v>413953</v>
       </c>
       <c r="L28" s="5">
         <f t="shared" si="3"/>
-        <v>0.97787654531019619</v>
+        <v>0.9781128312729197</v>
       </c>
       <c r="M28" s="7">
         <v>688530</v>
@@ -5329,14 +5329,14 @@
       </c>
       <c r="O28" s="4">
         <f t="shared" si="4"/>
-        <v>102569</v>
+        <v>102750</v>
       </c>
       <c r="P28" s="6">
-        <v>680732</v>
+        <v>680913</v>
       </c>
       <c r="Q28" s="5">
         <f t="shared" si="5"/>
-        <v>0.98867442232001512</v>
+        <v>0.98893730120691914</v>
       </c>
       <c r="R28" s="7">
         <v>417505</v>
@@ -5346,14 +5346,14 @@
       </c>
       <c r="T28" s="4">
         <f t="shared" si="6"/>
-        <v>65363</v>
+        <v>65478</v>
       </c>
       <c r="U28" s="13">
-        <v>414192</v>
+        <v>414307</v>
       </c>
       <c r="V28" s="5">
         <f t="shared" si="7"/>
-        <v>0.99206476569142887</v>
+        <v>0.99234021149447316</v>
       </c>
       <c r="W28" s="7">
         <v>426115</v>
@@ -5363,14 +5363,14 @@
       </c>
       <c r="Y28" s="4">
         <f t="shared" si="8"/>
-        <v>67467</v>
+        <v>67601</v>
       </c>
       <c r="Z28" s="13">
-        <v>416132</v>
+        <v>416266</v>
       </c>
       <c r="AA28" s="5">
         <f t="shared" si="9"/>
-        <v>0.97657205214554754</v>
+        <v>0.976886521244265</v>
       </c>
       <c r="AB28" s="7">
         <v>693825</v>
@@ -5380,14 +5380,14 @@
       </c>
       <c r="AD28" s="4">
         <f t="shared" si="10"/>
-        <v>117826</v>
+        <v>118078</v>
       </c>
       <c r="AE28" s="6">
-        <v>685891</v>
+        <v>686143</v>
       </c>
       <c r="AF28" s="5">
         <f t="shared" si="11"/>
-        <v>0.98856483983713472</v>
+        <v>0.98892804381508304</v>
       </c>
       <c r="AG28" s="7">
         <v>421441</v>
@@ -5397,14 +5397,14 @@
       </c>
       <c r="AI28" s="4">
         <f t="shared" si="12"/>
-        <v>72972</v>
+        <v>73134</v>
       </c>
       <c r="AJ28" s="6">
-        <v>416812</v>
+        <v>416974</v>
       </c>
       <c r="AK28" s="5">
         <f t="shared" si="13"/>
-        <v>0.98901625613075139</v>
+        <v>0.98940065157400447</v>
       </c>
       <c r="AL28" s="7">
         <v>428935</v>
@@ -5414,14 +5414,14 @@
       </c>
       <c r="AN28" s="4">
         <f t="shared" si="14"/>
-        <v>61793</v>
+        <v>61982</v>
       </c>
       <c r="AO28" s="6">
-        <v>421024</v>
+        <v>421213</v>
       </c>
       <c r="AP28" s="5">
         <f t="shared" si="15"/>
-        <v>0.98155664611188176</v>
+        <v>0.98199727231398692</v>
       </c>
       <c r="AQ28" s="7">
         <v>700018</v>
@@ -5431,14 +5431,14 @@
       </c>
       <c r="AS28" s="4">
         <f t="shared" si="16"/>
-        <v>94738</v>
+        <v>95104</v>
       </c>
       <c r="AT28" s="6">
-        <v>694674</v>
+        <v>695040</v>
       </c>
       <c r="AU28" s="5">
         <f t="shared" si="17"/>
-        <v>0.99236591059087054</v>
+        <v>0.99288875428917545</v>
       </c>
       <c r="AV28" s="7">
         <v>428584</v>
@@ -5448,14 +5448,14 @@
       </c>
       <c r="AX28" s="4">
         <f t="shared" si="18"/>
-        <v>63007</v>
+        <v>63239</v>
       </c>
       <c r="AY28" s="6">
-        <v>426424</v>
+        <v>426656</v>
       </c>
       <c r="AZ28" s="5">
         <f t="shared" si="19"/>
-        <v>0.99496014783566344</v>
+        <v>0.99550146529035144</v>
       </c>
       <c r="BA28" s="7">
         <v>438333</v>
@@ -5465,14 +5465,14 @@
       </c>
       <c r="BC28" s="4">
         <f t="shared" si="20"/>
-        <v>62885</v>
+        <v>63168</v>
       </c>
       <c r="BD28" s="6">
-        <v>431336</v>
+        <v>431619</v>
       </c>
       <c r="BE28" s="5">
         <f t="shared" si="21"/>
-        <v>0.98403725021844124</v>
+        <v>0.98468287808583888</v>
       </c>
       <c r="BF28" s="7">
         <v>711748</v>
@@ -5482,14 +5482,14 @@
       </c>
       <c r="BH28" s="4">
         <f t="shared" si="22"/>
-        <v>138233</v>
+        <v>138869</v>
       </c>
       <c r="BI28" s="6">
-        <v>705242</v>
+        <v>705878</v>
       </c>
       <c r="BJ28" s="5">
         <f t="shared" si="23"/>
-        <v>0.99085912429680167</v>
+        <v>0.99175269898896801</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.3">
@@ -5507,14 +5507,14 @@
       </c>
       <c r="E29" s="4">
         <f t="shared" si="0"/>
-        <v>25993</v>
+        <v>26019</v>
       </c>
       <c r="F29" s="13">
-        <v>135506</v>
+        <v>135532</v>
       </c>
       <c r="G29" s="5">
         <f t="shared" si="1"/>
-        <v>0.99058438235595125</v>
+        <v>0.99077444917174728</v>
       </c>
       <c r="H29" s="7">
         <v>138439</v>
@@ -5524,14 +5524,14 @@
       </c>
       <c r="J29" s="4">
         <f t="shared" si="2"/>
-        <v>24257</v>
+        <v>24288</v>
       </c>
       <c r="K29" s="13">
-        <v>136636</v>
+        <v>136667</v>
       </c>
       <c r="L29" s="5">
         <f t="shared" si="3"/>
-        <v>0.98697621335028429</v>
+        <v>0.98720013868924217</v>
       </c>
       <c r="M29" s="7">
         <v>184711</v>
@@ -5541,14 +5541,14 @@
       </c>
       <c r="O29" s="4">
         <f t="shared" si="4"/>
-        <v>32632</v>
+        <v>32681</v>
       </c>
       <c r="P29" s="6">
-        <v>182734</v>
+        <v>182783</v>
       </c>
       <c r="Q29" s="5">
         <f t="shared" si="5"/>
-        <v>0.98929679336910092</v>
+        <v>0.98956207264321017</v>
       </c>
       <c r="R29" s="7">
         <v>138323</v>
@@ -5558,14 +5558,14 @@
       </c>
       <c r="T29" s="4">
         <f t="shared" si="6"/>
-        <v>26871</v>
+        <v>26907</v>
       </c>
       <c r="U29" s="13">
-        <v>136833</v>
+        <v>136869</v>
       </c>
       <c r="V29" s="5">
         <f t="shared" si="7"/>
-        <v>0.98922811101552166</v>
+        <v>0.98948837142051571</v>
       </c>
       <c r="W29" s="7">
         <v>139858</v>
@@ -5575,14 +5575,14 @@
       </c>
       <c r="Y29" s="4">
         <f t="shared" si="8"/>
-        <v>25694</v>
+        <v>25733</v>
       </c>
       <c r="Z29" s="13">
-        <v>137246</v>
+        <v>137285</v>
       </c>
       <c r="AA29" s="5">
         <f t="shared" si="9"/>
-        <v>0.98132391425588816</v>
+        <v>0.98160276852235839</v>
       </c>
       <c r="AB29" s="7">
         <v>187429</v>
@@ -5592,14 +5592,14 @@
       </c>
       <c r="AD29" s="4">
         <f t="shared" si="10"/>
-        <v>35997</v>
+        <v>36058</v>
       </c>
       <c r="AE29" s="6">
-        <v>184097</v>
+        <v>184158</v>
       </c>
       <c r="AF29" s="5">
         <f t="shared" si="11"/>
-        <v>0.98222260162514874</v>
+        <v>0.9825480581980377</v>
       </c>
       <c r="AG29" s="7">
         <v>139419</v>
@@ -5609,14 +5609,14 @@
       </c>
       <c r="AI29" s="4">
         <f t="shared" si="12"/>
-        <v>37956</v>
+        <v>38006</v>
       </c>
       <c r="AJ29" s="6">
-        <v>137951</v>
+        <v>138001</v>
       </c>
       <c r="AK29" s="5">
         <f t="shared" si="13"/>
-        <v>0.98947058865721316</v>
+        <v>0.98982921983373862</v>
       </c>
       <c r="AL29" s="7">
         <v>141276</v>
@@ -5626,14 +5626,14 @@
       </c>
       <c r="AN29" s="4">
         <f t="shared" si="14"/>
-        <v>23601</v>
+        <v>23654</v>
       </c>
       <c r="AO29" s="6">
-        <v>139107</v>
+        <v>139160</v>
       </c>
       <c r="AP29" s="5">
         <f t="shared" si="15"/>
-        <v>0.9846470738129619</v>
+        <v>0.98502222599733857</v>
       </c>
       <c r="AQ29" s="7">
         <v>188424</v>
@@ -5643,14 +5643,14 @@
       </c>
       <c r="AS29" s="4">
         <f t="shared" si="16"/>
-        <v>29693</v>
+        <v>29790</v>
       </c>
       <c r="AT29" s="6">
-        <v>186702</v>
+        <v>186799</v>
       </c>
       <c r="AU29" s="5">
         <f t="shared" si="17"/>
-        <v>0.99086103681059734</v>
+        <v>0.9913758332271897</v>
       </c>
       <c r="AV29" s="7">
         <v>141887</v>
@@ -5660,14 +5660,14 @@
       </c>
       <c r="AX29" s="4">
         <f t="shared" si="18"/>
-        <v>24883</v>
+        <v>24969</v>
       </c>
       <c r="AY29" s="6">
-        <v>140472</v>
+        <v>140558</v>
       </c>
       <c r="AZ29" s="5">
         <f t="shared" si="19"/>
-        <v>0.99002727522606015</v>
+        <v>0.9906333913607307</v>
       </c>
       <c r="BA29" s="7">
         <v>143795</v>
@@ -5677,14 +5677,14 @@
       </c>
       <c r="BC29" s="4">
         <f t="shared" si="20"/>
-        <v>25405</v>
+        <v>25502</v>
       </c>
       <c r="BD29" s="6">
-        <v>141541</v>
+        <v>141638</v>
       </c>
       <c r="BE29" s="5">
         <f t="shared" si="21"/>
-        <v>0.98432490698563924</v>
+        <v>0.98499947842414548</v>
       </c>
       <c r="BF29" s="7">
         <v>191754</v>
@@ -5694,14 +5694,14 @@
       </c>
       <c r="BH29" s="4">
         <f t="shared" si="22"/>
-        <v>43685</v>
+        <v>43878</v>
       </c>
       <c r="BI29" s="6">
-        <v>188995</v>
+        <v>189188</v>
       </c>
       <c r="BJ29" s="5">
         <f t="shared" si="23"/>
-        <v>0.98561177341802519</v>
+        <v>0.98661827132680413</v>
       </c>
     </row>
     <row r="30" spans="1:62" x14ac:dyDescent="0.3">
@@ -5719,14 +5719,14 @@
       </c>
       <c r="E30" s="4">
         <f t="shared" si="0"/>
-        <v>41514</v>
+        <v>41572</v>
       </c>
       <c r="F30" s="13">
-        <v>176187</v>
+        <v>176245</v>
       </c>
       <c r="G30" s="5">
         <f t="shared" si="1"/>
-        <v>0.98844854863503251</v>
+        <v>0.98877394163122878</v>
       </c>
       <c r="H30" s="7">
         <v>181910</v>
@@ -5736,14 +5736,14 @@
       </c>
       <c r="J30" s="4">
         <f t="shared" si="2"/>
-        <v>39053</v>
+        <v>39122</v>
       </c>
       <c r="K30" s="13">
-        <v>178322</v>
+        <v>178391</v>
       </c>
       <c r="L30" s="5">
         <f t="shared" si="3"/>
-        <v>0.98027596063987688</v>
+        <v>0.98065526908911005</v>
       </c>
       <c r="M30" s="7">
         <v>304709</v>
@@ -5753,14 +5753,14 @@
       </c>
       <c r="O30" s="4">
         <f t="shared" si="4"/>
-        <v>61523</v>
+        <v>61649</v>
       </c>
       <c r="P30" s="6">
-        <v>300794</v>
+        <v>300920</v>
       </c>
       <c r="Q30" s="5">
         <f t="shared" si="5"/>
-        <v>0.98715167586123154</v>
+        <v>0.9875651851438586</v>
       </c>
       <c r="R30" s="7">
         <v>179361</v>
@@ -5770,14 +5770,14 @@
       </c>
       <c r="T30" s="4">
         <f t="shared" si="6"/>
-        <v>37604</v>
+        <v>37684</v>
       </c>
       <c r="U30" s="13">
-        <v>177991</v>
+        <v>178071</v>
       </c>
       <c r="V30" s="5">
         <f t="shared" si="7"/>
-        <v>0.99236177318369101</v>
+        <v>0.99280780102697908</v>
       </c>
       <c r="W30" s="7">
         <v>184404</v>
@@ -5787,14 +5787,14 @@
       </c>
       <c r="Y30" s="4">
         <f t="shared" si="8"/>
-        <v>38611</v>
+        <v>38704</v>
       </c>
       <c r="Z30" s="13">
-        <v>179144</v>
+        <v>179237</v>
       </c>
       <c r="AA30" s="5">
         <f t="shared" si="9"/>
-        <v>0.97147567297889414</v>
+        <v>0.97198000043383004</v>
       </c>
       <c r="AB30" s="7">
         <v>307610</v>
@@ -5804,14 +5804,14 @@
       </c>
       <c r="AD30" s="4">
         <f t="shared" si="10"/>
-        <v>66463</v>
+        <v>66649</v>
       </c>
       <c r="AE30" s="6">
-        <v>303659</v>
+        <v>303845</v>
       </c>
       <c r="AF30" s="5">
         <f t="shared" si="11"/>
-        <v>0.98715581418029319</v>
+        <v>0.98776047592731053</v>
       </c>
       <c r="AG30" s="7">
         <v>180656</v>
@@ -5821,14 +5821,14 @@
       </c>
       <c r="AI30" s="4">
         <f t="shared" si="12"/>
-        <v>38603</v>
+        <v>38723</v>
       </c>
       <c r="AJ30" s="6">
-        <v>178929</v>
+        <v>179049</v>
       </c>
       <c r="AK30" s="5">
         <f t="shared" si="13"/>
-        <v>0.99044039500487113</v>
+        <v>0.99110464086440531</v>
       </c>
       <c r="AL30" s="7">
         <v>185185</v>
@@ -5838,14 +5838,14 @@
       </c>
       <c r="AN30" s="4">
         <f t="shared" si="14"/>
-        <v>34453</v>
+        <v>34579</v>
       </c>
       <c r="AO30" s="6">
-        <v>181674</v>
+        <v>181800</v>
       </c>
       <c r="AP30" s="5">
         <f t="shared" si="15"/>
-        <v>0.98104058104058101</v>
+        <v>0.98172098172098177</v>
       </c>
       <c r="AQ30" s="7">
         <v>311830</v>
@@ -5855,14 +5855,14 @@
       </c>
       <c r="AS30" s="4">
         <f t="shared" si="16"/>
-        <v>55681</v>
+        <v>55923</v>
       </c>
       <c r="AT30" s="6">
-        <v>308616</v>
+        <v>308858</v>
       </c>
       <c r="AU30" s="5">
         <f t="shared" si="17"/>
-        <v>0.98969310201071092</v>
+        <v>0.99046916589167178</v>
       </c>
       <c r="AV30" s="7">
         <v>184055</v>
@@ -5872,14 +5872,14 @@
       </c>
       <c r="AX30" s="4">
         <f t="shared" si="18"/>
-        <v>36667</v>
+        <v>36828</v>
       </c>
       <c r="AY30" s="6">
-        <v>182610</v>
+        <v>182771</v>
       </c>
       <c r="AZ30" s="5">
         <f t="shared" si="19"/>
-        <v>0.9921490858710712</v>
+        <v>0.99302382440031511</v>
       </c>
       <c r="BA30" s="7">
         <v>188792</v>
@@ -5889,14 +5889,14 @@
       </c>
       <c r="BC30" s="4">
         <f t="shared" si="20"/>
-        <v>37002</v>
+        <v>37183</v>
       </c>
       <c r="BD30" s="6">
-        <v>184882</v>
+        <v>185063</v>
       </c>
       <c r="BE30" s="5">
         <f t="shared" si="21"/>
-        <v>0.97928937666850291</v>
+        <v>0.98024810373320903</v>
       </c>
       <c r="BF30" s="7">
         <v>315967</v>
@@ -5906,14 +5906,14 @@
       </c>
       <c r="BH30" s="4">
         <f t="shared" si="22"/>
-        <v>79116</v>
+        <v>79519</v>
       </c>
       <c r="BI30" s="6">
-        <v>312823</v>
+        <v>313226</v>
       </c>
       <c r="BJ30" s="5">
         <f t="shared" si="23"/>
-        <v>0.99004959378669288</v>
+        <v>0.99132504343808059</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
@@ -5931,14 +5931,14 @@
       </c>
       <c r="E31" s="4">
         <f t="shared" si="0"/>
-        <v>21566</v>
+        <v>21587</v>
       </c>
       <c r="F31" s="13">
-        <v>78951</v>
+        <v>78972</v>
       </c>
       <c r="G31" s="5">
         <f t="shared" si="1"/>
-        <v>1.0036356702472511</v>
+        <v>1.0039026250556156</v>
       </c>
       <c r="H31" s="7">
         <v>80911</v>
@@ -5948,14 +5948,14 @@
       </c>
       <c r="J31" s="4">
         <f t="shared" si="2"/>
-        <v>18831</v>
+        <v>18853</v>
       </c>
       <c r="K31" s="13">
-        <v>80523</v>
+        <v>80545</v>
       </c>
       <c r="L31" s="5">
         <f t="shared" si="3"/>
-        <v>0.99520460753173234</v>
+        <v>0.99547651122838676</v>
       </c>
       <c r="M31" s="7">
         <v>142260</v>
@@ -5965,14 +5965,14 @@
       </c>
       <c r="O31" s="4">
         <f t="shared" si="4"/>
-        <v>37854</v>
+        <v>37904</v>
       </c>
       <c r="P31" s="6">
-        <v>142391</v>
+        <v>142441</v>
       </c>
       <c r="Q31" s="5">
         <f t="shared" si="5"/>
-        <v>1.0009208491494446</v>
+        <v>1.0012723182904542</v>
       </c>
       <c r="R31" s="7">
         <v>79665</v>
@@ -5982,14 +5982,14 @@
       </c>
       <c r="T31" s="4">
         <f t="shared" si="6"/>
-        <v>20814</v>
+        <v>20837</v>
       </c>
       <c r="U31" s="13">
-        <v>80160</v>
+        <v>80183</v>
       </c>
       <c r="V31" s="5">
         <f t="shared" si="7"/>
-        <v>1.0062135191112784</v>
+        <v>1.0065022280800853</v>
       </c>
       <c r="W31" s="7">
         <v>81657</v>
@@ -5999,14 +5999,14 @@
       </c>
       <c r="Y31" s="4">
         <f t="shared" si="8"/>
-        <v>20851</v>
+        <v>20880</v>
       </c>
       <c r="Z31" s="13">
-        <v>80868</v>
+        <v>80897</v>
       </c>
       <c r="AA31" s="5">
         <f t="shared" si="9"/>
-        <v>0.99033763180131529</v>
+        <v>0.99069277587959392</v>
       </c>
       <c r="AB31" s="7">
         <v>144167</v>
@@ -6016,14 +6016,14 @@
       </c>
       <c r="AD31" s="4">
         <f t="shared" si="10"/>
-        <v>39605</v>
+        <v>39674</v>
       </c>
       <c r="AE31" s="6">
-        <v>144242</v>
+        <v>144311</v>
       </c>
       <c r="AF31" s="5">
         <f t="shared" si="11"/>
-        <v>1.000520230011029</v>
+        <v>1.0009988416211755</v>
       </c>
       <c r="AG31" s="7">
         <v>80917</v>
@@ -6033,14 +6033,14 @@
       </c>
       <c r="AI31" s="4">
         <f t="shared" si="12"/>
-        <v>20986</v>
+        <v>21018</v>
       </c>
       <c r="AJ31" s="6">
-        <v>81666</v>
+        <v>81698</v>
       </c>
       <c r="AK31" s="5">
         <f t="shared" si="13"/>
-        <v>1.0092563985318288</v>
+        <v>1.0096518654918003</v>
       </c>
       <c r="AL31" s="7">
         <v>83546</v>
@@ -6050,14 +6050,14 @@
       </c>
       <c r="AN31" s="4">
         <f t="shared" si="14"/>
-        <v>18131</v>
+        <v>18169</v>
       </c>
       <c r="AO31" s="6">
-        <v>82821</v>
+        <v>82859</v>
       </c>
       <c r="AP31" s="5">
         <f t="shared" si="15"/>
-        <v>0.99132214588370482</v>
+        <v>0.99177698513393819</v>
       </c>
       <c r="AQ31" s="7">
         <v>147023</v>
@@ -6067,14 +6067,14 @@
       </c>
       <c r="AS31" s="4">
         <f t="shared" si="16"/>
-        <v>32951</v>
+        <v>33049</v>
       </c>
       <c r="AT31" s="6">
-        <v>146906</v>
+        <v>147004</v>
       </c>
       <c r="AU31" s="5">
         <f t="shared" si="17"/>
-        <v>0.9992042061446168</v>
+        <v>0.99987076851921131</v>
       </c>
       <c r="AV31" s="7">
         <v>81694</v>
@@ -6084,14 +6084,14 @@
       </c>
       <c r="AX31" s="4">
         <f t="shared" si="18"/>
-        <v>18561</v>
+        <v>18614</v>
       </c>
       <c r="AY31" s="6">
-        <v>82536</v>
+        <v>82589</v>
       </c>
       <c r="AZ31" s="5">
         <f t="shared" si="19"/>
-        <v>1.0103067544740127</v>
+        <v>1.0109555169290279</v>
       </c>
       <c r="BA31" s="7">
         <v>83957</v>
@@ -6101,14 +6101,14 @@
       </c>
       <c r="BC31" s="4">
         <f t="shared" si="20"/>
-        <v>18386</v>
+        <v>18458</v>
       </c>
       <c r="BD31" s="6">
-        <v>83534</v>
+        <v>83606</v>
       </c>
       <c r="BE31" s="5">
         <f t="shared" si="21"/>
-        <v>0.99496170658789618</v>
+        <v>0.99581928844527556</v>
       </c>
       <c r="BF31" s="7">
         <v>148810</v>
@@ -6118,14 +6118,14 @@
       </c>
       <c r="BH31" s="4">
         <f t="shared" si="22"/>
-        <v>50046</v>
+        <v>50227</v>
       </c>
       <c r="BI31" s="6">
-        <v>148836</v>
+        <v>149017</v>
       </c>
       <c r="BJ31" s="5">
         <f t="shared" si="23"/>
-        <v>1.0001747194408979</v>
+        <v>1.0013910355486861</v>
       </c>
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.3">
@@ -6143,14 +6143,14 @@
       </c>
       <c r="E32" s="4">
         <f t="shared" si="0"/>
-        <v>47045</v>
+        <v>47077</v>
       </c>
       <c r="F32" s="13">
-        <v>218109</v>
+        <v>218141</v>
       </c>
       <c r="G32" s="5">
         <f t="shared" si="1"/>
-        <v>0.99324204323452936</v>
+        <v>0.99338776736963386</v>
       </c>
       <c r="H32" s="7">
         <v>225984</v>
@@ -6160,14 +6160,14 @@
       </c>
       <c r="J32" s="4">
         <f t="shared" si="2"/>
-        <v>42364</v>
+        <v>42400</v>
       </c>
       <c r="K32" s="13">
-        <v>222585</v>
+        <v>222621</v>
       </c>
       <c r="L32" s="5">
         <f t="shared" si="3"/>
-        <v>0.98495911214953269</v>
+        <v>0.98511841546304169</v>
       </c>
       <c r="M32" s="7">
         <v>469379</v>
@@ -6177,14 +6177,14 @@
       </c>
       <c r="O32" s="4">
         <f t="shared" si="4"/>
-        <v>100052</v>
+        <v>100133</v>
       </c>
       <c r="P32" s="6">
-        <v>465779</v>
+        <v>465860</v>
       </c>
       <c r="Q32" s="5">
         <f t="shared" si="5"/>
-        <v>0.99233029172587606</v>
+        <v>0.99250286016204392</v>
       </c>
       <c r="R32" s="7">
         <v>220673</v>
@@ -6194,14 +6194,14 @@
       </c>
       <c r="T32" s="4">
         <f t="shared" si="6"/>
-        <v>47692</v>
+        <v>47723</v>
       </c>
       <c r="U32" s="13">
-        <v>219941</v>
+        <v>219972</v>
       </c>
       <c r="V32" s="5">
         <f t="shared" si="7"/>
-        <v>0.99668287466069705</v>
+        <v>0.99682335401249811</v>
       </c>
       <c r="W32" s="7">
         <v>228851</v>
@@ -6211,14 +6211,14 @@
       </c>
       <c r="Y32" s="4">
         <f t="shared" si="8"/>
-        <v>48027</v>
+        <v>48078</v>
       </c>
       <c r="Z32" s="13">
-        <v>222977</v>
+        <v>223028</v>
       </c>
       <c r="AA32" s="5">
         <f t="shared" si="9"/>
-        <v>0.97433264438433742</v>
+        <v>0.97455549680796671</v>
       </c>
       <c r="AB32" s="7">
         <v>476427</v>
@@ -6228,14 +6228,14 @@
       </c>
       <c r="AD32" s="4">
         <f t="shared" si="10"/>
-        <v>106478</v>
+        <v>106589</v>
       </c>
       <c r="AE32" s="6">
-        <v>471612</v>
+        <v>471723</v>
       </c>
       <c r="AF32" s="5">
         <f t="shared" si="11"/>
-        <v>0.98989351988867125</v>
+        <v>0.99012650416538106</v>
       </c>
       <c r="AG32" s="7">
         <v>224544</v>
@@ -6245,14 +6245,14 @@
       </c>
       <c r="AI32" s="4">
         <f t="shared" si="12"/>
-        <v>46626</v>
+        <v>46676</v>
       </c>
       <c r="AJ32" s="6">
-        <v>223710</v>
+        <v>223760</v>
       </c>
       <c r="AK32" s="5">
         <f t="shared" si="13"/>
-        <v>0.9962858058999573</v>
+        <v>0.99650847940715404</v>
       </c>
       <c r="AL32" s="7">
         <v>231787</v>
@@ -6262,14 +6262,14 @@
       </c>
       <c r="AN32" s="4">
         <f t="shared" si="14"/>
-        <v>39711</v>
+        <v>39778</v>
       </c>
       <c r="AO32" s="6">
-        <v>227437</v>
+        <v>227504</v>
       </c>
       <c r="AP32" s="5">
         <f t="shared" si="15"/>
-        <v>0.98123276974118478</v>
+        <v>0.9815218282302286</v>
       </c>
       <c r="AQ32" s="7">
         <v>484390</v>
@@ -6279,14 +6279,14 @@
       </c>
       <c r="AS32" s="4">
         <f t="shared" si="16"/>
-        <v>80856</v>
+        <v>81040</v>
       </c>
       <c r="AT32" s="6">
-        <v>480256</v>
+        <v>480440</v>
       </c>
       <c r="AU32" s="5">
         <f t="shared" si="17"/>
-        <v>0.9914655546150829</v>
+        <v>0.99184541381944302</v>
       </c>
       <c r="AV32" s="7">
         <v>227629</v>
@@ -6296,14 +6296,14 @@
       </c>
       <c r="AX32" s="4">
         <f t="shared" si="18"/>
-        <v>40839</v>
+        <v>40925</v>
       </c>
       <c r="AY32" s="6">
-        <v>227521</v>
+        <v>227607</v>
       </c>
       <c r="AZ32" s="5">
         <f t="shared" si="19"/>
-        <v>0.99952554375760561</v>
+        <v>0.99990335150617893</v>
       </c>
       <c r="BA32" s="7">
         <v>234918</v>
@@ -6313,14 +6313,14 @@
       </c>
       <c r="BC32" s="4">
         <f t="shared" si="20"/>
-        <v>43681</v>
+        <v>43793</v>
       </c>
       <c r="BD32" s="6">
-        <v>231860</v>
+        <v>231972</v>
       </c>
       <c r="BE32" s="5">
         <f t="shared" si="21"/>
-        <v>0.98698269183289489</v>
+        <v>0.98745945393711854</v>
       </c>
       <c r="BF32" s="7">
         <v>492680</v>
@@ -6330,14 +6330,14 @@
       </c>
       <c r="BH32" s="4">
         <f t="shared" si="22"/>
-        <v>132310</v>
+        <v>132684</v>
       </c>
       <c r="BI32" s="6">
-        <v>489246</v>
+        <v>489620</v>
       </c>
       <c r="BJ32" s="5">
         <f t="shared" si="23"/>
-        <v>0.99302995859381338</v>
+        <v>0.99378907201428923</v>
       </c>
     </row>
     <row r="33" spans="1:62" x14ac:dyDescent="0.3">
@@ -6355,14 +6355,14 @@
       </c>
       <c r="E33" s="20">
         <f t="shared" si="0"/>
-        <v>75755</v>
+        <v>75775</v>
       </c>
       <c r="F33" s="13">
-        <v>664204</v>
+        <v>664224</v>
       </c>
       <c r="G33" s="21">
         <f t="shared" si="1"/>
-        <v>1.0011938282696122</v>
+        <v>1.0012239754481378</v>
       </c>
       <c r="H33" s="7">
         <v>674602</v>
@@ -6372,14 +6372,14 @@
       </c>
       <c r="J33" s="20">
         <f t="shared" si="2"/>
-        <v>68668</v>
+        <v>68693</v>
       </c>
       <c r="K33" s="13">
-        <v>671891</v>
+        <v>671916</v>
       </c>
       <c r="L33" s="21">
         <f t="shared" si="3"/>
-        <v>0.99598133417926427</v>
+        <v>0.99601839306731965</v>
       </c>
       <c r="M33" s="7">
         <v>1077651</v>
@@ -6389,14 +6389,14 @@
       </c>
       <c r="O33" s="20">
         <f t="shared" si="4"/>
-        <v>129383</v>
+        <v>129423</v>
       </c>
       <c r="P33" s="6">
-        <v>1076772</v>
+        <v>1076812</v>
       </c>
       <c r="Q33" s="21">
         <f t="shared" si="5"/>
-        <v>0.99918433704418219</v>
+        <v>0.99922145481236502</v>
       </c>
       <c r="R33" s="7">
         <v>670885</v>
@@ -6406,14 +6406,14 @@
       </c>
       <c r="T33" s="20">
         <f t="shared" si="6"/>
-        <v>79558</v>
+        <v>79584</v>
       </c>
       <c r="U33" s="13">
-        <v>672440</v>
+        <v>672466</v>
       </c>
       <c r="V33" s="21">
         <f t="shared" si="7"/>
-        <v>1.00231783390596</v>
+        <v>1.0023565886850951</v>
       </c>
       <c r="W33" s="7">
         <v>679851</v>
@@ -6423,14 +6423,14 @@
       </c>
       <c r="Y33" s="20">
         <f t="shared" si="8"/>
-        <v>75660</v>
+        <v>75685</v>
       </c>
       <c r="Z33" s="13">
-        <v>678445</v>
+        <v>678470</v>
       </c>
       <c r="AA33" s="21">
         <f t="shared" si="9"/>
-        <v>0.99793189978392327</v>
+        <v>0.99796867254736699</v>
       </c>
       <c r="AB33" s="7">
         <v>1091619</v>
@@ -6440,14 +6440,14 @@
       </c>
       <c r="AD33" s="20">
         <f t="shared" si="10"/>
-        <v>137503</v>
+        <v>137564</v>
       </c>
       <c r="AE33" s="6">
-        <v>1090497</v>
+        <v>1090558</v>
       </c>
       <c r="AF33" s="21">
         <f t="shared" si="11"/>
-        <v>0.99897216886111362</v>
+        <v>0.99902804916367338</v>
       </c>
       <c r="AG33" s="7">
         <v>681949</v>
@@ -6457,14 +6457,14 @@
       </c>
       <c r="AI33" s="20">
         <f t="shared" si="12"/>
-        <v>85501</v>
+        <v>85537</v>
       </c>
       <c r="AJ33" s="6">
-        <v>683812</v>
+        <v>683848</v>
       </c>
       <c r="AK33" s="21">
         <f t="shared" si="13"/>
-        <v>1.002731875844088</v>
+        <v>1.0027846657154713</v>
       </c>
       <c r="AL33" s="7">
         <v>691548</v>
@@ -6474,14 +6474,14 @@
       </c>
       <c r="AN33" s="20">
         <f t="shared" si="14"/>
-        <v>66432</v>
+        <v>66479</v>
       </c>
       <c r="AO33" s="6">
-        <v>689357</v>
+        <v>689404</v>
       </c>
       <c r="AP33" s="21">
         <f t="shared" si="15"/>
-        <v>0.99683174559105081</v>
+        <v>0.99689970905851799</v>
       </c>
       <c r="AQ33" s="7">
         <v>1107071</v>
@@ -6491,14 +6491,14 @@
       </c>
       <c r="AS33" s="20">
         <f t="shared" si="16"/>
-        <v>112057</v>
+        <v>112145</v>
       </c>
       <c r="AT33" s="6">
-        <v>1108700</v>
+        <v>1108788</v>
       </c>
       <c r="AU33" s="21">
         <f t="shared" si="17"/>
-        <v>1.0014714503405835</v>
+        <v>1.0015509393706457</v>
       </c>
       <c r="AV33" s="7">
         <v>697202</v>
@@ -6508,14 +6508,14 @@
       </c>
       <c r="AX33" s="20">
         <f t="shared" si="18"/>
-        <v>69828</v>
+        <v>69900</v>
       </c>
       <c r="AY33" s="6">
-        <v>700176</v>
+        <v>700248</v>
       </c>
       <c r="AZ33" s="21">
         <f t="shared" si="19"/>
-        <v>1.0042656217279928</v>
+        <v>1.0043688916555029</v>
       </c>
       <c r="BA33" s="7">
         <v>707985</v>
@@ -6525,14 +6525,14 @@
       </c>
       <c r="BC33" s="20">
         <f t="shared" si="20"/>
-        <v>69482</v>
+        <v>69577</v>
       </c>
       <c r="BD33" s="6">
-        <v>709611</v>
+        <v>709706</v>
       </c>
       <c r="BE33" s="21">
         <f t="shared" si="21"/>
-        <v>1.0022966588275175</v>
+        <v>1.0024308424613515</v>
       </c>
       <c r="BF33" s="7">
         <v>1132408</v>
@@ -6542,14 +6542,14 @@
       </c>
       <c r="BH33" s="20">
         <f t="shared" si="22"/>
-        <v>174446</v>
+        <v>174707</v>
       </c>
       <c r="BI33" s="6">
-        <v>1132896</v>
+        <v>1133157</v>
       </c>
       <c r="BJ33" s="21">
         <f t="shared" si="23"/>
-        <v>1.0004309400851989</v>
+        <v>1.0006614223848649</v>
       </c>
     </row>
     <row r="34" spans="1:62" x14ac:dyDescent="0.3">
@@ -6755,14 +6755,14 @@
       </c>
       <c r="E35" s="4">
         <f t="shared" ref="E35:E48" si="24">F35-D35</f>
-        <v>2220</v>
+        <v>2221</v>
       </c>
       <c r="F35" s="13">
-        <v>11910</v>
+        <v>11911</v>
       </c>
       <c r="G35" s="5">
         <f t="shared" ref="G35:G48" si="25">F35/C35</f>
-        <v>0.99316210807204808</v>
+        <v>0.99324549699799869</v>
       </c>
       <c r="H35" s="7">
         <v>12014</v>
@@ -6772,14 +6772,14 @@
       </c>
       <c r="J35" s="4">
         <f t="shared" ref="J35:J48" si="26">K35-I35</f>
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="K35" s="13">
-        <v>11941</v>
+        <v>11942</v>
       </c>
       <c r="L35" s="5">
         <f t="shared" ref="L35:L48" si="27">K35/H35</f>
-        <v>0.99392375561844515</v>
+        <v>0.99400699184285002</v>
       </c>
       <c r="M35" s="7">
         <v>14733</v>
@@ -6789,14 +6789,14 @@
       </c>
       <c r="O35" s="4">
         <f t="shared" ref="O35:O48" si="28">P35-N35</f>
-        <v>2657</v>
+        <v>2660</v>
       </c>
       <c r="P35" s="6">
-        <v>14664</v>
+        <v>14667</v>
       </c>
       <c r="Q35" s="5">
         <f t="shared" ref="Q35:Q48" si="29">P35/M35</f>
-        <v>0.99531663612298926</v>
+        <v>0.99552026063938093</v>
       </c>
       <c r="R35" s="7">
         <v>12053</v>
@@ -6806,14 +6806,14 @@
       </c>
       <c r="T35" s="4">
         <f t="shared" ref="T35:T48" si="30">U35-S35</f>
-        <v>2253</v>
+        <v>2254</v>
       </c>
       <c r="U35" s="13">
-        <v>11974</v>
+        <v>11975</v>
       </c>
       <c r="V35" s="5">
         <f t="shared" ref="V35:V48" si="31">U35/R35</f>
-        <v>0.99344561519953534</v>
+        <v>0.9935285820957438</v>
       </c>
       <c r="W35" s="7">
         <v>12107</v>
@@ -6823,14 +6823,14 @@
       </c>
       <c r="Y35" s="4">
         <f t="shared" ref="Y35:Y48" si="32">Z35-X35</f>
-        <v>2122</v>
+        <v>2124</v>
       </c>
       <c r="Z35" s="13">
-        <v>11983</v>
+        <v>11985</v>
       </c>
       <c r="AA35" s="5">
         <f t="shared" ref="AA35:AA48" si="33">Z35/W35</f>
-        <v>0.9897579912447344</v>
+        <v>0.98992318493433551</v>
       </c>
       <c r="AB35" s="7">
         <v>14785</v>
@@ -6840,14 +6840,14 @@
       </c>
       <c r="AD35" s="4">
         <f t="shared" ref="AD35:AD48" si="34">AE35-AC35</f>
-        <v>2890</v>
+        <v>2893</v>
       </c>
       <c r="AE35" s="6">
-        <v>14688</v>
+        <v>14691</v>
       </c>
       <c r="AF35" s="5">
         <f t="shared" ref="AF35:AF48" si="35">AE35/AB35</f>
-        <v>0.99343929658437602</v>
+        <v>0.9936422049374366</v>
       </c>
       <c r="AG35" s="7">
         <v>12076</v>
@@ -6857,14 +6857,14 @@
       </c>
       <c r="AI35" s="4">
         <f t="shared" si="12"/>
-        <v>2326</v>
+        <v>2328</v>
       </c>
       <c r="AJ35" s="6">
-        <v>12035</v>
+        <v>12037</v>
       </c>
       <c r="AK35" s="5">
         <f t="shared" ref="AK35:AK47" si="36">AJ35/AG35</f>
-        <v>0.99660483603842331</v>
+        <v>0.99677045379264662</v>
       </c>
       <c r="AL35" s="7">
         <v>12179</v>
@@ -6874,14 +6874,14 @@
       </c>
       <c r="AN35" s="4">
         <f t="shared" ref="AN35:AN48" si="37">AO35-AM35</f>
-        <v>1974</v>
+        <v>1976</v>
       </c>
       <c r="AO35" s="6">
-        <v>12091</v>
+        <v>12093</v>
       </c>
       <c r="AP35" s="5">
         <f t="shared" ref="AP35:AP48" si="38">AO35/AL35</f>
-        <v>0.99277444782001811</v>
+        <v>0.9929386649150177</v>
       </c>
       <c r="AQ35" s="7">
         <v>14849</v>
@@ -6891,14 +6891,14 @@
       </c>
       <c r="AS35" s="4">
         <f t="shared" ref="AS35:AS48" si="39">AT35-AR35</f>
-        <v>2353</v>
+        <v>2358</v>
       </c>
       <c r="AT35" s="6">
-        <v>14832</v>
+        <v>14837</v>
       </c>
       <c r="AU35" s="5">
         <f t="shared" ref="AU35:AU48" si="40">AT35/AQ35</f>
-        <v>0.99885514176038792</v>
+        <v>0.99919186477203847</v>
       </c>
       <c r="AV35" s="7">
         <v>12178</v>
@@ -6908,14 +6908,14 @@
       </c>
       <c r="AX35" s="4">
         <f t="shared" ref="AX35:AX48" si="41">AY35-AW35</f>
-        <v>2076</v>
+        <v>2077</v>
       </c>
       <c r="AY35" s="6">
-        <v>12195</v>
+        <v>12196</v>
       </c>
       <c r="AZ35" s="5">
         <f t="shared" ref="AZ35:AZ48" si="42">AY35/AV35</f>
-        <v>1.0013959599277384</v>
+        <v>1.0014780752176056</v>
       </c>
       <c r="BA35" s="7">
         <v>12308</v>
@@ -6925,14 +6925,14 @@
       </c>
       <c r="BC35" s="4">
         <f t="shared" ref="BC35:BC48" si="43">BD35-BB35</f>
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="BD35" s="6">
-        <v>12245</v>
+        <v>12248</v>
       </c>
       <c r="BE35" s="5">
         <f t="shared" ref="BE35:BE48" si="44">BD35/BA35</f>
-        <v>0.99488137796555087</v>
+        <v>0.99512512187195323</v>
       </c>
       <c r="BF35" s="7">
         <v>15013</v>
@@ -6942,14 +6942,14 @@
       </c>
       <c r="BH35" s="4">
         <f t="shared" ref="BH35:BH48" si="45">BI35-BG35</f>
-        <v>3310</v>
+        <v>3321</v>
       </c>
       <c r="BI35" s="6">
-        <v>14950</v>
+        <v>14961</v>
       </c>
       <c r="BJ35" s="5">
         <f t="shared" ref="BJ35:BJ48" si="46">BI35/BF35</f>
-        <v>0.99580363684806505</v>
+        <v>0.99653633517618068</v>
       </c>
     </row>
     <row r="36" spans="1:62" x14ac:dyDescent="0.3">
@@ -6967,14 +6967,14 @@
       </c>
       <c r="E36" s="4">
         <f t="shared" si="24"/>
-        <v>186663</v>
+        <v>186764</v>
       </c>
       <c r="F36" s="13">
-        <v>888347</v>
+        <v>888448</v>
       </c>
       <c r="G36" s="5">
         <f t="shared" si="25"/>
-        <v>0.99271067305865657</v>
+        <v>0.99282353861454742</v>
       </c>
       <c r="H36" s="7">
         <v>910737</v>
@@ -6984,14 +6984,14 @@
       </c>
       <c r="J36" s="4">
         <f t="shared" si="26"/>
-        <v>161818</v>
+        <v>161929</v>
       </c>
       <c r="K36" s="13">
-        <v>898615</v>
+        <v>898726</v>
       </c>
       <c r="L36" s="5">
         <f t="shared" si="27"/>
-        <v>0.98668990059698902</v>
+        <v>0.9868117799101167</v>
       </c>
       <c r="M36" s="7">
         <v>1579599</v>
@@ -7001,14 +7001,14 @@
       </c>
       <c r="O36" s="4">
         <f t="shared" si="28"/>
-        <v>319275</v>
+        <v>319515</v>
       </c>
       <c r="P36" s="6">
-        <v>1568101</v>
+        <v>1568341</v>
       </c>
       <c r="Q36" s="5">
         <f t="shared" si="29"/>
-        <v>0.99272093740246736</v>
+        <v>0.9928728746979455</v>
       </c>
       <c r="R36" s="7">
         <v>901122</v>
@@ -7018,14 +7018,14 @@
       </c>
       <c r="T36" s="4">
         <f t="shared" si="30"/>
-        <v>174308</v>
+        <v>174440</v>
       </c>
       <c r="U36" s="13">
-        <v>898604</v>
+        <v>898736</v>
       </c>
       <c r="V36" s="5">
         <f t="shared" si="31"/>
-        <v>0.99720570577568857</v>
+        <v>0.99735218982557305</v>
       </c>
       <c r="W36" s="7">
         <v>923866</v>
@@ -7035,14 +7035,14 @@
       </c>
       <c r="Y36" s="4">
         <f t="shared" si="32"/>
-        <v>178304</v>
+        <v>178475</v>
       </c>
       <c r="Z36" s="13">
-        <v>907533</v>
+        <v>907704</v>
       </c>
       <c r="AA36" s="5">
         <f t="shared" si="33"/>
-        <v>0.98232102924017117</v>
+        <v>0.98250612101755019</v>
       </c>
       <c r="AB36" s="7">
         <v>1592928</v>
@@ -7052,14 +7052,14 @@
       </c>
       <c r="AD36" s="4">
         <f t="shared" si="34"/>
-        <v>336799</v>
+        <v>337161</v>
       </c>
       <c r="AE36" s="6">
-        <v>1585088</v>
+        <v>1585450</v>
       </c>
       <c r="AF36" s="5">
         <f t="shared" si="35"/>
-        <v>0.99507824584664217</v>
+        <v>0.99530550031137632</v>
       </c>
       <c r="AG36" s="7">
         <v>914936</v>
@@ -7069,14 +7069,14 @@
       </c>
       <c r="AI36" s="4">
         <f t="shared" si="12"/>
-        <v>305467</v>
+        <v>305689</v>
       </c>
       <c r="AJ36" s="6">
-        <v>912693</v>
+        <v>912915</v>
       </c>
       <c r="AK36" s="5">
         <f t="shared" si="36"/>
-        <v>0.99754846240611361</v>
+        <v>0.9977911023284689</v>
       </c>
       <c r="AL36" s="7">
         <v>934551</v>
@@ -7086,14 +7086,14 @@
       </c>
       <c r="AN36" s="4">
         <f t="shared" si="37"/>
-        <v>162627</v>
+        <v>162878</v>
       </c>
       <c r="AO36" s="6">
-        <v>922771</v>
+        <v>923022</v>
       </c>
       <c r="AP36" s="5">
         <f t="shared" si="38"/>
-        <v>0.98739501643034999</v>
+        <v>0.98766359460318376</v>
       </c>
       <c r="AQ36" s="7">
         <v>1610673</v>
@@ -7103,14 +7103,14 @@
       </c>
       <c r="AS36" s="4">
         <f t="shared" si="39"/>
-        <v>274262</v>
+        <v>274862</v>
       </c>
       <c r="AT36" s="6">
-        <v>1609482</v>
+        <v>1610082</v>
       </c>
       <c r="AU36" s="5">
         <f t="shared" si="40"/>
-        <v>0.99926055754333742</v>
+        <v>0.99963307263485512</v>
       </c>
       <c r="AV36" s="7">
         <v>933166</v>
@@ -7120,14 +7120,14 @@
       </c>
       <c r="AX36" s="4">
         <f t="shared" si="41"/>
-        <v>163089</v>
+        <v>163441</v>
       </c>
       <c r="AY36" s="6">
-        <v>934415</v>
+        <v>934767</v>
       </c>
       <c r="AZ36" s="5">
         <f t="shared" si="42"/>
-        <v>1.0013384542514407</v>
+        <v>1.0017156647370351</v>
       </c>
       <c r="BA36" s="7">
         <v>952259</v>
@@ -7137,14 +7137,14 @@
       </c>
       <c r="BC36" s="4">
         <f t="shared" si="43"/>
-        <v>160141</v>
+        <v>160575</v>
       </c>
       <c r="BD36" s="6">
-        <v>945112</v>
+        <v>945546</v>
       </c>
       <c r="BE36" s="5">
         <f t="shared" si="44"/>
-        <v>0.99249468894491943</v>
+        <v>0.99295044730477733</v>
       </c>
       <c r="BF36" s="7">
         <v>1640364</v>
@@ -7154,14 +7154,14 @@
       </c>
       <c r="BH36" s="4">
         <f t="shared" si="45"/>
-        <v>392911</v>
+        <v>394220</v>
       </c>
       <c r="BI36" s="6">
-        <v>1637066</v>
+        <v>1638375</v>
       </c>
       <c r="BJ36" s="5">
         <f t="shared" si="46"/>
-        <v>0.99798947062968946</v>
+        <v>0.99878746424574061</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -7179,14 +7179,14 @@
       </c>
       <c r="E37" s="4">
         <f t="shared" si="24"/>
-        <v>134606</v>
+        <v>134706</v>
       </c>
       <c r="F37" s="13">
-        <v>700743</v>
+        <v>700843</v>
       </c>
       <c r="G37" s="5">
         <f t="shared" si="25"/>
-        <v>0.98724841291980492</v>
+        <v>0.98738929886699522</v>
       </c>
       <c r="H37" s="7">
         <v>717455</v>
@@ -7196,14 +7196,14 @@
       </c>
       <c r="J37" s="4">
         <f t="shared" si="26"/>
-        <v>120827</v>
+        <v>120933</v>
       </c>
       <c r="K37" s="13">
-        <v>706422</v>
+        <v>706528</v>
       </c>
       <c r="L37" s="5">
         <f t="shared" si="27"/>
-        <v>0.98462203204382159</v>
+        <v>0.98476977650166209</v>
       </c>
       <c r="M37" s="7">
         <v>885615</v>
@@ -7213,14 +7213,14 @@
       </c>
       <c r="O37" s="4">
         <f t="shared" si="28"/>
-        <v>156850</v>
+        <v>157018</v>
       </c>
       <c r="P37" s="6">
-        <v>877549</v>
+        <v>877717</v>
       </c>
       <c r="Q37" s="5">
         <f t="shared" si="29"/>
-        <v>0.99089220485199547</v>
+        <v>0.99108190353596093</v>
       </c>
       <c r="R37" s="7">
         <v>713906</v>
@@ -7230,14 +7230,14 @@
       </c>
       <c r="T37" s="4">
         <f t="shared" si="30"/>
-        <v>125177</v>
+        <v>125302</v>
       </c>
       <c r="U37" s="13">
-        <v>707485</v>
+        <v>707610</v>
       </c>
       <c r="V37" s="5">
         <f t="shared" si="31"/>
-        <v>0.99100581869321736</v>
+        <v>0.9911809117726984</v>
       </c>
       <c r="W37" s="7">
         <v>721933</v>
@@ -7247,14 +7247,14 @@
       </c>
       <c r="Y37" s="4">
         <f t="shared" si="32"/>
-        <v>128458</v>
+        <v>128627</v>
       </c>
       <c r="Z37" s="13">
-        <v>709081</v>
+        <v>709250</v>
       </c>
       <c r="AA37" s="5">
         <f t="shared" si="33"/>
-        <v>0.98219779397811158</v>
+        <v>0.98243188772365297</v>
       </c>
       <c r="AB37" s="7">
         <v>896229</v>
@@ -7264,14 +7264,14 @@
       </c>
       <c r="AD37" s="4">
         <f t="shared" si="34"/>
-        <v>180114</v>
+        <v>180357</v>
       </c>
       <c r="AE37" s="6">
-        <v>882902</v>
+        <v>883145</v>
       </c>
       <c r="AF37" s="5">
         <f t="shared" si="35"/>
-        <v>0.98512991657266169</v>
+        <v>0.98540105263275346</v>
       </c>
       <c r="AG37" s="7">
         <v>721282</v>
@@ -7281,14 +7281,14 @@
       </c>
       <c r="AI37" s="4">
         <f t="shared" si="12"/>
-        <v>136120</v>
+        <v>136324</v>
       </c>
       <c r="AJ37" s="6">
-        <v>711676</v>
+        <v>711880</v>
       </c>
       <c r="AK37" s="5">
         <f t="shared" si="36"/>
-        <v>0.98668204668908965</v>
+        <v>0.98696487642835951</v>
       </c>
       <c r="AL37" s="7">
         <v>727480</v>
@@ -7298,14 +7298,14 @@
       </c>
       <c r="AN37" s="4">
         <f t="shared" si="37"/>
-        <v>121576</v>
+        <v>121832</v>
       </c>
       <c r="AO37" s="6">
-        <v>717323</v>
+        <v>717579</v>
       </c>
       <c r="AP37" s="5">
         <f t="shared" si="38"/>
-        <v>0.98603810414032</v>
+        <v>0.98639000384890307</v>
       </c>
       <c r="AQ37" s="7">
         <v>903787</v>
@@ -7315,14 +7315,14 @@
       </c>
       <c r="AS37" s="4">
         <f t="shared" si="39"/>
-        <v>144712</v>
+        <v>145110</v>
       </c>
       <c r="AT37" s="6">
-        <v>895131</v>
+        <v>895529</v>
       </c>
       <c r="AU37" s="5">
         <f t="shared" si="40"/>
-        <v>0.99042252212080939</v>
+        <v>0.99086289136710304</v>
       </c>
       <c r="AV37" s="7">
         <v>732294</v>
@@ -7332,14 +7332,14 @@
       </c>
       <c r="AX37" s="4">
         <f t="shared" si="41"/>
-        <v>125518</v>
+        <v>125915</v>
       </c>
       <c r="AY37" s="6">
-        <v>725728</v>
+        <v>726125</v>
       </c>
       <c r="AZ37" s="5">
         <f t="shared" si="42"/>
-        <v>0.99103365588138093</v>
+        <v>0.99157578786662193</v>
       </c>
       <c r="BA37" s="7">
         <v>740889</v>
@@ -7349,14 +7349,14 @@
       </c>
       <c r="BC37" s="4">
         <f t="shared" si="43"/>
-        <v>122286</v>
+        <v>122787</v>
       </c>
       <c r="BD37" s="6">
-        <v>730445</v>
+        <v>730946</v>
       </c>
       <c r="BE37" s="5">
         <f t="shared" si="44"/>
-        <v>0.98590342143020071</v>
+        <v>0.98657963608583743</v>
       </c>
       <c r="BF37" s="7">
         <v>918028</v>
@@ -7366,14 +7366,14 @@
       </c>
       <c r="BH37" s="4">
         <f t="shared" si="45"/>
-        <v>216139</v>
+        <v>217044</v>
       </c>
       <c r="BI37" s="6">
-        <v>907165</v>
+        <v>908070</v>
       </c>
       <c r="BJ37" s="5">
         <f t="shared" si="46"/>
-        <v>0.98816702758521524</v>
+        <v>0.98915283629693207</v>
       </c>
     </row>
     <row r="38" spans="1:62" x14ac:dyDescent="0.3">
@@ -7391,14 +7391,14 @@
       </c>
       <c r="E38" s="4">
         <f t="shared" si="24"/>
-        <v>6136</v>
+        <v>6146</v>
       </c>
       <c r="F38" s="13">
-        <v>24492</v>
+        <v>24502</v>
       </c>
       <c r="G38" s="5">
         <f t="shared" si="25"/>
-        <v>1.0056251283104085</v>
+        <v>1.0060357216177376</v>
       </c>
       <c r="H38" s="7">
         <v>24747</v>
@@ -7408,14 +7408,14 @@
       </c>
       <c r="J38" s="4">
         <f t="shared" si="26"/>
-        <v>5617</v>
+        <v>5628</v>
       </c>
       <c r="K38" s="13">
-        <v>24714</v>
+        <v>24725</v>
       </c>
       <c r="L38" s="5">
         <f t="shared" si="27"/>
-        <v>0.99866650503091281</v>
+        <v>0.99911100335394187</v>
       </c>
       <c r="M38" s="7">
         <v>37604</v>
@@ -7425,14 +7425,14 @@
       </c>
       <c r="O38" s="4">
         <f t="shared" si="28"/>
-        <v>8970</v>
+        <v>8983</v>
       </c>
       <c r="P38" s="6">
-        <v>37759</v>
+        <v>37772</v>
       </c>
       <c r="Q38" s="5">
         <f t="shared" si="29"/>
-        <v>1.0041219019253271</v>
+        <v>1.0044676098287417</v>
       </c>
       <c r="R38" s="7">
         <v>24596</v>
@@ -7442,14 +7442,14 @@
       </c>
       <c r="T38" s="4">
         <f t="shared" si="30"/>
-        <v>5829</v>
+        <v>5844</v>
       </c>
       <c r="U38" s="13">
-        <v>24807</v>
+        <v>24822</v>
       </c>
       <c r="V38" s="5">
         <f t="shared" si="31"/>
-        <v>1.008578630671654</v>
+        <v>1.0091884859326721</v>
       </c>
       <c r="W38" s="7">
         <v>25148</v>
@@ -7459,14 +7459,14 @@
       </c>
       <c r="Y38" s="4">
         <f t="shared" si="32"/>
-        <v>6040</v>
+        <v>6052</v>
       </c>
       <c r="Z38" s="13">
-        <v>24992</v>
+        <v>25004</v>
       </c>
       <c r="AA38" s="5">
         <f t="shared" si="33"/>
-        <v>0.99379672339748693</v>
+        <v>0.99427389852075709</v>
       </c>
       <c r="AB38" s="7">
         <v>38035</v>
@@ -7476,14 +7476,14 @@
       </c>
       <c r="AD38" s="4">
         <f t="shared" si="34"/>
-        <v>9577</v>
+        <v>9595</v>
       </c>
       <c r="AE38" s="6">
-        <v>38165</v>
+        <v>38183</v>
       </c>
       <c r="AF38" s="5">
         <f t="shared" si="35"/>
-        <v>1.0034179045615881</v>
+        <v>1.0038911528855001</v>
       </c>
       <c r="AG38" s="7">
         <v>24962</v>
@@ -7493,14 +7493,14 @@
       </c>
       <c r="AI38" s="4">
         <f t="shared" si="12"/>
-        <v>6291</v>
+        <v>6302</v>
       </c>
       <c r="AJ38" s="6">
-        <v>25204</v>
+        <v>25215</v>
       </c>
       <c r="AK38" s="5">
         <f t="shared" si="36"/>
-        <v>1.0096947359987181</v>
+        <v>1.0101354058168417</v>
       </c>
       <c r="AL38" s="7">
         <v>25436</v>
@@ -7510,14 +7510,14 @@
       </c>
       <c r="AN38" s="4">
         <f t="shared" si="37"/>
-        <v>5883</v>
+        <v>5895</v>
       </c>
       <c r="AO38" s="6">
-        <v>25463</v>
+        <v>25475</v>
       </c>
       <c r="AP38" s="5">
         <f t="shared" si="38"/>
-        <v>1.0010614876552917</v>
+        <v>1.0015332599465325</v>
       </c>
       <c r="AQ38" s="7">
         <v>38569</v>
@@ -7527,14 +7527,14 @@
       </c>
       <c r="AS38" s="4">
         <f t="shared" si="39"/>
-        <v>8125</v>
+        <v>8150</v>
       </c>
       <c r="AT38" s="6">
-        <v>38861</v>
+        <v>38886</v>
       </c>
       <c r="AU38" s="5">
         <f t="shared" si="40"/>
-        <v>1.0075708470533329</v>
+        <v>1.0082190360133787</v>
       </c>
       <c r="AV38" s="7">
         <v>25488</v>
@@ -7544,14 +7544,14 @@
       </c>
       <c r="AX38" s="4">
         <f t="shared" si="41"/>
-        <v>5609</v>
+        <v>5633</v>
       </c>
       <c r="AY38" s="6">
-        <v>25664</v>
+        <v>25688</v>
       </c>
       <c r="AZ38" s="5">
         <f t="shared" si="42"/>
-        <v>1.0069052102950409</v>
+        <v>1.0078468298807282</v>
       </c>
       <c r="BA38" s="7">
         <v>25933</v>
@@ -7561,14 +7561,14 @@
       </c>
       <c r="BC38" s="4">
         <f t="shared" si="43"/>
-        <v>5575</v>
+        <v>5607</v>
       </c>
       <c r="BD38" s="6">
-        <v>25923</v>
+        <v>25955</v>
       </c>
       <c r="BE38" s="5">
         <f t="shared" si="44"/>
-        <v>0.99961439093047466</v>
+        <v>1.0008483399529557</v>
       </c>
       <c r="BF38" s="7">
         <v>39379</v>
@@ -7578,14 +7578,14 @@
       </c>
       <c r="BH38" s="4">
         <f t="shared" si="45"/>
-        <v>11541</v>
+        <v>11606</v>
       </c>
       <c r="BI38" s="6">
-        <v>39444</v>
+        <v>39509</v>
       </c>
       <c r="BJ38" s="5">
         <f t="shared" si="46"/>
-        <v>1.0016506259681557</v>
+        <v>1.0033012519363111</v>
       </c>
     </row>
     <row r="39" spans="1:62" x14ac:dyDescent="0.3">
@@ -7815,14 +7815,14 @@
       </c>
       <c r="E40" s="4">
         <f t="shared" si="24"/>
-        <v>64375</v>
+        <v>64433</v>
       </c>
       <c r="F40" s="13">
-        <v>289104</v>
+        <v>289162</v>
       </c>
       <c r="G40" s="5">
         <f t="shared" si="25"/>
-        <v>0.99025853919191087</v>
+        <v>0.99045720470768772</v>
       </c>
       <c r="H40" s="7">
         <v>293812</v>
@@ -7832,14 +7832,14 @@
       </c>
       <c r="J40" s="4">
         <f t="shared" si="26"/>
-        <v>59672</v>
+        <v>59744</v>
       </c>
       <c r="K40" s="13">
-        <v>290705</v>
+        <v>290777</v>
       </c>
       <c r="L40" s="5">
         <f t="shared" si="27"/>
-        <v>0.98942521067893752</v>
+        <v>0.98967026533974101</v>
       </c>
       <c r="M40" s="7">
         <v>351809</v>
@@ -7849,14 +7849,14 @@
       </c>
       <c r="O40" s="4">
         <f t="shared" si="28"/>
-        <v>72060</v>
+        <v>72140</v>
       </c>
       <c r="P40" s="6">
-        <v>349098</v>
+        <v>349178</v>
       </c>
       <c r="Q40" s="5">
         <f t="shared" si="29"/>
-        <v>0.99229411413579527</v>
+        <v>0.99252151025130109</v>
       </c>
       <c r="R40" s="7">
         <v>293831</v>
@@ -7866,14 +7866,14 @@
       </c>
       <c r="T40" s="4">
         <f t="shared" si="30"/>
-        <v>63136</v>
+        <v>63216</v>
       </c>
       <c r="U40" s="13">
-        <v>292744</v>
+        <v>292824</v>
       </c>
       <c r="V40" s="5">
         <f t="shared" si="31"/>
-        <v>0.99630059455945763</v>
+        <v>0.99657285990926758</v>
       </c>
       <c r="W40" s="7">
         <v>297227</v>
@@ -7883,14 +7883,14 @@
       </c>
       <c r="Y40" s="4">
         <f t="shared" si="32"/>
-        <v>66587</v>
+        <v>66677</v>
       </c>
       <c r="Z40" s="13">
-        <v>294132</v>
+        <v>294222</v>
       </c>
       <c r="AA40" s="5">
         <f t="shared" si="33"/>
-        <v>0.98958708327305389</v>
+        <v>0.98988988214395057</v>
       </c>
       <c r="AB40" s="7">
         <v>355500</v>
@@ -7900,14 +7900,14 @@
       </c>
       <c r="AD40" s="4">
         <f t="shared" si="34"/>
-        <v>82103</v>
+        <v>82217</v>
       </c>
       <c r="AE40" s="6">
-        <v>352654</v>
+        <v>352768</v>
       </c>
       <c r="AF40" s="5">
         <f t="shared" si="35"/>
-        <v>0.99199437412095637</v>
+        <v>0.99231504922644165</v>
       </c>
       <c r="AG40" s="7">
         <v>298328</v>
@@ -7917,14 +7917,14 @@
       </c>
       <c r="AI40" s="4">
         <f t="shared" si="12"/>
-        <v>79354</v>
+        <v>79464</v>
       </c>
       <c r="AJ40" s="6">
-        <v>295826</v>
+        <v>295936</v>
       </c>
       <c r="AK40" s="5">
         <f t="shared" si="36"/>
-        <v>0.99161325789064381</v>
+        <v>0.99198197956611511</v>
       </c>
       <c r="AL40" s="7">
         <v>299711</v>
@@ -7934,14 +7934,14 @@
       </c>
       <c r="AN40" s="4">
         <f t="shared" si="37"/>
-        <v>69374</v>
+        <v>69523</v>
       </c>
       <c r="AO40" s="6">
-        <v>297005</v>
+        <v>297154</v>
       </c>
       <c r="AP40" s="5">
         <f t="shared" si="38"/>
-        <v>0.99097130235460162</v>
+        <v>0.99146844793818045</v>
       </c>
       <c r="AQ40" s="7">
         <v>357015</v>
@@ -7951,14 +7951,14 @@
       </c>
       <c r="AS40" s="4">
         <f t="shared" si="39"/>
-        <v>76716</v>
+        <v>76915</v>
       </c>
       <c r="AT40" s="6">
-        <v>354913</v>
+        <v>355112</v>
       </c>
       <c r="AU40" s="5">
         <f t="shared" si="40"/>
-        <v>0.99411229220060782</v>
+        <v>0.99466969174964637</v>
       </c>
       <c r="AV40" s="7">
         <v>300800</v>
@@ -7968,14 +7968,14 @@
       </c>
       <c r="AX40" s="4">
         <f t="shared" si="41"/>
-        <v>66420</v>
+        <v>66620</v>
       </c>
       <c r="AY40" s="6">
-        <v>299120</v>
+        <v>299320</v>
       </c>
       <c r="AZ40" s="5">
         <f t="shared" si="42"/>
-        <v>0.99441489361702129</v>
+        <v>0.99507978723404256</v>
       </c>
       <c r="BA40" s="7">
         <v>303731</v>
@@ -7985,14 +7985,14 @@
       </c>
       <c r="BC40" s="4">
         <f t="shared" si="43"/>
-        <v>65194</v>
+        <v>65416</v>
       </c>
       <c r="BD40" s="6">
-        <v>300431</v>
+        <v>300653</v>
       </c>
       <c r="BE40" s="5">
         <f t="shared" si="44"/>
-        <v>0.98913512285542138</v>
+        <v>0.98986603277242036</v>
       </c>
       <c r="BF40" s="7">
         <v>361393</v>
@@ -8002,14 +8002,14 @@
       </c>
       <c r="BH40" s="4">
         <f t="shared" si="45"/>
-        <v>110206</v>
+        <v>110588</v>
       </c>
       <c r="BI40" s="6">
-        <v>358013</v>
+        <v>358395</v>
       </c>
       <c r="BJ40" s="5">
         <f t="shared" si="46"/>
-        <v>0.99064730086083574</v>
+        <v>0.99170432188780633</v>
       </c>
     </row>
     <row r="41" spans="1:62" x14ac:dyDescent="0.3">
@@ -8027,14 +8027,14 @@
       </c>
       <c r="E41" s="4">
         <f t="shared" si="24"/>
-        <v>152851</v>
+        <v>153018</v>
       </c>
       <c r="F41" s="13">
-        <v>944176</v>
+        <v>944343</v>
       </c>
       <c r="G41" s="5">
         <f t="shared" si="25"/>
-        <v>0.99135664547126856</v>
+        <v>0.99153199049147001</v>
       </c>
       <c r="H41" s="7">
         <v>959446</v>
@@ -8044,14 +8044,14 @@
       </c>
       <c r="J41" s="4">
         <f t="shared" si="26"/>
-        <v>141305</v>
+        <v>141479</v>
       </c>
       <c r="K41" s="13">
-        <v>947839</v>
+        <v>948013</v>
       </c>
       <c r="L41" s="5">
         <f t="shared" si="27"/>
-        <v>0.98790239367301547</v>
+        <v>0.98808374832976531</v>
       </c>
       <c r="M41" s="7">
         <v>1062442</v>
@@ -8061,14 +8061,14 @@
       </c>
       <c r="O41" s="4">
         <f t="shared" si="28"/>
-        <v>158208</v>
+        <v>158406</v>
       </c>
       <c r="P41" s="6">
-        <v>1051689</v>
+        <v>1051887</v>
       </c>
       <c r="Q41" s="5">
         <f t="shared" si="29"/>
-        <v>0.98987897692297555</v>
+        <v>0.99006534003738556</v>
       </c>
       <c r="R41" s="7">
         <v>959218</v>
@@ -8078,14 +8078,14 @@
       </c>
       <c r="T41" s="4">
         <f t="shared" si="30"/>
-        <v>144426</v>
+        <v>144626</v>
       </c>
       <c r="U41" s="13">
-        <v>951316</v>
+        <v>951516</v>
       </c>
       <c r="V41" s="5">
         <f t="shared" si="31"/>
-        <v>0.99176203949467168</v>
+        <v>0.99197054267121765</v>
       </c>
       <c r="W41" s="7">
         <v>961845</v>
@@ -8095,14 +8095,14 @@
       </c>
       <c r="Y41" s="4">
         <f t="shared" si="32"/>
-        <v>150641</v>
+        <v>150882</v>
       </c>
       <c r="Z41" s="13">
-        <v>950248</v>
+        <v>950489</v>
       </c>
       <c r="AA41" s="5">
         <f t="shared" si="33"/>
-        <v>0.98794296378314594</v>
+        <v>0.98819352390457926</v>
       </c>
       <c r="AB41" s="7">
         <v>1065577</v>
@@ -8112,14 +8112,14 @@
       </c>
       <c r="AD41" s="4">
         <f t="shared" si="34"/>
-        <v>183521</v>
+        <v>183799</v>
       </c>
       <c r="AE41" s="6">
-        <v>1054816</v>
+        <v>1055094</v>
       </c>
       <c r="AF41" s="5">
         <f t="shared" si="35"/>
-        <v>0.98990124599160834</v>
+        <v>0.99016213750859861</v>
       </c>
       <c r="AG41" s="7">
         <v>963364</v>
@@ -8129,14 +8129,14 @@
       </c>
       <c r="AI41" s="4">
         <f t="shared" si="12"/>
-        <v>170856</v>
+        <v>171136</v>
       </c>
       <c r="AJ41" s="6">
-        <v>956199</v>
+        <v>956479</v>
       </c>
       <c r="AK41" s="5">
         <f t="shared" si="36"/>
-        <v>0.99256252050107752</v>
+        <v>0.99285316868805562</v>
       </c>
       <c r="AL41" s="7">
         <v>968650</v>
@@ -8146,14 +8146,14 @@
       </c>
       <c r="AN41" s="4">
         <f t="shared" si="37"/>
-        <v>149408</v>
+        <v>149726</v>
       </c>
       <c r="AO41" s="6">
-        <v>958641</v>
+        <v>958959</v>
       </c>
       <c r="AP41" s="5">
         <f t="shared" si="38"/>
-        <v>0.98966706240644198</v>
+        <v>0.98999535435915964</v>
       </c>
       <c r="AQ41" s="7">
         <v>1071657</v>
@@ -8163,14 +8163,14 @@
       </c>
       <c r="AS41" s="4">
         <f t="shared" si="39"/>
-        <v>156560</v>
+        <v>156935</v>
       </c>
       <c r="AT41" s="6">
-        <v>1062965</v>
+        <v>1063340</v>
       </c>
       <c r="AU41" s="5">
         <f t="shared" si="40"/>
-        <v>0.99188919589010294</v>
+        <v>0.99223912128600844</v>
       </c>
       <c r="AV41" s="7">
         <v>970535</v>
@@ -8180,14 +8180,14 @@
       </c>
       <c r="AX41" s="4">
         <f t="shared" si="41"/>
-        <v>144532</v>
+        <v>144899</v>
       </c>
       <c r="AY41" s="6">
-        <v>964141</v>
+        <v>964508</v>
       </c>
       <c r="AZ41" s="5">
         <f t="shared" si="42"/>
-        <v>0.99341188107590139</v>
+        <v>0.99379002302853581</v>
       </c>
       <c r="BA41" s="7">
         <v>973311</v>
@@ -8197,14 +8197,14 @@
       </c>
       <c r="BC41" s="4">
         <f t="shared" si="43"/>
-        <v>140170</v>
+        <v>140613</v>
       </c>
       <c r="BD41" s="6">
-        <v>968742</v>
+        <v>969185</v>
       </c>
       <c r="BE41" s="5">
         <f t="shared" si="44"/>
-        <v>0.99530571420645608</v>
+        <v>0.9957608616362088</v>
       </c>
       <c r="BF41" s="7">
         <v>1078355</v>
@@ -8214,14 +8214,14 @@
       </c>
       <c r="BH41" s="4">
         <f t="shared" si="45"/>
-        <v>222559</v>
+        <v>223235</v>
       </c>
       <c r="BI41" s="6">
-        <v>1073386</v>
+        <v>1074062</v>
       </c>
       <c r="BJ41" s="5">
         <f t="shared" si="46"/>
-        <v>0.99539205549192988</v>
+        <v>0.99601893625012172</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.3">
@@ -8239,14 +8239,14 @@
       </c>
       <c r="E42" s="4">
         <f t="shared" si="24"/>
-        <v>3955</v>
+        <v>3960</v>
       </c>
       <c r="F42" s="13">
-        <v>18761</v>
+        <v>18766</v>
       </c>
       <c r="G42" s="5">
         <f t="shared" si="25"/>
-        <v>0.98669401493636266</v>
+        <v>0.98695697906805513</v>
       </c>
       <c r="H42" s="7">
         <v>19101</v>
@@ -8256,14 +8256,14 @@
       </c>
       <c r="J42" s="4">
         <f t="shared" si="26"/>
-        <v>3741</v>
+        <v>3746</v>
       </c>
       <c r="K42" s="13">
-        <v>18913</v>
+        <v>18918</v>
       </c>
       <c r="L42" s="5">
         <f t="shared" si="27"/>
-        <v>0.99015758337259829</v>
+        <v>0.9904193497722632</v>
       </c>
       <c r="M42" s="7">
         <v>21195</v>
@@ -8273,14 +8273,14 @@
       </c>
       <c r="O42" s="4">
         <f t="shared" si="28"/>
-        <v>4112</v>
+        <v>4117</v>
       </c>
       <c r="P42" s="6">
-        <v>20989</v>
+        <v>20994</v>
       </c>
       <c r="Q42" s="5">
         <f t="shared" si="29"/>
-        <v>0.99028072658645905</v>
+        <v>0.99051663128096246</v>
       </c>
       <c r="R42" s="7">
         <v>19210</v>
@@ -8290,14 +8290,14 @@
       </c>
       <c r="T42" s="4">
         <f t="shared" si="30"/>
-        <v>3882</v>
+        <v>3886</v>
       </c>
       <c r="U42" s="13">
-        <v>19065</v>
+        <v>19069</v>
       </c>
       <c r="V42" s="5">
         <f t="shared" si="31"/>
-        <v>0.99245184799583552</v>
+        <v>0.99266007287870905</v>
       </c>
       <c r="W42" s="7">
         <v>19384</v>
@@ -8307,14 +8307,14 @@
       </c>
       <c r="Y42" s="4">
         <f t="shared" si="32"/>
-        <v>4047</v>
+        <v>4053</v>
       </c>
       <c r="Z42" s="13">
-        <v>19072</v>
+        <v>19078</v>
       </c>
       <c r="AA42" s="5">
         <f t="shared" si="33"/>
-        <v>0.9839042509286009</v>
+        <v>0.9842137845645893</v>
       </c>
       <c r="AB42" s="7">
         <v>21463</v>
@@ -8324,14 +8324,14 @@
       </c>
       <c r="AD42" s="4">
         <f t="shared" si="34"/>
-        <v>4681</v>
+        <v>4685</v>
       </c>
       <c r="AE42" s="6">
-        <v>21148</v>
+        <v>21152</v>
       </c>
       <c r="AF42" s="5">
         <f t="shared" si="35"/>
-        <v>0.98532358011461585</v>
+        <v>0.98550994735125563</v>
       </c>
       <c r="AG42" s="7">
         <v>19423</v>
@@ -8341,14 +8341,14 @@
       </c>
       <c r="AI42" s="4">
         <f t="shared" si="12"/>
-        <v>4563</v>
+        <v>4567</v>
       </c>
       <c r="AJ42" s="6">
-        <v>19177</v>
+        <v>19181</v>
       </c>
       <c r="AK42" s="5">
         <f t="shared" si="36"/>
-        <v>0.9873346033053596</v>
+        <v>0.98754054471502861</v>
       </c>
       <c r="AL42" s="7">
         <v>19535</v>
@@ -8358,14 +8358,14 @@
       </c>
       <c r="AN42" s="4">
         <f t="shared" si="37"/>
-        <v>4082</v>
+        <v>4085</v>
       </c>
       <c r="AO42" s="6">
-        <v>19234</v>
+        <v>19237</v>
       </c>
       <c r="AP42" s="5">
         <f t="shared" si="38"/>
-        <v>0.98459175838239055</v>
+        <v>0.98474532889685185</v>
       </c>
       <c r="AQ42" s="7">
         <v>21570</v>
@@ -8375,14 +8375,14 @@
       </c>
       <c r="AS42" s="4">
         <f t="shared" si="39"/>
-        <v>4085</v>
+        <v>4088</v>
       </c>
       <c r="AT42" s="6">
-        <v>21283</v>
+        <v>21286</v>
       </c>
       <c r="AU42" s="5">
         <f t="shared" si="40"/>
-        <v>0.9866944830783495</v>
+        <v>0.98683356513676401</v>
       </c>
       <c r="AV42" s="7">
         <v>19570</v>
@@ -8392,14 +8392,14 @@
       </c>
       <c r="AX42" s="4">
         <f t="shared" si="41"/>
-        <v>3681</v>
+        <v>3688</v>
       </c>
       <c r="AY42" s="6">
-        <v>19313</v>
+        <v>19320</v>
       </c>
       <c r="AZ42" s="5">
         <f t="shared" si="42"/>
-        <v>0.98686765457332648</v>
+        <v>0.98722534491568725</v>
       </c>
       <c r="BA42" s="7">
         <v>19671</v>
@@ -8409,14 +8409,14 @@
       </c>
       <c r="BC42" s="4">
         <f t="shared" si="43"/>
-        <v>3577</v>
+        <v>3585</v>
       </c>
       <c r="BD42" s="6">
-        <v>19413</v>
+        <v>19421</v>
       </c>
       <c r="BE42" s="5">
         <f t="shared" si="44"/>
-        <v>0.98688424584413603</v>
+        <v>0.98729093589548067</v>
       </c>
       <c r="BF42" s="7">
         <v>21792</v>
@@ -8426,14 +8426,14 @@
       </c>
       <c r="BH42" s="4">
         <f t="shared" si="45"/>
-        <v>5278</v>
+        <v>5291</v>
       </c>
       <c r="BI42" s="6">
-        <v>21575</v>
+        <v>21588</v>
       </c>
       <c r="BJ42" s="5">
         <f t="shared" si="46"/>
-        <v>0.99004221732745967</v>
+        <v>0.99063876651982374</v>
       </c>
     </row>
     <row r="43" spans="1:62" x14ac:dyDescent="0.3">
@@ -8451,14 +8451,14 @@
       </c>
       <c r="E43" s="4">
         <f t="shared" si="24"/>
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="F43" s="13">
-        <v>3670</v>
+        <v>3671</v>
       </c>
       <c r="G43" s="5">
         <f t="shared" si="25"/>
-        <v>1.0002725538293813</v>
+        <v>1.0005451076587626</v>
       </c>
       <c r="H43" s="7">
         <v>3731</v>
@@ -8468,14 +8468,14 @@
       </c>
       <c r="J43" s="4">
         <f t="shared" si="26"/>
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="K43" s="13">
-        <v>3703</v>
+        <v>3705</v>
       </c>
       <c r="L43" s="5">
         <f t="shared" si="27"/>
-        <v>0.99249530956848031</v>
+        <v>0.99303135888501737</v>
       </c>
       <c r="M43" s="7">
         <v>4602</v>
@@ -8485,14 +8485,14 @@
       </c>
       <c r="O43" s="4">
         <f t="shared" si="28"/>
-        <v>1424</v>
+        <v>1427</v>
       </c>
       <c r="P43" s="6">
-        <v>4588</v>
+        <v>4591</v>
       </c>
       <c r="Q43" s="5">
         <f t="shared" si="29"/>
-        <v>0.99695784441547153</v>
+        <v>0.99760973489787053</v>
       </c>
       <c r="R43" s="7">
         <v>3744</v>
@@ -8502,14 +8502,14 @@
       </c>
       <c r="T43" s="4">
         <f t="shared" si="30"/>
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="U43" s="13">
-        <v>3734</v>
+        <v>3736</v>
       </c>
       <c r="V43" s="5">
         <f t="shared" si="31"/>
-        <v>0.99732905982905984</v>
+        <v>0.99786324786324787</v>
       </c>
       <c r="W43" s="7">
         <v>3795</v>
@@ -8519,14 +8519,14 @@
       </c>
       <c r="Y43" s="4">
         <f t="shared" si="32"/>
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="Z43" s="13">
-        <v>3757</v>
+        <v>3759</v>
       </c>
       <c r="AA43" s="5">
         <f t="shared" si="33"/>
-        <v>0.98998682476943345</v>
+        <v>0.99051383399209492</v>
       </c>
       <c r="AB43" s="7">
         <v>4656</v>
@@ -8536,14 +8536,14 @@
       </c>
       <c r="AD43" s="4">
         <f t="shared" si="34"/>
-        <v>1433</v>
+        <v>1438</v>
       </c>
       <c r="AE43" s="6">
-        <v>4626</v>
+        <v>4631</v>
       </c>
       <c r="AF43" s="5">
         <f t="shared" si="35"/>
-        <v>0.99355670103092786</v>
+        <v>0.99463058419243988</v>
       </c>
       <c r="AG43" s="7">
         <v>3765</v>
@@ -8553,14 +8553,14 @@
       </c>
       <c r="AI43" s="4">
         <f t="shared" si="12"/>
-        <v>1179</v>
+        <v>1184</v>
       </c>
       <c r="AJ43" s="6">
-        <v>3769</v>
+        <v>3774</v>
       </c>
       <c r="AK43" s="5">
         <f t="shared" si="36"/>
-        <v>1.0010624169986719</v>
+        <v>1.0023904382470119</v>
       </c>
       <c r="AL43" s="7">
         <v>3815</v>
@@ -8570,14 +8570,14 @@
       </c>
       <c r="AN43" s="4">
         <f t="shared" si="37"/>
-        <v>1150</v>
+        <v>1155</v>
       </c>
       <c r="AO43" s="6">
-        <v>3807</v>
+        <v>3812</v>
       </c>
       <c r="AP43" s="5">
         <f t="shared" si="38"/>
-        <v>0.99790301441677587</v>
+        <v>0.99921363040629096</v>
       </c>
       <c r="AQ43" s="7">
         <v>4752</v>
@@ -8587,14 +8587,14 @@
       </c>
       <c r="AS43" s="4">
         <f t="shared" si="39"/>
-        <v>1291</v>
+        <v>1298</v>
       </c>
       <c r="AT43" s="6">
-        <v>4753</v>
+        <v>4760</v>
       </c>
       <c r="AU43" s="5">
         <f t="shared" si="40"/>
-        <v>1.0002104377104377</v>
+        <v>1.0016835016835017</v>
       </c>
       <c r="AV43" s="7">
         <v>3858</v>
@@ -8604,14 +8604,14 @@
       </c>
       <c r="AX43" s="4">
         <f t="shared" si="41"/>
-        <v>1071</v>
+        <v>1076</v>
       </c>
       <c r="AY43" s="6">
-        <v>3828</v>
+        <v>3833</v>
       </c>
       <c r="AZ43" s="5">
         <f t="shared" si="42"/>
-        <v>0.99222395023328147</v>
+        <v>0.99351995852773456</v>
       </c>
       <c r="BA43" s="7">
         <v>3902</v>
@@ -8621,14 +8621,14 @@
       </c>
       <c r="BC43" s="4">
         <f t="shared" si="43"/>
-        <v>1103</v>
+        <v>1115</v>
       </c>
       <c r="BD43" s="6">
-        <v>3855</v>
+        <v>3867</v>
       </c>
       <c r="BE43" s="5">
         <f t="shared" si="44"/>
-        <v>0.98795489492567912</v>
+        <v>0.99103024090210146</v>
       </c>
       <c r="BF43" s="7">
         <v>4852</v>
@@ -8638,14 +8638,14 @@
       </c>
       <c r="BH43" s="4">
         <f t="shared" si="45"/>
-        <v>1864</v>
+        <v>1878</v>
       </c>
       <c r="BI43" s="6">
-        <v>4793</v>
+        <v>4807</v>
       </c>
       <c r="BJ43" s="5">
         <f t="shared" si="46"/>
-        <v>0.98784006595218465</v>
+        <v>0.99072547403132727</v>
       </c>
     </row>
     <row r="44" spans="1:62" x14ac:dyDescent="0.3">
@@ -8663,14 +8663,14 @@
       </c>
       <c r="E44" s="4">
         <f t="shared" si="24"/>
-        <v>81920</v>
+        <v>81979</v>
       </c>
       <c r="F44" s="13">
-        <v>359407</v>
+        <v>359466</v>
       </c>
       <c r="G44" s="5">
         <f t="shared" si="25"/>
-        <v>0.98814197734521059</v>
+        <v>0.98830419003629166</v>
       </c>
       <c r="H44" s="7">
         <v>368428</v>
@@ -8680,14 +8680,14 @@
       </c>
       <c r="J44" s="4">
         <f t="shared" si="26"/>
-        <v>72425</v>
+        <v>72495</v>
       </c>
       <c r="K44" s="13">
-        <v>362144</v>
+        <v>362214</v>
       </c>
       <c r="L44" s="5">
         <f t="shared" si="27"/>
-        <v>0.98294375020356761</v>
+        <v>0.98313374662077802</v>
       </c>
       <c r="M44" s="7">
         <v>437654</v>
@@ -8697,14 +8697,14 @@
       </c>
       <c r="O44" s="4">
         <f t="shared" si="28"/>
-        <v>87002</v>
+        <v>87097</v>
       </c>
       <c r="P44" s="6">
-        <v>430468</v>
+        <v>430563</v>
       </c>
       <c r="Q44" s="5">
         <f t="shared" si="29"/>
-        <v>0.9835806367587181</v>
+        <v>0.9837977032084706</v>
       </c>
       <c r="R44" s="7">
         <v>368991</v>
@@ -8714,14 +8714,14 @@
       </c>
       <c r="T44" s="4">
         <f t="shared" si="30"/>
-        <v>80816</v>
+        <v>80904</v>
       </c>
       <c r="U44" s="13">
-        <v>364566</v>
+        <v>364654</v>
       </c>
       <c r="V44" s="5">
         <f t="shared" si="31"/>
-        <v>0.9880078375895347</v>
+        <v>0.98824632579114391</v>
       </c>
       <c r="W44" s="7">
         <v>375659</v>
@@ -8731,14 +8731,14 @@
       </c>
       <c r="Y44" s="4">
         <f t="shared" si="32"/>
-        <v>79080</v>
+        <v>79184</v>
       </c>
       <c r="Z44" s="13">
-        <v>364579</v>
+        <v>364683</v>
       </c>
       <c r="AA44" s="5">
         <f t="shared" si="33"/>
-        <v>0.9705051655890049</v>
+        <v>0.97078201241019113</v>
       </c>
       <c r="AB44" s="7">
         <v>443838</v>
@@ -8748,14 +8748,14 @@
       </c>
       <c r="AD44" s="4">
         <f t="shared" si="34"/>
-        <v>99699</v>
+        <v>99838</v>
       </c>
       <c r="AE44" s="6">
-        <v>433458</v>
+        <v>433597</v>
       </c>
       <c r="AF44" s="5">
         <f t="shared" si="35"/>
-        <v>0.97661308855933926</v>
+        <v>0.97692626588980669</v>
       </c>
       <c r="AG44" s="7">
         <v>373881</v>
@@ -8765,14 +8765,14 @@
       </c>
       <c r="AI44" s="4">
         <f t="shared" si="12"/>
-        <v>83208</v>
+        <v>83343</v>
       </c>
       <c r="AJ44" s="6">
-        <v>366670</v>
+        <v>366805</v>
       </c>
       <c r="AK44" s="5">
         <f t="shared" si="36"/>
-        <v>0.98071311460063493</v>
+        <v>0.98107419205576107</v>
       </c>
       <c r="AL44" s="7">
         <v>377474</v>
@@ -8782,14 +8782,14 @@
       </c>
       <c r="AN44" s="4">
         <f t="shared" si="37"/>
-        <v>74382</v>
+        <v>74538</v>
       </c>
       <c r="AO44" s="6">
-        <v>369850</v>
+        <v>370006</v>
       </c>
       <c r="AP44" s="5">
         <f t="shared" si="38"/>
-        <v>0.97980258242951834</v>
+        <v>0.98021585592650085</v>
       </c>
       <c r="AQ44" s="7">
         <v>447335</v>
@@ -8799,14 +8799,14 @@
       </c>
       <c r="AS44" s="4">
         <f t="shared" si="39"/>
-        <v>79580</v>
+        <v>79802</v>
       </c>
       <c r="AT44" s="6">
-        <v>440191</v>
+        <v>440413</v>
       </c>
       <c r="AU44" s="5">
         <f t="shared" si="40"/>
-        <v>0.98402986576055973</v>
+        <v>0.98452613812914258</v>
       </c>
       <c r="AV44" s="7">
         <v>379419</v>
@@ -8816,14 +8816,14 @@
       </c>
       <c r="AX44" s="4">
         <f t="shared" si="41"/>
-        <v>74299</v>
+        <v>74514</v>
       </c>
       <c r="AY44" s="6">
-        <v>374137</v>
+        <v>374352</v>
       </c>
       <c r="AZ44" s="5">
         <f t="shared" si="42"/>
-        <v>0.98607871508806888</v>
+        <v>0.98664537094874005</v>
       </c>
       <c r="BA44" s="7">
         <v>384239</v>
@@ -8833,14 +8833,14 @@
       </c>
       <c r="BC44" s="4">
         <f t="shared" si="43"/>
-        <v>72913</v>
+        <v>73179</v>
       </c>
       <c r="BD44" s="6">
-        <v>376823</v>
+        <v>377089</v>
       </c>
       <c r="BE44" s="5">
         <f t="shared" si="44"/>
-        <v>0.98069951254297461</v>
+        <v>0.98139179000569954</v>
       </c>
       <c r="BF44" s="7">
         <v>454173</v>
@@ -8850,14 +8850,14 @@
       </c>
       <c r="BH44" s="4">
         <f t="shared" si="45"/>
-        <v>117922</v>
+        <v>118403</v>
       </c>
       <c r="BI44" s="6">
-        <v>447385</v>
+        <v>447866</v>
       </c>
       <c r="BJ44" s="5">
         <f t="shared" si="46"/>
-        <v>0.98505415337327407</v>
+        <v>0.98611322117342948</v>
       </c>
     </row>
     <row r="45" spans="1:62" x14ac:dyDescent="0.3">
@@ -8875,14 +8875,14 @@
       </c>
       <c r="E45" s="4">
         <f t="shared" si="24"/>
-        <v>56552</v>
+        <v>56594</v>
       </c>
       <c r="F45" s="13">
-        <v>262371</v>
+        <v>262413</v>
       </c>
       <c r="G45" s="5">
         <f t="shared" si="25"/>
-        <v>0.98405607939329842</v>
+        <v>0.98421360577896799</v>
       </c>
       <c r="H45" s="7">
         <v>269495</v>
@@ -8892,14 +8892,14 @@
       </c>
       <c r="J45" s="4">
         <f t="shared" si="26"/>
-        <v>50136</v>
+        <v>50180</v>
       </c>
       <c r="K45" s="13">
-        <v>263702</v>
+        <v>263746</v>
       </c>
       <c r="L45" s="5">
         <f t="shared" si="27"/>
-        <v>0.97850423941074971</v>
+        <v>0.97866750774596933</v>
       </c>
       <c r="M45" s="7">
         <v>320759</v>
@@ -8909,14 +8909,14 @@
       </c>
       <c r="O45" s="4">
         <f t="shared" si="28"/>
-        <v>60766</v>
+        <v>60819</v>
       </c>
       <c r="P45" s="6">
-        <v>314688</v>
+        <v>314741</v>
       </c>
       <c r="Q45" s="5">
         <f t="shared" si="29"/>
-        <v>0.98107301743676711</v>
+        <v>0.98123825052453706</v>
       </c>
       <c r="R45" s="7">
         <v>267358</v>
@@ -8926,14 +8926,14 @@
       </c>
       <c r="T45" s="4">
         <f t="shared" si="30"/>
-        <v>51862</v>
+        <v>51909</v>
       </c>
       <c r="U45" s="13">
-        <v>263914</v>
+        <v>263961</v>
       </c>
       <c r="V45" s="5">
         <f t="shared" si="31"/>
-        <v>0.98711839555951197</v>
+        <v>0.98729418981291006</v>
       </c>
       <c r="W45" s="7">
         <v>269851</v>
@@ -8943,14 +8943,14 @@
       </c>
       <c r="Y45" s="4">
         <f t="shared" si="32"/>
-        <v>56847</v>
+        <v>56905</v>
       </c>
       <c r="Z45" s="13">
-        <v>263851</v>
+        <v>263909</v>
       </c>
       <c r="AA45" s="5">
         <f t="shared" si="33"/>
-        <v>0.97776550763198955</v>
+        <v>0.97798044105821358</v>
       </c>
       <c r="AB45" s="7">
         <v>321990</v>
@@ -8960,14 +8960,14 @@
       </c>
       <c r="AD45" s="4">
         <f t="shared" si="34"/>
-        <v>71864</v>
+        <v>71950</v>
       </c>
       <c r="AE45" s="6">
-        <v>316271</v>
+        <v>316357</v>
       </c>
       <c r="AF45" s="5">
         <f t="shared" si="35"/>
-        <v>0.98223857883785215</v>
+        <v>0.9825056678778844</v>
       </c>
       <c r="AG45" s="7">
         <v>270238</v>
@@ -8977,14 +8977,14 @@
       </c>
       <c r="AI45" s="4">
         <f t="shared" si="12"/>
-        <v>57328</v>
+        <v>57396</v>
       </c>
       <c r="AJ45" s="6">
-        <v>266589</v>
+        <v>266657</v>
       </c>
       <c r="AK45" s="5">
         <f t="shared" si="36"/>
-        <v>0.98649708775227762</v>
+        <v>0.98674871779690498</v>
       </c>
       <c r="AL45" s="7">
         <v>273027</v>
@@ -8994,14 +8994,14 @@
       </c>
       <c r="AN45" s="4">
         <f t="shared" si="37"/>
-        <v>52369</v>
+        <v>52449</v>
       </c>
       <c r="AO45" s="6">
-        <v>269326</v>
+        <v>269406</v>
       </c>
       <c r="AP45" s="5">
         <f t="shared" si="38"/>
-        <v>0.986444564090731</v>
+        <v>0.98673757540463036</v>
       </c>
       <c r="AQ45" s="7">
         <v>326184</v>
@@ -9011,14 +9011,14 @@
       </c>
       <c r="AS45" s="4">
         <f t="shared" si="39"/>
-        <v>60692</v>
+        <v>60815</v>
       </c>
       <c r="AT45" s="6">
-        <v>322829</v>
+        <v>322952</v>
       </c>
       <c r="AU45" s="5">
         <f t="shared" si="40"/>
-        <v>0.98971439432958086</v>
+        <v>0.99009148210825793</v>
       </c>
       <c r="AV45" s="7">
         <v>274208</v>
@@ -9028,14 +9028,14 @@
       </c>
       <c r="AX45" s="4">
         <f t="shared" si="41"/>
-        <v>52373</v>
+        <v>52478</v>
       </c>
       <c r="AY45" s="6">
-        <v>272311</v>
+        <v>272416</v>
       </c>
       <c r="AZ45" s="5">
         <f t="shared" si="42"/>
-        <v>0.99308189403664371</v>
+        <v>0.99346481503092543</v>
       </c>
       <c r="BA45" s="7">
         <v>277741</v>
@@ -9045,14 +9045,14 @@
       </c>
       <c r="BC45" s="4">
         <f t="shared" si="43"/>
-        <v>50224</v>
+        <v>50350</v>
       </c>
       <c r="BD45" s="6">
-        <v>274619</v>
+        <v>274745</v>
       </c>
       <c r="BE45" s="5">
         <f t="shared" si="44"/>
-        <v>0.98875931173287346</v>
+        <v>0.98921297179746603</v>
       </c>
       <c r="BF45" s="7">
         <v>331328</v>
@@ -9062,14 +9062,14 @@
       </c>
       <c r="BH45" s="4">
         <f t="shared" si="45"/>
-        <v>86973</v>
+        <v>87208</v>
       </c>
       <c r="BI45" s="6">
-        <v>328852</v>
+        <v>329087</v>
       </c>
       <c r="BJ45" s="5">
         <f t="shared" si="46"/>
-        <v>0.99252704268881586</v>
+        <v>0.99323630963878695</v>
       </c>
     </row>
     <row r="46" spans="1:62" x14ac:dyDescent="0.3">
@@ -9121,14 +9121,14 @@
       </c>
       <c r="O46" s="4">
         <f t="shared" si="28"/>
-        <v>1806</v>
+        <v>1808</v>
       </c>
       <c r="P46" s="6">
-        <v>7674</v>
+        <v>7676</v>
       </c>
       <c r="Q46" s="5">
         <f t="shared" si="29"/>
-        <v>1.0149451130802805</v>
+        <v>1.0152096283560375</v>
       </c>
       <c r="R46" s="7">
         <v>2328</v>
@@ -9155,14 +9155,14 @@
       </c>
       <c r="Y46" s="4">
         <f t="shared" si="32"/>
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="Z46" s="13">
-        <v>2473</v>
+        <v>2474</v>
       </c>
       <c r="AA46" s="5">
         <f t="shared" si="33"/>
-        <v>0.98330019880715702</v>
+        <v>0.98369781312127236</v>
       </c>
       <c r="AB46" s="7">
         <v>7764</v>
@@ -9172,14 +9172,14 @@
       </c>
       <c r="AD46" s="4">
         <f t="shared" si="34"/>
-        <v>2015</v>
+        <v>2021</v>
       </c>
       <c r="AE46" s="6">
-        <v>7893</v>
+        <v>7899</v>
       </c>
       <c r="AF46" s="5">
         <f t="shared" si="35"/>
-        <v>1.0166151468315301</v>
+        <v>1.017387944358578</v>
       </c>
       <c r="AG46" s="7">
         <v>2401</v>
@@ -9189,14 +9189,14 @@
       </c>
       <c r="AI46" s="4">
         <f t="shared" si="12"/>
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="AJ46" s="6">
-        <v>2467</v>
+        <v>2470</v>
       </c>
       <c r="AK46" s="5">
         <f t="shared" si="36"/>
-        <v>1.0274885464389838</v>
+        <v>1.028738025822574</v>
       </c>
       <c r="AL46" s="7">
         <v>2561</v>
@@ -9206,14 +9206,14 @@
       </c>
       <c r="AN46" s="4">
         <f t="shared" si="37"/>
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="AO46" s="6">
-        <v>2559</v>
+        <v>2562</v>
       </c>
       <c r="AP46" s="5">
         <f t="shared" si="38"/>
-        <v>0.99921905505661845</v>
+        <v>1.0003904724716908</v>
       </c>
       <c r="AQ46" s="7">
         <v>7981</v>
@@ -9223,14 +9223,14 @@
       </c>
       <c r="AS46" s="4">
         <f t="shared" si="39"/>
-        <v>1869</v>
+        <v>1881</v>
       </c>
       <c r="AT46" s="6">
-        <v>8134</v>
+        <v>8146</v>
       </c>
       <c r="AU46" s="5">
         <f t="shared" si="40"/>
-        <v>1.0191705300087708</v>
+        <v>1.0206741009898508</v>
       </c>
       <c r="AV46" s="7">
         <v>2437</v>
@@ -9240,14 +9240,14 @@
       </c>
       <c r="AX46" s="4">
         <f t="shared" si="41"/>
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="AY46" s="6">
-        <v>2506</v>
+        <v>2511</v>
       </c>
       <c r="AZ46" s="5">
         <f t="shared" si="42"/>
-        <v>1.0283135002051702</v>
+        <v>1.0303652031185884</v>
       </c>
       <c r="BA46" s="7">
         <v>2592</v>
@@ -9257,14 +9257,14 @@
       </c>
       <c r="BC46" s="4">
         <f t="shared" si="43"/>
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="BD46" s="6">
-        <v>2568</v>
+        <v>2575</v>
       </c>
       <c r="BE46" s="5">
         <f t="shared" si="44"/>
-        <v>0.9907407407407407</v>
+        <v>0.99344135802469136</v>
       </c>
       <c r="BF46" s="7">
         <v>8179</v>
@@ -9274,14 +9274,14 @@
       </c>
       <c r="BH46" s="4">
         <f t="shared" si="45"/>
-        <v>1844</v>
+        <v>1869</v>
       </c>
       <c r="BI46" s="6">
-        <v>8293</v>
+        <v>8318</v>
       </c>
       <c r="BJ46" s="5">
         <f t="shared" si="46"/>
-        <v>1.0139381342462404</v>
+        <v>1.0169947426335737</v>
       </c>
     </row>
     <row r="47" spans="1:62" x14ac:dyDescent="0.3">
@@ -9497,10 +9497,10 @@
       </c>
     </row>
     <row r="48" spans="1:62" x14ac:dyDescent="0.3">
-      <c r="A48" s="23" t="s">
+      <c r="A48" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="B48" s="23"/>
+      <c r="B48" s="27"/>
       <c r="C48" s="9">
         <f>SUM(C10:C47)</f>
         <v>8203132</v>
@@ -9511,15 +9511,15 @@
       </c>
       <c r="E48" s="11">
         <f t="shared" si="24"/>
-        <v>1529659</v>
+        <v>1531173</v>
       </c>
       <c r="F48" s="10">
         <f>SUM(F10:F47)</f>
-        <v>8128552</v>
+        <v>8130066</v>
       </c>
       <c r="G48" s="12">
         <f t="shared" si="25"/>
-        <v>0.99090835061535032</v>
+        <v>0.99109291426737978</v>
       </c>
       <c r="H48" s="9">
         <f>SUM(H10:H47)</f>
@@ -9531,15 +9531,15 @@
       </c>
       <c r="J48" s="11">
         <f t="shared" si="26"/>
-        <v>1391948</v>
+        <v>1393646</v>
       </c>
       <c r="K48" s="10">
         <f>SUM(K10:K47)</f>
-        <v>8214867</v>
+        <v>8216565</v>
       </c>
       <c r="L48" s="12">
         <f t="shared" si="27"/>
-        <v>0.96575732353335353</v>
+        <v>0.96595694404277377</v>
       </c>
       <c r="M48" s="9">
         <f>SUM(M10:M47)</f>
@@ -9551,15 +9551,15 @@
       </c>
       <c r="O48" s="11">
         <f t="shared" si="28"/>
-        <v>2221435</v>
+        <v>2224392</v>
       </c>
       <c r="P48" s="10">
         <f>SUM(P10:P47)</f>
-        <v>12631689</v>
+        <v>12634646</v>
       </c>
       <c r="Q48" s="12">
         <f t="shared" si="29"/>
-        <v>0.99090116647125848</v>
+        <v>0.99113313028458983</v>
       </c>
       <c r="R48" s="9">
         <f>SUM(R10:R47)</f>
@@ -9571,15 +9571,15 @@
       </c>
       <c r="T48" s="11">
         <f t="shared" si="30"/>
-        <v>1482239</v>
+        <v>1484230</v>
       </c>
       <c r="U48" s="10">
         <f>SUM(U10:U47)</f>
-        <v>8212820</v>
+        <v>8214811</v>
       </c>
       <c r="V48" s="12">
         <f t="shared" si="31"/>
-        <v>0.99388492634525627</v>
+        <v>0.99412586975913286</v>
       </c>
       <c r="W48" s="9">
         <f>SUM(W10:W47)</f>
@@ -9591,15 +9591,15 @@
       </c>
       <c r="Y48" s="11">
         <f t="shared" si="32"/>
-        <v>1499921</v>
+        <v>1502303</v>
       </c>
       <c r="Z48" s="10">
         <f>SUM(Z10:Z47)</f>
-        <v>8252548</v>
+        <v>8254930</v>
       </c>
       <c r="AA48" s="12">
         <f t="shared" si="33"/>
-        <v>0.98065684197417402</v>
+        <v>0.98093989692854477</v>
       </c>
       <c r="AB48" s="9">
         <f>SUM(AB10:AB47)</f>
@@ -9611,15 +9611,15 @@
       </c>
       <c r="AD48" s="11">
         <f t="shared" si="34"/>
-        <v>2447421</v>
+        <v>2451710</v>
       </c>
       <c r="AE48" s="10">
         <f>SUM(AE10:AE47)</f>
-        <v>12727881</v>
+        <v>12732170</v>
       </c>
       <c r="AF48" s="12">
         <f t="shared" si="35"/>
-        <v>0.98901589977588422</v>
+        <v>0.98934917514152743</v>
       </c>
       <c r="AG48" s="9">
         <f>SUM(AG10:AG47)</f>
@@ -9631,15 +9631,15 @@
       </c>
       <c r="AI48" s="11">
         <f t="shared" ref="AI48" si="47">AJ48-AH48</f>
-        <v>1726271</v>
+        <v>1729203</v>
       </c>
       <c r="AJ48" s="10">
         <f>SUM(AJ10:AJ47)</f>
-        <v>8287609</v>
+        <v>8290541</v>
       </c>
       <c r="AK48" s="12">
         <f t="shared" ref="AK48" si="48">AJ48/AG48</f>
-        <v>0.99196005257349051</v>
+        <v>0.99231098936046314</v>
       </c>
       <c r="AL48" s="9">
         <f>SUM(AL10:AL47)</f>
@@ -9651,15 +9651,15 @@
       </c>
       <c r="AN48" s="11">
         <f t="shared" si="37"/>
-        <v>1395214</v>
+        <v>1398645</v>
       </c>
       <c r="AO48" s="10">
         <f>SUM(AO10:AO47)</f>
-        <v>8362700</v>
+        <v>8366131</v>
       </c>
       <c r="AP48" s="12">
         <f t="shared" si="38"/>
-        <v>0.98547599267023722</v>
+        <v>0.9858803080385814</v>
       </c>
       <c r="AQ48" s="9">
         <f>SUM(AQ10:AQ47)</f>
@@ -9671,15 +9671,15 @@
       </c>
       <c r="AS48" s="11">
         <f t="shared" si="39"/>
-        <v>2045428</v>
+        <v>2051877</v>
       </c>
       <c r="AT48" s="10">
         <f>SUM(AT10:AT47)</f>
-        <v>12904222</v>
+        <v>12910671</v>
       </c>
       <c r="AU48" s="12">
         <f t="shared" si="40"/>
-        <v>0.9929126156518624</v>
+        <v>0.99340883258445534</v>
       </c>
       <c r="AV48" s="9">
         <f>SUM(AV10:AV47)</f>
@@ -9691,15 +9691,15 @@
       </c>
       <c r="AX48" s="11">
         <f t="shared" si="41"/>
-        <v>1414806</v>
+        <v>1419340</v>
       </c>
       <c r="AY48" s="10">
         <f>SUM(AY10:AY47)</f>
-        <v>8443277</v>
+        <v>8447811</v>
       </c>
       <c r="AZ48" s="12">
         <f t="shared" si="42"/>
-        <v>0.99563270836819351</v>
+        <v>0.99616735844537818</v>
       </c>
       <c r="BA48" s="9">
         <f>SUM(BA10:BA47)</f>
@@ -9711,15 +9711,15 @@
       </c>
       <c r="BC48" s="11">
         <f t="shared" si="43"/>
-        <v>1403668</v>
+        <v>1409194</v>
       </c>
       <c r="BD48" s="10">
         <f>SUM(BD10:BD47)</f>
-        <v>8533722</v>
+        <v>8539248</v>
       </c>
       <c r="BE48" s="12">
         <f t="shared" si="44"/>
-        <v>0.98717486890644901</v>
+        <v>0.98781411264154806</v>
       </c>
       <c r="BF48" s="9">
         <f>SUM(BF10:BF47)</f>
@@ -9731,15 +9731,15 @@
       </c>
       <c r="BH48" s="11">
         <f t="shared" si="45"/>
-        <v>2954879</v>
+        <v>2967305</v>
       </c>
       <c r="BI48" s="10">
         <f>SUM(BI10:BI47)</f>
-        <v>13113497</v>
+        <v>13125923</v>
       </c>
       <c r="BJ48" s="12">
         <f t="shared" si="46"/>
-        <v>0.9927931535981237</v>
+        <v>0.99373389791114786</v>
       </c>
     </row>
     <row r="49" spans="1:62" x14ac:dyDescent="0.3">
@@ -10566,6 +10566,12 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="R8:V8"/>
+    <mergeCell ref="M8:Q8"/>
+    <mergeCell ref="C8:G8"/>
     <mergeCell ref="BF8:BJ8"/>
     <mergeCell ref="H8:L8"/>
     <mergeCell ref="A3:B3"/>
@@ -10576,12 +10582,6 @@
     <mergeCell ref="AL8:AP8"/>
     <mergeCell ref="AG8:AK8"/>
     <mergeCell ref="AB8:AF8"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="R8:V8"/>
-    <mergeCell ref="M8:Q8"/>
-    <mergeCell ref="C8:G8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/gstdatabase/GSTR-3B-2024-2025.xlsx
+++ b/gstdatabase/GSTR-3B-2024-2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\May-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 3B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jun-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 3B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C43DF8B-1BF7-4E56-BD14-C6E4CE357A6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23E6C9D3-04EE-4CDC-BDA4-499F96202267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -185,10 +185,10 @@
     <t>FINANCIAL YEAR 2024-2025</t>
   </si>
   <si>
-    <t>Data Considered upto 31st May 2026</t>
+    <t>Data Considered upto 30th Jun 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 31st May 2026</t>
+    <t>Filing %age as on 30th Jun 2026</t>
   </si>
 </sst>
 </file>
@@ -415,6 +415,15 @@
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="17" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -426,15 +435,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
@@ -865,10 +865,10 @@
       <c r="BJ2" s="2"/>
     </row>
     <row r="3" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="26"/>
+      <c r="B3" s="29"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -1189,100 +1189,100 @@
       <c r="BJ7" s="1"/>
     </row>
     <row r="8" spans="1:62" s="15" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="23">
+      <c r="C8" s="26">
         <v>45383</v>
       </c>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="23">
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="26">
         <v>45413</v>
       </c>
-      <c r="I8" s="24"/>
-      <c r="J8" s="24"/>
-      <c r="K8" s="24"/>
-      <c r="L8" s="25"/>
-      <c r="M8" s="23">
+      <c r="I8" s="27"/>
+      <c r="J8" s="27"/>
+      <c r="K8" s="27"/>
+      <c r="L8" s="28"/>
+      <c r="M8" s="26">
         <v>45444</v>
       </c>
-      <c r="N8" s="24"/>
-      <c r="O8" s="24"/>
-      <c r="P8" s="24"/>
-      <c r="Q8" s="25"/>
-      <c r="R8" s="23">
+      <c r="N8" s="27"/>
+      <c r="O8" s="27"/>
+      <c r="P8" s="27"/>
+      <c r="Q8" s="28"/>
+      <c r="R8" s="26">
         <v>45474</v>
       </c>
-      <c r="S8" s="24"/>
-      <c r="T8" s="24"/>
-      <c r="U8" s="24"/>
-      <c r="V8" s="25"/>
-      <c r="W8" s="23">
+      <c r="S8" s="27"/>
+      <c r="T8" s="27"/>
+      <c r="U8" s="27"/>
+      <c r="V8" s="28"/>
+      <c r="W8" s="26">
         <v>45505</v>
       </c>
-      <c r="X8" s="24"/>
-      <c r="Y8" s="24"/>
-      <c r="Z8" s="24"/>
-      <c r="AA8" s="25"/>
-      <c r="AB8" s="23">
+      <c r="X8" s="27"/>
+      <c r="Y8" s="27"/>
+      <c r="Z8" s="27"/>
+      <c r="AA8" s="28"/>
+      <c r="AB8" s="26">
         <v>45536</v>
       </c>
-      <c r="AC8" s="24"/>
-      <c r="AD8" s="24"/>
-      <c r="AE8" s="24"/>
-      <c r="AF8" s="25"/>
-      <c r="AG8" s="23">
+      <c r="AC8" s="27"/>
+      <c r="AD8" s="27"/>
+      <c r="AE8" s="27"/>
+      <c r="AF8" s="28"/>
+      <c r="AG8" s="26">
         <v>45566</v>
       </c>
-      <c r="AH8" s="24"/>
-      <c r="AI8" s="24"/>
-      <c r="AJ8" s="24"/>
-      <c r="AK8" s="25"/>
-      <c r="AL8" s="23">
+      <c r="AH8" s="27"/>
+      <c r="AI8" s="27"/>
+      <c r="AJ8" s="27"/>
+      <c r="AK8" s="28"/>
+      <c r="AL8" s="26">
         <v>45597</v>
       </c>
-      <c r="AM8" s="24"/>
-      <c r="AN8" s="24"/>
-      <c r="AO8" s="24"/>
-      <c r="AP8" s="25"/>
-      <c r="AQ8" s="23">
+      <c r="AM8" s="27"/>
+      <c r="AN8" s="27"/>
+      <c r="AO8" s="27"/>
+      <c r="AP8" s="28"/>
+      <c r="AQ8" s="26">
         <v>45627</v>
       </c>
-      <c r="AR8" s="24"/>
-      <c r="AS8" s="24"/>
-      <c r="AT8" s="24"/>
-      <c r="AU8" s="25"/>
-      <c r="AV8" s="23">
+      <c r="AR8" s="27"/>
+      <c r="AS8" s="27"/>
+      <c r="AT8" s="27"/>
+      <c r="AU8" s="28"/>
+      <c r="AV8" s="26">
         <v>45658</v>
       </c>
-      <c r="AW8" s="24"/>
-      <c r="AX8" s="24"/>
-      <c r="AY8" s="24"/>
-      <c r="AZ8" s="25"/>
-      <c r="BA8" s="23">
+      <c r="AW8" s="27"/>
+      <c r="AX8" s="27"/>
+      <c r="AY8" s="27"/>
+      <c r="AZ8" s="28"/>
+      <c r="BA8" s="26">
         <v>45689</v>
       </c>
-      <c r="BB8" s="24"/>
-      <c r="BC8" s="24"/>
-      <c r="BD8" s="24"/>
-      <c r="BE8" s="25"/>
-      <c r="BF8" s="23">
+      <c r="BB8" s="27"/>
+      <c r="BC8" s="27"/>
+      <c r="BD8" s="27"/>
+      <c r="BE8" s="28"/>
+      <c r="BF8" s="26">
         <v>45717</v>
       </c>
-      <c r="BG8" s="24"/>
-      <c r="BH8" s="24"/>
-      <c r="BI8" s="24"/>
-      <c r="BJ8" s="25"/>
+      <c r="BG8" s="27"/>
+      <c r="BH8" s="27"/>
+      <c r="BI8" s="27"/>
+      <c r="BJ8" s="28"/>
     </row>
     <row r="9" spans="1:62" s="15" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="28"/>
-      <c r="B9" s="29"/>
+      <c r="A9" s="24"/>
+      <c r="B9" s="25"/>
       <c r="C9" s="16" t="s">
         <v>2</v>
       </c>
@@ -1479,14 +1479,14 @@
       </c>
       <c r="E10" s="4">
         <f>F10-D10</f>
-        <v>15640</v>
+        <v>15642</v>
       </c>
       <c r="F10" s="13">
-        <v>73030</v>
+        <v>73032</v>
       </c>
       <c r="G10" s="5">
         <f>F10/C10</f>
-        <v>1.0016458647647786</v>
+        <v>1.0016732958441914</v>
       </c>
       <c r="H10" s="7">
         <v>74548</v>
@@ -1496,14 +1496,14 @@
       </c>
       <c r="J10" s="4">
         <f>K10-I10</f>
-        <v>15550</v>
+        <v>15554</v>
       </c>
       <c r="K10" s="13">
-        <v>74106</v>
+        <v>74110</v>
       </c>
       <c r="L10" s="5">
         <f>K10/H10</f>
-        <v>0.99407093416322367</v>
+        <v>0.99412459086762894</v>
       </c>
       <c r="M10" s="7">
         <v>129395</v>
@@ -1513,14 +1513,14 @@
       </c>
       <c r="O10" s="4">
         <f>P10-N10</f>
-        <v>25075</v>
+        <v>25082</v>
       </c>
       <c r="P10" s="6">
-        <v>129052</v>
+        <v>129059</v>
       </c>
       <c r="Q10" s="5">
         <f>P10/M10</f>
-        <v>0.99734920205572086</v>
+        <v>0.99740329997295107</v>
       </c>
       <c r="R10" s="7">
         <v>72583</v>
@@ -1530,14 +1530,14 @@
       </c>
       <c r="T10" s="4">
         <f>U10-S10</f>
-        <v>14230</v>
+        <v>14235</v>
       </c>
       <c r="U10" s="13">
-        <v>73058</v>
+        <v>73063</v>
       </c>
       <c r="V10" s="5">
         <f>U10/R10</f>
-        <v>1.006544232120469</v>
+        <v>1.0066131187743688</v>
       </c>
       <c r="W10" s="7">
         <v>74384</v>
@@ -1547,14 +1547,14 @@
       </c>
       <c r="Y10" s="4">
         <f>Z10-X10</f>
-        <v>15701</v>
+        <v>15707</v>
       </c>
       <c r="Z10" s="13">
-        <v>73658</v>
+        <v>73664</v>
       </c>
       <c r="AA10" s="5">
         <f>Z10/W10</f>
-        <v>0.99023983652398362</v>
+        <v>0.99032049903204988</v>
       </c>
       <c r="AB10" s="7">
         <v>130621</v>
@@ -1564,14 +1564,14 @@
       </c>
       <c r="AD10" s="4">
         <f>AE10-AC10</f>
-        <v>26355</v>
+        <v>26369</v>
       </c>
       <c r="AE10" s="6">
-        <v>129908</v>
+        <v>129922</v>
       </c>
       <c r="AF10" s="5">
         <f>AE10/AB10</f>
-        <v>0.99454145964278329</v>
+        <v>0.99464863995835284</v>
       </c>
       <c r="AG10" s="7">
         <v>72721</v>
@@ -1581,14 +1581,14 @@
       </c>
       <c r="AI10" s="4">
         <f>AJ10-AH10</f>
-        <v>14485</v>
+        <v>14494</v>
       </c>
       <c r="AJ10" s="6">
-        <v>72699</v>
+        <v>72708</v>
       </c>
       <c r="AK10" s="5">
         <f>AJ10/AG10</f>
-        <v>0.99969747390712449</v>
+        <v>0.99982123458148264</v>
       </c>
       <c r="AL10" s="7">
         <v>74187</v>
@@ -1598,14 +1598,14 @@
       </c>
       <c r="AN10" s="4">
         <f>AO10-AM10</f>
-        <v>13063</v>
+        <v>13075</v>
       </c>
       <c r="AO10" s="6">
-        <v>73748</v>
+        <v>73760</v>
       </c>
       <c r="AP10" s="5">
         <f>AO10/AL10</f>
-        <v>0.99408252119643603</v>
+        <v>0.99424427460336717</v>
       </c>
       <c r="AQ10" s="7">
         <v>132270</v>
@@ -1615,14 +1615,14 @@
       </c>
       <c r="AS10" s="4">
         <f>AT10-AR10</f>
-        <v>21531</v>
+        <v>21545</v>
       </c>
       <c r="AT10" s="6">
-        <v>132011</v>
+        <v>132025</v>
       </c>
       <c r="AU10" s="5">
         <f>AT10/AQ10</f>
-        <v>0.99804188402510019</v>
+        <v>0.99814772813185149</v>
       </c>
       <c r="AV10" s="7">
         <v>73561</v>
@@ -1632,14 +1632,14 @@
       </c>
       <c r="AX10" s="4">
         <f>AY10-AW10</f>
-        <v>12826</v>
+        <v>12839</v>
       </c>
       <c r="AY10" s="6">
-        <v>73575</v>
+        <v>73588</v>
       </c>
       <c r="AZ10" s="5">
         <f>AY10/AV10</f>
-        <v>1.0001903182392844</v>
+        <v>1.0003670423186199</v>
       </c>
       <c r="BA10" s="7">
         <v>75582</v>
@@ -1649,14 +1649,14 @@
       </c>
       <c r="BC10" s="4">
         <f>BD10-BB10</f>
-        <v>12511</v>
+        <v>12525</v>
       </c>
       <c r="BD10" s="6">
-        <v>74476</v>
+        <v>74490</v>
       </c>
       <c r="BE10" s="5">
         <f>BD10/BA10</f>
-        <v>0.98536688629567881</v>
+        <v>0.98555211558307532</v>
       </c>
       <c r="BF10" s="7">
         <v>134150</v>
@@ -1666,14 +1666,14 @@
       </c>
       <c r="BH10" s="4">
         <f>BI10-BG10</f>
-        <v>33039</v>
+        <v>33062</v>
       </c>
       <c r="BI10" s="6">
-        <v>133506</v>
+        <v>133529</v>
       </c>
       <c r="BJ10" s="5">
         <f>BI10/BF10</f>
-        <v>0.9951994036526276</v>
+        <v>0.99537085352217669</v>
       </c>
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.3">
@@ -1691,14 +1691,14 @@
       </c>
       <c r="E11" s="4">
         <f t="shared" ref="E11:E33" si="0">F11-D11</f>
-        <v>8247</v>
+        <v>8250</v>
       </c>
       <c r="F11" s="13">
-        <v>46485</v>
+        <v>46488</v>
       </c>
       <c r="G11" s="5">
         <f t="shared" ref="G11:G33" si="1">F11/C11</f>
-        <v>0.99879675984615712</v>
+        <v>0.99886121914011305</v>
       </c>
       <c r="H11" s="7">
         <v>47616</v>
@@ -1708,14 +1708,14 @@
       </c>
       <c r="J11" s="4">
         <f t="shared" ref="J11:J33" si="2">K11-I11</f>
-        <v>8141</v>
+        <v>8146</v>
       </c>
       <c r="K11" s="13">
-        <v>47138</v>
+        <v>47143</v>
       </c>
       <c r="L11" s="5">
         <f t="shared" ref="L11:L33" si="3">K11/H11</f>
-        <v>0.98996135752688175</v>
+        <v>0.99006636424731187</v>
       </c>
       <c r="M11" s="7">
         <v>108402</v>
@@ -1725,14 +1725,14 @@
       </c>
       <c r="O11" s="4">
         <f t="shared" ref="O11:O33" si="4">P11-N11</f>
-        <v>16815</v>
+        <v>16821</v>
       </c>
       <c r="P11" s="6">
-        <v>107773</v>
+        <v>107779</v>
       </c>
       <c r="Q11" s="5">
         <f t="shared" ref="Q11:Q33" si="5">P11/M11</f>
-        <v>0.99419752403092199</v>
+        <v>0.99425287356321834</v>
       </c>
       <c r="R11" s="7">
         <v>46539</v>
@@ -1742,14 +1742,14 @@
       </c>
       <c r="T11" s="4">
         <f t="shared" ref="T11:T33" si="6">U11-S11</f>
-        <v>8192</v>
+        <v>8195</v>
       </c>
       <c r="U11" s="13">
-        <v>46460</v>
+        <v>46463</v>
       </c>
       <c r="V11" s="5">
         <f t="shared" ref="V11:V33" si="7">U11/R11</f>
-        <v>0.99830249897935064</v>
+        <v>0.99836696104342593</v>
       </c>
       <c r="W11" s="7">
         <v>48300</v>
@@ -1759,14 +1759,14 @@
       </c>
       <c r="Y11" s="4">
         <f t="shared" ref="Y11:Y33" si="8">Z11-X11</f>
-        <v>8368</v>
+        <v>8372</v>
       </c>
       <c r="Z11" s="13">
-        <v>47073</v>
+        <v>47077</v>
       </c>
       <c r="AA11" s="5">
         <f t="shared" ref="AA11:AA33" si="9">Z11/W11</f>
-        <v>0.97459627329192544</v>
+        <v>0.97467908902691514</v>
       </c>
       <c r="AB11" s="7">
         <v>109219</v>
@@ -1776,14 +1776,14 @@
       </c>
       <c r="AD11" s="4">
         <f t="shared" ref="AD11:AD33" si="10">AE11-AC11</f>
-        <v>18132</v>
+        <v>18145</v>
       </c>
       <c r="AE11" s="6">
-        <v>108414</v>
+        <v>108427</v>
       </c>
       <c r="AF11" s="5">
         <f t="shared" ref="AF11:AF33" si="11">AE11/AB11</f>
-        <v>0.9926294875433761</v>
+        <v>0.99274851445261358</v>
       </c>
       <c r="AG11" s="7">
         <v>46763</v>
@@ -1793,14 +1793,14 @@
       </c>
       <c r="AI11" s="4">
         <f t="shared" ref="AI11:AI47" si="12">AJ11-AH11</f>
-        <v>8315</v>
+        <v>8321</v>
       </c>
       <c r="AJ11" s="6">
-        <v>46684</v>
+        <v>46690</v>
       </c>
       <c r="AK11" s="5">
         <f t="shared" ref="AK11:AK33" si="13">AJ11/AG11</f>
-        <v>0.99831063019908906</v>
+        <v>0.99843893676624684</v>
       </c>
       <c r="AL11" s="7">
         <v>48206</v>
@@ -1810,14 +1810,14 @@
       </c>
       <c r="AN11" s="4">
         <f t="shared" ref="AN11:AN33" si="14">AO11-AM11</f>
-        <v>7523</v>
+        <v>7528</v>
       </c>
       <c r="AO11" s="6">
-        <v>47212</v>
+        <v>47217</v>
       </c>
       <c r="AP11" s="5">
         <f t="shared" ref="AP11:AP33" si="15">AO11/AL11</f>
-        <v>0.9793801601460399</v>
+        <v>0.97948388167448031</v>
       </c>
       <c r="AQ11" s="7">
         <v>110196</v>
@@ -1827,14 +1827,14 @@
       </c>
       <c r="AS11" s="4">
         <f t="shared" ref="AS11:AS33" si="16">AT11-AR11</f>
-        <v>15088</v>
+        <v>15106</v>
       </c>
       <c r="AT11" s="6">
-        <v>109641</v>
+        <v>109659</v>
       </c>
       <c r="AU11" s="5">
         <f t="shared" ref="AU11:AU33" si="17">AT11/AQ11</f>
-        <v>0.99496351954698903</v>
+        <v>0.9951268648589785</v>
       </c>
       <c r="AV11" s="7">
         <v>47206</v>
@@ -1844,14 +1844,14 @@
       </c>
       <c r="AX11" s="4">
         <f t="shared" ref="AX11:AX33" si="18">AY11-AW11</f>
-        <v>7568</v>
+        <v>7574</v>
       </c>
       <c r="AY11" s="6">
-        <v>47024</v>
+        <v>47030</v>
       </c>
       <c r="AZ11" s="5">
         <f t="shared" ref="AZ11:AZ33" si="19">AY11/AV11</f>
-        <v>0.99614455789518286</v>
+        <v>0.99627166038215476</v>
       </c>
       <c r="BA11" s="7">
         <v>48813</v>
@@ -1861,14 +1861,14 @@
       </c>
       <c r="BC11" s="4">
         <f t="shared" ref="BC11:BC33" si="20">BD11-BB11</f>
-        <v>7427</v>
+        <v>7435</v>
       </c>
       <c r="BD11" s="6">
-        <v>47550</v>
+        <v>47558</v>
       </c>
       <c r="BE11" s="5">
         <f t="shared" ref="BE11:BE33" si="21">BD11/BA11</f>
-        <v>0.97412574519083028</v>
+        <v>0.97428963595763418</v>
       </c>
       <c r="BF11" s="7">
         <v>111276</v>
@@ -1878,14 +1878,14 @@
       </c>
       <c r="BH11" s="4">
         <f t="shared" ref="BH11:BH33" si="22">BI11-BG11</f>
-        <v>21067</v>
+        <v>21088</v>
       </c>
       <c r="BI11" s="6">
-        <v>110616</v>
+        <v>110637</v>
       </c>
       <c r="BJ11" s="5">
         <f t="shared" ref="BJ11:BJ33" si="23">BI11/BF11</f>
-        <v>0.99406880189798341</v>
+        <v>0.99425752183759297</v>
       </c>
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.3">
@@ -1903,14 +1903,14 @@
       </c>
       <c r="E12" s="4">
         <f t="shared" si="0"/>
-        <v>27449</v>
+        <v>27458</v>
       </c>
       <c r="F12" s="13">
-        <v>175774</v>
+        <v>175783</v>
       </c>
       <c r="G12" s="5">
         <f t="shared" si="1"/>
-        <v>0.99256314550146529</v>
+        <v>0.99261396683061254</v>
       </c>
       <c r="H12" s="7">
         <v>181172</v>
@@ -1920,14 +1920,14 @@
       </c>
       <c r="J12" s="4">
         <f t="shared" si="2"/>
-        <v>25308</v>
+        <v>25318</v>
       </c>
       <c r="K12" s="13">
-        <v>178134</v>
+        <v>178144</v>
       </c>
       <c r="L12" s="5">
         <f t="shared" si="3"/>
-        <v>0.98323140441127765</v>
+        <v>0.98328660057845585</v>
       </c>
       <c r="M12" s="7">
         <v>363483</v>
@@ -1937,14 +1937,14 @@
       </c>
       <c r="O12" s="4">
         <f t="shared" si="4"/>
-        <v>56194</v>
+        <v>56209</v>
       </c>
       <c r="P12" s="6">
-        <v>360428</v>
+        <v>360443</v>
       </c>
       <c r="Q12" s="5">
         <f t="shared" si="5"/>
-        <v>0.99159520527782596</v>
+        <v>0.99163647268235378</v>
       </c>
       <c r="R12" s="7">
         <v>177513</v>
@@ -1954,14 +1954,14 @@
       </c>
       <c r="T12" s="4">
         <f t="shared" si="6"/>
-        <v>27044</v>
+        <v>27053</v>
       </c>
       <c r="U12" s="13">
-        <v>177164</v>
+        <v>177173</v>
       </c>
       <c r="V12" s="5">
         <f t="shared" si="7"/>
-        <v>0.99803394680952939</v>
+        <v>0.99808464732160462</v>
       </c>
       <c r="W12" s="7">
         <v>182324</v>
@@ -1971,14 +1971,14 @@
       </c>
       <c r="Y12" s="4">
         <f t="shared" si="8"/>
-        <v>28713</v>
+        <v>28723</v>
       </c>
       <c r="Z12" s="13">
-        <v>178785</v>
+        <v>178795</v>
       </c>
       <c r="AA12" s="5">
         <f t="shared" si="9"/>
-        <v>0.98058950001096945</v>
+        <v>0.98064434742546236</v>
       </c>
       <c r="AB12" s="7">
         <v>365690</v>
@@ -1988,14 +1988,14 @@
       </c>
       <c r="AD12" s="4">
         <f t="shared" si="10"/>
-        <v>60833</v>
+        <v>60857</v>
       </c>
       <c r="AE12" s="6">
-        <v>362396</v>
+        <v>362420</v>
       </c>
       <c r="AF12" s="5">
         <f t="shared" si="11"/>
-        <v>0.99099237058710932</v>
+        <v>0.99105799994530885</v>
       </c>
       <c r="AG12" s="7">
         <v>180670</v>
@@ -2005,14 +2005,14 @@
       </c>
       <c r="AI12" s="4">
         <f t="shared" si="12"/>
-        <v>30031</v>
+        <v>30055</v>
       </c>
       <c r="AJ12" s="6">
-        <v>178408</v>
+        <v>178432</v>
       </c>
       <c r="AK12" s="5">
         <f t="shared" si="13"/>
-        <v>0.98747993579454252</v>
+        <v>0.98761277467205399</v>
       </c>
       <c r="AL12" s="7">
         <v>181581</v>
@@ -2022,14 +2022,14 @@
       </c>
       <c r="AN12" s="4">
         <f t="shared" si="14"/>
-        <v>25702</v>
+        <v>25713</v>
       </c>
       <c r="AO12" s="6">
-        <v>178565</v>
+        <v>178576</v>
       </c>
       <c r="AP12" s="5">
         <f t="shared" si="15"/>
-        <v>0.98339033268899279</v>
+        <v>0.9834509117143313</v>
       </c>
       <c r="AQ12" s="7">
         <v>363376</v>
@@ -2039,14 +2039,14 @@
       </c>
       <c r="AS12" s="4">
         <f t="shared" si="16"/>
-        <v>54160</v>
+        <v>54199</v>
       </c>
       <c r="AT12" s="6">
-        <v>362040</v>
+        <v>362079</v>
       </c>
       <c r="AU12" s="5">
         <f t="shared" si="17"/>
-        <v>0.99632336753115236</v>
+        <v>0.99643069437717402</v>
       </c>
       <c r="AV12" s="7">
         <v>179534</v>
@@ -2056,14 +2056,14 @@
       </c>
       <c r="AX12" s="4">
         <f t="shared" si="18"/>
-        <v>26101</v>
+        <v>26120</v>
       </c>
       <c r="AY12" s="6">
-        <v>178821</v>
+        <v>178840</v>
       </c>
       <c r="AZ12" s="5">
         <f t="shared" si="19"/>
-        <v>0.99602860739469956</v>
+        <v>0.99613443693116621</v>
       </c>
       <c r="BA12" s="7">
         <v>184469</v>
@@ -2073,14 +2073,14 @@
       </c>
       <c r="BC12" s="4">
         <f t="shared" si="20"/>
-        <v>26293</v>
+        <v>26314</v>
       </c>
       <c r="BD12" s="6">
-        <v>181870</v>
+        <v>181891</v>
       </c>
       <c r="BE12" s="5">
         <f t="shared" si="21"/>
-        <v>0.98591091186052937</v>
+        <v>0.98602475212637353</v>
       </c>
       <c r="BF12" s="7">
         <v>368393</v>
@@ -2090,14 +2090,14 @@
       </c>
       <c r="BH12" s="4">
         <f t="shared" si="22"/>
-        <v>77069</v>
+        <v>77131</v>
       </c>
       <c r="BI12" s="6">
-        <v>367032</v>
+        <v>367094</v>
       </c>
       <c r="BJ12" s="5">
         <f t="shared" si="23"/>
-        <v>0.99630557583884605</v>
+        <v>0.99647387436786261</v>
       </c>
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.3">
@@ -2251,14 +2251,14 @@
       </c>
       <c r="AS13" s="4">
         <f t="shared" si="16"/>
-        <v>4309</v>
+        <v>4310</v>
       </c>
       <c r="AT13" s="6">
-        <v>28956</v>
+        <v>28957</v>
       </c>
       <c r="AU13" s="5">
         <f t="shared" si="17"/>
-        <v>1.0007949400338714</v>
+        <v>1.0008295026440397</v>
       </c>
       <c r="AV13" s="7">
         <v>17858</v>
@@ -2285,14 +2285,14 @@
       </c>
       <c r="BC13" s="4">
         <f t="shared" si="20"/>
-        <v>2466</v>
+        <v>2467</v>
       </c>
       <c r="BD13" s="6">
-        <v>17928</v>
+        <v>17929</v>
       </c>
       <c r="BE13" s="5">
         <f t="shared" si="21"/>
-        <v>0.99456340841007429</v>
+        <v>0.99461888383446129</v>
       </c>
       <c r="BF13" s="7">
         <v>29023</v>
@@ -2302,14 +2302,14 @@
       </c>
       <c r="BH13" s="4">
         <f t="shared" si="22"/>
-        <v>5654</v>
+        <v>5656</v>
       </c>
       <c r="BI13" s="6">
-        <v>29075</v>
+        <v>29077</v>
       </c>
       <c r="BJ13" s="5">
         <f t="shared" si="23"/>
-        <v>1.0017916824587396</v>
+        <v>1.0018605933225373</v>
       </c>
     </row>
     <row r="14" spans="1:62" x14ac:dyDescent="0.3">
@@ -2327,14 +2327,14 @@
       </c>
       <c r="E14" s="4">
         <f t="shared" si="0"/>
-        <v>18620</v>
+        <v>18626</v>
       </c>
       <c r="F14" s="13">
-        <v>89930</v>
+        <v>89936</v>
       </c>
       <c r="G14" s="5">
         <f t="shared" si="1"/>
-        <v>0.99405314586373084</v>
+        <v>0.99411946765707215</v>
       </c>
       <c r="H14" s="7">
         <v>94129</v>
@@ -2344,14 +2344,14 @@
       </c>
       <c r="J14" s="4">
         <f t="shared" si="2"/>
-        <v>17764</v>
+        <v>17770</v>
       </c>
       <c r="K14" s="13">
-        <v>91383</v>
+        <v>91389</v>
       </c>
       <c r="L14" s="5">
         <f t="shared" si="3"/>
-        <v>0.97082726896068161</v>
+        <v>0.97089101127176536</v>
       </c>
       <c r="M14" s="7">
         <v>164995</v>
@@ -2361,14 +2361,14 @@
       </c>
       <c r="O14" s="4">
         <f t="shared" si="4"/>
-        <v>31686</v>
+        <v>31694</v>
       </c>
       <c r="P14" s="6">
-        <v>163651</v>
+        <v>163659</v>
       </c>
       <c r="Q14" s="5">
         <f t="shared" si="5"/>
-        <v>0.99185429861510954</v>
+        <v>0.99190278493287676</v>
       </c>
       <c r="R14" s="7">
         <v>91074</v>
@@ -2378,14 +2378,14 @@
       </c>
       <c r="T14" s="4">
         <f t="shared" si="6"/>
-        <v>18916</v>
+        <v>18920</v>
       </c>
       <c r="U14" s="13">
-        <v>90854</v>
+        <v>90858</v>
       </c>
       <c r="V14" s="5">
         <f t="shared" si="7"/>
-        <v>0.99758438193117682</v>
+        <v>0.99762830225970089</v>
       </c>
       <c r="W14" s="7">
         <v>93800</v>
@@ -2395,14 +2395,14 @@
       </c>
       <c r="Y14" s="4">
         <f t="shared" si="8"/>
-        <v>18575</v>
+        <v>18582</v>
       </c>
       <c r="Z14" s="13">
-        <v>91358</v>
+        <v>91365</v>
       </c>
       <c r="AA14" s="5">
         <f t="shared" si="9"/>
-        <v>0.97396588486140723</v>
+        <v>0.97404051172707884</v>
       </c>
       <c r="AB14" s="7">
         <v>166352</v>
@@ -2412,14 +2412,14 @@
       </c>
       <c r="AD14" s="4">
         <f t="shared" si="10"/>
-        <v>34966</v>
+        <v>34982</v>
       </c>
       <c r="AE14" s="6">
-        <v>164409</v>
+        <v>164425</v>
       </c>
       <c r="AF14" s="5">
         <f t="shared" si="11"/>
-        <v>0.9883199480619409</v>
+        <v>0.98841612965278447</v>
       </c>
       <c r="AG14" s="7">
         <v>92175</v>
@@ -2429,14 +2429,14 @@
       </c>
       <c r="AI14" s="4">
         <f t="shared" si="12"/>
-        <v>19132</v>
+        <v>19141</v>
       </c>
       <c r="AJ14" s="6">
-        <v>91579</v>
+        <v>91588</v>
       </c>
       <c r="AK14" s="5">
         <f t="shared" si="13"/>
-        <v>0.99353403851369682</v>
+        <v>0.99363167887171144</v>
       </c>
       <c r="AL14" s="7">
         <v>94655</v>
@@ -2446,14 +2446,14 @@
       </c>
       <c r="AN14" s="4">
         <f t="shared" si="14"/>
-        <v>17420</v>
+        <v>17433</v>
       </c>
       <c r="AO14" s="6">
-        <v>93003</v>
+        <v>93016</v>
       </c>
       <c r="AP14" s="5">
         <f t="shared" si="15"/>
-        <v>0.98254714489461725</v>
+        <v>0.98268448576409062</v>
       </c>
       <c r="AQ14" s="7">
         <v>168400</v>
@@ -2463,14 +2463,14 @@
       </c>
       <c r="AS14" s="4">
         <f t="shared" si="16"/>
-        <v>31338</v>
+        <v>31361</v>
       </c>
       <c r="AT14" s="6">
-        <v>167380</v>
+        <v>167403</v>
       </c>
       <c r="AU14" s="5">
         <f t="shared" si="17"/>
-        <v>0.99394299287410925</v>
+        <v>0.99407957244655587</v>
       </c>
       <c r="AV14" s="7">
         <v>94024</v>
@@ -2480,14 +2480,14 @@
       </c>
       <c r="AX14" s="4">
         <f t="shared" si="18"/>
-        <v>16953</v>
+        <v>16968</v>
       </c>
       <c r="AY14" s="6">
-        <v>93541</v>
+        <v>93556</v>
       </c>
       <c r="AZ14" s="5">
         <f t="shared" si="19"/>
-        <v>0.99486301369863017</v>
+        <v>0.99502254743469754</v>
       </c>
       <c r="BA14" s="7">
         <v>96514</v>
@@ -2497,14 +2497,14 @@
       </c>
       <c r="BC14" s="4">
         <f t="shared" si="20"/>
-        <v>16711</v>
+        <v>16731</v>
       </c>
       <c r="BD14" s="6">
-        <v>94939</v>
+        <v>94959</v>
       </c>
       <c r="BE14" s="5">
         <f t="shared" si="21"/>
-        <v>0.98368112398201302</v>
+        <v>0.98388834780446355</v>
       </c>
       <c r="BF14" s="7">
         <v>171502</v>
@@ -2514,14 +2514,14 @@
       </c>
       <c r="BH14" s="4">
         <f t="shared" si="22"/>
-        <v>39787</v>
+        <v>39829</v>
       </c>
       <c r="BI14" s="6">
-        <v>170588</v>
+        <v>170630</v>
       </c>
       <c r="BJ14" s="5">
         <f t="shared" si="23"/>
-        <v>0.99467061608610974</v>
+        <v>0.99491551118937394</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.3">
@@ -2539,14 +2539,14 @@
       </c>
       <c r="E15" s="4">
         <f t="shared" si="0"/>
-        <v>50766</v>
+        <v>50768</v>
       </c>
       <c r="F15" s="13">
-        <v>301912</v>
+        <v>301914</v>
       </c>
       <c r="G15" s="5">
         <f t="shared" si="1"/>
-        <v>0.99133478465018998</v>
+        <v>0.99134135169478999</v>
       </c>
       <c r="H15" s="7">
         <v>309950</v>
@@ -2556,14 +2556,14 @@
       </c>
       <c r="J15" s="4">
         <f t="shared" si="2"/>
-        <v>47821</v>
+        <v>47824</v>
       </c>
       <c r="K15" s="13">
-        <v>306454</v>
+        <v>306457</v>
       </c>
       <c r="L15" s="5">
         <f t="shared" si="3"/>
-        <v>0.98872076141313114</v>
+        <v>0.98873044039361191</v>
       </c>
       <c r="M15" s="7">
         <v>517862</v>
@@ -2573,14 +2573,14 @@
       </c>
       <c r="O15" s="4">
         <f t="shared" si="4"/>
-        <v>81188</v>
+        <v>81195</v>
       </c>
       <c r="P15" s="6">
-        <v>512937</v>
+        <v>512944</v>
       </c>
       <c r="Q15" s="5">
         <f t="shared" si="5"/>
-        <v>0.99048974437205284</v>
+        <v>0.99050326148665091</v>
       </c>
       <c r="R15" s="7">
         <v>307768</v>
@@ -2590,14 +2590,14 @@
       </c>
       <c r="T15" s="4">
         <f t="shared" si="6"/>
-        <v>52551</v>
+        <v>52555</v>
       </c>
       <c r="U15" s="13">
-        <v>306403</v>
+        <v>306407</v>
       </c>
       <c r="V15" s="5">
         <f t="shared" si="7"/>
-        <v>0.99556484104910192</v>
+        <v>0.99557783785188847</v>
       </c>
       <c r="W15" s="7">
         <v>314114</v>
@@ -2607,14 +2607,14 @@
       </c>
       <c r="Y15" s="4">
         <f t="shared" si="8"/>
-        <v>50987</v>
+        <v>50992</v>
       </c>
       <c r="Z15" s="13">
-        <v>308548</v>
+        <v>308553</v>
       </c>
       <c r="AA15" s="5">
         <f t="shared" si="9"/>
-        <v>0.98228031861044085</v>
+        <v>0.98229623639825037</v>
       </c>
       <c r="AB15" s="7">
         <v>523203</v>
@@ -2624,14 +2624,14 @@
       </c>
       <c r="AD15" s="4">
         <f t="shared" si="10"/>
-        <v>91398</v>
+        <v>91408</v>
       </c>
       <c r="AE15" s="6">
-        <v>519175</v>
+        <v>519185</v>
       </c>
       <c r="AF15" s="5">
         <f t="shared" si="11"/>
-        <v>0.99230126738569924</v>
+        <v>0.99232038042595316</v>
       </c>
       <c r="AG15" s="7">
         <v>312916</v>
@@ -2641,14 +2641,14 @@
       </c>
       <c r="AI15" s="4">
         <f t="shared" si="12"/>
-        <v>54270</v>
+        <v>54276</v>
       </c>
       <c r="AJ15" s="6">
-        <v>310810</v>
+        <v>310816</v>
       </c>
       <c r="AK15" s="5">
         <f t="shared" si="13"/>
-        <v>0.99326975929642458</v>
+        <v>0.99328893377136351</v>
       </c>
       <c r="AL15" s="7">
         <v>318942</v>
@@ -2658,14 +2658,14 @@
       </c>
       <c r="AN15" s="4">
         <f t="shared" si="14"/>
-        <v>48585</v>
+        <v>48591</v>
       </c>
       <c r="AO15" s="6">
-        <v>313898</v>
+        <v>313904</v>
       </c>
       <c r="AP15" s="5">
         <f t="shared" si="15"/>
-        <v>0.98418521235835987</v>
+        <v>0.98420402455618894</v>
       </c>
       <c r="AQ15" s="7">
         <v>530087</v>
@@ -2675,14 +2675,14 @@
       </c>
       <c r="AS15" s="4">
         <f t="shared" si="16"/>
-        <v>77495</v>
+        <v>77511</v>
       </c>
       <c r="AT15" s="6">
-        <v>526534</v>
+        <v>526550</v>
       </c>
       <c r="AU15" s="5">
         <f t="shared" si="17"/>
-        <v>0.99329732666524551</v>
+        <v>0.99332751038980394</v>
       </c>
       <c r="AV15" s="7">
         <v>317508</v>
@@ -2692,14 +2692,14 @@
       </c>
       <c r="AX15" s="4">
         <f t="shared" si="18"/>
-        <v>49763</v>
+        <v>49776</v>
       </c>
       <c r="AY15" s="6">
-        <v>316774</v>
+        <v>316787</v>
       </c>
       <c r="AZ15" s="5">
         <f t="shared" si="19"/>
-        <v>0.99768824722526672</v>
+        <v>0.99772919107550051</v>
       </c>
       <c r="BA15" s="7">
         <v>324414</v>
@@ -2709,14 +2709,14 @@
       </c>
       <c r="BC15" s="4">
         <f t="shared" si="20"/>
-        <v>49260</v>
+        <v>49274</v>
       </c>
       <c r="BD15" s="6">
-        <v>320636</v>
+        <v>320650</v>
       </c>
       <c r="BE15" s="5">
         <f t="shared" si="21"/>
-        <v>0.98835438667874997</v>
+        <v>0.98839754141313263</v>
       </c>
       <c r="BF15" s="7">
         <v>538701</v>
@@ -2726,14 +2726,14 @@
       </c>
       <c r="BH15" s="4">
         <f t="shared" si="22"/>
-        <v>107817</v>
+        <v>107854</v>
       </c>
       <c r="BI15" s="6">
-        <v>536100</v>
+        <v>536137</v>
       </c>
       <c r="BJ15" s="5">
         <f t="shared" si="23"/>
-        <v>0.99517171863427023</v>
+        <v>0.99524040237534361</v>
       </c>
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.3">
@@ -2751,14 +2751,14 @@
       </c>
       <c r="E16" s="4">
         <f t="shared" si="0"/>
-        <v>75555</v>
+        <v>75585</v>
       </c>
       <c r="F16" s="13">
-        <v>440470</v>
+        <v>440500</v>
       </c>
       <c r="G16" s="5">
         <f t="shared" si="1"/>
-        <v>0.98831443329040247</v>
+        <v>0.98838174646269283</v>
       </c>
       <c r="H16" s="7">
         <v>453561</v>
@@ -2768,14 +2768,14 @@
       </c>
       <c r="J16" s="4">
         <f t="shared" si="2"/>
-        <v>72315</v>
+        <v>72349</v>
       </c>
       <c r="K16" s="13">
-        <v>444538</v>
+        <v>444572</v>
       </c>
       <c r="L16" s="5">
         <f t="shared" si="3"/>
-        <v>0.98010631425541439</v>
+        <v>0.98018127660887955</v>
       </c>
       <c r="M16" s="7">
         <v>776551</v>
@@ -2785,14 +2785,14 @@
       </c>
       <c r="O16" s="4">
         <f t="shared" si="4"/>
-        <v>126555</v>
+        <v>126624</v>
       </c>
       <c r="P16" s="6">
-        <v>768539</v>
+        <v>768608</v>
       </c>
       <c r="Q16" s="5">
         <f t="shared" si="5"/>
-        <v>0.98968258362940742</v>
+        <v>0.98977143806395196</v>
       </c>
       <c r="R16" s="7">
         <v>446959</v>
@@ -2802,14 +2802,14 @@
       </c>
       <c r="T16" s="4">
         <f t="shared" si="6"/>
-        <v>79211</v>
+        <v>79256</v>
       </c>
       <c r="U16" s="13">
-        <v>443696</v>
+        <v>443741</v>
       </c>
       <c r="V16" s="5">
         <f t="shared" si="7"/>
-        <v>0.99269955409780319</v>
+        <v>0.99280023447340804</v>
       </c>
       <c r="W16" s="7">
         <v>453618</v>
@@ -2819,14 +2819,14 @@
       </c>
       <c r="Y16" s="4">
         <f t="shared" si="8"/>
-        <v>73718</v>
+        <v>73772</v>
       </c>
       <c r="Z16" s="13">
-        <v>443065</v>
+        <v>443119</v>
       </c>
       <c r="AA16" s="5">
         <f t="shared" si="9"/>
-        <v>0.9767359319956439</v>
+        <v>0.97685497489076711</v>
       </c>
       <c r="AB16" s="7">
         <v>775718</v>
@@ -2836,14 +2836,14 @@
       </c>
       <c r="AD16" s="4">
         <f t="shared" si="10"/>
-        <v>135603</v>
+        <v>135701</v>
       </c>
       <c r="AE16" s="6">
-        <v>767291</v>
+        <v>767389</v>
       </c>
       <c r="AF16" s="5">
         <f t="shared" si="11"/>
-        <v>0.98913651610507947</v>
+        <v>0.98926285067511643</v>
       </c>
       <c r="AG16" s="7">
         <v>444751</v>
@@ -2853,14 +2853,14 @@
       </c>
       <c r="AI16" s="4">
         <f t="shared" si="12"/>
-        <v>79449</v>
+        <v>79507</v>
       </c>
       <c r="AJ16" s="6">
-        <v>439487</v>
+        <v>439545</v>
       </c>
       <c r="AK16" s="5">
         <f t="shared" si="13"/>
-        <v>0.98816416376804095</v>
+        <v>0.98829457381770924</v>
       </c>
       <c r="AL16" s="7">
         <v>448369</v>
@@ -2870,14 +2870,14 @@
       </c>
       <c r="AN16" s="4">
         <f t="shared" si="14"/>
-        <v>70631</v>
+        <v>70689</v>
       </c>
       <c r="AO16" s="6">
-        <v>440038</v>
+        <v>440096</v>
       </c>
       <c r="AP16" s="5">
         <f t="shared" si="15"/>
-        <v>0.98141932203163018</v>
+        <v>0.9815486797704569</v>
       </c>
       <c r="AQ16" s="7">
         <v>770483</v>
@@ -2887,14 +2887,14 @@
       </c>
       <c r="AS16" s="4">
         <f t="shared" si="16"/>
-        <v>116511</v>
+        <v>116632</v>
       </c>
       <c r="AT16" s="6">
-        <v>766850</v>
+        <v>766971</v>
       </c>
       <c r="AU16" s="5">
         <f t="shared" si="17"/>
-        <v>0.99528477591329079</v>
+        <v>0.99544182026079742</v>
       </c>
       <c r="AV16" s="7">
         <v>444563</v>
@@ -2904,14 +2904,14 @@
       </c>
       <c r="AX16" s="4">
         <f t="shared" si="18"/>
-        <v>72174</v>
+        <v>72242</v>
       </c>
       <c r="AY16" s="6">
-        <v>444236</v>
+        <v>444304</v>
       </c>
       <c r="AZ16" s="5">
         <f t="shared" si="19"/>
-        <v>0.99926444620897381</v>
+        <v>0.99941740540710766</v>
       </c>
       <c r="BA16" s="7">
         <v>453397</v>
@@ -2921,14 +2921,14 @@
       </c>
       <c r="BC16" s="4">
         <f t="shared" si="20"/>
-        <v>71401</v>
+        <v>71485</v>
       </c>
       <c r="BD16" s="6">
-        <v>447858</v>
+        <v>447942</v>
       </c>
       <c r="BE16" s="5">
         <f t="shared" si="21"/>
-        <v>0.98778333337009283</v>
+        <v>0.98796860146847021</v>
       </c>
       <c r="BF16" s="7">
         <v>780218</v>
@@ -2938,14 +2938,14 @@
       </c>
       <c r="BH16" s="4">
         <f t="shared" si="22"/>
-        <v>150801</v>
+        <v>150972</v>
       </c>
       <c r="BI16" s="6">
-        <v>776779</v>
+        <v>776950</v>
       </c>
       <c r="BJ16" s="5">
         <f t="shared" si="23"/>
-        <v>0.99559225754853131</v>
+        <v>0.99581142706269277</v>
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.3">
@@ -2963,14 +2963,14 @@
       </c>
       <c r="E17" s="4">
         <f t="shared" si="0"/>
-        <v>54505</v>
+        <v>54518</v>
       </c>
       <c r="F17" s="13">
-        <v>322859</v>
+        <v>322872</v>
       </c>
       <c r="G17" s="5">
         <f t="shared" si="1"/>
-        <v>0.99658605096229536</v>
+        <v>0.99662617875387771</v>
       </c>
       <c r="H17" s="7">
         <v>333085</v>
@@ -2980,14 +2980,14 @@
       </c>
       <c r="J17" s="4">
         <f t="shared" si="2"/>
-        <v>50219</v>
+        <v>50238</v>
       </c>
       <c r="K17" s="13">
-        <v>329448</v>
+        <v>329467</v>
       </c>
       <c r="L17" s="5">
         <f t="shared" si="3"/>
-        <v>0.98908086524460725</v>
+        <v>0.9891379077412672</v>
       </c>
       <c r="M17" s="7">
         <v>731481</v>
@@ -2997,14 +2997,14 @@
       </c>
       <c r="O17" s="4">
         <f t="shared" si="4"/>
-        <v>121218</v>
+        <v>121278</v>
       </c>
       <c r="P17" s="6">
-        <v>726899</v>
+        <v>726959</v>
       </c>
       <c r="Q17" s="5">
         <f t="shared" si="5"/>
-        <v>0.99373599587685801</v>
+        <v>0.99381802124730512</v>
       </c>
       <c r="R17" s="7">
         <v>324758</v>
@@ -3014,14 +3014,14 @@
       </c>
       <c r="T17" s="4">
         <f t="shared" si="6"/>
-        <v>57822</v>
+        <v>57844</v>
       </c>
       <c r="U17" s="13">
-        <v>324933</v>
+        <v>324955</v>
       </c>
       <c r="V17" s="5">
         <f t="shared" si="7"/>
-        <v>1.0005388627839806</v>
+        <v>1.0006066055339669</v>
       </c>
       <c r="W17" s="7">
         <v>336053</v>
@@ -3031,14 +3031,14 @@
       </c>
       <c r="Y17" s="4">
         <f t="shared" si="8"/>
-        <v>57060</v>
+        <v>57090</v>
       </c>
       <c r="Z17" s="13">
-        <v>327946</v>
+        <v>327976</v>
       </c>
       <c r="AA17" s="5">
         <f t="shared" si="9"/>
-        <v>0.97587582911028914</v>
+        <v>0.97596510074303755</v>
       </c>
       <c r="AB17" s="7">
         <v>736224</v>
@@ -3048,14 +3048,14 @@
       </c>
       <c r="AD17" s="4">
         <f t="shared" si="10"/>
-        <v>130883</v>
+        <v>130962</v>
       </c>
       <c r="AE17" s="6">
-        <v>728666</v>
+        <v>728745</v>
       </c>
       <c r="AF17" s="5">
         <f t="shared" si="11"/>
-        <v>0.98973410266440653</v>
+        <v>0.98984140696309819</v>
       </c>
       <c r="AG17" s="7">
         <v>328692</v>
@@ -3065,14 +3065,14 @@
       </c>
       <c r="AI17" s="4">
         <f t="shared" si="12"/>
-        <v>57722</v>
+        <v>57750</v>
       </c>
       <c r="AJ17" s="6">
-        <v>327468</v>
+        <v>327496</v>
       </c>
       <c r="AK17" s="5">
         <f t="shared" si="13"/>
-        <v>0.99627614910006934</v>
+        <v>0.99636133523176718</v>
       </c>
       <c r="AL17" s="7">
         <v>339621</v>
@@ -3082,14 +3082,14 @@
       </c>
       <c r="AN17" s="4">
         <f t="shared" si="14"/>
-        <v>51605</v>
+        <v>51641</v>
       </c>
       <c r="AO17" s="6">
-        <v>333211</v>
+        <v>333247</v>
       </c>
       <c r="AP17" s="5">
         <f t="shared" si="15"/>
-        <v>0.98112601988687387</v>
+        <v>0.98123202039920976</v>
       </c>
       <c r="AQ17" s="7">
         <v>745574</v>
@@ -3099,14 +3099,14 @@
       </c>
       <c r="AS17" s="4">
         <f t="shared" si="16"/>
-        <v>114267</v>
+        <v>114369</v>
       </c>
       <c r="AT17" s="6">
-        <v>740062</v>
+        <v>740164</v>
       </c>
       <c r="AU17" s="5">
         <f t="shared" si="17"/>
-        <v>0.9926070383355643</v>
+        <v>0.99274384568131402</v>
       </c>
       <c r="AV17" s="7">
         <v>334329</v>
@@ -3116,14 +3116,14 @@
       </c>
       <c r="AX17" s="4">
         <f t="shared" si="18"/>
-        <v>53655</v>
+        <v>53696</v>
       </c>
       <c r="AY17" s="6">
-        <v>333745</v>
+        <v>333786</v>
       </c>
       <c r="AZ17" s="5">
         <f t="shared" si="19"/>
-        <v>0.99825321763891262</v>
+        <v>0.99837585133207107</v>
       </c>
       <c r="BA17" s="7">
         <v>348862</v>
@@ -3133,14 +3133,14 @@
       </c>
       <c r="BC17" s="4">
         <f t="shared" si="20"/>
-        <v>52573</v>
+        <v>52619</v>
       </c>
       <c r="BD17" s="6">
-        <v>340558</v>
+        <v>340604</v>
       </c>
       <c r="BE17" s="5">
         <f t="shared" si="21"/>
-        <v>0.97619689160756973</v>
+        <v>0.9763287489035779</v>
       </c>
       <c r="BF17" s="7">
         <v>757181</v>
@@ -3150,14 +3150,14 @@
       </c>
       <c r="BH17" s="4">
         <f t="shared" si="22"/>
-        <v>157226</v>
+        <v>157382</v>
       </c>
       <c r="BI17" s="6">
-        <v>753640</v>
+        <v>753796</v>
       </c>
       <c r="BJ17" s="5">
         <f t="shared" si="23"/>
-        <v>0.9953234431397513</v>
+        <v>0.99552947049648632</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -3175,14 +3175,14 @@
       </c>
       <c r="E18" s="4">
         <f t="shared" si="0"/>
-        <v>184117</v>
+        <v>184156</v>
       </c>
       <c r="F18" s="13">
-        <v>989528</v>
+        <v>989567</v>
       </c>
       <c r="G18" s="5">
         <f t="shared" si="1"/>
-        <v>0.99106216423022842</v>
+        <v>0.99110122469582917</v>
       </c>
       <c r="H18" s="7">
         <v>1018686</v>
@@ -3192,14 +3192,14 @@
       </c>
       <c r="J18" s="4">
         <f t="shared" si="2"/>
-        <v>172390</v>
+        <v>172432</v>
       </c>
       <c r="K18" s="13">
-        <v>1002367</v>
+        <v>1002409</v>
       </c>
       <c r="L18" s="5">
         <f t="shared" si="3"/>
-        <v>0.98398034330500272</v>
+        <v>0.98402157288899617</v>
       </c>
       <c r="M18" s="7">
         <v>1536859</v>
@@ -3209,14 +3209,14 @@
       </c>
       <c r="O18" s="4">
         <f t="shared" si="4"/>
-        <v>262017</v>
+        <v>262090</v>
       </c>
       <c r="P18" s="6">
-        <v>1520986</v>
+        <v>1521059</v>
       </c>
       <c r="Q18" s="5">
         <f t="shared" si="5"/>
-        <v>0.98967179162174279</v>
+        <v>0.98971929109957391</v>
       </c>
       <c r="R18" s="7">
         <v>1011292</v>
@@ -3226,14 +3226,14 @@
       </c>
       <c r="T18" s="4">
         <f t="shared" si="6"/>
-        <v>185781</v>
+        <v>185828</v>
       </c>
       <c r="U18" s="13">
-        <v>1004123</v>
+        <v>1004170</v>
       </c>
       <c r="V18" s="5">
         <f t="shared" si="7"/>
-        <v>0.9929110484410042</v>
+        <v>0.99295752364302303</v>
       </c>
       <c r="W18" s="7">
         <v>1030498</v>
@@ -3243,14 +3243,14 @@
       </c>
       <c r="Y18" s="4">
         <f t="shared" si="8"/>
-        <v>182905</v>
+        <v>182970</v>
       </c>
       <c r="Z18" s="13">
-        <v>1009223</v>
+        <v>1009288</v>
       </c>
       <c r="AA18" s="5">
         <f t="shared" si="9"/>
-        <v>0.97935464212448742</v>
+        <v>0.97941771842351955</v>
       </c>
       <c r="AB18" s="7">
         <v>1557879</v>
@@ -3260,14 +3260,14 @@
       </c>
       <c r="AD18" s="4">
         <f t="shared" si="10"/>
-        <v>285050</v>
+        <v>285158</v>
       </c>
       <c r="AE18" s="6">
-        <v>1537480</v>
+        <v>1537588</v>
       </c>
       <c r="AF18" s="5">
         <f t="shared" si="11"/>
-        <v>0.98690591502934444</v>
+        <v>0.9869752400539451</v>
       </c>
       <c r="AG18" s="7">
         <v>1025067</v>
@@ -3277,14 +3277,14 @@
       </c>
       <c r="AI18" s="4">
         <f t="shared" si="12"/>
-        <v>195237</v>
+        <v>195308</v>
       </c>
       <c r="AJ18" s="6">
-        <v>1018891</v>
+        <v>1018962</v>
       </c>
       <c r="AK18" s="5">
         <f t="shared" si="13"/>
-        <v>0.99397502797378123</v>
+        <v>0.99404429173897901</v>
       </c>
       <c r="AL18" s="7">
         <v>1045736</v>
@@ -3294,14 +3294,14 @@
       </c>
       <c r="AN18" s="4">
         <f t="shared" si="14"/>
-        <v>168662</v>
+        <v>168750</v>
       </c>
       <c r="AO18" s="6">
-        <v>1032093</v>
+        <v>1032181</v>
       </c>
       <c r="AP18" s="5">
         <f t="shared" si="15"/>
-        <v>0.98695368620760882</v>
+        <v>0.98703783746567009</v>
       </c>
       <c r="AQ18" s="7">
         <v>1584961</v>
@@ -3311,14 +3311,14 @@
       </c>
       <c r="AS18" s="4">
         <f t="shared" si="16"/>
-        <v>240397</v>
+        <v>240547</v>
       </c>
       <c r="AT18" s="6">
-        <v>1570806</v>
+        <v>1570956</v>
       </c>
       <c r="AU18" s="5">
         <f t="shared" si="17"/>
-        <v>0.9910691808820532</v>
+        <v>0.99116382043469842</v>
       </c>
       <c r="AV18" s="7">
         <v>1051416</v>
@@ -3328,14 +3328,14 @@
       </c>
       <c r="AX18" s="4">
         <f t="shared" si="18"/>
-        <v>176949</v>
+        <v>177065</v>
       </c>
       <c r="AY18" s="6">
-        <v>1046479</v>
+        <v>1046595</v>
       </c>
       <c r="AZ18" s="5">
         <f t="shared" si="19"/>
-        <v>0.99530442755293813</v>
+        <v>0.99541475495902665</v>
       </c>
       <c r="BA18" s="7">
         <v>1075670</v>
@@ -3345,14 +3345,14 @@
       </c>
       <c r="BC18" s="4">
         <f t="shared" si="20"/>
-        <v>179423</v>
+        <v>179569</v>
       </c>
       <c r="BD18" s="6">
-        <v>1060699</v>
+        <v>1060845</v>
       </c>
       <c r="BE18" s="5">
         <f t="shared" si="21"/>
-        <v>0.98608216274507976</v>
+        <v>0.98621789210445587</v>
       </c>
       <c r="BF18" s="7">
         <v>1620029</v>
@@ -3362,14 +3362,14 @@
       </c>
       <c r="BH18" s="4">
         <f t="shared" si="22"/>
-        <v>349376</v>
+        <v>349703</v>
       </c>
       <c r="BI18" s="6">
-        <v>1604904</v>
+        <v>1605231</v>
       </c>
       <c r="BJ18" s="5">
         <f t="shared" si="23"/>
-        <v>0.99066374737736174</v>
+        <v>0.99086559561588095</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -3387,14 +3387,14 @@
       </c>
       <c r="E19" s="4">
         <f t="shared" si="0"/>
-        <v>63421</v>
+        <v>63449</v>
       </c>
       <c r="F19" s="13">
-        <v>284995</v>
+        <v>285023</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" si="1"/>
-        <v>0.97813738781253756</v>
+        <v>0.97823348720676817</v>
       </c>
       <c r="H19" s="7">
         <v>301141</v>
@@ -3404,14 +3404,14 @@
       </c>
       <c r="J19" s="4">
         <f t="shared" si="2"/>
-        <v>54134</v>
+        <v>54163</v>
       </c>
       <c r="K19" s="13">
-        <v>289139</v>
+        <v>289168</v>
       </c>
       <c r="L19" s="5">
         <f t="shared" si="3"/>
-        <v>0.96014491550469716</v>
+        <v>0.96024121590882672</v>
       </c>
       <c r="M19" s="7">
         <v>505864</v>
@@ -3421,14 +3421,14 @@
       </c>
       <c r="O19" s="4">
         <f t="shared" si="4"/>
-        <v>88392</v>
+        <v>88452</v>
       </c>
       <c r="P19" s="6">
-        <v>496213</v>
+        <v>496273</v>
       </c>
       <c r="Q19" s="5">
         <f t="shared" si="5"/>
-        <v>0.98092174971929214</v>
+        <v>0.9810403586734775</v>
       </c>
       <c r="R19" s="7">
         <v>293000</v>
@@ -3438,14 +3438,14 @@
       </c>
       <c r="T19" s="4">
         <f t="shared" si="6"/>
-        <v>54055</v>
+        <v>54085</v>
       </c>
       <c r="U19" s="13">
-        <v>286787</v>
+        <v>286817</v>
       </c>
       <c r="V19" s="5">
         <f t="shared" si="7"/>
-        <v>0.97879522184300338</v>
+        <v>0.97889761092150174</v>
       </c>
       <c r="W19" s="7">
         <v>302979</v>
@@ -3455,14 +3455,14 @@
       </c>
       <c r="Y19" s="4">
         <f t="shared" si="8"/>
-        <v>59645</v>
+        <v>59683</v>
       </c>
       <c r="Z19" s="13">
-        <v>287705</v>
+        <v>287743</v>
       </c>
       <c r="AA19" s="5">
         <f t="shared" si="9"/>
-        <v>0.9495872651239855</v>
+        <v>0.94971268635780037</v>
       </c>
       <c r="AB19" s="7">
         <v>514622</v>
@@ -3472,14 +3472,14 @@
       </c>
       <c r="AD19" s="4">
         <f t="shared" si="10"/>
-        <v>103484</v>
+        <v>103568</v>
       </c>
       <c r="AE19" s="6">
-        <v>497117</v>
+        <v>497201</v>
       </c>
       <c r="AF19" s="5">
         <f t="shared" si="11"/>
-        <v>0.96598474219912867</v>
+        <v>0.9661479688004011</v>
       </c>
       <c r="AG19" s="7">
         <v>295766</v>
@@ -3489,14 +3489,14 @@
       </c>
       <c r="AI19" s="4">
         <f t="shared" si="12"/>
-        <v>61630</v>
+        <v>61675</v>
       </c>
       <c r="AJ19" s="6">
-        <v>287474</v>
+        <v>287519</v>
       </c>
       <c r="AK19" s="5">
         <f t="shared" si="13"/>
-        <v>0.97196432314735293</v>
+        <v>0.97211647045299321</v>
       </c>
       <c r="AL19" s="7">
         <v>302797</v>
@@ -3506,14 +3506,14 @@
       </c>
       <c r="AN19" s="4">
         <f t="shared" si="14"/>
-        <v>54563</v>
+        <v>54620</v>
       </c>
       <c r="AO19" s="6">
-        <v>291138</v>
+        <v>291195</v>
       </c>
       <c r="AP19" s="5">
         <f t="shared" si="15"/>
-        <v>0.96149565550517346</v>
+        <v>0.96168390043494489</v>
       </c>
       <c r="AQ19" s="7">
         <v>519490</v>
@@ -3523,14 +3523,14 @@
       </c>
       <c r="AS19" s="4">
         <f t="shared" si="16"/>
-        <v>88300</v>
+        <v>88433</v>
       </c>
       <c r="AT19" s="6">
-        <v>505972</v>
+        <v>506105</v>
       </c>
       <c r="AU19" s="5">
         <f t="shared" si="17"/>
-        <v>0.97397832489557068</v>
+        <v>0.97423434522319963</v>
       </c>
       <c r="AV19" s="7">
         <v>299668</v>
@@ -3540,14 +3540,14 @@
       </c>
       <c r="AX19" s="4">
         <f t="shared" si="18"/>
-        <v>55852</v>
+        <v>55930</v>
       </c>
       <c r="AY19" s="6">
-        <v>294802</v>
+        <v>294880</v>
       </c>
       <c r="AZ19" s="5">
         <f t="shared" si="19"/>
-        <v>0.98376202997984441</v>
+        <v>0.98402231803195539</v>
       </c>
       <c r="BA19" s="7">
         <v>313772</v>
@@ -3557,14 +3557,14 @@
       </c>
       <c r="BC19" s="4">
         <f t="shared" si="20"/>
-        <v>57753</v>
+        <v>57854</v>
       </c>
       <c r="BD19" s="6">
-        <v>299409</v>
+        <v>299510</v>
       </c>
       <c r="BE19" s="5">
         <f t="shared" si="21"/>
-        <v>0.95422472368471378</v>
+        <v>0.95454661346455383</v>
       </c>
       <c r="BF19" s="7">
         <v>528004</v>
@@ -3574,14 +3574,14 @@
       </c>
       <c r="BH19" s="4">
         <f t="shared" si="22"/>
-        <v>133136</v>
+        <v>133349</v>
       </c>
       <c r="BI19" s="6">
-        <v>516543</v>
+        <v>516756</v>
       </c>
       <c r="BJ19" s="5">
         <f t="shared" si="23"/>
-        <v>0.97829372504753753</v>
+        <v>0.97869713108234024</v>
       </c>
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.3">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="E20" s="4">
         <f t="shared" si="0"/>
-        <v>1833</v>
+        <v>1835</v>
       </c>
       <c r="F20" s="13">
-        <v>6420</v>
+        <v>6422</v>
       </c>
       <c r="G20" s="5">
         <f t="shared" si="1"/>
-        <v>0.99350046425255334</v>
+        <v>0.99380996595481275</v>
       </c>
       <c r="H20" s="7">
         <v>6957</v>
@@ -3616,14 +3616,14 @@
       </c>
       <c r="J20" s="4">
         <f t="shared" si="2"/>
-        <v>1657</v>
+        <v>1659</v>
       </c>
       <c r="K20" s="13">
-        <v>6471</v>
+        <v>6473</v>
       </c>
       <c r="L20" s="5">
         <f t="shared" si="3"/>
-        <v>0.93014230271668819</v>
+        <v>0.93042978295242207</v>
       </c>
       <c r="M20" s="7">
         <v>9947</v>
@@ -3633,14 +3633,14 @@
       </c>
       <c r="O20" s="4">
         <f t="shared" si="4"/>
-        <v>2290</v>
+        <v>2293</v>
       </c>
       <c r="P20" s="6">
-        <v>9833</v>
+        <v>9836</v>
       </c>
       <c r="Q20" s="5">
         <f t="shared" si="5"/>
-        <v>0.98853925806775911</v>
+        <v>0.98884085653966025</v>
       </c>
       <c r="R20" s="7">
         <v>6587</v>
@@ -3650,14 +3650,14 @@
       </c>
       <c r="T20" s="4">
         <f t="shared" si="6"/>
-        <v>1616</v>
+        <v>1620</v>
       </c>
       <c r="U20" s="13">
-        <v>6517</v>
+        <v>6521</v>
       </c>
       <c r="V20" s="5">
         <f t="shared" si="7"/>
-        <v>0.98937300743889478</v>
+        <v>0.98998026415667228</v>
       </c>
       <c r="W20" s="7">
         <v>6643</v>
@@ -3667,14 +3667,14 @@
       </c>
       <c r="Y20" s="4">
         <f t="shared" si="8"/>
-        <v>1720</v>
+        <v>1725</v>
       </c>
       <c r="Z20" s="13">
-        <v>6513</v>
+        <v>6518</v>
       </c>
       <c r="AA20" s="5">
         <f t="shared" si="9"/>
-        <v>0.98043052837573386</v>
+        <v>0.98118320036128259</v>
       </c>
       <c r="AB20" s="7">
         <v>9927</v>
@@ -3684,14 +3684,14 @@
       </c>
       <c r="AD20" s="4">
         <f t="shared" si="10"/>
-        <v>2694</v>
+        <v>2698</v>
       </c>
       <c r="AE20" s="6">
-        <v>9877</v>
+        <v>9881</v>
       </c>
       <c r="AF20" s="5">
         <f t="shared" si="11"/>
-        <v>0.99496323159061151</v>
+        <v>0.9953661730633625</v>
       </c>
       <c r="AG20" s="7">
         <v>6546</v>
@@ -3701,14 +3701,14 @@
       </c>
       <c r="AI20" s="4">
         <f t="shared" si="12"/>
-        <v>1801</v>
+        <v>1806</v>
       </c>
       <c r="AJ20" s="6">
-        <v>6486</v>
+        <v>6491</v>
       </c>
       <c r="AK20" s="5">
         <f t="shared" si="13"/>
-        <v>0.99083409715857007</v>
+        <v>0.99159792239535594</v>
       </c>
       <c r="AL20" s="7">
         <v>6627</v>
@@ -3718,14 +3718,14 @@
       </c>
       <c r="AN20" s="4">
         <f t="shared" si="14"/>
-        <v>1630</v>
+        <v>1635</v>
       </c>
       <c r="AO20" s="6">
-        <v>6552</v>
+        <v>6557</v>
       </c>
       <c r="AP20" s="5">
         <f t="shared" si="15"/>
-        <v>0.98868266183793574</v>
+        <v>0.98943715104873997</v>
       </c>
       <c r="AQ20" s="7">
         <v>9949</v>
@@ -3735,14 +3735,14 @@
       </c>
       <c r="AS20" s="4">
         <f t="shared" si="16"/>
-        <v>2367</v>
+        <v>2372</v>
       </c>
       <c r="AT20" s="6">
-        <v>9967</v>
+        <v>9972</v>
       </c>
       <c r="AU20" s="5">
         <f t="shared" si="17"/>
-        <v>1.0018092270579957</v>
+        <v>1.0023117901296612</v>
       </c>
       <c r="AV20" s="7">
         <v>6437</v>
@@ -3752,14 +3752,14 @@
       </c>
       <c r="AX20" s="4">
         <f t="shared" si="18"/>
-        <v>1569</v>
+        <v>1573</v>
       </c>
       <c r="AY20" s="6">
-        <v>6440</v>
+        <v>6444</v>
       </c>
       <c r="AZ20" s="5">
         <f t="shared" si="19"/>
-        <v>1.0004660556159701</v>
+        <v>1.0010874631039304</v>
       </c>
       <c r="BA20" s="7">
         <v>6564</v>
@@ -3769,14 +3769,14 @@
       </c>
       <c r="BC20" s="4">
         <f t="shared" si="20"/>
-        <v>1603</v>
+        <v>1607</v>
       </c>
       <c r="BD20" s="6">
-        <v>6516</v>
+        <v>6520</v>
       </c>
       <c r="BE20" s="5">
         <f t="shared" si="21"/>
-        <v>0.99268738574040216</v>
+        <v>0.99329677026203533</v>
       </c>
       <c r="BF20" s="7">
         <v>10109</v>
@@ -3786,14 +3786,14 @@
       </c>
       <c r="BH20" s="4">
         <f t="shared" si="22"/>
-        <v>3036</v>
+        <v>3044</v>
       </c>
       <c r="BI20" s="6">
-        <v>10060</v>
+        <v>10068</v>
       </c>
       <c r="BJ20" s="5">
         <f t="shared" si="23"/>
-        <v>0.99515283410822042</v>
+        <v>0.99594420813136808</v>
       </c>
     </row>
     <row r="21" spans="1:62" x14ac:dyDescent="0.3">
@@ -3811,14 +3811,14 @@
       </c>
       <c r="E21" s="4">
         <f t="shared" si="0"/>
-        <v>4197</v>
+        <v>4205</v>
       </c>
       <c r="F21" s="13">
-        <v>10910</v>
+        <v>10918</v>
       </c>
       <c r="G21" s="5">
         <f t="shared" si="1"/>
-        <v>0.9929917174842996</v>
+        <v>0.9937198507326841</v>
       </c>
       <c r="H21" s="7">
         <v>10970</v>
@@ -3828,14 +3828,14 @@
       </c>
       <c r="J21" s="4">
         <f t="shared" si="2"/>
-        <v>3477</v>
+        <v>3483</v>
       </c>
       <c r="K21" s="13">
-        <v>10954</v>
+        <v>10960</v>
       </c>
       <c r="L21" s="5">
         <f t="shared" si="3"/>
-        <v>0.99854147675478577</v>
+        <v>0.99908842297174116</v>
       </c>
       <c r="M21" s="7">
         <v>14288</v>
@@ -3845,14 +3845,14 @@
       </c>
       <c r="O21" s="4">
         <f t="shared" si="4"/>
-        <v>4644</v>
+        <v>4657</v>
       </c>
       <c r="P21" s="6">
-        <v>14526</v>
+        <v>14539</v>
       </c>
       <c r="Q21" s="5">
         <f t="shared" si="5"/>
-        <v>1.0166573348264278</v>
+        <v>1.01756718924972</v>
       </c>
       <c r="R21" s="7">
         <v>10910</v>
@@ -3862,14 +3862,14 @@
       </c>
       <c r="T21" s="4">
         <f t="shared" si="6"/>
-        <v>3687</v>
+        <v>3697</v>
       </c>
       <c r="U21" s="13">
-        <v>11185</v>
+        <v>11195</v>
       </c>
       <c r="V21" s="5">
         <f t="shared" si="7"/>
-        <v>1.0252062328139322</v>
+        <v>1.0261228230980752</v>
       </c>
       <c r="W21" s="7">
         <v>11256</v>
@@ -3879,14 +3879,14 @@
       </c>
       <c r="Y21" s="4">
         <f t="shared" si="8"/>
-        <v>3668</v>
+        <v>3680</v>
       </c>
       <c r="Z21" s="13">
-        <v>11307</v>
+        <v>11319</v>
       </c>
       <c r="AA21" s="5">
         <f t="shared" si="9"/>
-        <v>1.0045309168443497</v>
+        <v>1.0055970149253732</v>
       </c>
       <c r="AB21" s="7">
         <v>14831</v>
@@ -3896,14 +3896,14 @@
       </c>
       <c r="AD21" s="4">
         <f t="shared" si="10"/>
-        <v>4884</v>
+        <v>4899</v>
       </c>
       <c r="AE21" s="6">
-        <v>14973</v>
+        <v>14988</v>
       </c>
       <c r="AF21" s="5">
         <f t="shared" si="11"/>
-        <v>1.0095745398152518</v>
+        <v>1.0105859348661588</v>
       </c>
       <c r="AG21" s="7">
         <v>11222</v>
@@ -3913,14 +3913,14 @@
       </c>
       <c r="AI21" s="4">
         <f t="shared" si="12"/>
-        <v>3705</v>
+        <v>3716</v>
       </c>
       <c r="AJ21" s="6">
-        <v>11348</v>
+        <v>11359</v>
       </c>
       <c r="AK21" s="5">
         <f t="shared" si="13"/>
-        <v>1.0112279451078239</v>
+        <v>1.012208162537872</v>
       </c>
       <c r="AL21" s="7">
         <v>11337</v>
@@ -3930,14 +3930,14 @@
       </c>
       <c r="AN21" s="4">
         <f t="shared" si="14"/>
-        <v>3485</v>
+        <v>3496</v>
       </c>
       <c r="AO21" s="6">
-        <v>11510</v>
+        <v>11521</v>
       </c>
       <c r="AP21" s="5">
         <f t="shared" si="15"/>
-        <v>1.0152597688982976</v>
+        <v>1.0162300432213107</v>
       </c>
       <c r="AQ21" s="7">
         <v>15149</v>
@@ -3947,14 +3947,14 @@
       </c>
       <c r="AS21" s="4">
         <f t="shared" si="16"/>
-        <v>4564</v>
+        <v>4577</v>
       </c>
       <c r="AT21" s="6">
-        <v>15378</v>
+        <v>15391</v>
       </c>
       <c r="AU21" s="5">
         <f t="shared" si="17"/>
-        <v>1.0151165093405505</v>
+        <v>1.0159746517921975</v>
       </c>
       <c r="AV21" s="7">
         <v>11422</v>
@@ -3964,14 +3964,14 @@
       </c>
       <c r="AX21" s="4">
         <f t="shared" si="18"/>
-        <v>3620</v>
+        <v>3632</v>
       </c>
       <c r="AY21" s="6">
-        <v>11694</v>
+        <v>11706</v>
       </c>
       <c r="AZ21" s="5">
         <f t="shared" si="19"/>
-        <v>1.0238136928734023</v>
+        <v>1.0248642969707582</v>
       </c>
       <c r="BA21" s="7">
         <v>11689</v>
@@ -3981,14 +3981,14 @@
       </c>
       <c r="BC21" s="4">
         <f t="shared" si="20"/>
-        <v>3497</v>
+        <v>3510</v>
       </c>
       <c r="BD21" s="6">
-        <v>11819</v>
+        <v>11832</v>
       </c>
       <c r="BE21" s="5">
         <f t="shared" si="21"/>
-        <v>1.0111215672854821</v>
+        <v>1.0122337240140302</v>
       </c>
       <c r="BF21" s="7">
         <v>15725</v>
@@ -3998,14 +3998,14 @@
       </c>
       <c r="BH21" s="4">
         <f t="shared" si="22"/>
-        <v>6330</v>
+        <v>6351</v>
       </c>
       <c r="BI21" s="6">
-        <v>15775</v>
+        <v>15796</v>
       </c>
       <c r="BJ21" s="5">
         <f t="shared" si="23"/>
-        <v>1.0031796502384738</v>
+        <v>1.0045151033386328</v>
       </c>
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.3">
@@ -4023,14 +4023,14 @@
       </c>
       <c r="E22" s="4">
         <f t="shared" si="0"/>
-        <v>1809</v>
+        <v>1811</v>
       </c>
       <c r="F22" s="13">
-        <v>6680</v>
+        <v>6682</v>
       </c>
       <c r="G22" s="5">
         <f t="shared" si="1"/>
-        <v>0.98875074008288932</v>
+        <v>0.98904677323860268</v>
       </c>
       <c r="H22" s="7">
         <v>6770</v>
@@ -4040,14 +4040,14 @@
       </c>
       <c r="J22" s="4">
         <f t="shared" si="2"/>
-        <v>1673</v>
+        <v>1675</v>
       </c>
       <c r="K22" s="13">
-        <v>6765</v>
+        <v>6767</v>
       </c>
       <c r="L22" s="5">
         <f t="shared" si="3"/>
-        <v>0.99926144756277691</v>
+        <v>0.99955686853766612</v>
       </c>
       <c r="M22" s="7">
         <v>8074</v>
@@ -4057,14 +4057,14 @@
       </c>
       <c r="O22" s="4">
         <f t="shared" si="4"/>
-        <v>1990</v>
+        <v>1993</v>
       </c>
       <c r="P22" s="6">
-        <v>8077</v>
+        <v>8080</v>
       </c>
       <c r="Q22" s="5">
         <f t="shared" si="5"/>
-        <v>1.0003715630418628</v>
+        <v>1.0007431260837256</v>
       </c>
       <c r="R22" s="7">
         <v>6748</v>
@@ -4074,14 +4074,14 @@
       </c>
       <c r="T22" s="4">
         <f t="shared" si="6"/>
-        <v>1755</v>
+        <v>1758</v>
       </c>
       <c r="U22" s="13">
-        <v>6790</v>
+        <v>6793</v>
       </c>
       <c r="V22" s="5">
         <f t="shared" si="7"/>
-        <v>1.0062240663900415</v>
+        <v>1.0066686425607587</v>
       </c>
       <c r="W22" s="7">
         <v>6876</v>
@@ -4091,14 +4091,14 @@
       </c>
       <c r="Y22" s="4">
         <f t="shared" si="8"/>
-        <v>1685</v>
+        <v>1688</v>
       </c>
       <c r="Z22" s="13">
-        <v>6851</v>
+        <v>6854</v>
       </c>
       <c r="AA22" s="5">
         <f t="shared" si="9"/>
-        <v>0.99636416521233273</v>
+        <v>0.99680046538685285</v>
       </c>
       <c r="AB22" s="7">
         <v>8219</v>
@@ -4108,14 +4108,14 @@
       </c>
       <c r="AD22" s="4">
         <f t="shared" si="10"/>
-        <v>2247</v>
+        <v>2251</v>
       </c>
       <c r="AE22" s="6">
-        <v>8232</v>
+        <v>8236</v>
       </c>
       <c r="AF22" s="5">
         <f t="shared" si="11"/>
-        <v>1.0015817009368537</v>
+        <v>1.0020683781481932</v>
       </c>
       <c r="AG22" s="7">
         <v>6901</v>
@@ -4125,14 +4125,14 @@
       </c>
       <c r="AI22" s="4">
         <f t="shared" si="12"/>
-        <v>1725</v>
+        <v>1730</v>
       </c>
       <c r="AJ22" s="6">
-        <v>6907</v>
+        <v>6912</v>
       </c>
       <c r="AK22" s="5">
         <f t="shared" si="13"/>
-        <v>1.0008694392117083</v>
+        <v>1.0015939718881322</v>
       </c>
       <c r="AL22" s="7">
         <v>6948</v>
@@ -4142,14 +4142,14 @@
       </c>
       <c r="AN22" s="4">
         <f t="shared" si="14"/>
-        <v>1712</v>
+        <v>1718</v>
       </c>
       <c r="AO22" s="6">
-        <v>6941</v>
+        <v>6947</v>
       </c>
       <c r="AP22" s="5">
         <f t="shared" si="15"/>
-        <v>0.99899251583189408</v>
+        <v>0.99985607369027063</v>
       </c>
       <c r="AQ22" s="7">
         <v>8297</v>
@@ -4159,14 +4159,14 @@
       </c>
       <c r="AS22" s="4">
         <f t="shared" si="16"/>
-        <v>2126</v>
+        <v>2131</v>
       </c>
       <c r="AT22" s="6">
-        <v>8301</v>
+        <v>8306</v>
       </c>
       <c r="AU22" s="5">
         <f t="shared" si="17"/>
-        <v>1.0004821019645656</v>
+        <v>1.0010847294202725</v>
       </c>
       <c r="AV22" s="7">
         <v>6958</v>
@@ -4176,14 +4176,14 @@
       </c>
       <c r="AX22" s="4">
         <f t="shared" si="18"/>
-        <v>1857</v>
+        <v>1864</v>
       </c>
       <c r="AY22" s="6">
-        <v>6983</v>
+        <v>6990</v>
       </c>
       <c r="AZ22" s="5">
         <f t="shared" si="19"/>
-        <v>1.0035929864903708</v>
+        <v>1.0045990227076746</v>
       </c>
       <c r="BA22" s="7">
         <v>7049</v>
@@ -4193,14 +4193,14 @@
       </c>
       <c r="BC22" s="4">
         <f t="shared" si="20"/>
-        <v>1737</v>
+        <v>1744</v>
       </c>
       <c r="BD22" s="6">
-        <v>7043</v>
+        <v>7050</v>
       </c>
       <c r="BE22" s="5">
         <f t="shared" si="21"/>
-        <v>0.99914881543481349</v>
+        <v>1.0001418640941977</v>
       </c>
       <c r="BF22" s="7">
         <v>8436</v>
@@ -4210,14 +4210,14 @@
       </c>
       <c r="BH22" s="4">
         <f t="shared" si="22"/>
-        <v>2666</v>
+        <v>2672</v>
       </c>
       <c r="BI22" s="6">
-        <v>8405</v>
+        <v>8411</v>
       </c>
       <c r="BJ22" s="5">
         <f t="shared" si="23"/>
-        <v>0.99632527264106208</v>
+        <v>0.99703651019440498</v>
       </c>
     </row>
     <row r="23" spans="1:62" x14ac:dyDescent="0.3">
@@ -4235,14 +4235,14 @@
       </c>
       <c r="E23" s="4">
         <f t="shared" si="0"/>
-        <v>3052</v>
+        <v>3053</v>
       </c>
       <c r="F23" s="13">
-        <v>8677</v>
+        <v>8678</v>
       </c>
       <c r="G23" s="5">
         <f t="shared" si="1"/>
-        <v>0.98512715712988197</v>
+        <v>0.98524069028156225</v>
       </c>
       <c r="H23" s="7">
         <v>8878</v>
@@ -4252,14 +4252,14 @@
       </c>
       <c r="J23" s="4">
         <f t="shared" si="2"/>
-        <v>2883</v>
+        <v>2884</v>
       </c>
       <c r="K23" s="13">
-        <v>8790</v>
+        <v>8791</v>
       </c>
       <c r="L23" s="5">
         <f t="shared" si="3"/>
-        <v>0.99008785762559137</v>
+        <v>0.99020049560711876</v>
       </c>
       <c r="M23" s="7">
         <v>11255</v>
@@ -4269,14 +4269,14 @@
       </c>
       <c r="O23" s="4">
         <f t="shared" si="4"/>
-        <v>3404</v>
+        <v>3407</v>
       </c>
       <c r="P23" s="6">
-        <v>11210</v>
+        <v>11213</v>
       </c>
       <c r="Q23" s="5">
         <f t="shared" si="5"/>
-        <v>0.99600177698800529</v>
+        <v>0.99626832518880493</v>
       </c>
       <c r="R23" s="7">
         <v>8944</v>
@@ -4286,14 +4286,14 @@
       </c>
       <c r="T23" s="4">
         <f t="shared" si="6"/>
-        <v>2658</v>
+        <v>2661</v>
       </c>
       <c r="U23" s="13">
-        <v>8916</v>
+        <v>8919</v>
       </c>
       <c r="V23" s="5">
         <f t="shared" si="7"/>
-        <v>0.99686940966010729</v>
+        <v>0.99720483005366722</v>
       </c>
       <c r="W23" s="7">
         <v>10422</v>
@@ -4303,14 +4303,14 @@
       </c>
       <c r="Y23" s="4">
         <f t="shared" si="8"/>
-        <v>2948</v>
+        <v>2951</v>
       </c>
       <c r="Z23" s="13">
-        <v>9025</v>
+        <v>9028</v>
       </c>
       <c r="AA23" s="5">
         <f t="shared" si="9"/>
-        <v>0.86595663020533487</v>
+        <v>0.86624448282479372</v>
       </c>
       <c r="AB23" s="7">
         <v>11673</v>
@@ -4320,14 +4320,14 @@
       </c>
       <c r="AD23" s="4">
         <f t="shared" si="10"/>
-        <v>3724</v>
+        <v>3727</v>
       </c>
       <c r="AE23" s="6">
-        <v>11396</v>
+        <v>11399</v>
       </c>
       <c r="AF23" s="5">
         <f t="shared" si="11"/>
-        <v>0.97627002484365633</v>
+        <v>0.97652702818469972</v>
       </c>
       <c r="AG23" s="7">
         <v>9370</v>
@@ -4337,14 +4337,14 @@
       </c>
       <c r="AI23" s="4">
         <f t="shared" si="12"/>
-        <v>4409</v>
+        <v>4414</v>
       </c>
       <c r="AJ23" s="6">
-        <v>8995</v>
+        <v>9000</v>
       </c>
       <c r="AK23" s="5">
         <f t="shared" si="13"/>
-        <v>0.95997865528281745</v>
+        <v>0.96051227321237997</v>
       </c>
       <c r="AL23" s="7">
         <v>9238</v>
@@ -4354,14 +4354,14 @@
       </c>
       <c r="AN23" s="4">
         <f t="shared" si="14"/>
-        <v>2629</v>
+        <v>2635</v>
       </c>
       <c r="AO23" s="6">
-        <v>9032</v>
+        <v>9038</v>
       </c>
       <c r="AP23" s="5">
         <f t="shared" si="15"/>
-        <v>0.977700801039186</v>
+        <v>0.9783502922710543</v>
       </c>
       <c r="AQ23" s="7">
         <v>11727</v>
@@ -4371,14 +4371,14 @@
       </c>
       <c r="AS23" s="4">
         <f t="shared" si="16"/>
-        <v>3109</v>
+        <v>3115</v>
       </c>
       <c r="AT23" s="6">
-        <v>11521</v>
+        <v>11527</v>
       </c>
       <c r="AU23" s="5">
         <f t="shared" si="17"/>
-        <v>0.98243370000852737</v>
+        <v>0.98294533981410426</v>
       </c>
       <c r="AV23" s="7">
         <v>9359</v>
@@ -4388,14 +4388,14 @@
       </c>
       <c r="AX23" s="4">
         <f t="shared" si="18"/>
-        <v>2768</v>
+        <v>2775</v>
       </c>
       <c r="AY23" s="6">
-        <v>9151</v>
+        <v>9158</v>
       </c>
       <c r="AZ23" s="5">
         <f t="shared" si="19"/>
-        <v>0.9777754033550593</v>
+        <v>0.9785233465113794</v>
       </c>
       <c r="BA23" s="7">
         <v>9570</v>
@@ -4405,14 +4405,14 @@
       </c>
       <c r="BC23" s="4">
         <f t="shared" si="20"/>
-        <v>2897</v>
+        <v>2903</v>
       </c>
       <c r="BD23" s="6">
-        <v>9206</v>
+        <v>9212</v>
       </c>
       <c r="BE23" s="5">
         <f t="shared" si="21"/>
-        <v>0.96196447230929993</v>
+        <v>0.96259143155694882</v>
       </c>
       <c r="BF23" s="7">
         <v>11968</v>
@@ -4422,14 +4422,14 @@
       </c>
       <c r="BH23" s="4">
         <f t="shared" si="22"/>
-        <v>4305</v>
+        <v>4311</v>
       </c>
       <c r="BI23" s="6">
-        <v>11705</v>
+        <v>11711</v>
       </c>
       <c r="BJ23" s="5">
         <f t="shared" si="23"/>
-        <v>0.97802473262032086</v>
+        <v>0.97852606951871657</v>
       </c>
     </row>
     <row r="24" spans="1:62" x14ac:dyDescent="0.3">
@@ -4515,14 +4515,14 @@
       </c>
       <c r="Y24" s="4">
         <f t="shared" si="8"/>
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="Z24" s="13">
-        <v>6403</v>
+        <v>6405</v>
       </c>
       <c r="AA24" s="5">
         <f t="shared" si="9"/>
-        <v>0.97905198776758406</v>
+        <v>0.97935779816513757</v>
       </c>
       <c r="AB24" s="7">
         <v>7473</v>
@@ -4532,14 +4532,14 @@
       </c>
       <c r="AD24" s="4">
         <f t="shared" si="10"/>
-        <v>1728</v>
+        <v>1730</v>
       </c>
       <c r="AE24" s="6">
-        <v>7372</v>
+        <v>7374</v>
       </c>
       <c r="AF24" s="5">
         <f t="shared" si="11"/>
-        <v>0.98648467817476249</v>
+        <v>0.98675230830991567</v>
       </c>
       <c r="AG24" s="7">
         <v>6660</v>
@@ -4549,14 +4549,14 @@
       </c>
       <c r="AI24" s="4">
         <f t="shared" si="12"/>
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="AJ24" s="6">
-        <v>6584</v>
+        <v>6586</v>
       </c>
       <c r="AK24" s="5">
         <f t="shared" si="13"/>
-        <v>0.98858858858858856</v>
+        <v>0.98888888888888893</v>
       </c>
       <c r="AL24" s="7">
         <v>6723</v>
@@ -4566,14 +4566,14 @@
       </c>
       <c r="AN24" s="4">
         <f t="shared" si="14"/>
-        <v>1368</v>
+        <v>1370</v>
       </c>
       <c r="AO24" s="6">
-        <v>6631</v>
+        <v>6633</v>
       </c>
       <c r="AP24" s="5">
         <f t="shared" si="15"/>
-        <v>0.98631563290197832</v>
+        <v>0.98661311914323957</v>
       </c>
       <c r="AQ24" s="7">
         <v>7657</v>
@@ -4583,14 +4583,14 @@
       </c>
       <c r="AS24" s="4">
         <f t="shared" si="16"/>
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="AT24" s="6">
-        <v>7554</v>
+        <v>7556</v>
       </c>
       <c r="AU24" s="5">
         <f t="shared" si="17"/>
-        <v>0.9865482564973227</v>
+        <v>0.98680945540028731</v>
       </c>
       <c r="AV24" s="7">
         <v>6786</v>
@@ -4600,14 +4600,14 @@
       </c>
       <c r="AX24" s="4">
         <f t="shared" si="18"/>
-        <v>1435</v>
+        <v>1438</v>
       </c>
       <c r="AY24" s="6">
-        <v>6738</v>
+        <v>6741</v>
       </c>
       <c r="AZ24" s="5">
         <f t="shared" si="19"/>
-        <v>0.99292661361626877</v>
+        <v>0.99336870026525204</v>
       </c>
       <c r="BA24" s="7">
         <v>7025</v>
@@ -4617,14 +4617,14 @@
       </c>
       <c r="BC24" s="4">
         <f t="shared" si="20"/>
-        <v>1288</v>
+        <v>1291</v>
       </c>
       <c r="BD24" s="6">
-        <v>6798</v>
+        <v>6801</v>
       </c>
       <c r="BE24" s="5">
         <f t="shared" si="21"/>
-        <v>0.9676868327402135</v>
+        <v>0.96811387900355872</v>
       </c>
       <c r="BF24" s="7">
         <v>7878</v>
@@ -4634,14 +4634,14 @@
       </c>
       <c r="BH24" s="4">
         <f t="shared" si="22"/>
-        <v>1968</v>
+        <v>1971</v>
       </c>
       <c r="BI24" s="6">
-        <v>7738</v>
+        <v>7741</v>
       </c>
       <c r="BJ24" s="5">
         <f t="shared" si="23"/>
-        <v>0.98222899212998227</v>
+        <v>0.98260979944148263</v>
       </c>
     </row>
     <row r="25" spans="1:62" x14ac:dyDescent="0.3">
@@ -4659,14 +4659,14 @@
       </c>
       <c r="E25" s="4">
         <f t="shared" si="0"/>
-        <v>4284</v>
+        <v>4285</v>
       </c>
       <c r="F25" s="13">
-        <v>20228</v>
+        <v>20229</v>
       </c>
       <c r="G25" s="5">
         <f t="shared" si="1"/>
-        <v>0.96655198776758411</v>
+        <v>0.96659977064220182</v>
       </c>
       <c r="H25" s="7">
         <v>20519</v>
@@ -4676,14 +4676,14 @@
       </c>
       <c r="J25" s="4">
         <f t="shared" si="2"/>
-        <v>3842</v>
+        <v>3843</v>
       </c>
       <c r="K25" s="13">
-        <v>20329</v>
+        <v>20330</v>
       </c>
       <c r="L25" s="5">
         <f t="shared" si="3"/>
-        <v>0.9907402894877918</v>
+        <v>0.99078902480627706</v>
       </c>
       <c r="M25" s="7">
         <v>27924</v>
@@ -4693,14 +4693,14 @@
       </c>
       <c r="O25" s="4">
         <f t="shared" si="4"/>
-        <v>5548</v>
+        <v>5549</v>
       </c>
       <c r="P25" s="6">
-        <v>27880</v>
+        <v>27881</v>
       </c>
       <c r="Q25" s="5">
         <f t="shared" si="5"/>
-        <v>0.99842429451367998</v>
+        <v>0.99846010600200541</v>
       </c>
       <c r="R25" s="7">
         <v>20481</v>
@@ -4710,14 +4710,14 @@
       </c>
       <c r="T25" s="4">
         <f t="shared" si="6"/>
-        <v>4497</v>
+        <v>4498</v>
       </c>
       <c r="U25" s="13">
-        <v>20518</v>
+        <v>20519</v>
       </c>
       <c r="V25" s="5">
         <f t="shared" si="7"/>
-        <v>1.0018065524144328</v>
+        <v>1.0018553781553634</v>
       </c>
       <c r="W25" s="7">
         <v>20934</v>
@@ -4727,14 +4727,14 @@
       </c>
       <c r="Y25" s="4">
         <f t="shared" si="8"/>
-        <v>4221</v>
+        <v>4222</v>
       </c>
       <c r="Z25" s="13">
-        <v>20620</v>
+        <v>20621</v>
       </c>
       <c r="AA25" s="5">
         <f t="shared" si="9"/>
-        <v>0.98500047769179322</v>
+        <v>0.9850482468711188</v>
       </c>
       <c r="AB25" s="7">
         <v>28211</v>
@@ -4744,14 +4744,14 @@
       </c>
       <c r="AD25" s="4">
         <f t="shared" si="10"/>
-        <v>6226</v>
+        <v>6229</v>
       </c>
       <c r="AE25" s="6">
-        <v>28185</v>
+        <v>28188</v>
       </c>
       <c r="AF25" s="5">
         <f t="shared" si="11"/>
-        <v>0.99907837368402397</v>
+        <v>0.99918471518202123</v>
       </c>
       <c r="AG25" s="7">
         <v>20778</v>
@@ -4761,14 +4761,14 @@
       </c>
       <c r="AI25" s="4">
         <f t="shared" si="12"/>
-        <v>4154</v>
+        <v>4156</v>
       </c>
       <c r="AJ25" s="6">
-        <v>20719</v>
+        <v>20721</v>
       </c>
       <c r="AK25" s="5">
         <f t="shared" si="13"/>
-        <v>0.9971604581769179</v>
+        <v>0.99725671383193759</v>
       </c>
       <c r="AL25" s="7">
         <v>21081</v>
@@ -4778,14 +4778,14 @@
       </c>
       <c r="AN25" s="4">
         <f t="shared" si="14"/>
-        <v>4095</v>
+        <v>4100</v>
       </c>
       <c r="AO25" s="6">
-        <v>20890</v>
+        <v>20895</v>
       </c>
       <c r="AP25" s="5">
         <f t="shared" si="15"/>
-        <v>0.9909397087424695</v>
+        <v>0.99117688914188129</v>
       </c>
       <c r="AQ25" s="7">
         <v>28478</v>
@@ -4795,14 +4795,14 @@
       </c>
       <c r="AS25" s="4">
         <f t="shared" si="16"/>
-        <v>5120</v>
+        <v>5126</v>
       </c>
       <c r="AT25" s="6">
-        <v>28445</v>
+        <v>28451</v>
       </c>
       <c r="AU25" s="5">
         <f t="shared" si="17"/>
-        <v>0.99884121075918253</v>
+        <v>0.99905189971205843</v>
       </c>
       <c r="AV25" s="7">
         <v>21086</v>
@@ -4812,14 +4812,14 @@
       </c>
       <c r="AX25" s="4">
         <f t="shared" si="18"/>
-        <v>4323</v>
+        <v>4330</v>
       </c>
       <c r="AY25" s="6">
-        <v>21055</v>
+        <v>21062</v>
       </c>
       <c r="AZ25" s="5">
         <f t="shared" si="19"/>
-        <v>0.99852983021910269</v>
+        <v>0.99886180404059566</v>
       </c>
       <c r="BA25" s="7">
         <v>21405</v>
@@ -4829,14 +4829,14 @@
       </c>
       <c r="BC25" s="4">
         <f t="shared" si="20"/>
-        <v>4394</v>
+        <v>4400</v>
       </c>
       <c r="BD25" s="6">
-        <v>21226</v>
+        <v>21232</v>
       </c>
       <c r="BE25" s="5">
         <f t="shared" si="21"/>
-        <v>0.99163746788133611</v>
+        <v>0.99191777622050925</v>
       </c>
       <c r="BF25" s="7">
         <v>28924</v>
@@ -4846,14 +4846,14 @@
       </c>
       <c r="BH25" s="4">
         <f t="shared" si="22"/>
-        <v>7988</v>
+        <v>7997</v>
       </c>
       <c r="BI25" s="6">
-        <v>28802</v>
+        <v>28811</v>
       </c>
       <c r="BJ25" s="5">
         <f t="shared" si="23"/>
-        <v>0.99578204950905824</v>
+        <v>0.99609320979117688</v>
       </c>
     </row>
     <row r="26" spans="1:62" x14ac:dyDescent="0.3">
@@ -4871,14 +4871,14 @@
       </c>
       <c r="E26" s="4">
         <f t="shared" si="0"/>
-        <v>3352</v>
+        <v>3357</v>
       </c>
       <c r="F26" s="13">
-        <v>14068</v>
+        <v>14073</v>
       </c>
       <c r="G26" s="5">
         <f t="shared" si="1"/>
-        <v>0.99900582303650054</v>
+        <v>0.99936088623775032</v>
       </c>
       <c r="H26" s="7">
         <v>14494</v>
@@ -4888,14 +4888,14 @@
       </c>
       <c r="J26" s="4">
         <f t="shared" si="2"/>
-        <v>3064</v>
+        <v>3072</v>
       </c>
       <c r="K26" s="13">
-        <v>14331</v>
+        <v>14339</v>
       </c>
       <c r="L26" s="5">
         <f t="shared" si="3"/>
-        <v>0.98875396715882435</v>
+        <v>0.98930591969090653</v>
       </c>
       <c r="M26" s="7">
         <v>27473</v>
@@ -4905,14 +4905,14 @@
       </c>
       <c r="O26" s="4">
         <f t="shared" si="4"/>
-        <v>5272</v>
+        <v>5279</v>
       </c>
       <c r="P26" s="6">
-        <v>27387</v>
+        <v>27394</v>
       </c>
       <c r="Q26" s="5">
         <f t="shared" si="5"/>
-        <v>0.99686965384195392</v>
+        <v>0.99712444945946932</v>
       </c>
       <c r="R26" s="7">
         <v>14274</v>
@@ -4922,14 +4922,14 @@
       </c>
       <c r="T26" s="4">
         <f t="shared" si="6"/>
-        <v>3383</v>
+        <v>3391</v>
       </c>
       <c r="U26" s="13">
-        <v>14285</v>
+        <v>14293</v>
       </c>
       <c r="V26" s="5">
         <f t="shared" si="7"/>
-        <v>1.0007706319181728</v>
+        <v>1.001331091495026</v>
       </c>
       <c r="W26" s="7">
         <v>14651</v>
@@ -4939,14 +4939,14 @@
       </c>
       <c r="Y26" s="4">
         <f t="shared" si="8"/>
-        <v>3121</v>
+        <v>3130</v>
       </c>
       <c r="Z26" s="13">
-        <v>14434</v>
+        <v>14443</v>
       </c>
       <c r="AA26" s="5">
         <f t="shared" si="9"/>
-        <v>0.98518872431915905</v>
+        <v>0.98580301685891747</v>
       </c>
       <c r="AB26" s="7">
         <v>28023</v>
@@ -4956,14 +4956,14 @@
       </c>
       <c r="AD26" s="4">
         <f t="shared" si="10"/>
-        <v>5756</v>
+        <v>5769</v>
       </c>
       <c r="AE26" s="6">
-        <v>27645</v>
+        <v>27658</v>
       </c>
       <c r="AF26" s="5">
         <f t="shared" si="11"/>
-        <v>0.98651108018413447</v>
+        <v>0.98697498483388646</v>
       </c>
       <c r="AG26" s="7">
         <v>14346</v>
@@ -4973,14 +4973,14 @@
       </c>
       <c r="AI26" s="4">
         <f t="shared" si="12"/>
-        <v>3072</v>
+        <v>3081</v>
       </c>
       <c r="AJ26" s="6">
-        <v>14303</v>
+        <v>14312</v>
       </c>
       <c r="AK26" s="5">
         <f t="shared" si="13"/>
-        <v>0.99700264882197132</v>
+        <v>0.99763000139411684</v>
       </c>
       <c r="AL26" s="7">
         <v>14687</v>
@@ -4990,14 +4990,14 @@
       </c>
       <c r="AN26" s="4">
         <f t="shared" si="14"/>
-        <v>2988</v>
+        <v>2997</v>
       </c>
       <c r="AO26" s="6">
-        <v>14431</v>
+        <v>14440</v>
       </c>
       <c r="AP26" s="5">
         <f t="shared" si="15"/>
-        <v>0.98256961939129839</v>
+        <v>0.98318240620957309</v>
       </c>
       <c r="AQ26" s="7">
         <v>27948</v>
@@ -5007,14 +5007,14 @@
       </c>
       <c r="AS26" s="4">
         <f t="shared" si="16"/>
-        <v>5304</v>
+        <v>5318</v>
       </c>
       <c r="AT26" s="6">
-        <v>27777</v>
+        <v>27791</v>
       </c>
       <c r="AU26" s="5">
         <f t="shared" si="17"/>
-        <v>0.99388149420352079</v>
+        <v>0.9943824245026478</v>
       </c>
       <c r="AV26" s="7">
         <v>14478</v>
@@ -5024,14 +5024,14 @@
       </c>
       <c r="AX26" s="4">
         <f t="shared" si="18"/>
-        <v>3173</v>
+        <v>3182</v>
       </c>
       <c r="AY26" s="6">
-        <v>14430</v>
+        <v>14439</v>
       </c>
       <c r="AZ26" s="5">
         <f t="shared" si="19"/>
-        <v>0.99668462494819732</v>
+        <v>0.99730625777041026</v>
       </c>
       <c r="BA26" s="7">
         <v>14902</v>
@@ -5041,14 +5041,14 @@
       </c>
       <c r="BC26" s="4">
         <f t="shared" si="20"/>
-        <v>3076</v>
+        <v>3087</v>
       </c>
       <c r="BD26" s="6">
-        <v>14542</v>
+        <v>14553</v>
       </c>
       <c r="BE26" s="5">
         <f t="shared" si="21"/>
-        <v>0.97584216883639785</v>
+        <v>0.976580324788619</v>
       </c>
       <c r="BF26" s="7">
         <v>28105</v>
@@ -5058,14 +5058,14 @@
       </c>
       <c r="BH26" s="4">
         <f t="shared" si="22"/>
-        <v>6548</v>
+        <v>6563</v>
       </c>
       <c r="BI26" s="6">
-        <v>27887</v>
+        <v>27902</v>
       </c>
       <c r="BJ26" s="5">
         <f t="shared" si="23"/>
-        <v>0.99224337306529087</v>
+        <v>0.99277708592777081</v>
       </c>
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
@@ -5083,14 +5083,14 @@
       </c>
       <c r="E27" s="4">
         <f t="shared" si="0"/>
-        <v>36714</v>
+        <v>36747</v>
       </c>
       <c r="F27" s="13">
-        <v>125248</v>
+        <v>125281</v>
       </c>
       <c r="G27" s="5">
         <f t="shared" si="1"/>
-        <v>0.96988469609794248</v>
+        <v>0.97014023866126675</v>
       </c>
       <c r="H27" s="7">
         <v>129298</v>
@@ -5100,14 +5100,14 @@
       </c>
       <c r="J27" s="4">
         <f t="shared" si="2"/>
-        <v>32431</v>
+        <v>32466</v>
       </c>
       <c r="K27" s="13">
-        <v>126096</v>
+        <v>126131</v>
       </c>
       <c r="L27" s="5">
         <f t="shared" si="3"/>
-        <v>0.97523550248263702</v>
+        <v>0.97550619499141522</v>
       </c>
       <c r="M27" s="7">
         <v>186733</v>
@@ -5117,14 +5117,14 @@
       </c>
       <c r="O27" s="4">
         <f t="shared" si="4"/>
-        <v>47741</v>
+        <v>47803</v>
       </c>
       <c r="P27" s="6">
-        <v>185289</v>
+        <v>185351</v>
       </c>
       <c r="Q27" s="5">
         <f t="shared" si="5"/>
-        <v>0.99226703367910329</v>
+        <v>0.99259905854883712</v>
       </c>
       <c r="R27" s="7">
         <v>126872</v>
@@ -5134,14 +5134,14 @@
       </c>
       <c r="T27" s="4">
         <f t="shared" si="6"/>
-        <v>32538</v>
+        <v>32579</v>
       </c>
       <c r="U27" s="13">
-        <v>125761</v>
+        <v>125802</v>
       </c>
       <c r="V27" s="5">
         <f t="shared" si="7"/>
-        <v>0.99124314269499969</v>
+        <v>0.99156630304558924</v>
       </c>
       <c r="W27" s="7">
         <v>129739</v>
@@ -5151,14 +5151,14 @@
       </c>
       <c r="Y27" s="4">
         <f t="shared" si="8"/>
-        <v>33775</v>
+        <v>33827</v>
       </c>
       <c r="Z27" s="13">
-        <v>126636</v>
+        <v>126688</v>
       </c>
       <c r="AA27" s="5">
         <f t="shared" si="9"/>
-        <v>0.97608275075343576</v>
+        <v>0.97648355544593379</v>
       </c>
       <c r="AB27" s="7">
         <v>188270</v>
@@ -5168,14 +5168,14 @@
       </c>
       <c r="AD27" s="4">
         <f t="shared" si="10"/>
-        <v>52399</v>
+        <v>52490</v>
       </c>
       <c r="AE27" s="6">
-        <v>186730</v>
+        <v>186821</v>
       </c>
       <c r="AF27" s="5">
         <f t="shared" si="11"/>
-        <v>0.99182025813990549</v>
+        <v>0.99230360652254745</v>
       </c>
       <c r="AG27" s="7">
         <v>127800</v>
@@ -5185,14 +5185,14 @@
       </c>
       <c r="AI27" s="4">
         <f t="shared" si="12"/>
-        <v>34157</v>
+        <v>34219</v>
       </c>
       <c r="AJ27" s="6">
-        <v>126843</v>
+        <v>126905</v>
       </c>
       <c r="AK27" s="5">
         <f t="shared" si="13"/>
-        <v>0.99251173708920193</v>
+        <v>0.99299687010954618</v>
       </c>
       <c r="AL27" s="7">
         <v>130262</v>
@@ -5202,14 +5202,14 @@
       </c>
       <c r="AN27" s="4">
         <f t="shared" si="14"/>
-        <v>30926</v>
+        <v>30994</v>
       </c>
       <c r="AO27" s="6">
-        <v>127760</v>
+        <v>127828</v>
       </c>
       <c r="AP27" s="5">
         <f t="shared" si="15"/>
-        <v>0.9807925565398965</v>
+        <v>0.98131458138213756</v>
       </c>
       <c r="AQ27" s="7">
         <v>189830</v>
@@ -5219,14 +5219,14 @@
       </c>
       <c r="AS27" s="4">
         <f t="shared" si="16"/>
-        <v>44945</v>
+        <v>45067</v>
       </c>
       <c r="AT27" s="6">
-        <v>188759</v>
+        <v>188881</v>
       </c>
       <c r="AU27" s="5">
         <f t="shared" si="17"/>
-        <v>0.99435810988779438</v>
+        <v>0.99500079018068799</v>
       </c>
       <c r="AV27" s="7">
         <v>128733</v>
@@ -5236,14 +5236,14 @@
       </c>
       <c r="AX27" s="4">
         <f t="shared" si="18"/>
-        <v>30809</v>
+        <v>30891</v>
       </c>
       <c r="AY27" s="6">
-        <v>128550</v>
+        <v>128632</v>
       </c>
       <c r="AZ27" s="5">
         <f t="shared" si="19"/>
-        <v>0.99857845307729953</v>
+        <v>0.99921543038692484</v>
       </c>
       <c r="BA27" s="7">
         <v>132099</v>
@@ -5253,14 +5253,14 @@
       </c>
       <c r="BC27" s="4">
         <f t="shared" si="20"/>
-        <v>31283</v>
+        <v>31377</v>
       </c>
       <c r="BD27" s="6">
-        <v>129959</v>
+        <v>130053</v>
       </c>
       <c r="BE27" s="5">
         <f t="shared" si="21"/>
-        <v>0.98380002876630401</v>
+        <v>0.98451161628778416</v>
       </c>
       <c r="BF27" s="7">
         <v>192460</v>
@@ -5270,14 +5270,14 @@
       </c>
       <c r="BH27" s="4">
         <f t="shared" si="22"/>
-        <v>64826</v>
+        <v>65010</v>
       </c>
       <c r="BI27" s="6">
-        <v>191232</v>
+        <v>191416</v>
       </c>
       <c r="BJ27" s="5">
         <f t="shared" si="23"/>
-        <v>0.9936194533929128</v>
+        <v>0.99457549620700403</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -5295,14 +5295,14 @@
       </c>
       <c r="E28" s="4">
         <f t="shared" si="0"/>
-        <v>69854</v>
+        <v>69876</v>
       </c>
       <c r="F28" s="13">
-        <v>409699</v>
+        <v>409721</v>
       </c>
       <c r="G28" s="5">
         <f t="shared" si="1"/>
-        <v>0.99118647512229585</v>
+        <v>0.99123969981274584</v>
       </c>
       <c r="H28" s="7">
         <v>423216</v>
@@ -5312,14 +5312,14 @@
       </c>
       <c r="J28" s="4">
         <f t="shared" si="2"/>
-        <v>63900</v>
+        <v>63916</v>
       </c>
       <c r="K28" s="13">
-        <v>413953</v>
+        <v>413969</v>
       </c>
       <c r="L28" s="5">
         <f t="shared" si="3"/>
-        <v>0.9781128312729197</v>
+        <v>0.97815063702695548</v>
       </c>
       <c r="M28" s="7">
         <v>688530</v>
@@ -5329,14 +5329,14 @@
       </c>
       <c r="O28" s="4">
         <f t="shared" si="4"/>
-        <v>102750</v>
+        <v>102796</v>
       </c>
       <c r="P28" s="6">
-        <v>680913</v>
+        <v>680959</v>
       </c>
       <c r="Q28" s="5">
         <f t="shared" si="5"/>
-        <v>0.98893730120691914</v>
+        <v>0.98900411020580081</v>
       </c>
       <c r="R28" s="7">
         <v>417505</v>
@@ -5346,14 +5346,14 @@
       </c>
       <c r="T28" s="4">
         <f t="shared" si="6"/>
-        <v>65478</v>
+        <v>65508</v>
       </c>
       <c r="U28" s="13">
-        <v>414307</v>
+        <v>414337</v>
       </c>
       <c r="V28" s="5">
         <f t="shared" si="7"/>
-        <v>0.99234021149447316</v>
+        <v>0.9924120669213542</v>
       </c>
       <c r="W28" s="7">
         <v>426115</v>
@@ -5363,14 +5363,14 @@
       </c>
       <c r="Y28" s="4">
         <f t="shared" si="8"/>
-        <v>67601</v>
+        <v>67639</v>
       </c>
       <c r="Z28" s="13">
-        <v>416266</v>
+        <v>416304</v>
       </c>
       <c r="AA28" s="5">
         <f t="shared" si="9"/>
-        <v>0.976886521244265</v>
+        <v>0.976975699048379</v>
       </c>
       <c r="AB28" s="7">
         <v>693825</v>
@@ -5380,14 +5380,14 @@
       </c>
       <c r="AD28" s="4">
         <f t="shared" si="10"/>
-        <v>118078</v>
+        <v>118149</v>
       </c>
       <c r="AE28" s="6">
-        <v>686143</v>
+        <v>686214</v>
       </c>
       <c r="AF28" s="5">
         <f t="shared" si="11"/>
-        <v>0.98892804381508304</v>
+        <v>0.98903037509458436</v>
       </c>
       <c r="AG28" s="7">
         <v>421441</v>
@@ -5397,14 +5397,14 @@
       </c>
       <c r="AI28" s="4">
         <f t="shared" si="12"/>
-        <v>73134</v>
+        <v>73182</v>
       </c>
       <c r="AJ28" s="6">
-        <v>416974</v>
+        <v>417022</v>
       </c>
       <c r="AK28" s="5">
         <f t="shared" si="13"/>
-        <v>0.98940065157400447</v>
+        <v>0.98951454652015347</v>
       </c>
       <c r="AL28" s="7">
         <v>428935</v>
@@ -5414,14 +5414,14 @@
       </c>
       <c r="AN28" s="4">
         <f t="shared" si="14"/>
-        <v>61982</v>
+        <v>62033</v>
       </c>
       <c r="AO28" s="6">
-        <v>421213</v>
+        <v>421264</v>
       </c>
       <c r="AP28" s="5">
         <f t="shared" si="15"/>
-        <v>0.98199727231398692</v>
+        <v>0.98211617144788832</v>
       </c>
       <c r="AQ28" s="7">
         <v>700018</v>
@@ -5431,14 +5431,14 @@
       </c>
       <c r="AS28" s="4">
         <f t="shared" si="16"/>
-        <v>95104</v>
+        <v>95208</v>
       </c>
       <c r="AT28" s="6">
-        <v>695040</v>
+        <v>695144</v>
       </c>
       <c r="AU28" s="5">
         <f t="shared" si="17"/>
-        <v>0.99288875428917545</v>
+        <v>0.99303732189743688</v>
       </c>
       <c r="AV28" s="7">
         <v>428584</v>
@@ -5448,14 +5448,14 @@
       </c>
       <c r="AX28" s="4">
         <f t="shared" si="18"/>
-        <v>63239</v>
+        <v>63304</v>
       </c>
       <c r="AY28" s="6">
-        <v>426656</v>
+        <v>426721</v>
       </c>
       <c r="AZ28" s="5">
         <f t="shared" si="19"/>
-        <v>0.99550146529035144</v>
+        <v>0.99565312750825974</v>
       </c>
       <c r="BA28" s="7">
         <v>438333</v>
@@ -5465,14 +5465,14 @@
       </c>
       <c r="BC28" s="4">
         <f t="shared" si="20"/>
-        <v>63168</v>
+        <v>63250</v>
       </c>
       <c r="BD28" s="6">
-        <v>431619</v>
+        <v>431701</v>
       </c>
       <c r="BE28" s="5">
         <f t="shared" si="21"/>
-        <v>0.98468287808583888</v>
+        <v>0.98486995047144521</v>
       </c>
       <c r="BF28" s="7">
         <v>711748</v>
@@ -5482,14 +5482,14 @@
       </c>
       <c r="BH28" s="4">
         <f t="shared" si="22"/>
-        <v>138869</v>
+        <v>139056</v>
       </c>
       <c r="BI28" s="6">
-        <v>705878</v>
+        <v>706065</v>
       </c>
       <c r="BJ28" s="5">
         <f t="shared" si="23"/>
-        <v>0.99175269898896801</v>
+        <v>0.99201543242833135</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.3">
@@ -5507,14 +5507,14 @@
       </c>
       <c r="E29" s="4">
         <f t="shared" si="0"/>
-        <v>26019</v>
+        <v>26022</v>
       </c>
       <c r="F29" s="13">
-        <v>135532</v>
+        <v>135535</v>
       </c>
       <c r="G29" s="5">
         <f t="shared" si="1"/>
-        <v>0.99077444917174728</v>
+        <v>0.99079637995818526</v>
       </c>
       <c r="H29" s="7">
         <v>138439</v>
@@ -5524,14 +5524,14 @@
       </c>
       <c r="J29" s="4">
         <f t="shared" si="2"/>
-        <v>24288</v>
+        <v>24293</v>
       </c>
       <c r="K29" s="13">
-        <v>136667</v>
+        <v>136672</v>
       </c>
       <c r="L29" s="5">
         <f t="shared" si="3"/>
-        <v>0.98720013868924217</v>
+        <v>0.98723625567939666</v>
       </c>
       <c r="M29" s="7">
         <v>184711</v>
@@ -5541,14 +5541,14 @@
       </c>
       <c r="O29" s="4">
         <f t="shared" si="4"/>
-        <v>32681</v>
+        <v>32693</v>
       </c>
       <c r="P29" s="6">
-        <v>182783</v>
+        <v>182795</v>
       </c>
       <c r="Q29" s="5">
         <f t="shared" si="5"/>
-        <v>0.98956207264321017</v>
+        <v>0.98962703899605331</v>
       </c>
       <c r="R29" s="7">
         <v>138323</v>
@@ -5558,14 +5558,14 @@
       </c>
       <c r="T29" s="4">
         <f t="shared" si="6"/>
-        <v>26907</v>
+        <v>26917</v>
       </c>
       <c r="U29" s="13">
-        <v>136869</v>
+        <v>136879</v>
       </c>
       <c r="V29" s="5">
         <f t="shared" si="7"/>
-        <v>0.98948837142051571</v>
+        <v>0.98956066597745851</v>
       </c>
       <c r="W29" s="7">
         <v>139858</v>
@@ -5575,14 +5575,14 @@
       </c>
       <c r="Y29" s="4">
         <f t="shared" si="8"/>
-        <v>25733</v>
+        <v>25743</v>
       </c>
       <c r="Z29" s="13">
-        <v>137285</v>
+        <v>137295</v>
       </c>
       <c r="AA29" s="5">
         <f t="shared" si="9"/>
-        <v>0.98160276852235839</v>
+        <v>0.98167426961632509</v>
       </c>
       <c r="AB29" s="7">
         <v>187429</v>
@@ -5592,14 +5592,14 @@
       </c>
       <c r="AD29" s="4">
         <f t="shared" si="10"/>
-        <v>36058</v>
+        <v>36073</v>
       </c>
       <c r="AE29" s="6">
-        <v>184158</v>
+        <v>184173</v>
       </c>
       <c r="AF29" s="5">
         <f t="shared" si="11"/>
-        <v>0.9825480581980377</v>
+        <v>0.98262808850284644</v>
       </c>
       <c r="AG29" s="7">
         <v>139419</v>
@@ -5609,14 +5609,14 @@
       </c>
       <c r="AI29" s="4">
         <f t="shared" si="12"/>
-        <v>38006</v>
+        <v>38024</v>
       </c>
       <c r="AJ29" s="6">
-        <v>138001</v>
+        <v>138019</v>
       </c>
       <c r="AK29" s="5">
         <f t="shared" si="13"/>
-        <v>0.98982921983373862</v>
+        <v>0.9899583270572877</v>
       </c>
       <c r="AL29" s="7">
         <v>141276</v>
@@ -5626,14 +5626,14 @@
       </c>
       <c r="AN29" s="4">
         <f t="shared" si="14"/>
-        <v>23654</v>
+        <v>23669</v>
       </c>
       <c r="AO29" s="6">
-        <v>139160</v>
+        <v>139175</v>
       </c>
       <c r="AP29" s="5">
         <f t="shared" si="15"/>
-        <v>0.98502222599733857</v>
+        <v>0.98512840114386024</v>
       </c>
       <c r="AQ29" s="7">
         <v>188424</v>
@@ -5643,14 +5643,14 @@
       </c>
       <c r="AS29" s="4">
         <f t="shared" si="16"/>
-        <v>29790</v>
+        <v>29811</v>
       </c>
       <c r="AT29" s="6">
-        <v>186799</v>
+        <v>186820</v>
       </c>
       <c r="AU29" s="5">
         <f t="shared" si="17"/>
-        <v>0.9913758332271897</v>
+        <v>0.99148728399779218</v>
       </c>
       <c r="AV29" s="7">
         <v>141887</v>
@@ -5660,14 +5660,14 @@
       </c>
       <c r="AX29" s="4">
         <f t="shared" si="18"/>
-        <v>24969</v>
+        <v>24987</v>
       </c>
       <c r="AY29" s="6">
-        <v>140558</v>
+        <v>140576</v>
       </c>
       <c r="AZ29" s="5">
         <f t="shared" si="19"/>
-        <v>0.9906333913607307</v>
+        <v>0.99076025287728964</v>
       </c>
       <c r="BA29" s="7">
         <v>143795</v>
@@ -5677,14 +5677,14 @@
       </c>
       <c r="BC29" s="4">
         <f t="shared" si="20"/>
-        <v>25502</v>
+        <v>25522</v>
       </c>
       <c r="BD29" s="6">
-        <v>141638</v>
+        <v>141658</v>
       </c>
       <c r="BE29" s="5">
         <f t="shared" si="21"/>
-        <v>0.98499947842414548</v>
+        <v>0.98513856531868282</v>
       </c>
       <c r="BF29" s="7">
         <v>191754</v>
@@ -5694,14 +5694,14 @@
       </c>
       <c r="BH29" s="4">
         <f t="shared" si="22"/>
-        <v>43878</v>
+        <v>43920</v>
       </c>
       <c r="BI29" s="6">
-        <v>189188</v>
+        <v>189230</v>
       </c>
       <c r="BJ29" s="5">
         <f t="shared" si="23"/>
-        <v>0.98661827132680413</v>
+        <v>0.98683730195980268</v>
       </c>
     </row>
     <row r="30" spans="1:62" x14ac:dyDescent="0.3">
@@ -5719,14 +5719,14 @@
       </c>
       <c r="E30" s="4">
         <f t="shared" si="0"/>
-        <v>41572</v>
+        <v>41587</v>
       </c>
       <c r="F30" s="13">
-        <v>176245</v>
+        <v>176260</v>
       </c>
       <c r="G30" s="5">
         <f t="shared" si="1"/>
-        <v>0.98877394163122878</v>
+        <v>0.98885809499231403</v>
       </c>
       <c r="H30" s="7">
         <v>181910</v>
@@ -5736,14 +5736,14 @@
       </c>
       <c r="J30" s="4">
         <f t="shared" si="2"/>
-        <v>39122</v>
+        <v>39136</v>
       </c>
       <c r="K30" s="13">
-        <v>178391</v>
+        <v>178405</v>
       </c>
       <c r="L30" s="5">
         <f t="shared" si="3"/>
-        <v>0.98065526908911005</v>
+        <v>0.98073223022373701</v>
       </c>
       <c r="M30" s="7">
         <v>304709</v>
@@ -5753,14 +5753,14 @@
       </c>
       <c r="O30" s="4">
         <f t="shared" si="4"/>
-        <v>61649</v>
+        <v>61674</v>
       </c>
       <c r="P30" s="6">
-        <v>300920</v>
+        <v>300945</v>
       </c>
       <c r="Q30" s="5">
         <f t="shared" si="5"/>
-        <v>0.9875651851438586</v>
+        <v>0.98764723063644333</v>
       </c>
       <c r="R30" s="7">
         <v>179361</v>
@@ -5770,14 +5770,14 @@
       </c>
       <c r="T30" s="4">
         <f t="shared" si="6"/>
-        <v>37684</v>
+        <v>37698</v>
       </c>
       <c r="U30" s="13">
-        <v>178071</v>
+        <v>178085</v>
       </c>
       <c r="V30" s="5">
         <f t="shared" si="7"/>
-        <v>0.99280780102697908</v>
+        <v>0.99288585589955458</v>
       </c>
       <c r="W30" s="7">
         <v>184404</v>
@@ -5787,14 +5787,14 @@
       </c>
       <c r="Y30" s="4">
         <f t="shared" si="8"/>
-        <v>38704</v>
+        <v>38727</v>
       </c>
       <c r="Z30" s="13">
-        <v>179237</v>
+        <v>179260</v>
       </c>
       <c r="AA30" s="5">
         <f t="shared" si="9"/>
-        <v>0.97198000043383004</v>
+        <v>0.97210472657859914</v>
       </c>
       <c r="AB30" s="7">
         <v>307610</v>
@@ -5804,14 +5804,14 @@
       </c>
       <c r="AD30" s="4">
         <f t="shared" si="10"/>
-        <v>66649</v>
+        <v>66688</v>
       </c>
       <c r="AE30" s="6">
-        <v>303845</v>
+        <v>303884</v>
       </c>
       <c r="AF30" s="5">
         <f t="shared" si="11"/>
-        <v>0.98776047592731053</v>
+        <v>0.98788725984200776</v>
       </c>
       <c r="AG30" s="7">
         <v>180656</v>
@@ -5821,14 +5821,14 @@
       </c>
       <c r="AI30" s="4">
         <f t="shared" si="12"/>
-        <v>38723</v>
+        <v>38749</v>
       </c>
       <c r="AJ30" s="6">
-        <v>179049</v>
+        <v>179075</v>
       </c>
       <c r="AK30" s="5">
         <f t="shared" si="13"/>
-        <v>0.99110464086440531</v>
+        <v>0.99124856080063772</v>
       </c>
       <c r="AL30" s="7">
         <v>185185</v>
@@ -5838,14 +5838,14 @@
       </c>
       <c r="AN30" s="4">
         <f t="shared" si="14"/>
-        <v>34579</v>
+        <v>34609</v>
       </c>
       <c r="AO30" s="6">
-        <v>181800</v>
+        <v>181830</v>
       </c>
       <c r="AP30" s="5">
         <f t="shared" si="15"/>
-        <v>0.98172098172098177</v>
+        <v>0.98188298188298184</v>
       </c>
       <c r="AQ30" s="7">
         <v>311830</v>
@@ -5855,14 +5855,14 @@
       </c>
       <c r="AS30" s="4">
         <f t="shared" si="16"/>
-        <v>55923</v>
+        <v>55991</v>
       </c>
       <c r="AT30" s="6">
-        <v>308858</v>
+        <v>308926</v>
       </c>
       <c r="AU30" s="5">
         <f t="shared" si="17"/>
-        <v>0.99046916589167178</v>
+        <v>0.99068723342847065</v>
       </c>
       <c r="AV30" s="7">
         <v>184055</v>
@@ -5872,14 +5872,14 @@
       </c>
       <c r="AX30" s="4">
         <f t="shared" si="18"/>
-        <v>36828</v>
+        <v>36866</v>
       </c>
       <c r="AY30" s="6">
-        <v>182771</v>
+        <v>182809</v>
       </c>
       <c r="AZ30" s="5">
         <f t="shared" si="19"/>
-        <v>0.99302382440031511</v>
+        <v>0.99323028442585093</v>
       </c>
       <c r="BA30" s="7">
         <v>188792</v>
@@ -5889,14 +5889,14 @@
       </c>
       <c r="BC30" s="4">
         <f t="shared" si="20"/>
-        <v>37183</v>
+        <v>37226</v>
       </c>
       <c r="BD30" s="6">
-        <v>185063</v>
+        <v>185106</v>
       </c>
       <c r="BE30" s="5">
         <f t="shared" si="21"/>
-        <v>0.98024810373320903</v>
+        <v>0.9804758676215094</v>
       </c>
       <c r="BF30" s="7">
         <v>315967</v>
@@ -5906,14 +5906,14 @@
       </c>
       <c r="BH30" s="4">
         <f t="shared" si="22"/>
-        <v>79519</v>
+        <v>79611</v>
       </c>
       <c r="BI30" s="6">
-        <v>313226</v>
+        <v>313318</v>
       </c>
       <c r="BJ30" s="5">
         <f t="shared" si="23"/>
-        <v>0.99132504343808059</v>
+        <v>0.99161621308554371</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
@@ -5931,14 +5931,14 @@
       </c>
       <c r="E31" s="4">
         <f t="shared" si="0"/>
-        <v>21587</v>
+        <v>21591</v>
       </c>
       <c r="F31" s="13">
-        <v>78972</v>
+        <v>78976</v>
       </c>
       <c r="G31" s="5">
         <f t="shared" si="1"/>
-        <v>1.0039026250556156</v>
+        <v>1.0039534735905422</v>
       </c>
       <c r="H31" s="7">
         <v>80911</v>
@@ -5948,14 +5948,14 @@
       </c>
       <c r="J31" s="4">
         <f t="shared" si="2"/>
-        <v>18853</v>
+        <v>18857</v>
       </c>
       <c r="K31" s="13">
-        <v>80545</v>
+        <v>80549</v>
       </c>
       <c r="L31" s="5">
         <f t="shared" si="3"/>
-        <v>0.99547651122838676</v>
+        <v>0.99552594826414209</v>
       </c>
       <c r="M31" s="7">
         <v>142260</v>
@@ -5965,14 +5965,14 @@
       </c>
       <c r="O31" s="4">
         <f t="shared" si="4"/>
-        <v>37904</v>
+        <v>37912</v>
       </c>
       <c r="P31" s="6">
-        <v>142441</v>
+        <v>142449</v>
       </c>
       <c r="Q31" s="5">
         <f t="shared" si="5"/>
-        <v>1.0012723182904542</v>
+        <v>1.0013285533530156</v>
       </c>
       <c r="R31" s="7">
         <v>79665</v>
@@ -5982,14 +5982,14 @@
       </c>
       <c r="T31" s="4">
         <f t="shared" si="6"/>
-        <v>20837</v>
+        <v>20842</v>
       </c>
       <c r="U31" s="13">
-        <v>80183</v>
+        <v>80188</v>
       </c>
       <c r="V31" s="5">
         <f t="shared" si="7"/>
-        <v>1.0065022280800853</v>
+        <v>1.0065649908993912</v>
       </c>
       <c r="W31" s="7">
         <v>81657</v>
@@ -5999,14 +5999,14 @@
       </c>
       <c r="Y31" s="4">
         <f t="shared" si="8"/>
-        <v>20880</v>
+        <v>20886</v>
       </c>
       <c r="Z31" s="13">
-        <v>80897</v>
+        <v>80903</v>
       </c>
       <c r="AA31" s="5">
         <f t="shared" si="9"/>
-        <v>0.99069277587959392</v>
+        <v>0.99076625396475504</v>
       </c>
       <c r="AB31" s="7">
         <v>144167</v>
@@ -6016,14 +6016,14 @@
       </c>
       <c r="AD31" s="4">
         <f t="shared" si="10"/>
-        <v>39674</v>
+        <v>39684</v>
       </c>
       <c r="AE31" s="6">
-        <v>144311</v>
+        <v>144321</v>
       </c>
       <c r="AF31" s="5">
         <f t="shared" si="11"/>
-        <v>1.0009988416211755</v>
+        <v>1.0010682056226459</v>
       </c>
       <c r="AG31" s="7">
         <v>80917</v>
@@ -6033,14 +6033,14 @@
       </c>
       <c r="AI31" s="4">
         <f t="shared" si="12"/>
-        <v>21018</v>
+        <v>21028</v>
       </c>
       <c r="AJ31" s="6">
-        <v>81698</v>
+        <v>81708</v>
       </c>
       <c r="AK31" s="5">
         <f t="shared" si="13"/>
-        <v>1.0096518654918003</v>
+        <v>1.0097754489167914</v>
       </c>
       <c r="AL31" s="7">
         <v>83546</v>
@@ -6050,14 +6050,14 @@
       </c>
       <c r="AN31" s="4">
         <f t="shared" si="14"/>
-        <v>18169</v>
+        <v>18182</v>
       </c>
       <c r="AO31" s="6">
-        <v>82859</v>
+        <v>82872</v>
       </c>
       <c r="AP31" s="5">
         <f t="shared" si="15"/>
-        <v>0.99177698513393819</v>
+        <v>0.9919325880353338</v>
       </c>
       <c r="AQ31" s="7">
         <v>147023</v>
@@ -6067,14 +6067,14 @@
       </c>
       <c r="AS31" s="4">
         <f t="shared" si="16"/>
-        <v>33049</v>
+        <v>33070</v>
       </c>
       <c r="AT31" s="6">
-        <v>147004</v>
+        <v>147025</v>
       </c>
       <c r="AU31" s="5">
         <f t="shared" si="17"/>
-        <v>0.99987076851921131</v>
+        <v>1.0000136033137672</v>
       </c>
       <c r="AV31" s="7">
         <v>81694</v>
@@ -6084,14 +6084,14 @@
       </c>
       <c r="AX31" s="4">
         <f t="shared" si="18"/>
-        <v>18614</v>
+        <v>18629</v>
       </c>
       <c r="AY31" s="6">
-        <v>82589</v>
+        <v>82604</v>
       </c>
       <c r="AZ31" s="5">
         <f t="shared" si="19"/>
-        <v>1.0109555169290279</v>
+        <v>1.0111391289445981</v>
       </c>
       <c r="BA31" s="7">
         <v>83957</v>
@@ -6101,14 +6101,14 @@
       </c>
       <c r="BC31" s="4">
         <f t="shared" si="20"/>
-        <v>18458</v>
+        <v>18471</v>
       </c>
       <c r="BD31" s="6">
-        <v>83606</v>
+        <v>83619</v>
       </c>
       <c r="BE31" s="5">
         <f t="shared" si="21"/>
-        <v>0.99581928844527556</v>
+        <v>0.99597412961396903</v>
       </c>
       <c r="BF31" s="7">
         <v>148810</v>
@@ -6118,14 +6118,14 @@
       </c>
       <c r="BH31" s="4">
         <f t="shared" si="22"/>
-        <v>50227</v>
+        <v>50267</v>
       </c>
       <c r="BI31" s="6">
-        <v>149017</v>
+        <v>149057</v>
       </c>
       <c r="BJ31" s="5">
         <f t="shared" si="23"/>
-        <v>1.0013910355486861</v>
+        <v>1.001659834688529</v>
       </c>
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.3">
@@ -6143,14 +6143,14 @@
       </c>
       <c r="E32" s="4">
         <f t="shared" si="0"/>
-        <v>47077</v>
+        <v>47084</v>
       </c>
       <c r="F32" s="13">
-        <v>218141</v>
+        <v>218148</v>
       </c>
       <c r="G32" s="5">
         <f t="shared" si="1"/>
-        <v>0.99338776736963386</v>
+        <v>0.99341964452418796</v>
       </c>
       <c r="H32" s="7">
         <v>225984</v>
@@ -6160,14 +6160,14 @@
       </c>
       <c r="J32" s="4">
         <f t="shared" si="2"/>
-        <v>42400</v>
+        <v>42408</v>
       </c>
       <c r="K32" s="13">
-        <v>222621</v>
+        <v>222629</v>
       </c>
       <c r="L32" s="5">
         <f t="shared" si="3"/>
-        <v>0.98511841546304169</v>
+        <v>0.98515381619937692</v>
       </c>
       <c r="M32" s="7">
         <v>469379</v>
@@ -6177,14 +6177,14 @@
       </c>
       <c r="O32" s="4">
         <f t="shared" si="4"/>
-        <v>100133</v>
+        <v>100148</v>
       </c>
       <c r="P32" s="6">
-        <v>465860</v>
+        <v>465875</v>
       </c>
       <c r="Q32" s="5">
         <f t="shared" si="5"/>
-        <v>0.99250286016204392</v>
+        <v>0.99253481727985271</v>
       </c>
       <c r="R32" s="7">
         <v>220673</v>
@@ -6194,14 +6194,14 @@
       </c>
       <c r="T32" s="4">
         <f t="shared" si="6"/>
-        <v>47723</v>
+        <v>47729</v>
       </c>
       <c r="U32" s="13">
-        <v>219972</v>
+        <v>219978</v>
       </c>
       <c r="V32" s="5">
         <f t="shared" si="7"/>
-        <v>0.99682335401249811</v>
+        <v>0.99685054356445968</v>
       </c>
       <c r="W32" s="7">
         <v>228851</v>
@@ -6211,14 +6211,14 @@
       </c>
       <c r="Y32" s="4">
         <f t="shared" si="8"/>
-        <v>48078</v>
+        <v>48085</v>
       </c>
       <c r="Z32" s="13">
-        <v>223028</v>
+        <v>223035</v>
       </c>
       <c r="AA32" s="5">
         <f t="shared" si="9"/>
-        <v>0.97455549680796671</v>
+        <v>0.97458608439552374</v>
       </c>
       <c r="AB32" s="7">
         <v>476427</v>
@@ -6228,14 +6228,14 @@
       </c>
       <c r="AD32" s="4">
         <f t="shared" si="10"/>
-        <v>106589</v>
+        <v>106608</v>
       </c>
       <c r="AE32" s="6">
-        <v>471723</v>
+        <v>471742</v>
       </c>
       <c r="AF32" s="5">
         <f t="shared" si="11"/>
-        <v>0.99012650416538106</v>
+        <v>0.99016638435688997</v>
       </c>
       <c r="AG32" s="7">
         <v>224544</v>
@@ -6245,14 +6245,14 @@
       </c>
       <c r="AI32" s="4">
         <f t="shared" si="12"/>
-        <v>46676</v>
+        <v>46684</v>
       </c>
       <c r="AJ32" s="6">
-        <v>223760</v>
+        <v>223768</v>
       </c>
       <c r="AK32" s="5">
         <f t="shared" si="13"/>
-        <v>0.99650847940715404</v>
+        <v>0.99654410716830555</v>
       </c>
       <c r="AL32" s="7">
         <v>231787</v>
@@ -6262,14 +6262,14 @@
       </c>
       <c r="AN32" s="4">
         <f t="shared" si="14"/>
-        <v>39778</v>
+        <v>39787</v>
       </c>
       <c r="AO32" s="6">
-        <v>227504</v>
+        <v>227513</v>
       </c>
       <c r="AP32" s="5">
         <f t="shared" si="15"/>
-        <v>0.9815218282302286</v>
+        <v>0.98156065698248818</v>
       </c>
       <c r="AQ32" s="7">
         <v>484390</v>
@@ -6279,14 +6279,14 @@
       </c>
       <c r="AS32" s="4">
         <f t="shared" si="16"/>
-        <v>81040</v>
+        <v>81068</v>
       </c>
       <c r="AT32" s="6">
-        <v>480440</v>
+        <v>480468</v>
       </c>
       <c r="AU32" s="5">
         <f t="shared" si="17"/>
-        <v>0.99184541381944302</v>
+        <v>0.99190321848097607</v>
       </c>
       <c r="AV32" s="7">
         <v>227629</v>
@@ -6296,14 +6296,14 @@
       </c>
       <c r="AX32" s="4">
         <f t="shared" si="18"/>
-        <v>40925</v>
+        <v>40939</v>
       </c>
       <c r="AY32" s="6">
-        <v>227607</v>
+        <v>227621</v>
       </c>
       <c r="AZ32" s="5">
         <f t="shared" si="19"/>
-        <v>0.99990335150617893</v>
+        <v>0.99996485509315591</v>
       </c>
       <c r="BA32" s="7">
         <v>234918</v>
@@ -6313,14 +6313,14 @@
       </c>
       <c r="BC32" s="4">
         <f t="shared" si="20"/>
-        <v>43793</v>
+        <v>43816</v>
       </c>
       <c r="BD32" s="6">
-        <v>231972</v>
+        <v>231995</v>
       </c>
       <c r="BE32" s="5">
         <f t="shared" si="21"/>
-        <v>0.98745945393711854</v>
+        <v>0.98755736044066444</v>
       </c>
       <c r="BF32" s="7">
         <v>492680</v>
@@ -6330,14 +6330,14 @@
       </c>
       <c r="BH32" s="4">
         <f t="shared" si="22"/>
-        <v>132684</v>
+        <v>132751</v>
       </c>
       <c r="BI32" s="6">
-        <v>489620</v>
+        <v>489687</v>
       </c>
       <c r="BJ32" s="5">
         <f t="shared" si="23"/>
-        <v>0.99378907201428923</v>
+        <v>0.99392506292116589</v>
       </c>
     </row>
     <row r="33" spans="1:62" x14ac:dyDescent="0.3">
@@ -6355,14 +6355,14 @@
       </c>
       <c r="E33" s="20">
         <f t="shared" si="0"/>
-        <v>75775</v>
+        <v>75783</v>
       </c>
       <c r="F33" s="13">
-        <v>664224</v>
+        <v>664232</v>
       </c>
       <c r="G33" s="21">
         <f t="shared" si="1"/>
-        <v>1.0012239754481378</v>
+        <v>1.0012360343195481</v>
       </c>
       <c r="H33" s="7">
         <v>674602</v>
@@ -6372,14 +6372,14 @@
       </c>
       <c r="J33" s="20">
         <f t="shared" si="2"/>
-        <v>68693</v>
+        <v>68703</v>
       </c>
       <c r="K33" s="13">
-        <v>671916</v>
+        <v>671926</v>
       </c>
       <c r="L33" s="21">
         <f t="shared" si="3"/>
-        <v>0.99601839306731965</v>
+        <v>0.99603321662254185</v>
       </c>
       <c r="M33" s="7">
         <v>1077651</v>
@@ -6389,14 +6389,14 @@
       </c>
       <c r="O33" s="20">
         <f t="shared" si="4"/>
-        <v>129423</v>
+        <v>129433</v>
       </c>
       <c r="P33" s="6">
-        <v>1076812</v>
+        <v>1076822</v>
       </c>
       <c r="Q33" s="21">
         <f t="shared" si="5"/>
-        <v>0.99922145481236502</v>
+        <v>0.99923073425441078</v>
       </c>
       <c r="R33" s="7">
         <v>670885</v>
@@ -6406,14 +6406,14 @@
       </c>
       <c r="T33" s="20">
         <f t="shared" si="6"/>
-        <v>79584</v>
+        <v>79592</v>
       </c>
       <c r="U33" s="13">
-        <v>672466</v>
+        <v>672474</v>
       </c>
       <c r="V33" s="21">
         <f t="shared" si="7"/>
-        <v>1.0023565886850951</v>
+        <v>1.0023685132325213</v>
       </c>
       <c r="W33" s="7">
         <v>679851</v>
@@ -6423,14 +6423,14 @@
       </c>
       <c r="Y33" s="20">
         <f t="shared" si="8"/>
-        <v>75685</v>
+        <v>75694</v>
       </c>
       <c r="Z33" s="13">
-        <v>678470</v>
+        <v>678479</v>
       </c>
       <c r="AA33" s="21">
         <f t="shared" si="9"/>
-        <v>0.99796867254736699</v>
+        <v>0.99798191074220677</v>
       </c>
       <c r="AB33" s="7">
         <v>1091619</v>
@@ -6440,14 +6440,14 @@
       </c>
       <c r="AD33" s="20">
         <f t="shared" si="10"/>
-        <v>137564</v>
+        <v>137579</v>
       </c>
       <c r="AE33" s="6">
-        <v>1090558</v>
+        <v>1090573</v>
       </c>
       <c r="AF33" s="21">
         <f t="shared" si="11"/>
-        <v>0.99902804916367338</v>
+        <v>0.99904179022167994</v>
       </c>
       <c r="AG33" s="7">
         <v>681949</v>
@@ -6457,14 +6457,14 @@
       </c>
       <c r="AI33" s="20">
         <f t="shared" si="12"/>
-        <v>85537</v>
+        <v>85545</v>
       </c>
       <c r="AJ33" s="6">
-        <v>683848</v>
+        <v>683856</v>
       </c>
       <c r="AK33" s="21">
         <f t="shared" si="13"/>
-        <v>1.0027846657154713</v>
+        <v>1.0027963967980009</v>
       </c>
       <c r="AL33" s="7">
         <v>691548</v>
@@ -6474,14 +6474,14 @@
       </c>
       <c r="AN33" s="20">
         <f t="shared" si="14"/>
-        <v>66479</v>
+        <v>66486</v>
       </c>
       <c r="AO33" s="6">
-        <v>689404</v>
+        <v>689411</v>
       </c>
       <c r="AP33" s="21">
         <f t="shared" si="15"/>
-        <v>0.99689970905851799</v>
+        <v>0.99690983127707689</v>
       </c>
       <c r="AQ33" s="7">
         <v>1107071</v>
@@ -6491,14 +6491,14 @@
       </c>
       <c r="AS33" s="20">
         <f t="shared" si="16"/>
-        <v>112145</v>
+        <v>112162</v>
       </c>
       <c r="AT33" s="6">
-        <v>1108788</v>
+        <v>1108805</v>
       </c>
       <c r="AU33" s="21">
         <f t="shared" si="17"/>
-        <v>1.0015509393706457</v>
+        <v>1.0015662952059985</v>
       </c>
       <c r="AV33" s="7">
         <v>697202</v>
@@ -6508,14 +6508,14 @@
       </c>
       <c r="AX33" s="20">
         <f t="shared" si="18"/>
-        <v>69900</v>
+        <v>69913</v>
       </c>
       <c r="AY33" s="6">
-        <v>700248</v>
+        <v>700261</v>
       </c>
       <c r="AZ33" s="21">
         <f t="shared" si="19"/>
-        <v>1.0043688916555029</v>
+        <v>1.0043875376146367</v>
       </c>
       <c r="BA33" s="7">
         <v>707985</v>
@@ -6525,14 +6525,14 @@
       </c>
       <c r="BC33" s="20">
         <f t="shared" si="20"/>
-        <v>69577</v>
+        <v>69593</v>
       </c>
       <c r="BD33" s="6">
-        <v>709706</v>
+        <v>709722</v>
       </c>
       <c r="BE33" s="21">
         <f t="shared" si="21"/>
-        <v>1.0024308424613515</v>
+        <v>1.0024534418102078</v>
       </c>
       <c r="BF33" s="7">
         <v>1132408</v>
@@ -6542,14 +6542,14 @@
       </c>
       <c r="BH33" s="20">
         <f t="shared" si="22"/>
-        <v>174707</v>
+        <v>174752</v>
       </c>
       <c r="BI33" s="6">
-        <v>1133157</v>
+        <v>1133202</v>
       </c>
       <c r="BJ33" s="21">
         <f t="shared" si="23"/>
-        <v>1.0006614223848649</v>
+        <v>1.0007011607123935</v>
       </c>
     </row>
     <row r="34" spans="1:62" x14ac:dyDescent="0.3">
@@ -6789,14 +6789,14 @@
       </c>
       <c r="O35" s="4">
         <f t="shared" ref="O35:O48" si="28">P35-N35</f>
-        <v>2660</v>
+        <v>2661</v>
       </c>
       <c r="P35" s="6">
-        <v>14667</v>
+        <v>14668</v>
       </c>
       <c r="Q35" s="5">
         <f t="shared" ref="Q35:Q48" si="29">P35/M35</f>
-        <v>0.99552026063938093</v>
+        <v>0.99558813547817826</v>
       </c>
       <c r="R35" s="7">
         <v>12053</v>
@@ -6806,14 +6806,14 @@
       </c>
       <c r="T35" s="4">
         <f t="shared" ref="T35:T48" si="30">U35-S35</f>
-        <v>2254</v>
+        <v>2255</v>
       </c>
       <c r="U35" s="13">
-        <v>11975</v>
+        <v>11976</v>
       </c>
       <c r="V35" s="5">
         <f t="shared" ref="V35:V48" si="31">U35/R35</f>
-        <v>0.9935285820957438</v>
+        <v>0.99361154899195225</v>
       </c>
       <c r="W35" s="7">
         <v>12107</v>
@@ -6823,14 +6823,14 @@
       </c>
       <c r="Y35" s="4">
         <f t="shared" ref="Y35:Y48" si="32">Z35-X35</f>
-        <v>2124</v>
+        <v>2125</v>
       </c>
       <c r="Z35" s="13">
-        <v>11985</v>
+        <v>11986</v>
       </c>
       <c r="AA35" s="5">
         <f t="shared" ref="AA35:AA48" si="33">Z35/W35</f>
-        <v>0.98992318493433551</v>
+        <v>0.99000578177913601</v>
       </c>
       <c r="AB35" s="7">
         <v>14785</v>
@@ -6840,14 +6840,14 @@
       </c>
       <c r="AD35" s="4">
         <f t="shared" ref="AD35:AD48" si="34">AE35-AC35</f>
-        <v>2893</v>
+        <v>2895</v>
       </c>
       <c r="AE35" s="6">
-        <v>14691</v>
+        <v>14693</v>
       </c>
       <c r="AF35" s="5">
         <f t="shared" ref="AF35:AF48" si="35">AE35/AB35</f>
-        <v>0.9936422049374366</v>
+        <v>0.99377747717281029</v>
       </c>
       <c r="AG35" s="7">
         <v>12076</v>
@@ -6857,14 +6857,14 @@
       </c>
       <c r="AI35" s="4">
         <f t="shared" si="12"/>
-        <v>2328</v>
+        <v>2330</v>
       </c>
       <c r="AJ35" s="6">
-        <v>12037</v>
+        <v>12039</v>
       </c>
       <c r="AK35" s="5">
         <f t="shared" ref="AK35:AK47" si="36">AJ35/AG35</f>
-        <v>0.99677045379264662</v>
+        <v>0.99693607154686981</v>
       </c>
       <c r="AL35" s="7">
         <v>12179</v>
@@ -6874,14 +6874,14 @@
       </c>
       <c r="AN35" s="4">
         <f t="shared" ref="AN35:AN48" si="37">AO35-AM35</f>
-        <v>1976</v>
+        <v>1978</v>
       </c>
       <c r="AO35" s="6">
-        <v>12093</v>
+        <v>12095</v>
       </c>
       <c r="AP35" s="5">
         <f t="shared" ref="AP35:AP48" si="38">AO35/AL35</f>
-        <v>0.9929386649150177</v>
+        <v>0.99310288201001728</v>
       </c>
       <c r="AQ35" s="7">
         <v>14849</v>
@@ -6891,14 +6891,14 @@
       </c>
       <c r="AS35" s="4">
         <f t="shared" ref="AS35:AS48" si="39">AT35-AR35</f>
-        <v>2358</v>
+        <v>2361</v>
       </c>
       <c r="AT35" s="6">
-        <v>14837</v>
+        <v>14840</v>
       </c>
       <c r="AU35" s="5">
         <f t="shared" ref="AU35:AU48" si="40">AT35/AQ35</f>
-        <v>0.99919186477203847</v>
+        <v>0.99939389857902894</v>
       </c>
       <c r="AV35" s="7">
         <v>12178</v>
@@ -6908,14 +6908,14 @@
       </c>
       <c r="AX35" s="4">
         <f t="shared" ref="AX35:AX48" si="41">AY35-AW35</f>
-        <v>2077</v>
+        <v>2079</v>
       </c>
       <c r="AY35" s="6">
-        <v>12196</v>
+        <v>12198</v>
       </c>
       <c r="AZ35" s="5">
         <f t="shared" ref="AZ35:AZ48" si="42">AY35/AV35</f>
-        <v>1.0014780752176056</v>
+        <v>1.0016423057973394</v>
       </c>
       <c r="BA35" s="7">
         <v>12308</v>
@@ -6925,14 +6925,14 @@
       </c>
       <c r="BC35" s="4">
         <f t="shared" ref="BC35:BC48" si="43">BD35-BB35</f>
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="BD35" s="6">
-        <v>12248</v>
+        <v>12250</v>
       </c>
       <c r="BE35" s="5">
         <f t="shared" ref="BE35:BE48" si="44">BD35/BA35</f>
-        <v>0.99512512187195323</v>
+        <v>0.99528761780955477</v>
       </c>
       <c r="BF35" s="7">
         <v>15013</v>
@@ -6942,14 +6942,14 @@
       </c>
       <c r="BH35" s="4">
         <f t="shared" ref="BH35:BH48" si="45">BI35-BG35</f>
-        <v>3321</v>
+        <v>3323</v>
       </c>
       <c r="BI35" s="6">
-        <v>14961</v>
+        <v>14963</v>
       </c>
       <c r="BJ35" s="5">
         <f t="shared" ref="BJ35:BJ48" si="46">BI35/BF35</f>
-        <v>0.99653633517618068</v>
+        <v>0.99666955305401983</v>
       </c>
     </row>
     <row r="36" spans="1:62" x14ac:dyDescent="0.3">
@@ -6967,14 +6967,14 @@
       </c>
       <c r="E36" s="4">
         <f t="shared" si="24"/>
-        <v>186764</v>
+        <v>186795</v>
       </c>
       <c r="F36" s="13">
-        <v>888448</v>
+        <v>888479</v>
       </c>
       <c r="G36" s="5">
         <f t="shared" si="25"/>
-        <v>0.99282353861454742</v>
+        <v>0.99285818051784058</v>
       </c>
       <c r="H36" s="7">
         <v>910737</v>
@@ -6984,14 +6984,14 @@
       </c>
       <c r="J36" s="4">
         <f t="shared" si="26"/>
-        <v>161929</v>
+        <v>161960</v>
       </c>
       <c r="K36" s="13">
-        <v>898726</v>
+        <v>898757</v>
       </c>
       <c r="L36" s="5">
         <f t="shared" si="27"/>
-        <v>0.9868117799101167</v>
+        <v>0.98684581827684614</v>
       </c>
       <c r="M36" s="7">
         <v>1579599</v>
@@ -7001,14 +7001,14 @@
       </c>
       <c r="O36" s="4">
         <f t="shared" si="28"/>
-        <v>319515</v>
+        <v>319579</v>
       </c>
       <c r="P36" s="6">
-        <v>1568341</v>
+        <v>1568405</v>
       </c>
       <c r="Q36" s="5">
         <f t="shared" si="29"/>
-        <v>0.9928728746979455</v>
+        <v>0.99291339131007295</v>
       </c>
       <c r="R36" s="7">
         <v>901122</v>
@@ -7018,14 +7018,14 @@
       </c>
       <c r="T36" s="4">
         <f t="shared" si="30"/>
-        <v>174440</v>
+        <v>174478</v>
       </c>
       <c r="U36" s="13">
-        <v>898736</v>
+        <v>898774</v>
       </c>
       <c r="V36" s="5">
         <f t="shared" si="31"/>
-        <v>0.99735218982557305</v>
+        <v>0.99739435947629729</v>
       </c>
       <c r="W36" s="7">
         <v>923866</v>
@@ -7035,14 +7035,14 @@
       </c>
       <c r="Y36" s="4">
         <f t="shared" si="32"/>
-        <v>178475</v>
+        <v>178520</v>
       </c>
       <c r="Z36" s="13">
-        <v>907704</v>
+        <v>907749</v>
       </c>
       <c r="AA36" s="5">
         <f t="shared" si="33"/>
-        <v>0.98250612101755019</v>
+        <v>0.98255482938001837</v>
       </c>
       <c r="AB36" s="7">
         <v>1592928</v>
@@ -7052,14 +7052,14 @@
       </c>
       <c r="AD36" s="4">
         <f t="shared" si="34"/>
-        <v>337161</v>
+        <v>337248</v>
       </c>
       <c r="AE36" s="6">
-        <v>1585450</v>
+        <v>1585537</v>
       </c>
       <c r="AF36" s="5">
         <f t="shared" si="35"/>
-        <v>0.99530550031137632</v>
+        <v>0.9953601167158842</v>
       </c>
       <c r="AG36" s="7">
         <v>914936</v>
@@ -7069,14 +7069,14 @@
       </c>
       <c r="AI36" s="4">
         <f t="shared" si="12"/>
-        <v>305689</v>
+        <v>305742</v>
       </c>
       <c r="AJ36" s="6">
-        <v>912915</v>
+        <v>912968</v>
       </c>
       <c r="AK36" s="5">
         <f t="shared" si="36"/>
-        <v>0.9977911023284689</v>
+        <v>0.99784902987749968</v>
       </c>
       <c r="AL36" s="7">
         <v>934551</v>
@@ -7086,14 +7086,14 @@
       </c>
       <c r="AN36" s="4">
         <f t="shared" si="37"/>
-        <v>162878</v>
+        <v>162939</v>
       </c>
       <c r="AO36" s="6">
-        <v>923022</v>
+        <v>923083</v>
       </c>
       <c r="AP36" s="5">
         <f t="shared" si="38"/>
-        <v>0.98766359460318376</v>
+        <v>0.98772886658941028</v>
       </c>
       <c r="AQ36" s="7">
         <v>1610673</v>
@@ -7103,14 +7103,14 @@
       </c>
       <c r="AS36" s="4">
         <f t="shared" si="39"/>
-        <v>274862</v>
+        <v>274982</v>
       </c>
       <c r="AT36" s="6">
-        <v>1610082</v>
+        <v>1610202</v>
       </c>
       <c r="AU36" s="5">
         <f t="shared" si="40"/>
-        <v>0.99963307263485512</v>
+        <v>0.9997075756531586</v>
       </c>
       <c r="AV36" s="7">
         <v>933166</v>
@@ -7120,14 +7120,14 @@
       </c>
       <c r="AX36" s="4">
         <f t="shared" si="41"/>
-        <v>163441</v>
+        <v>163511</v>
       </c>
       <c r="AY36" s="6">
-        <v>934767</v>
+        <v>934837</v>
       </c>
       <c r="AZ36" s="5">
         <f t="shared" si="42"/>
-        <v>1.0017156647370351</v>
+        <v>1.0017906781858748</v>
       </c>
       <c r="BA36" s="7">
         <v>952259</v>
@@ -7137,14 +7137,14 @@
       </c>
       <c r="BC36" s="4">
         <f t="shared" si="43"/>
-        <v>160575</v>
+        <v>160663</v>
       </c>
       <c r="BD36" s="6">
-        <v>945546</v>
+        <v>945634</v>
       </c>
       <c r="BE36" s="5">
         <f t="shared" si="44"/>
-        <v>0.99295044730477733</v>
+        <v>0.99304285913811263</v>
       </c>
       <c r="BF36" s="7">
         <v>1640364</v>
@@ -7154,14 +7154,14 @@
       </c>
       <c r="BH36" s="4">
         <f t="shared" si="45"/>
-        <v>394220</v>
+        <v>394456</v>
       </c>
       <c r="BI36" s="6">
-        <v>1638375</v>
+        <v>1638611</v>
       </c>
       <c r="BJ36" s="5">
         <f t="shared" si="46"/>
-        <v>0.99878746424574061</v>
+        <v>0.99893133475253049</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -7179,14 +7179,14 @@
       </c>
       <c r="E37" s="4">
         <f t="shared" si="24"/>
-        <v>134706</v>
+        <v>134736</v>
       </c>
       <c r="F37" s="13">
-        <v>700843</v>
+        <v>700873</v>
       </c>
       <c r="G37" s="5">
         <f t="shared" si="25"/>
-        <v>0.98738929886699522</v>
+        <v>0.98743156465115234</v>
       </c>
       <c r="H37" s="7">
         <v>717455</v>
@@ -7196,14 +7196,14 @@
       </c>
       <c r="J37" s="4">
         <f t="shared" si="26"/>
-        <v>120933</v>
+        <v>120969</v>
       </c>
       <c r="K37" s="13">
-        <v>706528</v>
+        <v>706564</v>
       </c>
       <c r="L37" s="5">
         <f t="shared" si="27"/>
-        <v>0.98476977650166209</v>
+        <v>0.98481995386470234</v>
       </c>
       <c r="M37" s="7">
         <v>885615</v>
@@ -7213,14 +7213,14 @@
       </c>
       <c r="O37" s="4">
         <f t="shared" si="28"/>
-        <v>157018</v>
+        <v>157063</v>
       </c>
       <c r="P37" s="6">
-        <v>877717</v>
+        <v>877762</v>
       </c>
       <c r="Q37" s="5">
         <f t="shared" si="29"/>
-        <v>0.99108190353596093</v>
+        <v>0.99113271568345163</v>
       </c>
       <c r="R37" s="7">
         <v>713906</v>
@@ -7230,14 +7230,14 @@
       </c>
       <c r="T37" s="4">
         <f t="shared" si="30"/>
-        <v>125302</v>
+        <v>125339</v>
       </c>
       <c r="U37" s="13">
-        <v>707610</v>
+        <v>707647</v>
       </c>
       <c r="V37" s="5">
         <f t="shared" si="31"/>
-        <v>0.9911809117726984</v>
+        <v>0.99123273932422473</v>
       </c>
       <c r="W37" s="7">
         <v>721933</v>
@@ -7247,14 +7247,14 @@
       </c>
       <c r="Y37" s="4">
         <f t="shared" si="32"/>
-        <v>128627</v>
+        <v>128666</v>
       </c>
       <c r="Z37" s="13">
-        <v>709250</v>
+        <v>709289</v>
       </c>
       <c r="AA37" s="5">
         <f t="shared" si="33"/>
-        <v>0.98243188772365297</v>
+        <v>0.98248590935723956</v>
       </c>
       <c r="AB37" s="7">
         <v>896229</v>
@@ -7264,14 +7264,14 @@
       </c>
       <c r="AD37" s="4">
         <f t="shared" si="34"/>
-        <v>180357</v>
+        <v>180416</v>
       </c>
       <c r="AE37" s="6">
-        <v>883145</v>
+        <v>883204</v>
       </c>
       <c r="AF37" s="5">
         <f t="shared" si="35"/>
-        <v>0.98540105263275346</v>
+        <v>0.98546688402182925</v>
       </c>
       <c r="AG37" s="7">
         <v>721282</v>
@@ -7281,14 +7281,14 @@
       </c>
       <c r="AI37" s="4">
         <f t="shared" si="12"/>
-        <v>136324</v>
+        <v>136372</v>
       </c>
       <c r="AJ37" s="6">
-        <v>711880</v>
+        <v>711928</v>
       </c>
       <c r="AK37" s="5">
         <f t="shared" si="36"/>
-        <v>0.98696487642835951</v>
+        <v>0.98703142460230531</v>
       </c>
       <c r="AL37" s="7">
         <v>727480</v>
@@ -7298,14 +7298,14 @@
       </c>
       <c r="AN37" s="4">
         <f t="shared" si="37"/>
-        <v>121832</v>
+        <v>121886</v>
       </c>
       <c r="AO37" s="6">
-        <v>717579</v>
+        <v>717633</v>
       </c>
       <c r="AP37" s="5">
         <f t="shared" si="38"/>
-        <v>0.98639000384890307</v>
+        <v>0.98646423269368233</v>
       </c>
       <c r="AQ37" s="7">
         <v>903787</v>
@@ -7315,14 +7315,14 @@
       </c>
       <c r="AS37" s="4">
         <f t="shared" si="39"/>
-        <v>145110</v>
+        <v>145201</v>
       </c>
       <c r="AT37" s="6">
-        <v>895529</v>
+        <v>895620</v>
       </c>
       <c r="AU37" s="5">
         <f t="shared" si="40"/>
-        <v>0.99086289136710304</v>
+        <v>0.99096357880783859</v>
       </c>
       <c r="AV37" s="7">
         <v>732294</v>
@@ -7332,14 +7332,14 @@
       </c>
       <c r="AX37" s="4">
         <f t="shared" si="41"/>
-        <v>125915</v>
+        <v>125995</v>
       </c>
       <c r="AY37" s="6">
-        <v>726125</v>
+        <v>726205</v>
       </c>
       <c r="AZ37" s="5">
         <f t="shared" si="42"/>
-        <v>0.99157578786662193</v>
+        <v>0.99168503360672078</v>
       </c>
       <c r="BA37" s="7">
         <v>740889</v>
@@ -7349,14 +7349,14 @@
       </c>
       <c r="BC37" s="4">
         <f t="shared" si="43"/>
-        <v>122787</v>
+        <v>122882</v>
       </c>
       <c r="BD37" s="6">
-        <v>730946</v>
+        <v>731041</v>
       </c>
       <c r="BE37" s="5">
         <f t="shared" si="44"/>
-        <v>0.98657963608583743</v>
+        <v>0.98670786042173664</v>
       </c>
       <c r="BF37" s="7">
         <v>918028</v>
@@ -7366,14 +7366,14 @@
       </c>
       <c r="BH37" s="4">
         <f t="shared" si="45"/>
-        <v>217044</v>
+        <v>217233</v>
       </c>
       <c r="BI37" s="6">
-        <v>908070</v>
+        <v>908259</v>
       </c>
       <c r="BJ37" s="5">
         <f t="shared" si="46"/>
-        <v>0.98915283629693207</v>
+        <v>0.98935871237042883</v>
       </c>
     </row>
     <row r="38" spans="1:62" x14ac:dyDescent="0.3">
@@ -7391,14 +7391,14 @@
       </c>
       <c r="E38" s="4">
         <f t="shared" si="24"/>
-        <v>6146</v>
+        <v>6148</v>
       </c>
       <c r="F38" s="13">
-        <v>24502</v>
+        <v>24504</v>
       </c>
       <c r="G38" s="5">
         <f t="shared" si="25"/>
-        <v>1.0060357216177376</v>
+        <v>1.0061178402792035</v>
       </c>
       <c r="H38" s="7">
         <v>24747</v>
@@ -7408,14 +7408,14 @@
       </c>
       <c r="J38" s="4">
         <f t="shared" si="26"/>
-        <v>5628</v>
+        <v>5630</v>
       </c>
       <c r="K38" s="13">
-        <v>24725</v>
+        <v>24727</v>
       </c>
       <c r="L38" s="5">
         <f t="shared" si="27"/>
-        <v>0.99911100335394187</v>
+        <v>0.99919182123085626</v>
       </c>
       <c r="M38" s="7">
         <v>37604</v>
@@ -7425,14 +7425,14 @@
       </c>
       <c r="O38" s="4">
         <f t="shared" si="28"/>
-        <v>8983</v>
+        <v>8987</v>
       </c>
       <c r="P38" s="6">
-        <v>37772</v>
+        <v>37776</v>
       </c>
       <c r="Q38" s="5">
         <f t="shared" si="29"/>
-        <v>1.0044676098287417</v>
+        <v>1.0045739814913308</v>
       </c>
       <c r="R38" s="7">
         <v>24596</v>
@@ -7442,14 +7442,14 @@
       </c>
       <c r="T38" s="4">
         <f t="shared" si="30"/>
-        <v>5844</v>
+        <v>5847</v>
       </c>
       <c r="U38" s="13">
-        <v>24822</v>
+        <v>24825</v>
       </c>
       <c r="V38" s="5">
         <f t="shared" si="31"/>
-        <v>1.0091884859326721</v>
+        <v>1.0093104569848756</v>
       </c>
       <c r="W38" s="7">
         <v>25148</v>
@@ -7459,14 +7459,14 @@
       </c>
       <c r="Y38" s="4">
         <f t="shared" si="32"/>
-        <v>6052</v>
+        <v>6055</v>
       </c>
       <c r="Z38" s="13">
-        <v>25004</v>
+        <v>25007</v>
       </c>
       <c r="AA38" s="5">
         <f t="shared" si="33"/>
-        <v>0.99427389852075709</v>
+        <v>0.99439319230157464</v>
       </c>
       <c r="AB38" s="7">
         <v>38035</v>
@@ -7476,14 +7476,14 @@
       </c>
       <c r="AD38" s="4">
         <f t="shared" si="34"/>
-        <v>9595</v>
+        <v>9597</v>
       </c>
       <c r="AE38" s="6">
-        <v>38183</v>
+        <v>38185</v>
       </c>
       <c r="AF38" s="5">
         <f t="shared" si="35"/>
-        <v>1.0038911528855001</v>
+        <v>1.0039437360326016</v>
       </c>
       <c r="AG38" s="7">
         <v>24962</v>
@@ -7493,14 +7493,14 @@
       </c>
       <c r="AI38" s="4">
         <f t="shared" si="12"/>
-        <v>6302</v>
+        <v>6305</v>
       </c>
       <c r="AJ38" s="6">
-        <v>25215</v>
+        <v>25218</v>
       </c>
       <c r="AK38" s="5">
         <f t="shared" si="36"/>
-        <v>1.0101354058168417</v>
+        <v>1.0102555884945117</v>
       </c>
       <c r="AL38" s="7">
         <v>25436</v>
@@ -7510,14 +7510,14 @@
       </c>
       <c r="AN38" s="4">
         <f t="shared" si="37"/>
-        <v>5895</v>
+        <v>5898</v>
       </c>
       <c r="AO38" s="6">
-        <v>25475</v>
+        <v>25478</v>
       </c>
       <c r="AP38" s="5">
         <f t="shared" si="38"/>
-        <v>1.0015332599465325</v>
+        <v>1.0016512030193427</v>
       </c>
       <c r="AQ38" s="7">
         <v>38569</v>
@@ -7527,14 +7527,14 @@
       </c>
       <c r="AS38" s="4">
         <f t="shared" si="39"/>
-        <v>8150</v>
+        <v>8153</v>
       </c>
       <c r="AT38" s="6">
-        <v>38886</v>
+        <v>38889</v>
       </c>
       <c r="AU38" s="5">
         <f t="shared" si="40"/>
-        <v>1.0082190360133787</v>
+        <v>1.0082968186885841</v>
       </c>
       <c r="AV38" s="7">
         <v>25488</v>
@@ -7544,14 +7544,14 @@
       </c>
       <c r="AX38" s="4">
         <f t="shared" si="41"/>
-        <v>5633</v>
+        <v>5635</v>
       </c>
       <c r="AY38" s="6">
-        <v>25688</v>
+        <v>25690</v>
       </c>
       <c r="AZ38" s="5">
         <f t="shared" si="42"/>
-        <v>1.0078468298807282</v>
+        <v>1.0079252981795355</v>
       </c>
       <c r="BA38" s="7">
         <v>25933</v>
@@ -7561,14 +7561,14 @@
       </c>
       <c r="BC38" s="4">
         <f t="shared" si="43"/>
-        <v>5607</v>
+        <v>5611</v>
       </c>
       <c r="BD38" s="6">
-        <v>25955</v>
+        <v>25959</v>
       </c>
       <c r="BE38" s="5">
         <f t="shared" si="44"/>
-        <v>1.0008483399529557</v>
+        <v>1.0010025835807659</v>
       </c>
       <c r="BF38" s="7">
         <v>39379</v>
@@ -7578,14 +7578,14 @@
       </c>
       <c r="BH38" s="4">
         <f t="shared" si="45"/>
-        <v>11606</v>
+        <v>11614</v>
       </c>
       <c r="BI38" s="6">
-        <v>39509</v>
+        <v>39517</v>
       </c>
       <c r="BJ38" s="5">
         <f t="shared" si="46"/>
-        <v>1.0033012519363111</v>
+        <v>1.0035044059016227</v>
       </c>
     </row>
     <row r="39" spans="1:62" x14ac:dyDescent="0.3">
@@ -7815,14 +7815,14 @@
       </c>
       <c r="E40" s="4">
         <f t="shared" si="24"/>
-        <v>64433</v>
+        <v>64449</v>
       </c>
       <c r="F40" s="13">
-        <v>289162</v>
+        <v>289178</v>
       </c>
       <c r="G40" s="5">
         <f t="shared" si="25"/>
-        <v>0.99045720470768772</v>
+        <v>0.99051200898790193</v>
       </c>
       <c r="H40" s="7">
         <v>293812</v>
@@ -7832,14 +7832,14 @@
       </c>
       <c r="J40" s="4">
         <f t="shared" si="26"/>
-        <v>59744</v>
+        <v>59761</v>
       </c>
       <c r="K40" s="13">
-        <v>290777</v>
+        <v>290794</v>
       </c>
       <c r="L40" s="5">
         <f t="shared" si="27"/>
-        <v>0.98967026533974101</v>
+        <v>0.98972812546798639</v>
       </c>
       <c r="M40" s="7">
         <v>351809</v>
@@ -7849,14 +7849,14 @@
       </c>
       <c r="O40" s="4">
         <f t="shared" si="28"/>
-        <v>72140</v>
+        <v>72160</v>
       </c>
       <c r="P40" s="6">
-        <v>349178</v>
+        <v>349198</v>
       </c>
       <c r="Q40" s="5">
         <f t="shared" si="29"/>
-        <v>0.99252151025130109</v>
+        <v>0.99257835928017757</v>
       </c>
       <c r="R40" s="7">
         <v>293831</v>
@@ -7866,14 +7866,14 @@
       </c>
       <c r="T40" s="4">
         <f t="shared" si="30"/>
-        <v>63216</v>
+        <v>63237</v>
       </c>
       <c r="U40" s="13">
-        <v>292824</v>
+        <v>292845</v>
       </c>
       <c r="V40" s="5">
         <f t="shared" si="31"/>
-        <v>0.99657285990926758</v>
+        <v>0.99664432956359272</v>
       </c>
       <c r="W40" s="7">
         <v>297227</v>
@@ -7883,14 +7883,14 @@
       </c>
       <c r="Y40" s="4">
         <f t="shared" si="32"/>
-        <v>66677</v>
+        <v>66703</v>
       </c>
       <c r="Z40" s="13">
-        <v>294222</v>
+        <v>294248</v>
       </c>
       <c r="AA40" s="5">
         <f t="shared" si="33"/>
-        <v>0.98988988214395057</v>
+        <v>0.98997735737332071</v>
       </c>
       <c r="AB40" s="7">
         <v>355500</v>
@@ -7900,14 +7900,14 @@
       </c>
       <c r="AD40" s="4">
         <f t="shared" si="34"/>
-        <v>82217</v>
+        <v>82253</v>
       </c>
       <c r="AE40" s="6">
-        <v>352768</v>
+        <v>352804</v>
       </c>
       <c r="AF40" s="5">
         <f t="shared" si="35"/>
-        <v>0.99231504922644165</v>
+        <v>0.99241631504922645</v>
       </c>
       <c r="AG40" s="7">
         <v>298328</v>
@@ -7917,14 +7917,14 @@
       </c>
       <c r="AI40" s="4">
         <f t="shared" si="12"/>
-        <v>79464</v>
+        <v>79497</v>
       </c>
       <c r="AJ40" s="6">
-        <v>295936</v>
+        <v>295969</v>
       </c>
       <c r="AK40" s="5">
         <f t="shared" si="36"/>
-        <v>0.99198197956611511</v>
+        <v>0.99209259606875655</v>
       </c>
       <c r="AL40" s="7">
         <v>299711</v>
@@ -7934,14 +7934,14 @@
       </c>
       <c r="AN40" s="4">
         <f t="shared" si="37"/>
-        <v>69523</v>
+        <v>69557</v>
       </c>
       <c r="AO40" s="6">
-        <v>297154</v>
+        <v>297188</v>
       </c>
       <c r="AP40" s="5">
         <f t="shared" si="38"/>
-        <v>0.99146844793818045</v>
+        <v>0.99158189055456758</v>
       </c>
       <c r="AQ40" s="7">
         <v>357015</v>
@@ -7951,14 +7951,14 @@
       </c>
       <c r="AS40" s="4">
         <f t="shared" si="39"/>
-        <v>76915</v>
+        <v>76968</v>
       </c>
       <c r="AT40" s="6">
-        <v>355112</v>
+        <v>355165</v>
       </c>
       <c r="AU40" s="5">
         <f t="shared" si="40"/>
-        <v>0.99466969174964637</v>
+        <v>0.99481814489587272</v>
       </c>
       <c r="AV40" s="7">
         <v>300800</v>
@@ -7968,14 +7968,14 @@
       </c>
       <c r="AX40" s="4">
         <f t="shared" si="41"/>
-        <v>66620</v>
+        <v>66666</v>
       </c>
       <c r="AY40" s="6">
-        <v>299320</v>
+        <v>299366</v>
       </c>
       <c r="AZ40" s="5">
         <f t="shared" si="42"/>
-        <v>0.99507978723404256</v>
+        <v>0.99523271276595748</v>
       </c>
       <c r="BA40" s="7">
         <v>303731</v>
@@ -7985,14 +7985,14 @@
       </c>
       <c r="BC40" s="4">
         <f t="shared" si="43"/>
-        <v>65416</v>
+        <v>65462</v>
       </c>
       <c r="BD40" s="6">
-        <v>300653</v>
+        <v>300699</v>
       </c>
       <c r="BE40" s="5">
         <f t="shared" si="44"/>
-        <v>0.98986603277242036</v>
+        <v>0.99001748257504174</v>
       </c>
       <c r="BF40" s="7">
         <v>361393</v>
@@ -8002,14 +8002,14 @@
       </c>
       <c r="BH40" s="4">
         <f t="shared" si="45"/>
-        <v>110588</v>
+        <v>110665</v>
       </c>
       <c r="BI40" s="6">
-        <v>358395</v>
+        <v>358472</v>
       </c>
       <c r="BJ40" s="5">
         <f t="shared" si="46"/>
-        <v>0.99170432188780633</v>
+        <v>0.99191738633565119</v>
       </c>
     </row>
     <row r="41" spans="1:62" x14ac:dyDescent="0.3">
@@ -8027,14 +8027,14 @@
       </c>
       <c r="E41" s="4">
         <f t="shared" si="24"/>
-        <v>153018</v>
+        <v>153060</v>
       </c>
       <c r="F41" s="13">
-        <v>944343</v>
+        <v>944385</v>
       </c>
       <c r="G41" s="5">
         <f t="shared" si="25"/>
-        <v>0.99153199049147001</v>
+        <v>0.99157608923906559</v>
       </c>
       <c r="H41" s="7">
         <v>959446</v>
@@ -8044,14 +8044,14 @@
       </c>
       <c r="J41" s="4">
         <f t="shared" si="26"/>
-        <v>141479</v>
+        <v>141525</v>
       </c>
       <c r="K41" s="13">
-        <v>948013</v>
+        <v>948059</v>
       </c>
       <c r="L41" s="5">
         <f t="shared" si="27"/>
-        <v>0.98808374832976531</v>
+        <v>0.98813169266430834</v>
       </c>
       <c r="M41" s="7">
         <v>1062442</v>
@@ -8061,14 +8061,14 @@
       </c>
       <c r="O41" s="4">
         <f t="shared" si="28"/>
-        <v>158406</v>
+        <v>158461</v>
       </c>
       <c r="P41" s="6">
-        <v>1051887</v>
+        <v>1051942</v>
       </c>
       <c r="Q41" s="5">
         <f t="shared" si="29"/>
-        <v>0.99006534003738556</v>
+        <v>0.99011710756916615</v>
       </c>
       <c r="R41" s="7">
         <v>959218</v>
@@ -8078,14 +8078,14 @@
       </c>
       <c r="T41" s="4">
         <f t="shared" si="30"/>
-        <v>144626</v>
+        <v>144675</v>
       </c>
       <c r="U41" s="13">
-        <v>951516</v>
+        <v>951565</v>
       </c>
       <c r="V41" s="5">
         <f t="shared" si="31"/>
-        <v>0.99197054267121765</v>
+        <v>0.9920216259494713</v>
       </c>
       <c r="W41" s="7">
         <v>961845</v>
@@ -8095,14 +8095,14 @@
       </c>
       <c r="Y41" s="4">
         <f t="shared" si="32"/>
-        <v>150882</v>
+        <v>150947</v>
       </c>
       <c r="Z41" s="13">
-        <v>950489</v>
+        <v>950554</v>
       </c>
       <c r="AA41" s="5">
         <f t="shared" si="33"/>
-        <v>0.98819352390457926</v>
+        <v>0.98826110236056741</v>
       </c>
       <c r="AB41" s="7">
         <v>1065577</v>
@@ -8112,14 +8112,14 @@
       </c>
       <c r="AD41" s="4">
         <f t="shared" si="34"/>
-        <v>183799</v>
+        <v>183873</v>
       </c>
       <c r="AE41" s="6">
-        <v>1055094</v>
+        <v>1055168</v>
       </c>
       <c r="AF41" s="5">
         <f t="shared" si="35"/>
-        <v>0.99016213750859861</v>
+        <v>0.99023158345197015</v>
       </c>
       <c r="AG41" s="7">
         <v>963364</v>
@@ -8129,14 +8129,14 @@
       </c>
       <c r="AI41" s="4">
         <f t="shared" si="12"/>
-        <v>171136</v>
+        <v>171202</v>
       </c>
       <c r="AJ41" s="6">
-        <v>956479</v>
+        <v>956545</v>
       </c>
       <c r="AK41" s="5">
         <f t="shared" si="36"/>
-        <v>0.99285316868805562</v>
+        <v>0.99292167861784331</v>
       </c>
       <c r="AL41" s="7">
         <v>968650</v>
@@ -8146,14 +8146,14 @@
       </c>
       <c r="AN41" s="4">
         <f t="shared" si="37"/>
-        <v>149726</v>
+        <v>149810</v>
       </c>
       <c r="AO41" s="6">
-        <v>958959</v>
+        <v>959043</v>
       </c>
       <c r="AP41" s="5">
         <f t="shared" si="38"/>
-        <v>0.98999535435915964</v>
+        <v>0.99008207298817941</v>
       </c>
       <c r="AQ41" s="7">
         <v>1071657</v>
@@ -8163,14 +8163,14 @@
       </c>
       <c r="AS41" s="4">
         <f t="shared" si="39"/>
-        <v>156935</v>
+        <v>157037</v>
       </c>
       <c r="AT41" s="6">
-        <v>1063340</v>
+        <v>1063442</v>
       </c>
       <c r="AU41" s="5">
         <f t="shared" si="40"/>
-        <v>0.99223912128600844</v>
+        <v>0.9923343009936948</v>
       </c>
       <c r="AV41" s="7">
         <v>970535</v>
@@ -8180,14 +8180,14 @@
       </c>
       <c r="AX41" s="4">
         <f t="shared" si="41"/>
-        <v>144899</v>
+        <v>145001</v>
       </c>
       <c r="AY41" s="6">
-        <v>964508</v>
+        <v>964610</v>
       </c>
       <c r="AZ41" s="5">
         <f t="shared" si="42"/>
-        <v>0.99379002302853581</v>
+        <v>0.99389511970202005</v>
       </c>
       <c r="BA41" s="7">
         <v>973311</v>
@@ -8197,14 +8197,14 @@
       </c>
       <c r="BC41" s="4">
         <f t="shared" si="43"/>
-        <v>140613</v>
+        <v>140726</v>
       </c>
       <c r="BD41" s="6">
-        <v>969185</v>
+        <v>969298</v>
       </c>
       <c r="BE41" s="5">
         <f t="shared" si="44"/>
-        <v>0.9957608616362088</v>
+        <v>0.99587696019052496</v>
       </c>
       <c r="BF41" s="7">
         <v>1078355</v>
@@ -8214,14 +8214,14 @@
       </c>
       <c r="BH41" s="4">
         <f t="shared" si="45"/>
-        <v>223235</v>
+        <v>223372</v>
       </c>
       <c r="BI41" s="6">
-        <v>1074062</v>
+        <v>1074199</v>
       </c>
       <c r="BJ41" s="5">
         <f t="shared" si="46"/>
-        <v>0.99601893625012172</v>
+        <v>0.99614598161087953</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.3">
@@ -8239,14 +8239,14 @@
       </c>
       <c r="E42" s="4">
         <f t="shared" si="24"/>
-        <v>3960</v>
+        <v>3962</v>
       </c>
       <c r="F42" s="13">
-        <v>18766</v>
+        <v>18768</v>
       </c>
       <c r="G42" s="5">
         <f t="shared" si="25"/>
-        <v>0.98695697906805513</v>
+        <v>0.98706216472073205</v>
       </c>
       <c r="H42" s="7">
         <v>19101</v>
@@ -8256,14 +8256,14 @@
       </c>
       <c r="J42" s="4">
         <f t="shared" si="26"/>
-        <v>3746</v>
+        <v>3749</v>
       </c>
       <c r="K42" s="13">
-        <v>18918</v>
+        <v>18921</v>
       </c>
       <c r="L42" s="5">
         <f t="shared" si="27"/>
-        <v>0.9904193497722632</v>
+        <v>0.99057640961206217</v>
       </c>
       <c r="M42" s="7">
         <v>21195</v>
@@ -8273,14 +8273,14 @@
       </c>
       <c r="O42" s="4">
         <f t="shared" si="28"/>
-        <v>4117</v>
+        <v>4119</v>
       </c>
       <c r="P42" s="6">
-        <v>20994</v>
+        <v>20996</v>
       </c>
       <c r="Q42" s="5">
         <f t="shared" si="29"/>
-        <v>0.99051663128096246</v>
+        <v>0.99061099315876389</v>
       </c>
       <c r="R42" s="7">
         <v>19210</v>
@@ -8290,14 +8290,14 @@
       </c>
       <c r="T42" s="4">
         <f t="shared" si="30"/>
-        <v>3886</v>
+        <v>3888</v>
       </c>
       <c r="U42" s="13">
-        <v>19069</v>
+        <v>19071</v>
       </c>
       <c r="V42" s="5">
         <f t="shared" si="31"/>
-        <v>0.99266007287870905</v>
+        <v>0.99276418532014576</v>
       </c>
       <c r="W42" s="7">
         <v>19384</v>
@@ -8307,14 +8307,14 @@
       </c>
       <c r="Y42" s="4">
         <f t="shared" si="32"/>
-        <v>4053</v>
+        <v>4056</v>
       </c>
       <c r="Z42" s="13">
-        <v>19078</v>
+        <v>19081</v>
       </c>
       <c r="AA42" s="5">
         <f t="shared" si="33"/>
-        <v>0.9842137845645893</v>
+        <v>0.98436855138258361</v>
       </c>
       <c r="AB42" s="7">
         <v>21463</v>
@@ -8324,14 +8324,14 @@
       </c>
       <c r="AD42" s="4">
         <f t="shared" si="34"/>
-        <v>4685</v>
+        <v>4688</v>
       </c>
       <c r="AE42" s="6">
-        <v>21152</v>
+        <v>21155</v>
       </c>
       <c r="AF42" s="5">
         <f t="shared" si="35"/>
-        <v>0.98550994735125563</v>
+        <v>0.98564972277873553</v>
       </c>
       <c r="AG42" s="7">
         <v>19423</v>
@@ -8341,14 +8341,14 @@
       </c>
       <c r="AI42" s="4">
         <f t="shared" si="12"/>
-        <v>4567</v>
+        <v>4570</v>
       </c>
       <c r="AJ42" s="6">
-        <v>19181</v>
+        <v>19184</v>
       </c>
       <c r="AK42" s="5">
         <f t="shared" si="36"/>
-        <v>0.98754054471502861</v>
+        <v>0.98769500077228034</v>
       </c>
       <c r="AL42" s="7">
         <v>19535</v>
@@ -8358,14 +8358,14 @@
       </c>
       <c r="AN42" s="4">
         <f t="shared" si="37"/>
-        <v>4085</v>
+        <v>4088</v>
       </c>
       <c r="AO42" s="6">
-        <v>19237</v>
+        <v>19240</v>
       </c>
       <c r="AP42" s="5">
         <f t="shared" si="38"/>
-        <v>0.98474532889685185</v>
+        <v>0.98489889941131303</v>
       </c>
       <c r="AQ42" s="7">
         <v>21570</v>
@@ -8375,14 +8375,14 @@
       </c>
       <c r="AS42" s="4">
         <f t="shared" si="39"/>
-        <v>4088</v>
+        <v>4091</v>
       </c>
       <c r="AT42" s="6">
-        <v>21286</v>
+        <v>21289</v>
       </c>
       <c r="AU42" s="5">
         <f t="shared" si="40"/>
-        <v>0.98683356513676401</v>
+        <v>0.98697264719517852</v>
       </c>
       <c r="AV42" s="7">
         <v>19570</v>
@@ -8392,14 +8392,14 @@
       </c>
       <c r="AX42" s="4">
         <f t="shared" si="41"/>
-        <v>3688</v>
+        <v>3692</v>
       </c>
       <c r="AY42" s="6">
-        <v>19320</v>
+        <v>19324</v>
       </c>
       <c r="AZ42" s="5">
         <f t="shared" si="42"/>
-        <v>0.98722534491568725</v>
+        <v>0.98742973939703627</v>
       </c>
       <c r="BA42" s="7">
         <v>19671</v>
@@ -8409,14 +8409,14 @@
       </c>
       <c r="BC42" s="4">
         <f t="shared" si="43"/>
-        <v>3585</v>
+        <v>3590</v>
       </c>
       <c r="BD42" s="6">
-        <v>19421</v>
+        <v>19426</v>
       </c>
       <c r="BE42" s="5">
         <f t="shared" si="44"/>
-        <v>0.98729093589548067</v>
+        <v>0.9875451171775711</v>
       </c>
       <c r="BF42" s="7">
         <v>21792</v>
@@ -8426,14 +8426,14 @@
       </c>
       <c r="BH42" s="4">
         <f t="shared" si="45"/>
-        <v>5291</v>
+        <v>5297</v>
       </c>
       <c r="BI42" s="6">
-        <v>21588</v>
+        <v>21594</v>
       </c>
       <c r="BJ42" s="5">
         <f t="shared" si="46"/>
-        <v>0.99063876651982374</v>
+        <v>0.99091409691629961</v>
       </c>
     </row>
     <row r="43" spans="1:62" x14ac:dyDescent="0.3">
@@ -8451,14 +8451,14 @@
       </c>
       <c r="E43" s="4">
         <f t="shared" si="24"/>
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="F43" s="13">
-        <v>3671</v>
+        <v>3672</v>
       </c>
       <c r="G43" s="5">
         <f t="shared" si="25"/>
-        <v>1.0005451076587626</v>
+        <v>1.0008176614881439</v>
       </c>
       <c r="H43" s="7">
         <v>3731</v>
@@ -8468,14 +8468,14 @@
       </c>
       <c r="J43" s="4">
         <f t="shared" si="26"/>
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="K43" s="13">
-        <v>3705</v>
+        <v>3706</v>
       </c>
       <c r="L43" s="5">
         <f t="shared" si="27"/>
-        <v>0.99303135888501737</v>
+        <v>0.99329938354328595</v>
       </c>
       <c r="M43" s="7">
         <v>4602</v>
@@ -8485,14 +8485,14 @@
       </c>
       <c r="O43" s="4">
         <f t="shared" si="28"/>
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="P43" s="6">
-        <v>4591</v>
+        <v>4592</v>
       </c>
       <c r="Q43" s="5">
         <f t="shared" si="29"/>
-        <v>0.99760973489787053</v>
+        <v>0.99782703172533682</v>
       </c>
       <c r="R43" s="7">
         <v>3744</v>
@@ -8502,14 +8502,14 @@
       </c>
       <c r="T43" s="4">
         <f t="shared" si="30"/>
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="U43" s="13">
-        <v>3736</v>
+        <v>3737</v>
       </c>
       <c r="V43" s="5">
         <f t="shared" si="31"/>
-        <v>0.99786324786324787</v>
+        <v>0.99813034188034189</v>
       </c>
       <c r="W43" s="7">
         <v>3795</v>
@@ -8519,14 +8519,14 @@
       </c>
       <c r="Y43" s="4">
         <f t="shared" si="32"/>
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="Z43" s="13">
-        <v>3759</v>
+        <v>3760</v>
       </c>
       <c r="AA43" s="5">
         <f t="shared" si="33"/>
-        <v>0.99051383399209492</v>
+        <v>0.99077733860342554</v>
       </c>
       <c r="AB43" s="7">
         <v>4656</v>
@@ -8536,14 +8536,14 @@
       </c>
       <c r="AD43" s="4">
         <f t="shared" si="34"/>
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="AE43" s="6">
-        <v>4631</v>
+        <v>4632</v>
       </c>
       <c r="AF43" s="5">
         <f t="shared" si="35"/>
-        <v>0.99463058419243988</v>
+        <v>0.99484536082474229</v>
       </c>
       <c r="AG43" s="7">
         <v>3765</v>
@@ -8638,14 +8638,14 @@
       </c>
       <c r="BH43" s="4">
         <f t="shared" si="45"/>
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="BI43" s="6">
-        <v>4807</v>
+        <v>4808</v>
       </c>
       <c r="BJ43" s="5">
         <f t="shared" si="46"/>
-        <v>0.99072547403132727</v>
+        <v>0.99093157460840886</v>
       </c>
     </row>
     <row r="44" spans="1:62" x14ac:dyDescent="0.3">
@@ -8663,14 +8663,14 @@
       </c>
       <c r="E44" s="4">
         <f t="shared" si="24"/>
-        <v>81979</v>
+        <v>81989</v>
       </c>
       <c r="F44" s="13">
-        <v>359466</v>
+        <v>359476</v>
       </c>
       <c r="G44" s="5">
         <f t="shared" si="25"/>
-        <v>0.98830419003629166</v>
+        <v>0.98833168371274605</v>
       </c>
       <c r="H44" s="7">
         <v>368428</v>
@@ -8680,14 +8680,14 @@
       </c>
       <c r="J44" s="4">
         <f t="shared" si="26"/>
-        <v>72495</v>
+        <v>72509</v>
       </c>
       <c r="K44" s="13">
-        <v>362214</v>
+        <v>362228</v>
       </c>
       <c r="L44" s="5">
         <f t="shared" si="27"/>
-        <v>0.98313374662077802</v>
+        <v>0.98317174590422007</v>
       </c>
       <c r="M44" s="7">
         <v>437654</v>
@@ -8697,14 +8697,14 @@
       </c>
       <c r="O44" s="4">
         <f t="shared" si="28"/>
-        <v>87097</v>
+        <v>87116</v>
       </c>
       <c r="P44" s="6">
-        <v>430563</v>
+        <v>430582</v>
       </c>
       <c r="Q44" s="5">
         <f t="shared" si="29"/>
-        <v>0.9837977032084706</v>
+        <v>0.9838411164984211</v>
       </c>
       <c r="R44" s="7">
         <v>368991</v>
@@ -8714,14 +8714,14 @@
       </c>
       <c r="T44" s="4">
         <f t="shared" si="30"/>
-        <v>80904</v>
+        <v>80923</v>
       </c>
       <c r="U44" s="13">
-        <v>364654</v>
+        <v>364673</v>
       </c>
       <c r="V44" s="5">
         <f t="shared" si="31"/>
-        <v>0.98824632579114391</v>
+        <v>0.9882978175619459</v>
       </c>
       <c r="W44" s="7">
         <v>375659</v>
@@ -8731,14 +8731,14 @@
       </c>
       <c r="Y44" s="4">
         <f t="shared" si="32"/>
-        <v>79184</v>
+        <v>79205</v>
       </c>
       <c r="Z44" s="13">
-        <v>364683</v>
+        <v>364704</v>
       </c>
       <c r="AA44" s="5">
         <f t="shared" si="33"/>
-        <v>0.97078201241019113</v>
+        <v>0.97083791417216148</v>
       </c>
       <c r="AB44" s="7">
         <v>443838</v>
@@ -8748,14 +8748,14 @@
       </c>
       <c r="AD44" s="4">
         <f t="shared" si="34"/>
-        <v>99838</v>
+        <v>99871</v>
       </c>
       <c r="AE44" s="6">
-        <v>433597</v>
+        <v>433630</v>
       </c>
       <c r="AF44" s="5">
         <f t="shared" si="35"/>
-        <v>0.97692626588980669</v>
+        <v>0.97700061734236365</v>
       </c>
       <c r="AG44" s="7">
         <v>373881</v>
@@ -8765,14 +8765,14 @@
       </c>
       <c r="AI44" s="4">
         <f t="shared" si="12"/>
-        <v>83343</v>
+        <v>83368</v>
       </c>
       <c r="AJ44" s="6">
-        <v>366805</v>
+        <v>366830</v>
       </c>
       <c r="AK44" s="5">
         <f t="shared" si="36"/>
-        <v>0.98107419205576107</v>
+        <v>0.98114105825115483</v>
       </c>
       <c r="AL44" s="7">
         <v>377474</v>
@@ -8782,14 +8782,14 @@
       </c>
       <c r="AN44" s="4">
         <f t="shared" si="37"/>
-        <v>74538</v>
+        <v>74567</v>
       </c>
       <c r="AO44" s="6">
-        <v>370006</v>
+        <v>370035</v>
       </c>
       <c r="AP44" s="5">
         <f t="shared" si="38"/>
-        <v>0.98021585592650085</v>
+        <v>0.9802926824099143</v>
       </c>
       <c r="AQ44" s="7">
         <v>447335</v>
@@ -8799,14 +8799,14 @@
       </c>
       <c r="AS44" s="4">
         <f t="shared" si="39"/>
-        <v>79802</v>
+        <v>79831</v>
       </c>
       <c r="AT44" s="6">
-        <v>440413</v>
+        <v>440442</v>
       </c>
       <c r="AU44" s="5">
         <f t="shared" si="40"/>
-        <v>0.98452613812914258</v>
+        <v>0.98459096650161515</v>
       </c>
       <c r="AV44" s="7">
         <v>379419</v>
@@ -8816,14 +8816,14 @@
       </c>
       <c r="AX44" s="4">
         <f t="shared" si="41"/>
-        <v>74514</v>
+        <v>74547</v>
       </c>
       <c r="AY44" s="6">
-        <v>374352</v>
+        <v>374385</v>
       </c>
       <c r="AZ44" s="5">
         <f t="shared" si="42"/>
-        <v>0.98664537094874005</v>
+        <v>0.98673234603433146</v>
       </c>
       <c r="BA44" s="7">
         <v>384239</v>
@@ -8833,14 +8833,14 @@
       </c>
       <c r="BC44" s="4">
         <f t="shared" si="43"/>
-        <v>73179</v>
+        <v>73226</v>
       </c>
       <c r="BD44" s="6">
-        <v>377089</v>
+        <v>377136</v>
       </c>
       <c r="BE44" s="5">
         <f t="shared" si="44"/>
-        <v>0.98139179000569954</v>
+        <v>0.98151410970775999</v>
       </c>
       <c r="BF44" s="7">
         <v>454173</v>
@@ -8850,14 +8850,14 @@
       </c>
       <c r="BH44" s="4">
         <f t="shared" si="45"/>
-        <v>118403</v>
+        <v>118469</v>
       </c>
       <c r="BI44" s="6">
-        <v>447866</v>
+        <v>447932</v>
       </c>
       <c r="BJ44" s="5">
         <f t="shared" si="46"/>
-        <v>0.98611322117342948</v>
+        <v>0.98625854024787907</v>
       </c>
     </row>
     <row r="45" spans="1:62" x14ac:dyDescent="0.3">
@@ -8875,14 +8875,14 @@
       </c>
       <c r="E45" s="4">
         <f t="shared" si="24"/>
-        <v>56594</v>
+        <v>56607</v>
       </c>
       <c r="F45" s="13">
-        <v>262413</v>
+        <v>262426</v>
       </c>
       <c r="G45" s="5">
         <f t="shared" si="25"/>
-        <v>0.98421360577896799</v>
+        <v>0.98426236394596089</v>
       </c>
       <c r="H45" s="7">
         <v>269495</v>
@@ -8892,14 +8892,14 @@
       </c>
       <c r="J45" s="4">
         <f t="shared" si="26"/>
-        <v>50180</v>
+        <v>50194</v>
       </c>
       <c r="K45" s="13">
-        <v>263746</v>
+        <v>263760</v>
       </c>
       <c r="L45" s="5">
         <f t="shared" si="27"/>
-        <v>0.97866750774596933</v>
+        <v>0.97871945676172101</v>
       </c>
       <c r="M45" s="7">
         <v>320759</v>
@@ -8909,14 +8909,14 @@
       </c>
       <c r="O45" s="4">
         <f t="shared" si="28"/>
-        <v>60819</v>
+        <v>60839</v>
       </c>
       <c r="P45" s="6">
-        <v>314741</v>
+        <v>314761</v>
       </c>
       <c r="Q45" s="5">
         <f t="shared" si="29"/>
-        <v>0.98123825052453706</v>
+        <v>0.98130060263312957</v>
       </c>
       <c r="R45" s="7">
         <v>267358</v>
@@ -8926,14 +8926,14 @@
       </c>
       <c r="T45" s="4">
         <f t="shared" si="30"/>
-        <v>51909</v>
+        <v>51921</v>
       </c>
       <c r="U45" s="13">
-        <v>263961</v>
+        <v>263973</v>
       </c>
       <c r="V45" s="5">
         <f t="shared" si="31"/>
-        <v>0.98729418981291006</v>
+        <v>0.9873390734520755</v>
       </c>
       <c r="W45" s="7">
         <v>269851</v>
@@ -8943,14 +8943,14 @@
       </c>
       <c r="Y45" s="4">
         <f t="shared" si="32"/>
-        <v>56905</v>
+        <v>56918</v>
       </c>
       <c r="Z45" s="13">
-        <v>263909</v>
+        <v>263922</v>
       </c>
       <c r="AA45" s="5">
         <f t="shared" si="33"/>
-        <v>0.97798044105821358</v>
+        <v>0.97802861579167766</v>
       </c>
       <c r="AB45" s="7">
         <v>321990</v>
@@ -8960,14 +8960,14 @@
       </c>
       <c r="AD45" s="4">
         <f t="shared" si="34"/>
-        <v>71950</v>
+        <v>71968</v>
       </c>
       <c r="AE45" s="6">
-        <v>316357</v>
+        <v>316375</v>
       </c>
       <c r="AF45" s="5">
         <f t="shared" si="35"/>
-        <v>0.9825056678778844</v>
+        <v>0.98256157023510049</v>
       </c>
       <c r="AG45" s="7">
         <v>270238</v>
@@ -8977,14 +8977,14 @@
       </c>
       <c r="AI45" s="4">
         <f t="shared" si="12"/>
-        <v>57396</v>
+        <v>57415</v>
       </c>
       <c r="AJ45" s="6">
-        <v>266657</v>
+        <v>266676</v>
       </c>
       <c r="AK45" s="5">
         <f t="shared" si="36"/>
-        <v>0.98674871779690498</v>
+        <v>0.98681902619172734</v>
       </c>
       <c r="AL45" s="7">
         <v>273027</v>
@@ -8994,14 +8994,14 @@
       </c>
       <c r="AN45" s="4">
         <f t="shared" si="37"/>
-        <v>52449</v>
+        <v>52468</v>
       </c>
       <c r="AO45" s="6">
-        <v>269406</v>
+        <v>269425</v>
       </c>
       <c r="AP45" s="5">
         <f t="shared" si="38"/>
-        <v>0.98673757540463036</v>
+        <v>0.98680716559168136</v>
       </c>
       <c r="AQ45" s="7">
         <v>326184</v>
@@ -9011,14 +9011,14 @@
       </c>
       <c r="AS45" s="4">
         <f t="shared" si="39"/>
-        <v>60815</v>
+        <v>60851</v>
       </c>
       <c r="AT45" s="6">
-        <v>322952</v>
+        <v>322988</v>
       </c>
       <c r="AU45" s="5">
         <f t="shared" si="40"/>
-        <v>0.99009148210825793</v>
+        <v>0.99020184926299271</v>
       </c>
       <c r="AV45" s="7">
         <v>274208</v>
@@ -9028,14 +9028,14 @@
       </c>
       <c r="AX45" s="4">
         <f t="shared" si="41"/>
-        <v>52478</v>
+        <v>52503</v>
       </c>
       <c r="AY45" s="6">
-        <v>272416</v>
+        <v>272441</v>
       </c>
       <c r="AZ45" s="5">
         <f t="shared" si="42"/>
-        <v>0.99346481503092543</v>
+        <v>0.99355598669623058</v>
       </c>
       <c r="BA45" s="7">
         <v>277741</v>
@@ -9045,14 +9045,14 @@
       </c>
       <c r="BC45" s="4">
         <f t="shared" si="43"/>
-        <v>50350</v>
+        <v>50376</v>
       </c>
       <c r="BD45" s="6">
-        <v>274745</v>
+        <v>274771</v>
       </c>
       <c r="BE45" s="5">
         <f t="shared" si="44"/>
-        <v>0.98921297179746603</v>
+        <v>0.989306584191747</v>
       </c>
       <c r="BF45" s="7">
         <v>331328</v>
@@ -9062,14 +9062,14 @@
       </c>
       <c r="BH45" s="4">
         <f t="shared" si="45"/>
-        <v>87208</v>
+        <v>87260</v>
       </c>
       <c r="BI45" s="6">
-        <v>329087</v>
+        <v>329139</v>
       </c>
       <c r="BJ45" s="5">
         <f t="shared" si="46"/>
-        <v>0.99323630963878695</v>
+        <v>0.99339325381495069</v>
       </c>
     </row>
     <row r="46" spans="1:62" x14ac:dyDescent="0.3">
@@ -9087,14 +9087,14 @@
       </c>
       <c r="E46" s="4">
         <f t="shared" si="24"/>
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F46" s="13">
-        <v>2477</v>
+        <v>2478</v>
       </c>
       <c r="G46" s="5">
         <f t="shared" si="25"/>
-        <v>1.0227085053674649</v>
+        <v>1.023121387283237</v>
       </c>
       <c r="H46" s="7">
         <v>2553</v>
@@ -9104,14 +9104,14 @@
       </c>
       <c r="J46" s="4">
         <f t="shared" si="26"/>
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="K46" s="13">
-        <v>2554</v>
+        <v>2555</v>
       </c>
       <c r="L46" s="5">
         <f t="shared" si="27"/>
-        <v>1.0003916960438699</v>
+        <v>1.0007833920877398</v>
       </c>
       <c r="M46" s="7">
         <v>7561</v>
@@ -9121,14 +9121,14 @@
       </c>
       <c r="O46" s="4">
         <f t="shared" si="28"/>
-        <v>1808</v>
+        <v>1811</v>
       </c>
       <c r="P46" s="6">
-        <v>7676</v>
+        <v>7679</v>
       </c>
       <c r="Q46" s="5">
         <f t="shared" si="29"/>
-        <v>1.0152096283560375</v>
+        <v>1.0156064012696733</v>
       </c>
       <c r="R46" s="7">
         <v>2328</v>
@@ -9138,14 +9138,14 @@
       </c>
       <c r="T46" s="4">
         <f t="shared" si="30"/>
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="U46" s="13">
-        <v>2390</v>
+        <v>2391</v>
       </c>
       <c r="V46" s="5">
         <f t="shared" si="31"/>
-        <v>1.0266323024054982</v>
+        <v>1.027061855670103</v>
       </c>
       <c r="W46" s="7">
         <v>2515</v>
@@ -9155,14 +9155,14 @@
       </c>
       <c r="Y46" s="4">
         <f t="shared" si="32"/>
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="Z46" s="13">
-        <v>2474</v>
+        <v>2475</v>
       </c>
       <c r="AA46" s="5">
         <f t="shared" si="33"/>
-        <v>0.98369781312127236</v>
+        <v>0.98409542743538769</v>
       </c>
       <c r="AB46" s="7">
         <v>7764</v>
@@ -9172,14 +9172,14 @@
       </c>
       <c r="AD46" s="4">
         <f t="shared" si="34"/>
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="AE46" s="6">
-        <v>7899</v>
+        <v>7902</v>
       </c>
       <c r="AF46" s="5">
         <f t="shared" si="35"/>
-        <v>1.017387944358578</v>
+        <v>1.017774343122102</v>
       </c>
       <c r="AG46" s="7">
         <v>2401</v>
@@ -9189,14 +9189,14 @@
       </c>
       <c r="AI46" s="4">
         <f t="shared" si="12"/>
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="AJ46" s="6">
-        <v>2470</v>
+        <v>2471</v>
       </c>
       <c r="AK46" s="5">
         <f t="shared" si="36"/>
-        <v>1.028738025822574</v>
+        <v>1.0291545189504374</v>
       </c>
       <c r="AL46" s="7">
         <v>2561</v>
@@ -9206,14 +9206,14 @@
       </c>
       <c r="AN46" s="4">
         <f t="shared" si="37"/>
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AO46" s="6">
-        <v>2562</v>
+        <v>2563</v>
       </c>
       <c r="AP46" s="5">
         <f t="shared" si="38"/>
-        <v>1.0003904724716908</v>
+        <v>1.0007809449433815</v>
       </c>
       <c r="AQ46" s="7">
         <v>7981</v>
@@ -9223,14 +9223,14 @@
       </c>
       <c r="AS46" s="4">
         <f t="shared" si="39"/>
-        <v>1881</v>
+        <v>1884</v>
       </c>
       <c r="AT46" s="6">
-        <v>8146</v>
+        <v>8149</v>
       </c>
       <c r="AU46" s="5">
         <f t="shared" si="40"/>
-        <v>1.0206741009898508</v>
+        <v>1.021049993735121</v>
       </c>
       <c r="AV46" s="7">
         <v>2437</v>
@@ -9240,14 +9240,14 @@
       </c>
       <c r="AX46" s="4">
         <f t="shared" si="41"/>
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AY46" s="6">
-        <v>2511</v>
+        <v>2512</v>
       </c>
       <c r="AZ46" s="5">
         <f t="shared" si="42"/>
-        <v>1.0303652031185884</v>
+        <v>1.030775543701272</v>
       </c>
       <c r="BA46" s="7">
         <v>2592</v>
@@ -9257,14 +9257,14 @@
       </c>
       <c r="BC46" s="4">
         <f t="shared" si="43"/>
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="BD46" s="6">
-        <v>2575</v>
+        <v>2576</v>
       </c>
       <c r="BE46" s="5">
         <f t="shared" si="44"/>
-        <v>0.99344135802469136</v>
+        <v>0.99382716049382713</v>
       </c>
       <c r="BF46" s="7">
         <v>8179</v>
@@ -9274,14 +9274,14 @@
       </c>
       <c r="BH46" s="4">
         <f t="shared" si="45"/>
-        <v>1869</v>
+        <v>1877</v>
       </c>
       <c r="BI46" s="6">
-        <v>8318</v>
+        <v>8326</v>
       </c>
       <c r="BJ46" s="5">
         <f t="shared" si="46"/>
-        <v>1.0169947426335737</v>
+        <v>1.0179728573175204</v>
       </c>
     </row>
     <row r="47" spans="1:62" x14ac:dyDescent="0.3">
@@ -9497,10 +9497,10 @@
       </c>
     </row>
     <row r="48" spans="1:62" x14ac:dyDescent="0.3">
-      <c r="A48" s="27" t="s">
+      <c r="A48" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="B48" s="27"/>
+      <c r="B48" s="23"/>
       <c r="C48" s="9">
         <f>SUM(C10:C47)</f>
         <v>8203132</v>
@@ -9511,15 +9511,15 @@
       </c>
       <c r="E48" s="11">
         <f t="shared" si="24"/>
-        <v>1531173</v>
+        <v>1531564</v>
       </c>
       <c r="F48" s="10">
         <f>SUM(F10:F47)</f>
-        <v>8130066</v>
+        <v>8130457</v>
       </c>
       <c r="G48" s="12">
         <f t="shared" si="25"/>
-        <v>0.99109291426737978</v>
+        <v>0.99114057898861074</v>
       </c>
       <c r="H48" s="9">
         <f>SUM(H10:H47)</f>
@@ -9531,15 +9531,15 @@
       </c>
       <c r="J48" s="11">
         <f t="shared" si="26"/>
-        <v>1393646</v>
+        <v>1394075</v>
       </c>
       <c r="K48" s="10">
         <f>SUM(K10:K47)</f>
-        <v>8216565</v>
+        <v>8216994</v>
       </c>
       <c r="L48" s="12">
         <f t="shared" si="27"/>
-        <v>0.96595694404277377</v>
+        <v>0.96600737819974747</v>
       </c>
       <c r="M48" s="9">
         <f>SUM(M10:M47)</f>
@@ -9551,15 +9551,15 @@
       </c>
       <c r="O48" s="11">
         <f t="shared" si="28"/>
-        <v>2224392</v>
+        <v>2225139</v>
       </c>
       <c r="P48" s="10">
         <f>SUM(P10:P47)</f>
-        <v>12634646</v>
+        <v>12635393</v>
       </c>
       <c r="Q48" s="12">
         <f t="shared" si="29"/>
-        <v>0.99113313028458983</v>
+        <v>0.99119172919177911</v>
       </c>
       <c r="R48" s="9">
         <f>SUM(R10:R47)</f>
@@ -9571,15 +9571,15 @@
       </c>
       <c r="T48" s="11">
         <f t="shared" si="30"/>
-        <v>1484230</v>
+        <v>1484726</v>
       </c>
       <c r="U48" s="10">
         <f>SUM(U10:U47)</f>
-        <v>8214811</v>
+        <v>8215307</v>
       </c>
       <c r="V48" s="12">
         <f t="shared" si="31"/>
-        <v>0.99412586975913286</v>
+        <v>0.9941858938341116</v>
       </c>
       <c r="W48" s="9">
         <f>SUM(W10:W47)</f>
@@ -9591,15 +9591,15 @@
       </c>
       <c r="Y48" s="11">
         <f t="shared" si="32"/>
-        <v>1502303</v>
+        <v>1502920</v>
       </c>
       <c r="Z48" s="10">
         <f>SUM(Z10:Z47)</f>
-        <v>8254930</v>
+        <v>8255547</v>
       </c>
       <c r="AA48" s="12">
         <f t="shared" si="33"/>
-        <v>0.98093989692854477</v>
+        <v>0.98101321552923615</v>
       </c>
       <c r="AB48" s="9">
         <f>SUM(AB10:AB47)</f>
@@ -9611,15 +9611,15 @@
       </c>
       <c r="AD48" s="11">
         <f t="shared" si="34"/>
-        <v>2451710</v>
+        <v>2452778</v>
       </c>
       <c r="AE48" s="10">
         <f>SUM(AE10:AE47)</f>
-        <v>12732170</v>
+        <v>12733238</v>
       </c>
       <c r="AF48" s="12">
         <f t="shared" si="35"/>
-        <v>0.98934917514152743</v>
+        <v>0.98943216373805509</v>
       </c>
       <c r="AG48" s="9">
         <f>SUM(AG10:AG47)</f>
@@ -9631,15 +9631,15 @@
       </c>
       <c r="AI48" s="11">
         <f t="shared" ref="AI48" si="47">AJ48-AH48</f>
-        <v>1729203</v>
+        <v>1729931</v>
       </c>
       <c r="AJ48" s="10">
         <f>SUM(AJ10:AJ47)</f>
-        <v>8290541</v>
+        <v>8291269</v>
       </c>
       <c r="AK48" s="12">
         <f t="shared" ref="AK48" si="48">AJ48/AG48</f>
-        <v>0.99231098936046314</v>
+        <v>0.99239812509747416</v>
       </c>
       <c r="AL48" s="9">
         <f>SUM(AL10:AL47)</f>
@@ -9651,15 +9651,15 @@
       </c>
       <c r="AN48" s="11">
         <f t="shared" si="37"/>
-        <v>1398645</v>
+        <v>1399458</v>
       </c>
       <c r="AO48" s="10">
         <f>SUM(AO10:AO47)</f>
-        <v>8366131</v>
+        <v>8366944</v>
       </c>
       <c r="AP48" s="12">
         <f t="shared" si="38"/>
-        <v>0.9858803080385814</v>
+        <v>0.98597611345812786</v>
       </c>
       <c r="AQ48" s="9">
         <f>SUM(AQ10:AQ47)</f>
@@ -9671,15 +9671,15 @@
       </c>
       <c r="AS48" s="11">
         <f t="shared" si="39"/>
-        <v>2051877</v>
+        <v>2053369</v>
       </c>
       <c r="AT48" s="10">
         <f>SUM(AT10:AT47)</f>
-        <v>12910671</v>
+        <v>12912163</v>
       </c>
       <c r="AU48" s="12">
         <f t="shared" si="40"/>
-        <v>0.99340883258445534</v>
+        <v>0.9935236342069439</v>
       </c>
       <c r="AV48" s="9">
         <f>SUM(AV10:AV47)</f>
@@ -9691,15 +9691,15 @@
       </c>
       <c r="AX48" s="11">
         <f t="shared" si="41"/>
-        <v>1419340</v>
+        <v>1420368</v>
       </c>
       <c r="AY48" s="10">
         <f>SUM(AY10:AY47)</f>
-        <v>8447811</v>
+        <v>8448839</v>
       </c>
       <c r="AZ48" s="12">
         <f t="shared" si="42"/>
-        <v>0.99616735844537818</v>
+        <v>0.99628858038612489</v>
       </c>
       <c r="BA48" s="9">
         <f>SUM(BA10:BA47)</f>
@@ -9711,15 +9711,15 @@
       </c>
       <c r="BC48" s="11">
         <f t="shared" si="43"/>
-        <v>1409194</v>
+        <v>1410417</v>
       </c>
       <c r="BD48" s="10">
         <f>SUM(BD10:BD47)</f>
-        <v>8539248</v>
+        <v>8540471</v>
       </c>
       <c r="BE48" s="12">
         <f t="shared" si="44"/>
-        <v>0.98781411264154806</v>
+        <v>0.98795558840847286</v>
       </c>
       <c r="BF48" s="9">
         <f>SUM(BF10:BF47)</f>
@@ -9731,15 +9731,15 @@
       </c>
       <c r="BH48" s="11">
         <f t="shared" si="45"/>
-        <v>2967305</v>
+        <v>2969866</v>
       </c>
       <c r="BI48" s="10">
         <f>SUM(BI10:BI47)</f>
-        <v>13125923</v>
+        <v>13128484</v>
       </c>
       <c r="BJ48" s="12">
         <f t="shared" si="46"/>
-        <v>0.99373389791114786</v>
+        <v>0.993927785420053</v>
       </c>
     </row>
     <row r="49" spans="1:62" x14ac:dyDescent="0.3">
@@ -10566,12 +10566,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="R8:V8"/>
-    <mergeCell ref="M8:Q8"/>
-    <mergeCell ref="C8:G8"/>
     <mergeCell ref="BF8:BJ8"/>
     <mergeCell ref="H8:L8"/>
     <mergeCell ref="A3:B3"/>
@@ -10582,6 +10576,12 @@
     <mergeCell ref="AL8:AP8"/>
     <mergeCell ref="AG8:AK8"/>
     <mergeCell ref="AB8:AF8"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="R8:V8"/>
+    <mergeCell ref="M8:Q8"/>
+    <mergeCell ref="C8:G8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/gstdatabase/GSTR-3B-2024-2025.xlsx
+++ b/gstdatabase/GSTR-3B-2024-2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jun-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 3B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jul-26\GST Statistics Downloads 31st Jul 26\Downloads\GSTR 3B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23E6C9D3-04EE-4CDC-BDA4-499F96202267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7528456A-D3E5-40A0-A548-0BD785C6E894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -185,10 +185,10 @@
     <t>FINANCIAL YEAR 2024-2025</t>
   </si>
   <si>
-    <t>Data Considered upto 30th Jun 2026</t>
+    <t>Data Considered upto 31st Jul 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 30th Jun 2026</t>
+    <t>Filing %age as on 31st Jul 2026</t>
   </si>
 </sst>
 </file>
@@ -415,15 +415,6 @@
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="17" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -435,6 +426,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
@@ -727,7 +727,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:BJ61"/>
+  <dimension ref="A1:BJ59"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="29.77734375" customWidth="1"/>
@@ -865,10 +865,10 @@
       <c r="BJ2" s="2"/>
     </row>
     <row r="3" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="29"/>
+      <c r="B3" s="26"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -1189,100 +1189,100 @@
       <c r="BJ7" s="1"/>
     </row>
     <row r="8" spans="1:62" s="15" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="23">
         <v>45383</v>
       </c>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="26">
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="23">
         <v>45413</v>
       </c>
-      <c r="I8" s="27"/>
-      <c r="J8" s="27"/>
-      <c r="K8" s="27"/>
-      <c r="L8" s="28"/>
-      <c r="M8" s="26">
+      <c r="I8" s="24"/>
+      <c r="J8" s="24"/>
+      <c r="K8" s="24"/>
+      <c r="L8" s="25"/>
+      <c r="M8" s="23">
         <v>45444</v>
       </c>
-      <c r="N8" s="27"/>
-      <c r="O8" s="27"/>
-      <c r="P8" s="27"/>
-      <c r="Q8" s="28"/>
-      <c r="R8" s="26">
+      <c r="N8" s="24"/>
+      <c r="O8" s="24"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="25"/>
+      <c r="R8" s="23">
         <v>45474</v>
       </c>
-      <c r="S8" s="27"/>
-      <c r="T8" s="27"/>
-      <c r="U8" s="27"/>
-      <c r="V8" s="28"/>
-      <c r="W8" s="26">
+      <c r="S8" s="24"/>
+      <c r="T8" s="24"/>
+      <c r="U8" s="24"/>
+      <c r="V8" s="25"/>
+      <c r="W8" s="23">
         <v>45505</v>
       </c>
-      <c r="X8" s="27"/>
-      <c r="Y8" s="27"/>
-      <c r="Z8" s="27"/>
-      <c r="AA8" s="28"/>
-      <c r="AB8" s="26">
+      <c r="X8" s="24"/>
+      <c r="Y8" s="24"/>
+      <c r="Z8" s="24"/>
+      <c r="AA8" s="25"/>
+      <c r="AB8" s="23">
         <v>45536</v>
       </c>
-      <c r="AC8" s="27"/>
-      <c r="AD8" s="27"/>
-      <c r="AE8" s="27"/>
-      <c r="AF8" s="28"/>
-      <c r="AG8" s="26">
+      <c r="AC8" s="24"/>
+      <c r="AD8" s="24"/>
+      <c r="AE8" s="24"/>
+      <c r="AF8" s="25"/>
+      <c r="AG8" s="23">
         <v>45566</v>
       </c>
-      <c r="AH8" s="27"/>
-      <c r="AI8" s="27"/>
-      <c r="AJ8" s="27"/>
-      <c r="AK8" s="28"/>
-      <c r="AL8" s="26">
+      <c r="AH8" s="24"/>
+      <c r="AI8" s="24"/>
+      <c r="AJ8" s="24"/>
+      <c r="AK8" s="25"/>
+      <c r="AL8" s="23">
         <v>45597</v>
       </c>
-      <c r="AM8" s="27"/>
-      <c r="AN8" s="27"/>
-      <c r="AO8" s="27"/>
-      <c r="AP8" s="28"/>
-      <c r="AQ8" s="26">
+      <c r="AM8" s="24"/>
+      <c r="AN8" s="24"/>
+      <c r="AO8" s="24"/>
+      <c r="AP8" s="25"/>
+      <c r="AQ8" s="23">
         <v>45627</v>
       </c>
-      <c r="AR8" s="27"/>
-      <c r="AS8" s="27"/>
-      <c r="AT8" s="27"/>
-      <c r="AU8" s="28"/>
-      <c r="AV8" s="26">
+      <c r="AR8" s="24"/>
+      <c r="AS8" s="24"/>
+      <c r="AT8" s="24"/>
+      <c r="AU8" s="25"/>
+      <c r="AV8" s="23">
         <v>45658</v>
       </c>
-      <c r="AW8" s="27"/>
-      <c r="AX8" s="27"/>
-      <c r="AY8" s="27"/>
-      <c r="AZ8" s="28"/>
-      <c r="BA8" s="26">
+      <c r="AW8" s="24"/>
+      <c r="AX8" s="24"/>
+      <c r="AY8" s="24"/>
+      <c r="AZ8" s="25"/>
+      <c r="BA8" s="23">
         <v>45689</v>
       </c>
-      <c r="BB8" s="27"/>
-      <c r="BC8" s="27"/>
-      <c r="BD8" s="27"/>
-      <c r="BE8" s="28"/>
-      <c r="BF8" s="26">
+      <c r="BB8" s="24"/>
+      <c r="BC8" s="24"/>
+      <c r="BD8" s="24"/>
+      <c r="BE8" s="25"/>
+      <c r="BF8" s="23">
         <v>45717</v>
       </c>
-      <c r="BG8" s="27"/>
-      <c r="BH8" s="27"/>
-      <c r="BI8" s="27"/>
-      <c r="BJ8" s="28"/>
+      <c r="BG8" s="24"/>
+      <c r="BH8" s="24"/>
+      <c r="BI8" s="24"/>
+      <c r="BJ8" s="25"/>
     </row>
     <row r="9" spans="1:62" s="15" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="24"/>
-      <c r="B9" s="25"/>
+      <c r="A9" s="28"/>
+      <c r="B9" s="29"/>
       <c r="C9" s="16" t="s">
         <v>2</v>
       </c>
@@ -1479,14 +1479,14 @@
       </c>
       <c r="E10" s="4">
         <f>F10-D10</f>
-        <v>15642</v>
+        <v>15644</v>
       </c>
       <c r="F10" s="13">
-        <v>73032</v>
+        <v>73034</v>
       </c>
       <c r="G10" s="5">
         <f>F10/C10</f>
-        <v>1.0016732958441914</v>
+        <v>1.0017007269236045</v>
       </c>
       <c r="H10" s="7">
         <v>74548</v>
@@ -1496,14 +1496,14 @@
       </c>
       <c r="J10" s="4">
         <f>K10-I10</f>
-        <v>15554</v>
+        <v>15558</v>
       </c>
       <c r="K10" s="13">
-        <v>74110</v>
+        <v>74114</v>
       </c>
       <c r="L10" s="5">
         <f>K10/H10</f>
-        <v>0.99412459086762894</v>
+        <v>0.9941782475720341</v>
       </c>
       <c r="M10" s="7">
         <v>129395</v>
@@ -1513,14 +1513,14 @@
       </c>
       <c r="O10" s="4">
         <f>P10-N10</f>
-        <v>25082</v>
+        <v>25088</v>
       </c>
       <c r="P10" s="6">
-        <v>129059</v>
+        <v>129065</v>
       </c>
       <c r="Q10" s="5">
         <f>P10/M10</f>
-        <v>0.99740329997295107</v>
+        <v>0.99744966961629122</v>
       </c>
       <c r="R10" s="7">
         <v>72583</v>
@@ -1530,14 +1530,14 @@
       </c>
       <c r="T10" s="4">
         <f>U10-S10</f>
-        <v>14235</v>
+        <v>14238</v>
       </c>
       <c r="U10" s="13">
-        <v>73063</v>
+        <v>73066</v>
       </c>
       <c r="V10" s="5">
         <f>U10/R10</f>
-        <v>1.0066131187743688</v>
+        <v>1.0066544507667086</v>
       </c>
       <c r="W10" s="7">
         <v>74384</v>
@@ -1547,14 +1547,14 @@
       </c>
       <c r="Y10" s="4">
         <f>Z10-X10</f>
-        <v>15707</v>
+        <v>15712</v>
       </c>
       <c r="Z10" s="13">
-        <v>73664</v>
+        <v>73669</v>
       </c>
       <c r="AA10" s="5">
         <f>Z10/W10</f>
-        <v>0.99032049903204988</v>
+        <v>0.99038771778877177</v>
       </c>
       <c r="AB10" s="7">
         <v>130621</v>
@@ -1564,14 +1564,14 @@
       </c>
       <c r="AD10" s="4">
         <f>AE10-AC10</f>
-        <v>26369</v>
+        <v>26375</v>
       </c>
       <c r="AE10" s="6">
-        <v>129922</v>
+        <v>129928</v>
       </c>
       <c r="AF10" s="5">
         <f>AE10/AB10</f>
-        <v>0.99464863995835284</v>
+        <v>0.99469457437931119</v>
       </c>
       <c r="AG10" s="7">
         <v>72721</v>
@@ -1581,14 +1581,14 @@
       </c>
       <c r="AI10" s="4">
         <f>AJ10-AH10</f>
-        <v>14494</v>
+        <v>14499</v>
       </c>
       <c r="AJ10" s="6">
-        <v>72708</v>
+        <v>72713</v>
       </c>
       <c r="AK10" s="5">
         <f>AJ10/AG10</f>
-        <v>0.99982123458148264</v>
+        <v>0.99988999051168159</v>
       </c>
       <c r="AL10" s="7">
         <v>74187</v>
@@ -1598,14 +1598,14 @@
       </c>
       <c r="AN10" s="4">
         <f>AO10-AM10</f>
-        <v>13075</v>
+        <v>13080</v>
       </c>
       <c r="AO10" s="6">
-        <v>73760</v>
+        <v>73765</v>
       </c>
       <c r="AP10" s="5">
         <f>AO10/AL10</f>
-        <v>0.99424427460336717</v>
+        <v>0.99431167185625513</v>
       </c>
       <c r="AQ10" s="7">
         <v>132270</v>
@@ -1615,14 +1615,14 @@
       </c>
       <c r="AS10" s="4">
         <f>AT10-AR10</f>
-        <v>21545</v>
+        <v>21559</v>
       </c>
       <c r="AT10" s="6">
-        <v>132025</v>
+        <v>132039</v>
       </c>
       <c r="AU10" s="5">
         <f>AT10/AQ10</f>
-        <v>0.99814772813185149</v>
+        <v>0.99825357223860289</v>
       </c>
       <c r="AV10" s="7">
         <v>73561</v>
@@ -1632,14 +1632,14 @@
       </c>
       <c r="AX10" s="4">
         <f>AY10-AW10</f>
-        <v>12839</v>
+        <v>12845</v>
       </c>
       <c r="AY10" s="6">
-        <v>73588</v>
+        <v>73594</v>
       </c>
       <c r="AZ10" s="5">
         <f>AY10/AV10</f>
-        <v>1.0003670423186199</v>
+        <v>1.0004486072783132</v>
       </c>
       <c r="BA10" s="7">
         <v>75582</v>
@@ -1649,14 +1649,14 @@
       </c>
       <c r="BC10" s="4">
         <f>BD10-BB10</f>
-        <v>12525</v>
+        <v>12533</v>
       </c>
       <c r="BD10" s="6">
-        <v>74490</v>
+        <v>74498</v>
       </c>
       <c r="BE10" s="5">
         <f>BD10/BA10</f>
-        <v>0.98555211558307532</v>
+        <v>0.985657960890159</v>
       </c>
       <c r="BF10" s="7">
         <v>134150</v>
@@ -1666,14 +1666,14 @@
       </c>
       <c r="BH10" s="4">
         <f>BI10-BG10</f>
-        <v>33062</v>
+        <v>33091</v>
       </c>
       <c r="BI10" s="6">
-        <v>133529</v>
+        <v>133558</v>
       </c>
       <c r="BJ10" s="5">
         <f>BI10/BF10</f>
-        <v>0.99537085352217669</v>
+        <v>0.99558702944465149</v>
       </c>
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.3">
@@ -1691,14 +1691,14 @@
       </c>
       <c r="E11" s="4">
         <f t="shared" ref="E11:E33" si="0">F11-D11</f>
-        <v>8250</v>
+        <v>8254</v>
       </c>
       <c r="F11" s="13">
-        <v>46488</v>
+        <v>46492</v>
       </c>
       <c r="G11" s="5">
         <f t="shared" ref="G11:G33" si="1">F11/C11</f>
-        <v>0.99886121914011305</v>
+        <v>0.99894716486538748</v>
       </c>
       <c r="H11" s="7">
         <v>47616</v>
@@ -1708,14 +1708,14 @@
       </c>
       <c r="J11" s="4">
         <f t="shared" ref="J11:J33" si="2">K11-I11</f>
-        <v>8146</v>
+        <v>8152</v>
       </c>
       <c r="K11" s="13">
-        <v>47143</v>
+        <v>47149</v>
       </c>
       <c r="L11" s="5">
         <f t="shared" ref="L11:L33" si="3">K11/H11</f>
-        <v>0.99006636424731187</v>
+        <v>0.990192372311828</v>
       </c>
       <c r="M11" s="7">
         <v>108402</v>
@@ -1725,14 +1725,14 @@
       </c>
       <c r="O11" s="4">
         <f t="shared" ref="O11:O33" si="4">P11-N11</f>
-        <v>16821</v>
+        <v>16835</v>
       </c>
       <c r="P11" s="6">
-        <v>107779</v>
+        <v>107793</v>
       </c>
       <c r="Q11" s="5">
         <f t="shared" ref="Q11:Q33" si="5">P11/M11</f>
-        <v>0.99425287356321834</v>
+        <v>0.9943820224719101</v>
       </c>
       <c r="R11" s="7">
         <v>46539</v>
@@ -1742,14 +1742,14 @@
       </c>
       <c r="T11" s="4">
         <f t="shared" ref="T11:T33" si="6">U11-S11</f>
-        <v>8195</v>
+        <v>8208</v>
       </c>
       <c r="U11" s="13">
-        <v>46463</v>
+        <v>46476</v>
       </c>
       <c r="V11" s="5">
         <f t="shared" ref="V11:V33" si="7">U11/R11</f>
-        <v>0.99836696104342593</v>
+        <v>0.99864629665441884</v>
       </c>
       <c r="W11" s="7">
         <v>48300</v>
@@ -1759,14 +1759,14 @@
       </c>
       <c r="Y11" s="4">
         <f t="shared" ref="Y11:Y33" si="8">Z11-X11</f>
-        <v>8372</v>
+        <v>8384</v>
       </c>
       <c r="Z11" s="13">
-        <v>47077</v>
+        <v>47089</v>
       </c>
       <c r="AA11" s="5">
         <f t="shared" ref="AA11:AA33" si="9">Z11/W11</f>
-        <v>0.97467908902691514</v>
+        <v>0.97492753623188411</v>
       </c>
       <c r="AB11" s="7">
         <v>109219</v>
@@ -1776,14 +1776,14 @@
       </c>
       <c r="AD11" s="4">
         <f t="shared" ref="AD11:AD33" si="10">AE11-AC11</f>
-        <v>18145</v>
+        <v>18162</v>
       </c>
       <c r="AE11" s="6">
-        <v>108427</v>
+        <v>108444</v>
       </c>
       <c r="AF11" s="5">
         <f t="shared" ref="AF11:AF33" si="11">AE11/AB11</f>
-        <v>0.99274851445261358</v>
+        <v>0.99290416502623169</v>
       </c>
       <c r="AG11" s="7">
         <v>46763</v>
@@ -1793,14 +1793,14 @@
       </c>
       <c r="AI11" s="4">
         <f t="shared" ref="AI11:AI47" si="12">AJ11-AH11</f>
-        <v>8321</v>
+        <v>8333</v>
       </c>
       <c r="AJ11" s="6">
-        <v>46690</v>
+        <v>46702</v>
       </c>
       <c r="AK11" s="5">
         <f t="shared" ref="AK11:AK33" si="13">AJ11/AG11</f>
-        <v>0.99843893676624684</v>
+        <v>0.99869554990056242</v>
       </c>
       <c r="AL11" s="7">
         <v>48206</v>
@@ -1810,14 +1810,14 @@
       </c>
       <c r="AN11" s="4">
         <f t="shared" ref="AN11:AN33" si="14">AO11-AM11</f>
-        <v>7528</v>
+        <v>7540</v>
       </c>
       <c r="AO11" s="6">
-        <v>47217</v>
+        <v>47229</v>
       </c>
       <c r="AP11" s="5">
         <f t="shared" ref="AP11:AP33" si="15">AO11/AL11</f>
-        <v>0.97948388167448031</v>
+        <v>0.97973281334273743</v>
       </c>
       <c r="AQ11" s="7">
         <v>110196</v>
@@ -1827,14 +1827,14 @@
       </c>
       <c r="AS11" s="4">
         <f t="shared" ref="AS11:AS33" si="16">AT11-AR11</f>
-        <v>15106</v>
+        <v>15129</v>
       </c>
       <c r="AT11" s="6">
-        <v>109659</v>
+        <v>109682</v>
       </c>
       <c r="AU11" s="5">
         <f t="shared" ref="AU11:AU33" si="17">AT11/AQ11</f>
-        <v>0.9951268648589785</v>
+        <v>0.99533558386874299</v>
       </c>
       <c r="AV11" s="7">
         <v>47206</v>
@@ -1844,14 +1844,14 @@
       </c>
       <c r="AX11" s="4">
         <f t="shared" ref="AX11:AX33" si="18">AY11-AW11</f>
-        <v>7574</v>
+        <v>7589</v>
       </c>
       <c r="AY11" s="6">
-        <v>47030</v>
+        <v>47045</v>
       </c>
       <c r="AZ11" s="5">
         <f t="shared" ref="AZ11:AZ33" si="19">AY11/AV11</f>
-        <v>0.99627166038215476</v>
+        <v>0.99658941659958478</v>
       </c>
       <c r="BA11" s="7">
         <v>48813</v>
@@ -1861,14 +1861,14 @@
       </c>
       <c r="BC11" s="4">
         <f t="shared" ref="BC11:BC33" si="20">BD11-BB11</f>
-        <v>7435</v>
+        <v>7449</v>
       </c>
       <c r="BD11" s="6">
-        <v>47558</v>
+        <v>47572</v>
       </c>
       <c r="BE11" s="5">
         <f t="shared" ref="BE11:BE33" si="21">BD11/BA11</f>
-        <v>0.97428963595763418</v>
+        <v>0.97457644479954109</v>
       </c>
       <c r="BF11" s="7">
         <v>111276</v>
@@ -1878,14 +1878,14 @@
       </c>
       <c r="BH11" s="4">
         <f t="shared" ref="BH11:BH33" si="22">BI11-BG11</f>
-        <v>21088</v>
+        <v>21116</v>
       </c>
       <c r="BI11" s="6">
-        <v>110637</v>
+        <v>110665</v>
       </c>
       <c r="BJ11" s="5">
         <f t="shared" ref="BJ11:BJ33" si="23">BI11/BF11</f>
-        <v>0.99425752183759297</v>
+        <v>0.99450914842373916</v>
       </c>
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.3">
@@ -1903,14 +1903,14 @@
       </c>
       <c r="E12" s="4">
         <f t="shared" si="0"/>
-        <v>27458</v>
+        <v>27465</v>
       </c>
       <c r="F12" s="13">
-        <v>175783</v>
+        <v>175790</v>
       </c>
       <c r="G12" s="5">
         <f t="shared" si="1"/>
-        <v>0.99261396683061254</v>
+        <v>0.99265349453106033</v>
       </c>
       <c r="H12" s="7">
         <v>181172</v>
@@ -1920,14 +1920,14 @@
       </c>
       <c r="J12" s="4">
         <f t="shared" si="2"/>
-        <v>25318</v>
+        <v>25324</v>
       </c>
       <c r="K12" s="13">
-        <v>178144</v>
+        <v>178150</v>
       </c>
       <c r="L12" s="5">
         <f t="shared" si="3"/>
-        <v>0.98328660057845585</v>
+        <v>0.98331971827876274</v>
       </c>
       <c r="M12" s="7">
         <v>363483</v>
@@ -1937,14 +1937,14 @@
       </c>
       <c r="O12" s="4">
         <f t="shared" si="4"/>
-        <v>56209</v>
+        <v>56219</v>
       </c>
       <c r="P12" s="6">
-        <v>360443</v>
+        <v>360453</v>
       </c>
       <c r="Q12" s="5">
         <f t="shared" si="5"/>
-        <v>0.99163647268235378</v>
+        <v>0.99166398428537239</v>
       </c>
       <c r="R12" s="7">
         <v>177513</v>
@@ -1954,14 +1954,14 @@
       </c>
       <c r="T12" s="4">
         <f t="shared" si="6"/>
-        <v>27053</v>
+        <v>27063</v>
       </c>
       <c r="U12" s="13">
-        <v>177173</v>
+        <v>177183</v>
       </c>
       <c r="V12" s="5">
         <f t="shared" si="7"/>
-        <v>0.99808464732160462</v>
+        <v>0.99814098122391037</v>
       </c>
       <c r="W12" s="7">
         <v>182324</v>
@@ -1971,14 +1971,14 @@
       </c>
       <c r="Y12" s="4">
         <f t="shared" si="8"/>
-        <v>28723</v>
+        <v>28731</v>
       </c>
       <c r="Z12" s="13">
-        <v>178795</v>
+        <v>178803</v>
       </c>
       <c r="AA12" s="5">
         <f t="shared" si="9"/>
-        <v>0.98064434742546236</v>
+        <v>0.98068822535705669</v>
       </c>
       <c r="AB12" s="7">
         <v>365690</v>
@@ -1988,14 +1988,14 @@
       </c>
       <c r="AD12" s="4">
         <f t="shared" si="10"/>
-        <v>60857</v>
+        <v>60872</v>
       </c>
       <c r="AE12" s="6">
-        <v>362420</v>
+        <v>362435</v>
       </c>
       <c r="AF12" s="5">
         <f t="shared" si="11"/>
-        <v>0.99105799994530885</v>
+        <v>0.99109901829418356</v>
       </c>
       <c r="AG12" s="7">
         <v>180670</v>
@@ -2005,14 +2005,14 @@
       </c>
       <c r="AI12" s="4">
         <f t="shared" si="12"/>
-        <v>30055</v>
+        <v>30071</v>
       </c>
       <c r="AJ12" s="6">
-        <v>178432</v>
+        <v>178448</v>
       </c>
       <c r="AK12" s="5">
         <f t="shared" si="13"/>
-        <v>0.98761277467205399</v>
+        <v>0.98770133392372839</v>
       </c>
       <c r="AL12" s="7">
         <v>181581</v>
@@ -2022,14 +2022,14 @@
       </c>
       <c r="AN12" s="4">
         <f t="shared" si="14"/>
-        <v>25713</v>
+        <v>25729</v>
       </c>
       <c r="AO12" s="6">
-        <v>178576</v>
+        <v>178592</v>
       </c>
       <c r="AP12" s="5">
         <f t="shared" si="15"/>
-        <v>0.9834509117143313</v>
+        <v>0.98353902666027837</v>
       </c>
       <c r="AQ12" s="7">
         <v>363376</v>
@@ -2039,14 +2039,14 @@
       </c>
       <c r="AS12" s="4">
         <f t="shared" si="16"/>
-        <v>54199</v>
+        <v>54229</v>
       </c>
       <c r="AT12" s="6">
-        <v>362079</v>
+        <v>362109</v>
       </c>
       <c r="AU12" s="5">
         <f t="shared" si="17"/>
-        <v>0.99643069437717402</v>
+        <v>0.99651325348949849</v>
       </c>
       <c r="AV12" s="7">
         <v>179534</v>
@@ -2056,14 +2056,14 @@
       </c>
       <c r="AX12" s="4">
         <f t="shared" si="18"/>
-        <v>26120</v>
+        <v>26132</v>
       </c>
       <c r="AY12" s="6">
-        <v>178840</v>
+        <v>178852</v>
       </c>
       <c r="AZ12" s="5">
         <f t="shared" si="19"/>
-        <v>0.99613443693116621</v>
+        <v>0.9962012766384083</v>
       </c>
       <c r="BA12" s="7">
         <v>184469</v>
@@ -2073,14 +2073,14 @@
       </c>
       <c r="BC12" s="4">
         <f t="shared" si="20"/>
-        <v>26314</v>
+        <v>26328</v>
       </c>
       <c r="BD12" s="6">
-        <v>181891</v>
+        <v>181905</v>
       </c>
       <c r="BE12" s="5">
         <f t="shared" si="21"/>
-        <v>0.98602475212637353</v>
+        <v>0.98610064563693633</v>
       </c>
       <c r="BF12" s="7">
         <v>368393</v>
@@ -2090,14 +2090,14 @@
       </c>
       <c r="BH12" s="4">
         <f t="shared" si="22"/>
-        <v>77131</v>
+        <v>77178</v>
       </c>
       <c r="BI12" s="6">
-        <v>367094</v>
+        <v>367141</v>
       </c>
       <c r="BJ12" s="5">
         <f t="shared" si="23"/>
-        <v>0.99647387436786261</v>
+        <v>0.99660145551082679</v>
       </c>
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.3">
@@ -2251,14 +2251,14 @@
       </c>
       <c r="AS13" s="4">
         <f t="shared" si="16"/>
-        <v>4310</v>
+        <v>4311</v>
       </c>
       <c r="AT13" s="6">
-        <v>28957</v>
+        <v>28958</v>
       </c>
       <c r="AU13" s="5">
         <f t="shared" si="17"/>
-        <v>1.0008295026440397</v>
+        <v>1.000864065254208</v>
       </c>
       <c r="AV13" s="7">
         <v>17858</v>
@@ -2268,14 +2268,14 @@
       </c>
       <c r="AX13" s="4">
         <f t="shared" si="18"/>
-        <v>2398</v>
+        <v>2399</v>
       </c>
       <c r="AY13" s="6">
-        <v>17907</v>
+        <v>17908</v>
       </c>
       <c r="AZ13" s="5">
         <f t="shared" si="19"/>
-        <v>1.0027438682943219</v>
+        <v>1.002799865606451</v>
       </c>
       <c r="BA13" s="7">
         <v>18026</v>
@@ -2302,14 +2302,14 @@
       </c>
       <c r="BH13" s="4">
         <f t="shared" si="22"/>
-        <v>5656</v>
+        <v>5658</v>
       </c>
       <c r="BI13" s="6">
-        <v>29077</v>
+        <v>29079</v>
       </c>
       <c r="BJ13" s="5">
         <f t="shared" si="23"/>
-        <v>1.0018605933225373</v>
+        <v>1.001929504186335</v>
       </c>
     </row>
     <row r="14" spans="1:62" x14ac:dyDescent="0.3">
@@ -2327,14 +2327,14 @@
       </c>
       <c r="E14" s="4">
         <f t="shared" si="0"/>
-        <v>18626</v>
+        <v>18633</v>
       </c>
       <c r="F14" s="13">
-        <v>89936</v>
+        <v>89943</v>
       </c>
       <c r="G14" s="5">
         <f t="shared" si="1"/>
-        <v>0.99411946765707215</v>
+        <v>0.99419684308263701</v>
       </c>
       <c r="H14" s="7">
         <v>94129</v>
@@ -2344,14 +2344,14 @@
       </c>
       <c r="J14" s="4">
         <f t="shared" si="2"/>
-        <v>17770</v>
+        <v>17777</v>
       </c>
       <c r="K14" s="13">
-        <v>91389</v>
+        <v>91396</v>
       </c>
       <c r="L14" s="5">
         <f t="shared" si="3"/>
-        <v>0.97089101127176536</v>
+        <v>0.97096537730136301</v>
       </c>
       <c r="M14" s="7">
         <v>164995</v>
@@ -2361,14 +2361,14 @@
       </c>
       <c r="O14" s="4">
         <f t="shared" si="4"/>
-        <v>31694</v>
+        <v>31710</v>
       </c>
       <c r="P14" s="6">
-        <v>163659</v>
+        <v>163675</v>
       </c>
       <c r="Q14" s="5">
         <f t="shared" si="5"/>
-        <v>0.99190278493287676</v>
+        <v>0.99199975756841119</v>
       </c>
       <c r="R14" s="7">
         <v>91074</v>
@@ -2378,14 +2378,14 @@
       </c>
       <c r="T14" s="4">
         <f t="shared" si="6"/>
-        <v>18920</v>
+        <v>18928</v>
       </c>
       <c r="U14" s="13">
-        <v>90858</v>
+        <v>90866</v>
       </c>
       <c r="V14" s="5">
         <f t="shared" si="7"/>
-        <v>0.99762830225970089</v>
+        <v>0.99771614291674904</v>
       </c>
       <c r="W14" s="7">
         <v>93800</v>
@@ -2395,14 +2395,14 @@
       </c>
       <c r="Y14" s="4">
         <f t="shared" si="8"/>
-        <v>18582</v>
+        <v>18593</v>
       </c>
       <c r="Z14" s="13">
-        <v>91365</v>
+        <v>91376</v>
       </c>
       <c r="AA14" s="5">
         <f t="shared" si="9"/>
-        <v>0.97404051172707884</v>
+        <v>0.9741577825159915</v>
       </c>
       <c r="AB14" s="7">
         <v>166352</v>
@@ -2412,14 +2412,14 @@
       </c>
       <c r="AD14" s="4">
         <f t="shared" si="10"/>
-        <v>34982</v>
+        <v>34998</v>
       </c>
       <c r="AE14" s="6">
-        <v>164425</v>
+        <v>164441</v>
       </c>
       <c r="AF14" s="5">
         <f t="shared" si="11"/>
-        <v>0.98841612965278447</v>
+        <v>0.98851231124362793</v>
       </c>
       <c r="AG14" s="7">
         <v>92175</v>
@@ -2429,14 +2429,14 @@
       </c>
       <c r="AI14" s="4">
         <f t="shared" si="12"/>
-        <v>19141</v>
+        <v>19153</v>
       </c>
       <c r="AJ14" s="6">
-        <v>91588</v>
+        <v>91600</v>
       </c>
       <c r="AK14" s="5">
         <f t="shared" si="13"/>
-        <v>0.99363167887171144</v>
+        <v>0.99376186601573091</v>
       </c>
       <c r="AL14" s="7">
         <v>94655</v>
@@ -2446,14 +2446,14 @@
       </c>
       <c r="AN14" s="4">
         <f t="shared" si="14"/>
-        <v>17433</v>
+        <v>17447</v>
       </c>
       <c r="AO14" s="6">
-        <v>93016</v>
+        <v>93030</v>
       </c>
       <c r="AP14" s="5">
         <f t="shared" si="15"/>
-        <v>0.98268448576409062</v>
+        <v>0.98283239131583122</v>
       </c>
       <c r="AQ14" s="7">
         <v>168400</v>
@@ -2463,14 +2463,14 @@
       </c>
       <c r="AS14" s="4">
         <f t="shared" si="16"/>
-        <v>31361</v>
+        <v>31389</v>
       </c>
       <c r="AT14" s="6">
-        <v>167403</v>
+        <v>167431</v>
       </c>
       <c r="AU14" s="5">
         <f t="shared" si="17"/>
-        <v>0.99407957244655587</v>
+        <v>0.99424584323040377</v>
       </c>
       <c r="AV14" s="7">
         <v>94024</v>
@@ -2480,14 +2480,14 @@
       </c>
       <c r="AX14" s="4">
         <f t="shared" si="18"/>
-        <v>16968</v>
+        <v>16988</v>
       </c>
       <c r="AY14" s="6">
-        <v>93556</v>
+        <v>93576</v>
       </c>
       <c r="AZ14" s="5">
         <f t="shared" si="19"/>
-        <v>0.99502254743469754</v>
+        <v>0.99523525908278743</v>
       </c>
       <c r="BA14" s="7">
         <v>96514</v>
@@ -2497,14 +2497,14 @@
       </c>
       <c r="BC14" s="4">
         <f t="shared" si="20"/>
-        <v>16731</v>
+        <v>16751</v>
       </c>
       <c r="BD14" s="6">
-        <v>94959</v>
+        <v>94979</v>
       </c>
       <c r="BE14" s="5">
         <f t="shared" si="21"/>
-        <v>0.98388834780446355</v>
+        <v>0.98409557162691419</v>
       </c>
       <c r="BF14" s="7">
         <v>171502</v>
@@ -2514,14 +2514,14 @@
       </c>
       <c r="BH14" s="4">
         <f t="shared" si="22"/>
-        <v>39829</v>
+        <v>39868</v>
       </c>
       <c r="BI14" s="6">
-        <v>170630</v>
+        <v>170669</v>
       </c>
       <c r="BJ14" s="5">
         <f t="shared" si="23"/>
-        <v>0.99491551118937394</v>
+        <v>0.99514291378526198</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.3">
@@ -2539,14 +2539,14 @@
       </c>
       <c r="E15" s="4">
         <f t="shared" si="0"/>
-        <v>50768</v>
+        <v>50772</v>
       </c>
       <c r="F15" s="13">
-        <v>301914</v>
+        <v>301918</v>
       </c>
       <c r="G15" s="5">
         <f t="shared" si="1"/>
-        <v>0.99134135169478999</v>
+        <v>0.99135448578399021</v>
       </c>
       <c r="H15" s="7">
         <v>309950</v>
@@ -2556,14 +2556,14 @@
       </c>
       <c r="J15" s="4">
         <f t="shared" si="2"/>
-        <v>47824</v>
+        <v>47831</v>
       </c>
       <c r="K15" s="13">
-        <v>306457</v>
+        <v>306464</v>
       </c>
       <c r="L15" s="5">
         <f t="shared" si="3"/>
-        <v>0.98873044039361191</v>
+        <v>0.98875302468140025</v>
       </c>
       <c r="M15" s="7">
         <v>517862</v>
@@ -2573,14 +2573,14 @@
       </c>
       <c r="O15" s="4">
         <f t="shared" si="4"/>
-        <v>81195</v>
+        <v>81205</v>
       </c>
       <c r="P15" s="6">
-        <v>512944</v>
+        <v>512954</v>
       </c>
       <c r="Q15" s="5">
         <f t="shared" si="5"/>
-        <v>0.99050326148665091</v>
+        <v>0.9905225716503625</v>
       </c>
       <c r="R15" s="7">
         <v>307768</v>
@@ -2590,14 +2590,14 @@
       </c>
       <c r="T15" s="4">
         <f t="shared" si="6"/>
-        <v>52555</v>
+        <v>52562</v>
       </c>
       <c r="U15" s="13">
-        <v>306407</v>
+        <v>306414</v>
       </c>
       <c r="V15" s="5">
         <f t="shared" si="7"/>
-        <v>0.99557783785188847</v>
+        <v>0.99560058225676484</v>
       </c>
       <c r="W15" s="7">
         <v>314114</v>
@@ -2607,14 +2607,14 @@
       </c>
       <c r="Y15" s="4">
         <f t="shared" si="8"/>
-        <v>50992</v>
+        <v>50998</v>
       </c>
       <c r="Z15" s="13">
-        <v>308553</v>
+        <v>308559</v>
       </c>
       <c r="AA15" s="5">
         <f t="shared" si="9"/>
-        <v>0.98229623639825037</v>
+        <v>0.98231533774362179</v>
       </c>
       <c r="AB15" s="7">
         <v>523203</v>
@@ -2624,14 +2624,14 @@
       </c>
       <c r="AD15" s="4">
         <f t="shared" si="10"/>
-        <v>91408</v>
+        <v>91414</v>
       </c>
       <c r="AE15" s="6">
-        <v>519185</v>
+        <v>519191</v>
       </c>
       <c r="AF15" s="5">
         <f t="shared" si="11"/>
-        <v>0.99232038042595316</v>
+        <v>0.99233184825010556</v>
       </c>
       <c r="AG15" s="7">
         <v>312916</v>
@@ -2641,14 +2641,14 @@
       </c>
       <c r="AI15" s="4">
         <f t="shared" si="12"/>
-        <v>54276</v>
+        <v>54281</v>
       </c>
       <c r="AJ15" s="6">
-        <v>310816</v>
+        <v>310821</v>
       </c>
       <c r="AK15" s="5">
         <f t="shared" si="13"/>
-        <v>0.99328893377136351</v>
+        <v>0.99330491250047936</v>
       </c>
       <c r="AL15" s="7">
         <v>318942</v>
@@ -2658,14 +2658,14 @@
       </c>
       <c r="AN15" s="4">
         <f t="shared" si="14"/>
-        <v>48591</v>
+        <v>48599</v>
       </c>
       <c r="AO15" s="6">
-        <v>313904</v>
+        <v>313912</v>
       </c>
       <c r="AP15" s="5">
         <f t="shared" si="15"/>
-        <v>0.98420402455618894</v>
+        <v>0.98422910748662762</v>
       </c>
       <c r="AQ15" s="7">
         <v>530087</v>
@@ -2675,14 +2675,14 @@
       </c>
       <c r="AS15" s="4">
         <f t="shared" si="16"/>
-        <v>77511</v>
+        <v>77523</v>
       </c>
       <c r="AT15" s="6">
-        <v>526550</v>
+        <v>526562</v>
       </c>
       <c r="AU15" s="5">
         <f t="shared" si="17"/>
-        <v>0.99332751038980394</v>
+        <v>0.99335014818322276</v>
       </c>
       <c r="AV15" s="7">
         <v>317508</v>
@@ -2692,14 +2692,14 @@
       </c>
       <c r="AX15" s="4">
         <f t="shared" si="18"/>
-        <v>49776</v>
+        <v>49783</v>
       </c>
       <c r="AY15" s="6">
-        <v>316787</v>
+        <v>316794</v>
       </c>
       <c r="AZ15" s="5">
         <f t="shared" si="19"/>
-        <v>0.99772919107550051</v>
+        <v>0.99775123776408781</v>
       </c>
       <c r="BA15" s="7">
         <v>324414</v>
@@ -2709,14 +2709,14 @@
       </c>
       <c r="BC15" s="4">
         <f t="shared" si="20"/>
-        <v>49274</v>
+        <v>49284</v>
       </c>
       <c r="BD15" s="6">
-        <v>320650</v>
+        <v>320660</v>
       </c>
       <c r="BE15" s="5">
         <f t="shared" si="21"/>
-        <v>0.98839754141313263</v>
+        <v>0.98842836622340591</v>
       </c>
       <c r="BF15" s="7">
         <v>538701</v>
@@ -2726,14 +2726,14 @@
       </c>
       <c r="BH15" s="4">
         <f t="shared" si="22"/>
-        <v>107854</v>
+        <v>107891</v>
       </c>
       <c r="BI15" s="6">
-        <v>536137</v>
+        <v>536174</v>
       </c>
       <c r="BJ15" s="5">
         <f t="shared" si="23"/>
-        <v>0.99524040237534361</v>
+        <v>0.99530908611641711</v>
       </c>
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.3">
@@ -2751,14 +2751,14 @@
       </c>
       <c r="E16" s="4">
         <f t="shared" si="0"/>
-        <v>75585</v>
+        <v>75616</v>
       </c>
       <c r="F16" s="13">
-        <v>440500</v>
+        <v>440531</v>
       </c>
       <c r="G16" s="5">
         <f t="shared" si="1"/>
-        <v>0.98838174646269283</v>
+        <v>0.98845130340739273</v>
       </c>
       <c r="H16" s="7">
         <v>453561</v>
@@ -2768,14 +2768,14 @@
       </c>
       <c r="J16" s="4">
         <f t="shared" si="2"/>
-        <v>72349</v>
+        <v>72386</v>
       </c>
       <c r="K16" s="13">
-        <v>444572</v>
+        <v>444609</v>
       </c>
       <c r="L16" s="5">
         <f t="shared" si="3"/>
-        <v>0.98018127660887955</v>
+        <v>0.98026285328765039</v>
       </c>
       <c r="M16" s="7">
         <v>776551</v>
@@ -2785,14 +2785,14 @@
       </c>
       <c r="O16" s="4">
         <f t="shared" si="4"/>
-        <v>126624</v>
+        <v>126693</v>
       </c>
       <c r="P16" s="6">
-        <v>768608</v>
+        <v>768677</v>
       </c>
       <c r="Q16" s="5">
         <f t="shared" si="5"/>
-        <v>0.98977143806395196</v>
+        <v>0.98986029249849661</v>
       </c>
       <c r="R16" s="7">
         <v>446959</v>
@@ -2802,14 +2802,14 @@
       </c>
       <c r="T16" s="4">
         <f t="shared" si="6"/>
-        <v>79256</v>
+        <v>79302</v>
       </c>
       <c r="U16" s="13">
-        <v>443741</v>
+        <v>443787</v>
       </c>
       <c r="V16" s="5">
         <f t="shared" si="7"/>
-        <v>0.99280023447340804</v>
+        <v>0.99290315219069314</v>
       </c>
       <c r="W16" s="7">
         <v>453618</v>
@@ -2819,14 +2819,14 @@
       </c>
       <c r="Y16" s="4">
         <f t="shared" si="8"/>
-        <v>73772</v>
+        <v>73820</v>
       </c>
       <c r="Z16" s="13">
-        <v>443119</v>
+        <v>443167</v>
       </c>
       <c r="AA16" s="5">
         <f t="shared" si="9"/>
-        <v>0.97685497489076711</v>
+        <v>0.97696079079754328</v>
       </c>
       <c r="AB16" s="7">
         <v>775718</v>
@@ -2836,14 +2836,14 @@
       </c>
       <c r="AD16" s="4">
         <f t="shared" si="10"/>
-        <v>135701</v>
+        <v>135787</v>
       </c>
       <c r="AE16" s="6">
-        <v>767389</v>
+        <v>767475</v>
       </c>
       <c r="AF16" s="5">
         <f t="shared" si="11"/>
-        <v>0.98926285067511643</v>
+        <v>0.98937371570596533</v>
       </c>
       <c r="AG16" s="7">
         <v>444751</v>
@@ -2853,14 +2853,14 @@
       </c>
       <c r="AI16" s="4">
         <f t="shared" si="12"/>
-        <v>79507</v>
+        <v>79561</v>
       </c>
       <c r="AJ16" s="6">
-        <v>439545</v>
+        <v>439599</v>
       </c>
       <c r="AK16" s="5">
         <f t="shared" si="13"/>
-        <v>0.98829457381770924</v>
+        <v>0.98841599007084868</v>
       </c>
       <c r="AL16" s="7">
         <v>448369</v>
@@ -2870,14 +2870,14 @@
       </c>
       <c r="AN16" s="4">
         <f t="shared" si="14"/>
-        <v>70689</v>
+        <v>70753</v>
       </c>
       <c r="AO16" s="6">
-        <v>440096</v>
+        <v>440160</v>
       </c>
       <c r="AP16" s="5">
         <f t="shared" si="15"/>
-        <v>0.9815486797704569</v>
+        <v>0.98169141934433468</v>
       </c>
       <c r="AQ16" s="7">
         <v>770483</v>
@@ -2887,14 +2887,14 @@
       </c>
       <c r="AS16" s="4">
         <f t="shared" si="16"/>
-        <v>116632</v>
+        <v>116755</v>
       </c>
       <c r="AT16" s="6">
-        <v>766971</v>
+        <v>767094</v>
       </c>
       <c r="AU16" s="5">
         <f t="shared" si="17"/>
-        <v>0.99544182026079742</v>
+        <v>0.99560146038264308</v>
       </c>
       <c r="AV16" s="7">
         <v>444563</v>
@@ -2904,14 +2904,14 @@
       </c>
       <c r="AX16" s="4">
         <f t="shared" si="18"/>
-        <v>72242</v>
+        <v>72310</v>
       </c>
       <c r="AY16" s="6">
-        <v>444304</v>
+        <v>444372</v>
       </c>
       <c r="AZ16" s="5">
         <f t="shared" si="19"/>
-        <v>0.99941740540710766</v>
+        <v>0.99957036460524151</v>
       </c>
       <c r="BA16" s="7">
         <v>453397</v>
@@ -2921,14 +2921,14 @@
       </c>
       <c r="BC16" s="4">
         <f t="shared" si="20"/>
-        <v>71485</v>
+        <v>71562</v>
       </c>
       <c r="BD16" s="6">
-        <v>447942</v>
+        <v>448019</v>
       </c>
       <c r="BE16" s="5">
         <f t="shared" si="21"/>
-        <v>0.98796860146847021</v>
+        <v>0.98813843055864947</v>
       </c>
       <c r="BF16" s="7">
         <v>780218</v>
@@ -2938,14 +2938,14 @@
       </c>
       <c r="BH16" s="4">
         <f t="shared" si="22"/>
-        <v>150972</v>
+        <v>151137</v>
       </c>
       <c r="BI16" s="6">
-        <v>776950</v>
+        <v>777115</v>
       </c>
       <c r="BJ16" s="5">
         <f t="shared" si="23"/>
-        <v>0.99581142706269277</v>
+        <v>0.99602290641846258</v>
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.3">
@@ -2963,14 +2963,14 @@
       </c>
       <c r="E17" s="4">
         <f t="shared" si="0"/>
-        <v>54518</v>
+        <v>54532</v>
       </c>
       <c r="F17" s="13">
-        <v>322872</v>
+        <v>322886</v>
       </c>
       <c r="G17" s="5">
         <f t="shared" si="1"/>
-        <v>0.99662617875387771</v>
+        <v>0.99666939329865878</v>
       </c>
       <c r="H17" s="7">
         <v>333085</v>
@@ -2980,14 +2980,14 @@
       </c>
       <c r="J17" s="4">
         <f t="shared" si="2"/>
-        <v>50238</v>
+        <v>50254</v>
       </c>
       <c r="K17" s="13">
-        <v>329467</v>
+        <v>329483</v>
       </c>
       <c r="L17" s="5">
         <f t="shared" si="3"/>
-        <v>0.9891379077412672</v>
+        <v>0.98918594352792832</v>
       </c>
       <c r="M17" s="7">
         <v>731481</v>
@@ -2997,14 +2997,14 @@
       </c>
       <c r="O17" s="4">
         <f t="shared" si="4"/>
-        <v>121278</v>
+        <v>121323</v>
       </c>
       <c r="P17" s="6">
-        <v>726959</v>
+        <v>727004</v>
       </c>
       <c r="Q17" s="5">
         <f t="shared" si="5"/>
-        <v>0.99381802124730512</v>
+        <v>0.99387954027514047</v>
       </c>
       <c r="R17" s="7">
         <v>324758</v>
@@ -3014,14 +3014,14 @@
       </c>
       <c r="T17" s="4">
         <f t="shared" si="6"/>
-        <v>57844</v>
+        <v>57865</v>
       </c>
       <c r="U17" s="13">
-        <v>324955</v>
+        <v>324976</v>
       </c>
       <c r="V17" s="5">
         <f t="shared" si="7"/>
-        <v>1.0006066055339669</v>
+        <v>1.0006712690680446</v>
       </c>
       <c r="W17" s="7">
         <v>336053</v>
@@ -3031,14 +3031,14 @@
       </c>
       <c r="Y17" s="4">
         <f t="shared" si="8"/>
-        <v>57090</v>
+        <v>57112</v>
       </c>
       <c r="Z17" s="13">
-        <v>327976</v>
+        <v>327998</v>
       </c>
       <c r="AA17" s="5">
         <f t="shared" si="9"/>
-        <v>0.97596510074303755</v>
+        <v>0.97603056660705301</v>
       </c>
       <c r="AB17" s="7">
         <v>736224</v>
@@ -3048,14 +3048,14 @@
       </c>
       <c r="AD17" s="4">
         <f t="shared" si="10"/>
-        <v>130962</v>
+        <v>131026</v>
       </c>
       <c r="AE17" s="6">
-        <v>728745</v>
+        <v>728809</v>
       </c>
       <c r="AF17" s="5">
         <f t="shared" si="11"/>
-        <v>0.98984140696309819</v>
+        <v>0.98992833702786109</v>
       </c>
       <c r="AG17" s="7">
         <v>328692</v>
@@ -3065,14 +3065,14 @@
       </c>
       <c r="AI17" s="4">
         <f t="shared" si="12"/>
-        <v>57750</v>
+        <v>57766</v>
       </c>
       <c r="AJ17" s="6">
-        <v>327496</v>
+        <v>327512</v>
       </c>
       <c r="AK17" s="5">
         <f t="shared" si="13"/>
-        <v>0.99636133523176718</v>
+        <v>0.99641001302130872</v>
       </c>
       <c r="AL17" s="7">
         <v>339621</v>
@@ -3082,14 +3082,14 @@
       </c>
       <c r="AN17" s="4">
         <f t="shared" si="14"/>
-        <v>51641</v>
+        <v>51666</v>
       </c>
       <c r="AO17" s="6">
-        <v>333247</v>
+        <v>333272</v>
       </c>
       <c r="AP17" s="5">
         <f t="shared" si="15"/>
-        <v>0.98123202039920976</v>
+        <v>0.98130563186610953</v>
       </c>
       <c r="AQ17" s="7">
         <v>745574</v>
@@ -3099,14 +3099,14 @@
       </c>
       <c r="AS17" s="4">
         <f t="shared" si="16"/>
-        <v>114369</v>
+        <v>114453</v>
       </c>
       <c r="AT17" s="6">
-        <v>740164</v>
+        <v>740248</v>
       </c>
       <c r="AU17" s="5">
         <f t="shared" si="17"/>
-        <v>0.99274384568131402</v>
+        <v>0.99285651055428437</v>
       </c>
       <c r="AV17" s="7">
         <v>334329</v>
@@ -3116,14 +3116,14 @@
       </c>
       <c r="AX17" s="4">
         <f t="shared" si="18"/>
-        <v>53696</v>
+        <v>53724</v>
       </c>
       <c r="AY17" s="6">
-        <v>333786</v>
+        <v>333814</v>
       </c>
       <c r="AZ17" s="5">
         <f t="shared" si="19"/>
-        <v>0.99837585133207107</v>
+        <v>0.99845960117130128</v>
       </c>
       <c r="BA17" s="7">
         <v>348862</v>
@@ -3133,14 +3133,14 @@
       </c>
       <c r="BC17" s="4">
         <f t="shared" si="20"/>
-        <v>52619</v>
+        <v>52655</v>
       </c>
       <c r="BD17" s="6">
-        <v>340604</v>
+        <v>340640</v>
       </c>
       <c r="BE17" s="5">
         <f t="shared" si="21"/>
-        <v>0.9763287489035779</v>
+        <v>0.97643194157001911</v>
       </c>
       <c r="BF17" s="7">
         <v>757181</v>
@@ -3150,14 +3150,14 @@
       </c>
       <c r="BH17" s="4">
         <f t="shared" si="22"/>
-        <v>157382</v>
+        <v>157515</v>
       </c>
       <c r="BI17" s="6">
-        <v>753796</v>
+        <v>753929</v>
       </c>
       <c r="BJ17" s="5">
         <f t="shared" si="23"/>
-        <v>0.99552947049648632</v>
+        <v>0.99570512202498473</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -3175,14 +3175,14 @@
       </c>
       <c r="E18" s="4">
         <f t="shared" si="0"/>
-        <v>184156</v>
+        <v>184196</v>
       </c>
       <c r="F18" s="13">
-        <v>989567</v>
+        <v>989607</v>
       </c>
       <c r="G18" s="5">
         <f t="shared" si="1"/>
-        <v>0.99110122469582917</v>
+        <v>0.99114128671182988</v>
       </c>
       <c r="H18" s="7">
         <v>1018686</v>
@@ -3192,14 +3192,14 @@
       </c>
       <c r="J18" s="4">
         <f t="shared" si="2"/>
-        <v>172432</v>
+        <v>172477</v>
       </c>
       <c r="K18" s="13">
-        <v>1002409</v>
+        <v>1002454</v>
       </c>
       <c r="L18" s="5">
         <f t="shared" si="3"/>
-        <v>0.98402157288899617</v>
+        <v>0.98406574744327502</v>
       </c>
       <c r="M18" s="7">
         <v>1536859</v>
@@ -3209,14 +3209,14 @@
       </c>
       <c r="O18" s="4">
         <f t="shared" si="4"/>
-        <v>262090</v>
+        <v>262175</v>
       </c>
       <c r="P18" s="6">
-        <v>1521059</v>
+        <v>1521144</v>
       </c>
       <c r="Q18" s="5">
         <f t="shared" si="5"/>
-        <v>0.98971929109957391</v>
+        <v>0.98977459871074702</v>
       </c>
       <c r="R18" s="7">
         <v>1011292</v>
@@ -3226,14 +3226,14 @@
       </c>
       <c r="T18" s="4">
         <f t="shared" si="6"/>
-        <v>185828</v>
+        <v>185880</v>
       </c>
       <c r="U18" s="13">
-        <v>1004170</v>
+        <v>1004222</v>
       </c>
       <c r="V18" s="5">
         <f t="shared" si="7"/>
-        <v>0.99295752364302303</v>
+        <v>0.99300894301546927</v>
       </c>
       <c r="W18" s="7">
         <v>1030498</v>
@@ -3243,14 +3243,14 @@
       </c>
       <c r="Y18" s="4">
         <f t="shared" si="8"/>
-        <v>182970</v>
+        <v>183032</v>
       </c>
       <c r="Z18" s="13">
-        <v>1009288</v>
+        <v>1009350</v>
       </c>
       <c r="AA18" s="5">
         <f t="shared" si="9"/>
-        <v>0.97941771842351955</v>
+        <v>0.97947788350875009</v>
       </c>
       <c r="AB18" s="7">
         <v>1557879</v>
@@ -3260,14 +3260,14 @@
       </c>
       <c r="AD18" s="4">
         <f t="shared" si="10"/>
-        <v>285158</v>
+        <v>285278</v>
       </c>
       <c r="AE18" s="6">
-        <v>1537588</v>
+        <v>1537708</v>
       </c>
       <c r="AF18" s="5">
         <f t="shared" si="11"/>
-        <v>0.9869752400539451</v>
+        <v>0.98705226785905709</v>
       </c>
       <c r="AG18" s="7">
         <v>1025067</v>
@@ -3277,14 +3277,14 @@
       </c>
       <c r="AI18" s="4">
         <f t="shared" si="12"/>
-        <v>195308</v>
+        <v>195390</v>
       </c>
       <c r="AJ18" s="6">
-        <v>1018962</v>
+        <v>1019044</v>
       </c>
       <c r="AK18" s="5">
         <f t="shared" si="13"/>
-        <v>0.99404429173897901</v>
+        <v>0.99412428651005247</v>
       </c>
       <c r="AL18" s="7">
         <v>1045736</v>
@@ -3294,14 +3294,14 @@
       </c>
       <c r="AN18" s="4">
         <f t="shared" si="14"/>
-        <v>168750</v>
+        <v>168838</v>
       </c>
       <c r="AO18" s="6">
-        <v>1032181</v>
+        <v>1032269</v>
       </c>
       <c r="AP18" s="5">
         <f t="shared" si="15"/>
-        <v>0.98703783746567009</v>
+        <v>0.98712198872373147</v>
       </c>
       <c r="AQ18" s="7">
         <v>1584961</v>
@@ -3311,14 +3311,14 @@
       </c>
       <c r="AS18" s="4">
         <f t="shared" si="16"/>
-        <v>240547</v>
+        <v>240718</v>
       </c>
       <c r="AT18" s="6">
-        <v>1570956</v>
+        <v>1571127</v>
       </c>
       <c r="AU18" s="5">
         <f t="shared" si="17"/>
-        <v>0.99116382043469842</v>
+        <v>0.99127170952471388</v>
       </c>
       <c r="AV18" s="7">
         <v>1051416</v>
@@ -3328,14 +3328,14 @@
       </c>
       <c r="AX18" s="4">
         <f t="shared" si="18"/>
-        <v>177065</v>
+        <v>177180</v>
       </c>
       <c r="AY18" s="6">
-        <v>1046595</v>
+        <v>1046710</v>
       </c>
       <c r="AZ18" s="5">
         <f t="shared" si="19"/>
-        <v>0.99541475495902665</v>
+        <v>0.99552413126678685</v>
       </c>
       <c r="BA18" s="7">
         <v>1075670</v>
@@ -3345,14 +3345,14 @@
       </c>
       <c r="BC18" s="4">
         <f t="shared" si="20"/>
-        <v>179569</v>
+        <v>179703</v>
       </c>
       <c r="BD18" s="6">
-        <v>1060845</v>
+        <v>1060979</v>
       </c>
       <c r="BE18" s="5">
         <f t="shared" si="21"/>
-        <v>0.98621789210445587</v>
+        <v>0.98634246562607486</v>
       </c>
       <c r="BF18" s="7">
         <v>1620029</v>
@@ -3362,14 +3362,14 @@
       </c>
       <c r="BH18" s="4">
         <f t="shared" si="22"/>
-        <v>349703</v>
+        <v>349986</v>
       </c>
       <c r="BI18" s="6">
-        <v>1605231</v>
+        <v>1605514</v>
       </c>
       <c r="BJ18" s="5">
         <f t="shared" si="23"/>
-        <v>0.99086559561588095</v>
+        <v>0.99104028384677068</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -3387,14 +3387,14 @@
       </c>
       <c r="E19" s="4">
         <f t="shared" si="0"/>
-        <v>63449</v>
+        <v>63469</v>
       </c>
       <c r="F19" s="13">
-        <v>285023</v>
+        <v>285043</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" si="1"/>
-        <v>0.97823348720676817</v>
+        <v>0.97830212963121854</v>
       </c>
       <c r="H19" s="7">
         <v>301141</v>
@@ -3404,14 +3404,14 @@
       </c>
       <c r="J19" s="4">
         <f t="shared" si="2"/>
-        <v>54163</v>
+        <v>54190</v>
       </c>
       <c r="K19" s="13">
-        <v>289168</v>
+        <v>289195</v>
       </c>
       <c r="L19" s="5">
         <f t="shared" si="3"/>
-        <v>0.96024121590882672</v>
+        <v>0.96033087490577507</v>
       </c>
       <c r="M19" s="7">
         <v>505864</v>
@@ -3421,14 +3421,14 @@
       </c>
       <c r="O19" s="4">
         <f t="shared" si="4"/>
-        <v>88452</v>
+        <v>88490</v>
       </c>
       <c r="P19" s="6">
-        <v>496273</v>
+        <v>496311</v>
       </c>
       <c r="Q19" s="5">
         <f t="shared" si="5"/>
-        <v>0.9810403586734775</v>
+        <v>0.98111547767779483</v>
       </c>
       <c r="R19" s="7">
         <v>293000</v>
@@ -3438,14 +3438,14 @@
       </c>
       <c r="T19" s="4">
         <f t="shared" si="6"/>
-        <v>54085</v>
+        <v>54106</v>
       </c>
       <c r="U19" s="13">
-        <v>286817</v>
+        <v>286838</v>
       </c>
       <c r="V19" s="5">
         <f t="shared" si="7"/>
-        <v>0.97889761092150174</v>
+        <v>0.9789692832764505</v>
       </c>
       <c r="W19" s="7">
         <v>302979</v>
@@ -3455,14 +3455,14 @@
       </c>
       <c r="Y19" s="4">
         <f t="shared" si="8"/>
-        <v>59683</v>
+        <v>59711</v>
       </c>
       <c r="Z19" s="13">
-        <v>287743</v>
+        <v>287771</v>
       </c>
       <c r="AA19" s="5">
         <f t="shared" si="9"/>
-        <v>0.94971268635780037</v>
+        <v>0.94980510200376922</v>
       </c>
       <c r="AB19" s="7">
         <v>514622</v>
@@ -3472,14 +3472,14 @@
       </c>
       <c r="AD19" s="4">
         <f t="shared" si="10"/>
-        <v>103568</v>
+        <v>103624</v>
       </c>
       <c r="AE19" s="6">
-        <v>497201</v>
+        <v>497257</v>
       </c>
       <c r="AF19" s="5">
         <f t="shared" si="11"/>
-        <v>0.9661479688004011</v>
+        <v>0.96625678653458269</v>
       </c>
       <c r="AG19" s="7">
         <v>295766</v>
@@ -3489,14 +3489,14 @@
       </c>
       <c r="AI19" s="4">
         <f t="shared" si="12"/>
-        <v>61675</v>
+        <v>61700</v>
       </c>
       <c r="AJ19" s="6">
-        <v>287519</v>
+        <v>287544</v>
       </c>
       <c r="AK19" s="5">
         <f t="shared" si="13"/>
-        <v>0.97211647045299321</v>
+        <v>0.97220099673390448</v>
       </c>
       <c r="AL19" s="7">
         <v>302797</v>
@@ -3506,14 +3506,14 @@
       </c>
       <c r="AN19" s="4">
         <f t="shared" si="14"/>
-        <v>54620</v>
+        <v>54656</v>
       </c>
       <c r="AO19" s="6">
-        <v>291195</v>
+        <v>291231</v>
       </c>
       <c r="AP19" s="5">
         <f t="shared" si="15"/>
-        <v>0.96168390043494489</v>
+        <v>0.96180279196953733</v>
       </c>
       <c r="AQ19" s="7">
         <v>519490</v>
@@ -3523,14 +3523,14 @@
       </c>
       <c r="AS19" s="4">
         <f t="shared" si="16"/>
-        <v>88433</v>
+        <v>88513</v>
       </c>
       <c r="AT19" s="6">
-        <v>506105</v>
+        <v>506185</v>
       </c>
       <c r="AU19" s="5">
         <f t="shared" si="17"/>
-        <v>0.97423434522319963</v>
+        <v>0.97438834241275096</v>
       </c>
       <c r="AV19" s="7">
         <v>299668</v>
@@ -3540,14 +3540,14 @@
       </c>
       <c r="AX19" s="4">
         <f t="shared" si="18"/>
-        <v>55930</v>
+        <v>55977</v>
       </c>
       <c r="AY19" s="6">
-        <v>294880</v>
+        <v>294927</v>
       </c>
       <c r="AZ19" s="5">
         <f t="shared" si="19"/>
-        <v>0.98402231803195539</v>
+        <v>0.98417915826848379</v>
       </c>
       <c r="BA19" s="7">
         <v>313772</v>
@@ -3557,14 +3557,14 @@
       </c>
       <c r="BC19" s="4">
         <f t="shared" si="20"/>
-        <v>57854</v>
+        <v>57921</v>
       </c>
       <c r="BD19" s="6">
-        <v>299510</v>
+        <v>299577</v>
       </c>
       <c r="BE19" s="5">
         <f t="shared" si="21"/>
-        <v>0.95454661346455383</v>
+        <v>0.95476014430860623</v>
       </c>
       <c r="BF19" s="7">
         <v>528004</v>
@@ -3574,14 +3574,14 @@
       </c>
       <c r="BH19" s="4">
         <f t="shared" si="22"/>
-        <v>133349</v>
+        <v>133510</v>
       </c>
       <c r="BI19" s="6">
-        <v>516756</v>
+        <v>516917</v>
       </c>
       <c r="BJ19" s="5">
         <f t="shared" si="23"/>
-        <v>0.97869713108234024</v>
+        <v>0.97900205301474985</v>
       </c>
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.3">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="E20" s="4">
         <f t="shared" si="0"/>
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="F20" s="13">
-        <v>6422</v>
+        <v>6423</v>
       </c>
       <c r="G20" s="5">
         <f t="shared" si="1"/>
-        <v>0.99380996595481275</v>
+        <v>0.99396471680594245</v>
       </c>
       <c r="H20" s="7">
         <v>6957</v>
@@ -3633,14 +3633,14 @@
       </c>
       <c r="O20" s="4">
         <f t="shared" si="4"/>
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="P20" s="6">
-        <v>9836</v>
+        <v>9837</v>
       </c>
       <c r="Q20" s="5">
         <f t="shared" si="5"/>
-        <v>0.98884085653966025</v>
+        <v>0.98894138936362719</v>
       </c>
       <c r="R20" s="7">
         <v>6587</v>
@@ -3701,14 +3701,14 @@
       </c>
       <c r="AI20" s="4">
         <f t="shared" si="12"/>
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="AJ20" s="6">
-        <v>6491</v>
+        <v>6492</v>
       </c>
       <c r="AK20" s="5">
         <f t="shared" si="13"/>
-        <v>0.99159792239535594</v>
+        <v>0.99175068744271311</v>
       </c>
       <c r="AL20" s="7">
         <v>6627</v>
@@ -3769,14 +3769,14 @@
       </c>
       <c r="BC20" s="4">
         <f t="shared" si="20"/>
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="BD20" s="6">
-        <v>6520</v>
+        <v>6521</v>
       </c>
       <c r="BE20" s="5">
         <f t="shared" si="21"/>
-        <v>0.99329677026203533</v>
+        <v>0.9934491163924436</v>
       </c>
       <c r="BF20" s="7">
         <v>10109</v>
@@ -3786,14 +3786,14 @@
       </c>
       <c r="BH20" s="4">
         <f t="shared" si="22"/>
-        <v>3044</v>
+        <v>3046</v>
       </c>
       <c r="BI20" s="6">
-        <v>10068</v>
+        <v>10070</v>
       </c>
       <c r="BJ20" s="5">
         <f t="shared" si="23"/>
-        <v>0.99594420813136808</v>
+        <v>0.99614205163715497</v>
       </c>
     </row>
     <row r="21" spans="1:62" x14ac:dyDescent="0.3">
@@ -3811,14 +3811,14 @@
       </c>
       <c r="E21" s="4">
         <f t="shared" si="0"/>
-        <v>4205</v>
+        <v>4210</v>
       </c>
       <c r="F21" s="13">
-        <v>10918</v>
+        <v>10923</v>
       </c>
       <c r="G21" s="5">
         <f t="shared" si="1"/>
-        <v>0.9937198507326841</v>
+        <v>0.99417493401292434</v>
       </c>
       <c r="H21" s="7">
         <v>10970</v>
@@ -3828,14 +3828,14 @@
       </c>
       <c r="J21" s="4">
         <f t="shared" si="2"/>
-        <v>3483</v>
+        <v>3488</v>
       </c>
       <c r="K21" s="13">
-        <v>10960</v>
+        <v>10965</v>
       </c>
       <c r="L21" s="5">
         <f t="shared" si="3"/>
-        <v>0.99908842297174116</v>
+        <v>0.99954421148587058</v>
       </c>
       <c r="M21" s="7">
         <v>14288</v>
@@ -3845,14 +3845,14 @@
       </c>
       <c r="O21" s="4">
         <f t="shared" si="4"/>
-        <v>4657</v>
+        <v>4662</v>
       </c>
       <c r="P21" s="6">
-        <v>14539</v>
+        <v>14544</v>
       </c>
       <c r="Q21" s="5">
         <f t="shared" si="5"/>
-        <v>1.01756718924972</v>
+        <v>1.0179171332586787</v>
       </c>
       <c r="R21" s="7">
         <v>10910</v>
@@ -3862,14 +3862,14 @@
       </c>
       <c r="T21" s="4">
         <f t="shared" si="6"/>
-        <v>3697</v>
+        <v>3702</v>
       </c>
       <c r="U21" s="13">
-        <v>11195</v>
+        <v>11200</v>
       </c>
       <c r="V21" s="5">
         <f t="shared" si="7"/>
-        <v>1.0261228230980752</v>
+        <v>1.0265811182401468</v>
       </c>
       <c r="W21" s="7">
         <v>11256</v>
@@ -3879,14 +3879,14 @@
       </c>
       <c r="Y21" s="4">
         <f t="shared" si="8"/>
-        <v>3680</v>
+        <v>3686</v>
       </c>
       <c r="Z21" s="13">
-        <v>11319</v>
+        <v>11325</v>
       </c>
       <c r="AA21" s="5">
         <f t="shared" si="9"/>
-        <v>1.0055970149253732</v>
+        <v>1.0061300639658848</v>
       </c>
       <c r="AB21" s="7">
         <v>14831</v>
@@ -3896,14 +3896,14 @@
       </c>
       <c r="AD21" s="4">
         <f t="shared" si="10"/>
-        <v>4899</v>
+        <v>4909</v>
       </c>
       <c r="AE21" s="6">
-        <v>14988</v>
+        <v>14998</v>
       </c>
       <c r="AF21" s="5">
         <f t="shared" si="11"/>
-        <v>1.0105859348661588</v>
+        <v>1.0112601982334299</v>
       </c>
       <c r="AG21" s="7">
         <v>11222</v>
@@ -3913,14 +3913,14 @@
       </c>
       <c r="AI21" s="4">
         <f t="shared" si="12"/>
-        <v>3716</v>
+        <v>3725</v>
       </c>
       <c r="AJ21" s="6">
-        <v>11359</v>
+        <v>11368</v>
       </c>
       <c r="AK21" s="5">
         <f t="shared" si="13"/>
-        <v>1.012208162537872</v>
+        <v>1.0130101586170024</v>
       </c>
       <c r="AL21" s="7">
         <v>11337</v>
@@ -3930,14 +3930,14 @@
       </c>
       <c r="AN21" s="4">
         <f t="shared" si="14"/>
-        <v>3496</v>
+        <v>3505</v>
       </c>
       <c r="AO21" s="6">
-        <v>11521</v>
+        <v>11530</v>
       </c>
       <c r="AP21" s="5">
         <f t="shared" si="15"/>
-        <v>1.0162300432213107</v>
+        <v>1.0170239040310487</v>
       </c>
       <c r="AQ21" s="7">
         <v>15149</v>
@@ -3947,14 +3947,14 @@
       </c>
       <c r="AS21" s="4">
         <f t="shared" si="16"/>
-        <v>4577</v>
+        <v>4594</v>
       </c>
       <c r="AT21" s="6">
-        <v>15391</v>
+        <v>15408</v>
       </c>
       <c r="AU21" s="5">
         <f t="shared" si="17"/>
-        <v>1.0159746517921975</v>
+        <v>1.0170968380751204</v>
       </c>
       <c r="AV21" s="7">
         <v>11422</v>
@@ -3964,14 +3964,14 @@
       </c>
       <c r="AX21" s="4">
         <f t="shared" si="18"/>
-        <v>3632</v>
+        <v>3644</v>
       </c>
       <c r="AY21" s="6">
-        <v>11706</v>
+        <v>11718</v>
       </c>
       <c r="AZ21" s="5">
         <f t="shared" si="19"/>
-        <v>1.0248642969707582</v>
+        <v>1.0259149010681141</v>
       </c>
       <c r="BA21" s="7">
         <v>11689</v>
@@ -3981,14 +3981,14 @@
       </c>
       <c r="BC21" s="4">
         <f t="shared" si="20"/>
-        <v>3510</v>
+        <v>3524</v>
       </c>
       <c r="BD21" s="6">
-        <v>11832</v>
+        <v>11846</v>
       </c>
       <c r="BE21" s="5">
         <f t="shared" si="21"/>
-        <v>1.0122337240140302</v>
+        <v>1.0134314312601591</v>
       </c>
       <c r="BF21" s="7">
         <v>15725</v>
@@ -3998,14 +3998,14 @@
       </c>
       <c r="BH21" s="4">
         <f t="shared" si="22"/>
-        <v>6351</v>
+        <v>6376</v>
       </c>
       <c r="BI21" s="6">
-        <v>15796</v>
+        <v>15821</v>
       </c>
       <c r="BJ21" s="5">
         <f t="shared" si="23"/>
-        <v>1.0045151033386328</v>
+        <v>1.0061049284578696</v>
       </c>
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.3">
@@ -4023,14 +4023,14 @@
       </c>
       <c r="E22" s="4">
         <f t="shared" si="0"/>
-        <v>1811</v>
+        <v>1814</v>
       </c>
       <c r="F22" s="13">
-        <v>6682</v>
+        <v>6685</v>
       </c>
       <c r="G22" s="5">
         <f t="shared" si="1"/>
-        <v>0.98904677323860268</v>
+        <v>0.98949082297217283</v>
       </c>
       <c r="H22" s="7">
         <v>6770</v>
@@ -4040,14 +4040,14 @@
       </c>
       <c r="J22" s="4">
         <f t="shared" si="2"/>
-        <v>1675</v>
+        <v>1678</v>
       </c>
       <c r="K22" s="13">
-        <v>6767</v>
+        <v>6770</v>
       </c>
       <c r="L22" s="5">
         <f t="shared" si="3"/>
-        <v>0.99955686853766612</v>
+        <v>1</v>
       </c>
       <c r="M22" s="7">
         <v>8074</v>
@@ -4057,14 +4057,14 @@
       </c>
       <c r="O22" s="4">
         <f t="shared" si="4"/>
-        <v>1993</v>
+        <v>2000</v>
       </c>
       <c r="P22" s="6">
-        <v>8080</v>
+        <v>8087</v>
       </c>
       <c r="Q22" s="5">
         <f t="shared" si="5"/>
-        <v>1.0007431260837256</v>
+        <v>1.0016101065147387</v>
       </c>
       <c r="R22" s="7">
         <v>6748</v>
@@ -4074,14 +4074,14 @@
       </c>
       <c r="T22" s="4">
         <f t="shared" si="6"/>
-        <v>1758</v>
+        <v>1761</v>
       </c>
       <c r="U22" s="13">
-        <v>6793</v>
+        <v>6796</v>
       </c>
       <c r="V22" s="5">
         <f t="shared" si="7"/>
-        <v>1.0066686425607587</v>
+        <v>1.007113218731476</v>
       </c>
       <c r="W22" s="7">
         <v>6876</v>
@@ -4091,14 +4091,14 @@
       </c>
       <c r="Y22" s="4">
         <f t="shared" si="8"/>
-        <v>1688</v>
+        <v>1691</v>
       </c>
       <c r="Z22" s="13">
-        <v>6854</v>
+        <v>6857</v>
       </c>
       <c r="AA22" s="5">
         <f t="shared" si="9"/>
-        <v>0.99680046538685285</v>
+        <v>0.99723676556137286</v>
       </c>
       <c r="AB22" s="7">
         <v>8219</v>
@@ -4108,14 +4108,14 @@
       </c>
       <c r="AD22" s="4">
         <f t="shared" si="10"/>
-        <v>2251</v>
+        <v>2257</v>
       </c>
       <c r="AE22" s="6">
-        <v>8236</v>
+        <v>8242</v>
       </c>
       <c r="AF22" s="5">
         <f t="shared" si="11"/>
-        <v>1.0020683781481932</v>
+        <v>1.0027983939652025</v>
       </c>
       <c r="AG22" s="7">
         <v>6901</v>
@@ -4125,14 +4125,14 @@
       </c>
       <c r="AI22" s="4">
         <f t="shared" si="12"/>
-        <v>1730</v>
+        <v>1733</v>
       </c>
       <c r="AJ22" s="6">
-        <v>6912</v>
+        <v>6915</v>
       </c>
       <c r="AK22" s="5">
         <f t="shared" si="13"/>
-        <v>1.0015939718881322</v>
+        <v>1.0020286914939864</v>
       </c>
       <c r="AL22" s="7">
         <v>6948</v>
@@ -4142,14 +4142,14 @@
       </c>
       <c r="AN22" s="4">
         <f t="shared" si="14"/>
-        <v>1718</v>
+        <v>1721</v>
       </c>
       <c r="AO22" s="6">
-        <v>6947</v>
+        <v>6950</v>
       </c>
       <c r="AP22" s="5">
         <f t="shared" si="15"/>
-        <v>0.99985607369027063</v>
+        <v>1.0002878526194587</v>
       </c>
       <c r="AQ22" s="7">
         <v>8297</v>
@@ -4159,14 +4159,14 @@
       </c>
       <c r="AS22" s="4">
         <f t="shared" si="16"/>
-        <v>2131</v>
+        <v>2137</v>
       </c>
       <c r="AT22" s="6">
-        <v>8306</v>
+        <v>8312</v>
       </c>
       <c r="AU22" s="5">
         <f t="shared" si="17"/>
-        <v>1.0010847294202725</v>
+        <v>1.0018078823671206</v>
       </c>
       <c r="AV22" s="7">
         <v>6958</v>
@@ -4176,14 +4176,14 @@
       </c>
       <c r="AX22" s="4">
         <f t="shared" si="18"/>
-        <v>1864</v>
+        <v>1870</v>
       </c>
       <c r="AY22" s="6">
-        <v>6990</v>
+        <v>6996</v>
       </c>
       <c r="AZ22" s="5">
         <f t="shared" si="19"/>
-        <v>1.0045990227076746</v>
+        <v>1.0054613394653635</v>
       </c>
       <c r="BA22" s="7">
         <v>7049</v>
@@ -4193,14 +4193,14 @@
       </c>
       <c r="BC22" s="4">
         <f t="shared" si="20"/>
-        <v>1744</v>
+        <v>1752</v>
       </c>
       <c r="BD22" s="6">
-        <v>7050</v>
+        <v>7058</v>
       </c>
       <c r="BE22" s="5">
         <f t="shared" si="21"/>
-        <v>1.0001418640941977</v>
+        <v>1.0012767768477799</v>
       </c>
       <c r="BF22" s="7">
         <v>8436</v>
@@ -4210,14 +4210,14 @@
       </c>
       <c r="BH22" s="4">
         <f t="shared" si="22"/>
-        <v>2672</v>
+        <v>2685</v>
       </c>
       <c r="BI22" s="6">
-        <v>8411</v>
+        <v>8424</v>
       </c>
       <c r="BJ22" s="5">
         <f t="shared" si="23"/>
-        <v>0.99703651019440498</v>
+        <v>0.99857752489331442</v>
       </c>
     </row>
     <row r="23" spans="1:62" x14ac:dyDescent="0.3">
@@ -4235,14 +4235,14 @@
       </c>
       <c r="E23" s="4">
         <f t="shared" si="0"/>
-        <v>3053</v>
+        <v>3057</v>
       </c>
       <c r="F23" s="13">
-        <v>8678</v>
+        <v>8682</v>
       </c>
       <c r="G23" s="5">
         <f t="shared" si="1"/>
-        <v>0.98524069028156225</v>
+        <v>0.98569482288828336</v>
       </c>
       <c r="H23" s="7">
         <v>8878</v>
@@ -4252,14 +4252,14 @@
       </c>
       <c r="J23" s="4">
         <f t="shared" si="2"/>
-        <v>2884</v>
+        <v>2888</v>
       </c>
       <c r="K23" s="13">
-        <v>8791</v>
+        <v>8795</v>
       </c>
       <c r="L23" s="5">
         <f t="shared" si="3"/>
-        <v>0.99020049560711876</v>
+        <v>0.99065104753322819</v>
       </c>
       <c r="M23" s="7">
         <v>11255</v>
@@ -4269,14 +4269,14 @@
       </c>
       <c r="O23" s="4">
         <f t="shared" si="4"/>
-        <v>3407</v>
+        <v>3415</v>
       </c>
       <c r="P23" s="6">
-        <v>11213</v>
+        <v>11221</v>
       </c>
       <c r="Q23" s="5">
         <f t="shared" si="5"/>
-        <v>0.99626832518880493</v>
+        <v>0.99697912039093739</v>
       </c>
       <c r="R23" s="7">
         <v>8944</v>
@@ -4286,14 +4286,14 @@
       </c>
       <c r="T23" s="4">
         <f t="shared" si="6"/>
-        <v>2661</v>
+        <v>2666</v>
       </c>
       <c r="U23" s="13">
-        <v>8919</v>
+        <v>8924</v>
       </c>
       <c r="V23" s="5">
         <f t="shared" si="7"/>
-        <v>0.99720483005366722</v>
+        <v>0.99776386404293382</v>
       </c>
       <c r="W23" s="7">
         <v>10422</v>
@@ -4303,14 +4303,14 @@
       </c>
       <c r="Y23" s="4">
         <f t="shared" si="8"/>
-        <v>2951</v>
+        <v>2958</v>
       </c>
       <c r="Z23" s="13">
-        <v>9028</v>
+        <v>9035</v>
       </c>
       <c r="AA23" s="5">
         <f t="shared" si="9"/>
-        <v>0.86624448282479372</v>
+        <v>0.86691613893686437</v>
       </c>
       <c r="AB23" s="7">
         <v>11673</v>
@@ -4320,14 +4320,14 @@
       </c>
       <c r="AD23" s="4">
         <f t="shared" si="10"/>
-        <v>3727</v>
+        <v>3734</v>
       </c>
       <c r="AE23" s="6">
-        <v>11399</v>
+        <v>11406</v>
       </c>
       <c r="AF23" s="5">
         <f t="shared" si="11"/>
-        <v>0.97652702818469972</v>
+        <v>0.97712670264713442</v>
       </c>
       <c r="AG23" s="7">
         <v>9370</v>
@@ -4337,14 +4337,14 @@
       </c>
       <c r="AI23" s="4">
         <f t="shared" si="12"/>
-        <v>4414</v>
+        <v>4419</v>
       </c>
       <c r="AJ23" s="6">
-        <v>9000</v>
+        <v>9005</v>
       </c>
       <c r="AK23" s="5">
         <f t="shared" si="13"/>
-        <v>0.96051227321237997</v>
+        <v>0.96104589114194239</v>
       </c>
       <c r="AL23" s="7">
         <v>9238</v>
@@ -4354,14 +4354,14 @@
       </c>
       <c r="AN23" s="4">
         <f t="shared" si="14"/>
-        <v>2635</v>
+        <v>2639</v>
       </c>
       <c r="AO23" s="6">
-        <v>9038</v>
+        <v>9042</v>
       </c>
       <c r="AP23" s="5">
         <f t="shared" si="15"/>
-        <v>0.9783502922710543</v>
+        <v>0.97878328642563328</v>
       </c>
       <c r="AQ23" s="7">
         <v>11727</v>
@@ -4371,14 +4371,14 @@
       </c>
       <c r="AS23" s="4">
         <f t="shared" si="16"/>
-        <v>3115</v>
+        <v>3123</v>
       </c>
       <c r="AT23" s="6">
-        <v>11527</v>
+        <v>11535</v>
       </c>
       <c r="AU23" s="5">
         <f t="shared" si="17"/>
-        <v>0.98294533981410426</v>
+        <v>0.98362752622154004</v>
       </c>
       <c r="AV23" s="7">
         <v>9359</v>
@@ -4388,14 +4388,14 @@
       </c>
       <c r="AX23" s="4">
         <f t="shared" si="18"/>
-        <v>2775</v>
+        <v>2782</v>
       </c>
       <c r="AY23" s="6">
-        <v>9158</v>
+        <v>9165</v>
       </c>
       <c r="AZ23" s="5">
         <f t="shared" si="19"/>
-        <v>0.9785233465113794</v>
+        <v>0.9792712896676995</v>
       </c>
       <c r="BA23" s="7">
         <v>9570</v>
@@ -4405,14 +4405,14 @@
       </c>
       <c r="BC23" s="4">
         <f t="shared" si="20"/>
-        <v>2903</v>
+        <v>2913</v>
       </c>
       <c r="BD23" s="6">
-        <v>9212</v>
+        <v>9222</v>
       </c>
       <c r="BE23" s="5">
         <f t="shared" si="21"/>
-        <v>0.96259143155694882</v>
+        <v>0.96363636363636362</v>
       </c>
       <c r="BF23" s="7">
         <v>11968</v>
@@ -4422,14 +4422,14 @@
       </c>
       <c r="BH23" s="4">
         <f t="shared" si="22"/>
-        <v>4311</v>
+        <v>4327</v>
       </c>
       <c r="BI23" s="6">
-        <v>11711</v>
+        <v>11727</v>
       </c>
       <c r="BJ23" s="5">
         <f t="shared" si="23"/>
-        <v>0.97852606951871657</v>
+        <v>0.9798629679144385</v>
       </c>
     </row>
     <row r="24" spans="1:62" x14ac:dyDescent="0.3">
@@ -4447,14 +4447,14 @@
       </c>
       <c r="E24" s="4">
         <f t="shared" si="0"/>
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="F24" s="13">
-        <v>6183</v>
+        <v>6184</v>
       </c>
       <c r="G24" s="5">
         <f t="shared" si="1"/>
-        <v>0.98928000000000005</v>
+        <v>0.98943999999999999</v>
       </c>
       <c r="H24" s="7">
         <v>6322</v>
@@ -4464,14 +4464,14 @@
       </c>
       <c r="J24" s="4">
         <f t="shared" si="2"/>
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="K24" s="13">
-        <v>6234</v>
+        <v>6235</v>
       </c>
       <c r="L24" s="5">
         <f t="shared" si="3"/>
-        <v>0.98608035431825369</v>
+        <v>0.98623853211009171</v>
       </c>
       <c r="M24" s="7">
         <v>7266</v>
@@ -4481,14 +4481,14 @@
       </c>
       <c r="O24" s="4">
         <f t="shared" si="4"/>
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="P24" s="6">
-        <v>7153</v>
+        <v>7154</v>
       </c>
       <c r="Q24" s="5">
         <f t="shared" si="5"/>
-        <v>0.98444811450591796</v>
+        <v>0.98458574181117531</v>
       </c>
       <c r="R24" s="7">
         <v>6403</v>
@@ -4498,14 +4498,14 @@
       </c>
       <c r="T24" s="4">
         <f t="shared" si="6"/>
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="U24" s="13">
-        <v>6298</v>
+        <v>6300</v>
       </c>
       <c r="V24" s="5">
         <f t="shared" si="7"/>
-        <v>0.9836014368264876</v>
+        <v>0.983913790410745</v>
       </c>
       <c r="W24" s="7">
         <v>6540</v>
@@ -4515,14 +4515,14 @@
       </c>
       <c r="Y24" s="4">
         <f t="shared" si="8"/>
-        <v>1298</v>
+        <v>1301</v>
       </c>
       <c r="Z24" s="13">
-        <v>6405</v>
+        <v>6408</v>
       </c>
       <c r="AA24" s="5">
         <f t="shared" si="9"/>
-        <v>0.97935779816513757</v>
+        <v>0.97981651376146794</v>
       </c>
       <c r="AB24" s="7">
         <v>7473</v>
@@ -4532,14 +4532,14 @@
       </c>
       <c r="AD24" s="4">
         <f t="shared" si="10"/>
-        <v>1730</v>
+        <v>1733</v>
       </c>
       <c r="AE24" s="6">
-        <v>7374</v>
+        <v>7377</v>
       </c>
       <c r="AF24" s="5">
         <f t="shared" si="11"/>
-        <v>0.98675230830991567</v>
+        <v>0.98715375351264556</v>
       </c>
       <c r="AG24" s="7">
         <v>6660</v>
@@ -4549,14 +4549,14 @@
       </c>
       <c r="AI24" s="4">
         <f t="shared" si="12"/>
-        <v>1432</v>
+        <v>1435</v>
       </c>
       <c r="AJ24" s="6">
-        <v>6586</v>
+        <v>6589</v>
       </c>
       <c r="AK24" s="5">
         <f t="shared" si="13"/>
-        <v>0.98888888888888893</v>
+        <v>0.98933933933933937</v>
       </c>
       <c r="AL24" s="7">
         <v>6723</v>
@@ -4566,14 +4566,14 @@
       </c>
       <c r="AN24" s="4">
         <f t="shared" si="14"/>
-        <v>1370</v>
+        <v>1373</v>
       </c>
       <c r="AO24" s="6">
-        <v>6633</v>
+        <v>6636</v>
       </c>
       <c r="AP24" s="5">
         <f t="shared" si="15"/>
-        <v>0.98661311914323957</v>
+        <v>0.98705934850513166</v>
       </c>
       <c r="AQ24" s="7">
         <v>7657</v>
@@ -4583,14 +4583,14 @@
       </c>
       <c r="AS24" s="4">
         <f t="shared" si="16"/>
-        <v>1573</v>
+        <v>1577</v>
       </c>
       <c r="AT24" s="6">
-        <v>7556</v>
+        <v>7560</v>
       </c>
       <c r="AU24" s="5">
         <f t="shared" si="17"/>
-        <v>0.98680945540028731</v>
+        <v>0.98733185320621653</v>
       </c>
       <c r="AV24" s="7">
         <v>6786</v>
@@ -4600,14 +4600,14 @@
       </c>
       <c r="AX24" s="4">
         <f t="shared" si="18"/>
-        <v>1438</v>
+        <v>1442</v>
       </c>
       <c r="AY24" s="6">
-        <v>6741</v>
+        <v>6745</v>
       </c>
       <c r="AZ24" s="5">
         <f t="shared" si="19"/>
-        <v>0.99336870026525204</v>
+        <v>0.99395814913056291</v>
       </c>
       <c r="BA24" s="7">
         <v>7025</v>
@@ -4617,14 +4617,14 @@
       </c>
       <c r="BC24" s="4">
         <f t="shared" si="20"/>
-        <v>1291</v>
+        <v>1296</v>
       </c>
       <c r="BD24" s="6">
-        <v>6801</v>
+        <v>6806</v>
       </c>
       <c r="BE24" s="5">
         <f t="shared" si="21"/>
-        <v>0.96811387900355872</v>
+        <v>0.96882562277580075</v>
       </c>
       <c r="BF24" s="7">
         <v>7878</v>
@@ -4634,14 +4634,14 @@
       </c>
       <c r="BH24" s="4">
         <f t="shared" si="22"/>
-        <v>1971</v>
+        <v>1978</v>
       </c>
       <c r="BI24" s="6">
-        <v>7741</v>
+        <v>7748</v>
       </c>
       <c r="BJ24" s="5">
         <f t="shared" si="23"/>
-        <v>0.98260979944148263</v>
+        <v>0.98349834983498352</v>
       </c>
     </row>
     <row r="25" spans="1:62" x14ac:dyDescent="0.3">
@@ -4659,14 +4659,14 @@
       </c>
       <c r="E25" s="4">
         <f t="shared" si="0"/>
-        <v>4285</v>
+        <v>4290</v>
       </c>
       <c r="F25" s="13">
-        <v>20229</v>
+        <v>20234</v>
       </c>
       <c r="G25" s="5">
         <f t="shared" si="1"/>
-        <v>0.96659977064220182</v>
+        <v>0.96683868501529047</v>
       </c>
       <c r="H25" s="7">
         <v>20519</v>
@@ -4676,14 +4676,14 @@
       </c>
       <c r="J25" s="4">
         <f t="shared" si="2"/>
-        <v>3843</v>
+        <v>3848</v>
       </c>
       <c r="K25" s="13">
-        <v>20330</v>
+        <v>20335</v>
       </c>
       <c r="L25" s="5">
         <f t="shared" si="3"/>
-        <v>0.99078902480627706</v>
+        <v>0.99103270139870359</v>
       </c>
       <c r="M25" s="7">
         <v>27924</v>
@@ -4693,14 +4693,14 @@
       </c>
       <c r="O25" s="4">
         <f t="shared" si="4"/>
-        <v>5549</v>
+        <v>5560</v>
       </c>
       <c r="P25" s="6">
-        <v>27881</v>
+        <v>27892</v>
       </c>
       <c r="Q25" s="5">
         <f t="shared" si="5"/>
-        <v>0.99846010600200541</v>
+        <v>0.9988540323735855</v>
       </c>
       <c r="R25" s="7">
         <v>20481</v>
@@ -4710,14 +4710,14 @@
       </c>
       <c r="T25" s="4">
         <f t="shared" si="6"/>
-        <v>4498</v>
+        <v>4506</v>
       </c>
       <c r="U25" s="13">
-        <v>20519</v>
+        <v>20527</v>
       </c>
       <c r="V25" s="5">
         <f t="shared" si="7"/>
-        <v>1.0018553781553634</v>
+        <v>1.0022459840828084</v>
       </c>
       <c r="W25" s="7">
         <v>20934</v>
@@ -4727,14 +4727,14 @@
       </c>
       <c r="Y25" s="4">
         <f t="shared" si="8"/>
-        <v>4222</v>
+        <v>4232</v>
       </c>
       <c r="Z25" s="13">
-        <v>20621</v>
+        <v>20631</v>
       </c>
       <c r="AA25" s="5">
         <f t="shared" si="9"/>
-        <v>0.9850482468711188</v>
+        <v>0.98552593866437377</v>
       </c>
       <c r="AB25" s="7">
         <v>28211</v>
@@ -4744,14 +4744,14 @@
       </c>
       <c r="AD25" s="4">
         <f t="shared" si="10"/>
-        <v>6229</v>
+        <v>6240</v>
       </c>
       <c r="AE25" s="6">
-        <v>28188</v>
+        <v>28199</v>
       </c>
       <c r="AF25" s="5">
         <f t="shared" si="11"/>
-        <v>0.99918471518202123</v>
+        <v>0.99957463400801105</v>
       </c>
       <c r="AG25" s="7">
         <v>20778</v>
@@ -4761,14 +4761,14 @@
       </c>
       <c r="AI25" s="4">
         <f t="shared" si="12"/>
-        <v>4156</v>
+        <v>4165</v>
       </c>
       <c r="AJ25" s="6">
-        <v>20721</v>
+        <v>20730</v>
       </c>
       <c r="AK25" s="5">
         <f t="shared" si="13"/>
-        <v>0.99725671383193759</v>
+        <v>0.99768986427952644</v>
       </c>
       <c r="AL25" s="7">
         <v>21081</v>
@@ -4778,14 +4778,14 @@
       </c>
       <c r="AN25" s="4">
         <f t="shared" si="14"/>
-        <v>4100</v>
+        <v>4110</v>
       </c>
       <c r="AO25" s="6">
-        <v>20895</v>
+        <v>20905</v>
       </c>
       <c r="AP25" s="5">
         <f t="shared" si="15"/>
-        <v>0.99117688914188129</v>
+        <v>0.99165124994070486</v>
       </c>
       <c r="AQ25" s="7">
         <v>28478</v>
@@ -4795,14 +4795,14 @@
       </c>
       <c r="AS25" s="4">
         <f t="shared" si="16"/>
-        <v>5126</v>
+        <v>5139</v>
       </c>
       <c r="AT25" s="6">
-        <v>28451</v>
+        <v>28464</v>
       </c>
       <c r="AU25" s="5">
         <f t="shared" si="17"/>
-        <v>0.99905189971205843</v>
+        <v>0.99950839244328959</v>
       </c>
       <c r="AV25" s="7">
         <v>21086</v>
@@ -4812,14 +4812,14 @@
       </c>
       <c r="AX25" s="4">
         <f t="shared" si="18"/>
-        <v>4330</v>
+        <v>4339</v>
       </c>
       <c r="AY25" s="6">
-        <v>21062</v>
+        <v>21071</v>
       </c>
       <c r="AZ25" s="5">
         <f t="shared" si="19"/>
-        <v>0.99886180404059566</v>
+        <v>0.99928862752537229</v>
       </c>
       <c r="BA25" s="7">
         <v>21405</v>
@@ -4829,14 +4829,14 @@
       </c>
       <c r="BC25" s="4">
         <f t="shared" si="20"/>
-        <v>4400</v>
+        <v>4409</v>
       </c>
       <c r="BD25" s="6">
-        <v>21232</v>
+        <v>21241</v>
       </c>
       <c r="BE25" s="5">
         <f t="shared" si="21"/>
-        <v>0.99191777622050925</v>
+        <v>0.99233823872926885</v>
       </c>
       <c r="BF25" s="7">
         <v>28924</v>
@@ -4846,14 +4846,14 @@
       </c>
       <c r="BH25" s="4">
         <f t="shared" si="22"/>
-        <v>7997</v>
+        <v>8014</v>
       </c>
       <c r="BI25" s="6">
-        <v>28811</v>
+        <v>28828</v>
       </c>
       <c r="BJ25" s="5">
         <f t="shared" si="23"/>
-        <v>0.99609320979117688</v>
+        <v>0.99668095699073433</v>
       </c>
     </row>
     <row r="26" spans="1:62" x14ac:dyDescent="0.3">
@@ -4871,14 +4871,14 @@
       </c>
       <c r="E26" s="4">
         <f t="shared" si="0"/>
-        <v>3357</v>
+        <v>3368</v>
       </c>
       <c r="F26" s="13">
-        <v>14073</v>
+        <v>14084</v>
       </c>
       <c r="G26" s="5">
         <f t="shared" si="1"/>
-        <v>0.99936088623775032</v>
+        <v>1.0001420252805</v>
       </c>
       <c r="H26" s="7">
         <v>14494</v>
@@ -4888,14 +4888,14 @@
       </c>
       <c r="J26" s="4">
         <f t="shared" si="2"/>
-        <v>3072</v>
+        <v>3083</v>
       </c>
       <c r="K26" s="13">
-        <v>14339</v>
+        <v>14350</v>
       </c>
       <c r="L26" s="5">
         <f t="shared" si="3"/>
-        <v>0.98930591969090653</v>
+        <v>0.99006485442251968</v>
       </c>
       <c r="M26" s="7">
         <v>27473</v>
@@ -4905,14 +4905,14 @@
       </c>
       <c r="O26" s="4">
         <f t="shared" si="4"/>
-        <v>5279</v>
+        <v>5295</v>
       </c>
       <c r="P26" s="6">
-        <v>27394</v>
+        <v>27410</v>
       </c>
       <c r="Q26" s="5">
         <f t="shared" si="5"/>
-        <v>0.99712444945946932</v>
+        <v>0.9977068394423616</v>
       </c>
       <c r="R26" s="7">
         <v>14274</v>
@@ -4922,14 +4922,14 @@
       </c>
       <c r="T26" s="4">
         <f t="shared" si="6"/>
-        <v>3391</v>
+        <v>3401</v>
       </c>
       <c r="U26" s="13">
-        <v>14293</v>
+        <v>14303</v>
       </c>
       <c r="V26" s="5">
         <f t="shared" si="7"/>
-        <v>1.001331091495026</v>
+        <v>1.0020316659660922</v>
       </c>
       <c r="W26" s="7">
         <v>14651</v>
@@ -4939,14 +4939,14 @@
       </c>
       <c r="Y26" s="4">
         <f t="shared" si="8"/>
-        <v>3130</v>
+        <v>3138</v>
       </c>
       <c r="Z26" s="13">
-        <v>14443</v>
+        <v>14451</v>
       </c>
       <c r="AA26" s="5">
         <f t="shared" si="9"/>
-        <v>0.98580301685891747</v>
+        <v>0.98634905467203604</v>
       </c>
       <c r="AB26" s="7">
         <v>28023</v>
@@ -4956,14 +4956,14 @@
       </c>
       <c r="AD26" s="4">
         <f t="shared" si="10"/>
-        <v>5769</v>
+        <v>5784</v>
       </c>
       <c r="AE26" s="6">
-        <v>27658</v>
+        <v>27673</v>
       </c>
       <c r="AF26" s="5">
         <f t="shared" si="11"/>
-        <v>0.98697498483388646</v>
+        <v>0.98751025942975412</v>
       </c>
       <c r="AG26" s="7">
         <v>14346</v>
@@ -4973,14 +4973,14 @@
       </c>
       <c r="AI26" s="4">
         <f t="shared" si="12"/>
-        <v>3081</v>
+        <v>3088</v>
       </c>
       <c r="AJ26" s="6">
-        <v>14312</v>
+        <v>14319</v>
       </c>
       <c r="AK26" s="5">
         <f t="shared" si="13"/>
-        <v>0.99763000139411684</v>
+        <v>0.99811794228356332</v>
       </c>
       <c r="AL26" s="7">
         <v>14687</v>
@@ -4990,14 +4990,14 @@
       </c>
       <c r="AN26" s="4">
         <f t="shared" si="14"/>
-        <v>2997</v>
+        <v>3007</v>
       </c>
       <c r="AO26" s="6">
-        <v>14440</v>
+        <v>14450</v>
       </c>
       <c r="AP26" s="5">
         <f t="shared" si="15"/>
-        <v>0.98318240620957309</v>
+        <v>0.98386328045210047</v>
       </c>
       <c r="AQ26" s="7">
         <v>27948</v>
@@ -5007,14 +5007,14 @@
       </c>
       <c r="AS26" s="4">
         <f t="shared" si="16"/>
-        <v>5318</v>
+        <v>5336</v>
       </c>
       <c r="AT26" s="6">
-        <v>27791</v>
+        <v>27809</v>
       </c>
       <c r="AU26" s="5">
         <f t="shared" si="17"/>
-        <v>0.9943824245026478</v>
+        <v>0.99502647774438246</v>
       </c>
       <c r="AV26" s="7">
         <v>14478</v>
@@ -5024,14 +5024,14 @@
       </c>
       <c r="AX26" s="4">
         <f t="shared" si="18"/>
-        <v>3182</v>
+        <v>3188</v>
       </c>
       <c r="AY26" s="6">
-        <v>14439</v>
+        <v>14445</v>
       </c>
       <c r="AZ26" s="5">
         <f t="shared" si="19"/>
-        <v>0.99730625777041026</v>
+        <v>0.9977206796518856</v>
       </c>
       <c r="BA26" s="7">
         <v>14902</v>
@@ -5041,14 +5041,14 @@
       </c>
       <c r="BC26" s="4">
         <f t="shared" si="20"/>
-        <v>3087</v>
+        <v>3095</v>
       </c>
       <c r="BD26" s="6">
-        <v>14553</v>
+        <v>14561</v>
       </c>
       <c r="BE26" s="5">
         <f t="shared" si="21"/>
-        <v>0.976580324788619</v>
+        <v>0.97711716548114347</v>
       </c>
       <c r="BF26" s="7">
         <v>28105</v>
@@ -5058,14 +5058,14 @@
       </c>
       <c r="BH26" s="4">
         <f t="shared" si="22"/>
-        <v>6563</v>
+        <v>6588</v>
       </c>
       <c r="BI26" s="6">
-        <v>27902</v>
+        <v>27927</v>
       </c>
       <c r="BJ26" s="5">
         <f t="shared" si="23"/>
-        <v>0.99277708592777081</v>
+        <v>0.99366660736523749</v>
       </c>
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
@@ -5083,14 +5083,14 @@
       </c>
       <c r="E27" s="4">
         <f t="shared" si="0"/>
-        <v>36747</v>
+        <v>36771</v>
       </c>
       <c r="F27" s="13">
-        <v>125281</v>
+        <v>125305</v>
       </c>
       <c r="G27" s="5">
         <f t="shared" si="1"/>
-        <v>0.97014023866126675</v>
+        <v>0.97032608779822982</v>
       </c>
       <c r="H27" s="7">
         <v>129298</v>
@@ -5100,14 +5100,14 @@
       </c>
       <c r="J27" s="4">
         <f t="shared" si="2"/>
-        <v>32466</v>
+        <v>32491</v>
       </c>
       <c r="K27" s="13">
-        <v>126131</v>
+        <v>126156</v>
       </c>
       <c r="L27" s="5">
         <f t="shared" si="3"/>
-        <v>0.97550619499141522</v>
+        <v>0.97569954678339954</v>
       </c>
       <c r="M27" s="7">
         <v>186733</v>
@@ -5117,14 +5117,14 @@
       </c>
       <c r="O27" s="4">
         <f t="shared" si="4"/>
-        <v>47803</v>
+        <v>47851</v>
       </c>
       <c r="P27" s="6">
-        <v>185351</v>
+        <v>185399</v>
       </c>
       <c r="Q27" s="5">
         <f t="shared" si="5"/>
-        <v>0.99259905854883712</v>
+        <v>0.99285611006088903</v>
       </c>
       <c r="R27" s="7">
         <v>126872</v>
@@ -5134,14 +5134,14 @@
       </c>
       <c r="T27" s="4">
         <f t="shared" si="6"/>
-        <v>32579</v>
+        <v>32607</v>
       </c>
       <c r="U27" s="13">
-        <v>125802</v>
+        <v>125830</v>
       </c>
       <c r="V27" s="5">
         <f t="shared" si="7"/>
-        <v>0.99156630304558924</v>
+        <v>0.99178699791916258</v>
       </c>
       <c r="W27" s="7">
         <v>129739</v>
@@ -5151,14 +5151,14 @@
       </c>
       <c r="Y27" s="4">
         <f t="shared" si="8"/>
-        <v>33827</v>
+        <v>33860</v>
       </c>
       <c r="Z27" s="13">
-        <v>126688</v>
+        <v>126721</v>
       </c>
       <c r="AA27" s="5">
         <f t="shared" si="9"/>
-        <v>0.97648355544593379</v>
+        <v>0.97673791227001905</v>
       </c>
       <c r="AB27" s="7">
         <v>188270</v>
@@ -5168,14 +5168,14 @@
       </c>
       <c r="AD27" s="4">
         <f t="shared" si="10"/>
-        <v>52490</v>
+        <v>52558</v>
       </c>
       <c r="AE27" s="6">
-        <v>186821</v>
+        <v>186889</v>
       </c>
       <c r="AF27" s="5">
         <f t="shared" si="11"/>
-        <v>0.99230360652254745</v>
+        <v>0.99266478992935681</v>
       </c>
       <c r="AG27" s="7">
         <v>127800</v>
@@ -5185,14 +5185,14 @@
       </c>
       <c r="AI27" s="4">
         <f t="shared" si="12"/>
-        <v>34219</v>
+        <v>34265</v>
       </c>
       <c r="AJ27" s="6">
-        <v>126905</v>
+        <v>126951</v>
       </c>
       <c r="AK27" s="5">
         <f t="shared" si="13"/>
-        <v>0.99299687010954618</v>
+        <v>0.99335680751173705</v>
       </c>
       <c r="AL27" s="7">
         <v>130262</v>
@@ -5202,14 +5202,14 @@
       </c>
       <c r="AN27" s="4">
         <f t="shared" si="14"/>
-        <v>30994</v>
+        <v>31040</v>
       </c>
       <c r="AO27" s="6">
-        <v>127828</v>
+        <v>127874</v>
       </c>
       <c r="AP27" s="5">
         <f t="shared" si="15"/>
-        <v>0.98131458138213756</v>
+        <v>0.98166771583424173</v>
       </c>
       <c r="AQ27" s="7">
         <v>189830</v>
@@ -5219,14 +5219,14 @@
       </c>
       <c r="AS27" s="4">
         <f t="shared" si="16"/>
-        <v>45067</v>
+        <v>45157</v>
       </c>
       <c r="AT27" s="6">
-        <v>188881</v>
+        <v>188971</v>
       </c>
       <c r="AU27" s="5">
         <f t="shared" si="17"/>
-        <v>0.99500079018068799</v>
+        <v>0.99547489859347837</v>
       </c>
       <c r="AV27" s="7">
         <v>128733</v>
@@ -5236,14 +5236,14 @@
       </c>
       <c r="AX27" s="4">
         <f t="shared" si="18"/>
-        <v>30891</v>
+        <v>30954</v>
       </c>
       <c r="AY27" s="6">
-        <v>128632</v>
+        <v>128695</v>
       </c>
       <c r="AZ27" s="5">
         <f t="shared" si="19"/>
-        <v>0.99921543038692484</v>
+        <v>0.99970481539310041</v>
       </c>
       <c r="BA27" s="7">
         <v>132099</v>
@@ -5253,14 +5253,14 @@
       </c>
       <c r="BC27" s="4">
         <f t="shared" si="20"/>
-        <v>31377</v>
+        <v>31446</v>
       </c>
       <c r="BD27" s="6">
-        <v>130053</v>
+        <v>130122</v>
       </c>
       <c r="BE27" s="5">
         <f t="shared" si="21"/>
-        <v>0.98451161628778416</v>
+        <v>0.98503395180887066</v>
       </c>
       <c r="BF27" s="7">
         <v>192460</v>
@@ -5270,14 +5270,14 @@
       </c>
       <c r="BH27" s="4">
         <f t="shared" si="22"/>
-        <v>65010</v>
+        <v>65145</v>
       </c>
       <c r="BI27" s="6">
-        <v>191416</v>
+        <v>191551</v>
       </c>
       <c r="BJ27" s="5">
         <f t="shared" si="23"/>
-        <v>0.99457549620700403</v>
+        <v>0.99527694066299488</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -5295,14 +5295,14 @@
       </c>
       <c r="E28" s="4">
         <f t="shared" si="0"/>
-        <v>69876</v>
+        <v>69893</v>
       </c>
       <c r="F28" s="13">
-        <v>409721</v>
+        <v>409738</v>
       </c>
       <c r="G28" s="5">
         <f t="shared" si="1"/>
-        <v>0.99123969981274584</v>
+        <v>0.99128082798263906</v>
       </c>
       <c r="H28" s="7">
         <v>423216</v>
@@ -5312,14 +5312,14 @@
       </c>
       <c r="J28" s="4">
         <f t="shared" si="2"/>
-        <v>63916</v>
+        <v>63942</v>
       </c>
       <c r="K28" s="13">
-        <v>413969</v>
+        <v>413995</v>
       </c>
       <c r="L28" s="5">
         <f t="shared" si="3"/>
-        <v>0.97815063702695548</v>
+        <v>0.97821207137726363</v>
       </c>
       <c r="M28" s="7">
         <v>688530</v>
@@ -5329,14 +5329,14 @@
       </c>
       <c r="O28" s="4">
         <f t="shared" si="4"/>
-        <v>102796</v>
+        <v>102848</v>
       </c>
       <c r="P28" s="6">
-        <v>680959</v>
+        <v>681011</v>
       </c>
       <c r="Q28" s="5">
         <f t="shared" si="5"/>
-        <v>0.98900411020580081</v>
+        <v>0.98907963342192784</v>
       </c>
       <c r="R28" s="7">
         <v>417505</v>
@@ -5346,14 +5346,14 @@
       </c>
       <c r="T28" s="4">
         <f t="shared" si="6"/>
-        <v>65508</v>
+        <v>65537</v>
       </c>
       <c r="U28" s="13">
-        <v>414337</v>
+        <v>414366</v>
       </c>
       <c r="V28" s="5">
         <f t="shared" si="7"/>
-        <v>0.9924120669213542</v>
+        <v>0.99248152716733928</v>
       </c>
       <c r="W28" s="7">
         <v>426115</v>
@@ -5363,14 +5363,14 @@
       </c>
       <c r="Y28" s="4">
         <f t="shared" si="8"/>
-        <v>67639</v>
+        <v>67669</v>
       </c>
       <c r="Z28" s="13">
-        <v>416304</v>
+        <v>416334</v>
       </c>
       <c r="AA28" s="5">
         <f t="shared" si="9"/>
-        <v>0.976975699048379</v>
+        <v>0.97704610257794255</v>
       </c>
       <c r="AB28" s="7">
         <v>693825</v>
@@ -5380,14 +5380,14 @@
       </c>
       <c r="AD28" s="4">
         <f t="shared" si="10"/>
-        <v>118149</v>
+        <v>118219</v>
       </c>
       <c r="AE28" s="6">
-        <v>686214</v>
+        <v>686284</v>
       </c>
       <c r="AF28" s="5">
         <f t="shared" si="11"/>
-        <v>0.98903037509458436</v>
+        <v>0.98913126508845894</v>
       </c>
       <c r="AG28" s="7">
         <v>421441</v>
@@ -5397,14 +5397,14 @@
       </c>
       <c r="AI28" s="4">
         <f t="shared" si="12"/>
-        <v>73182</v>
+        <v>73217</v>
       </c>
       <c r="AJ28" s="6">
-        <v>417022</v>
+        <v>417057</v>
       </c>
       <c r="AK28" s="5">
         <f t="shared" si="13"/>
-        <v>0.98951454652015347</v>
+        <v>0.98959759491838717</v>
       </c>
       <c r="AL28" s="7">
         <v>428935</v>
@@ -5414,14 +5414,14 @@
       </c>
       <c r="AN28" s="4">
         <f t="shared" si="14"/>
-        <v>62033</v>
+        <v>62077</v>
       </c>
       <c r="AO28" s="6">
-        <v>421264</v>
+        <v>421308</v>
       </c>
       <c r="AP28" s="5">
         <f t="shared" si="15"/>
-        <v>0.98211617144788832</v>
+        <v>0.98221875109282297</v>
       </c>
       <c r="AQ28" s="7">
         <v>700018</v>
@@ -5431,14 +5431,14 @@
       </c>
       <c r="AS28" s="4">
         <f t="shared" si="16"/>
-        <v>95208</v>
+        <v>95313</v>
       </c>
       <c r="AT28" s="6">
-        <v>695144</v>
+        <v>695249</v>
       </c>
       <c r="AU28" s="5">
         <f t="shared" si="17"/>
-        <v>0.99303732189743688</v>
+        <v>0.99318731804039329</v>
       </c>
       <c r="AV28" s="7">
         <v>428584</v>
@@ -5448,14 +5448,14 @@
       </c>
       <c r="AX28" s="4">
         <f t="shared" si="18"/>
-        <v>63304</v>
+        <v>63359</v>
       </c>
       <c r="AY28" s="6">
-        <v>426721</v>
+        <v>426776</v>
       </c>
       <c r="AZ28" s="5">
         <f t="shared" si="19"/>
-        <v>0.99565312750825974</v>
+        <v>0.99578145707725907</v>
       </c>
       <c r="BA28" s="7">
         <v>438333</v>
@@ -5465,14 +5465,14 @@
       </c>
       <c r="BC28" s="4">
         <f t="shared" si="20"/>
-        <v>63250</v>
+        <v>63318</v>
       </c>
       <c r="BD28" s="6">
-        <v>431701</v>
+        <v>431769</v>
       </c>
       <c r="BE28" s="5">
         <f t="shared" si="21"/>
-        <v>0.98486995047144521</v>
+        <v>0.98502508366926511</v>
       </c>
       <c r="BF28" s="7">
         <v>711748</v>
@@ -5482,14 +5482,14 @@
       </c>
       <c r="BH28" s="4">
         <f t="shared" si="22"/>
-        <v>139056</v>
+        <v>139216</v>
       </c>
       <c r="BI28" s="6">
-        <v>706065</v>
+        <v>706225</v>
       </c>
       <c r="BJ28" s="5">
         <f t="shared" si="23"/>
-        <v>0.99201543242833135</v>
+        <v>0.99224023109302728</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.3">
@@ -5507,14 +5507,14 @@
       </c>
       <c r="E29" s="4">
         <f t="shared" si="0"/>
-        <v>26022</v>
+        <v>26029</v>
       </c>
       <c r="F29" s="13">
-        <v>135535</v>
+        <v>135542</v>
       </c>
       <c r="G29" s="5">
         <f t="shared" si="1"/>
-        <v>0.99079637995818526</v>
+        <v>0.99084755179320727</v>
       </c>
       <c r="H29" s="7">
         <v>138439</v>
@@ -5524,14 +5524,14 @@
       </c>
       <c r="J29" s="4">
         <f t="shared" si="2"/>
-        <v>24293</v>
+        <v>24303</v>
       </c>
       <c r="K29" s="13">
-        <v>136672</v>
+        <v>136682</v>
       </c>
       <c r="L29" s="5">
         <f t="shared" si="3"/>
-        <v>0.98723625567939666</v>
+        <v>0.98730848965970575</v>
       </c>
       <c r="M29" s="7">
         <v>184711</v>
@@ -5541,14 +5541,14 @@
       </c>
       <c r="O29" s="4">
         <f t="shared" si="4"/>
-        <v>32693</v>
+        <v>32705</v>
       </c>
       <c r="P29" s="6">
-        <v>182795</v>
+        <v>182807</v>
       </c>
       <c r="Q29" s="5">
         <f t="shared" si="5"/>
-        <v>0.98962703899605331</v>
+        <v>0.98969200534889634</v>
       </c>
       <c r="R29" s="7">
         <v>138323</v>
@@ -5558,14 +5558,14 @@
       </c>
       <c r="T29" s="4">
         <f t="shared" si="6"/>
-        <v>26917</v>
+        <v>26927</v>
       </c>
       <c r="U29" s="13">
-        <v>136879</v>
+        <v>136889</v>
       </c>
       <c r="V29" s="5">
         <f t="shared" si="7"/>
-        <v>0.98956066597745851</v>
+        <v>0.98963296053440142</v>
       </c>
       <c r="W29" s="7">
         <v>139858</v>
@@ -5575,14 +5575,14 @@
       </c>
       <c r="Y29" s="4">
         <f t="shared" si="8"/>
-        <v>25743</v>
+        <v>25752</v>
       </c>
       <c r="Z29" s="13">
-        <v>137295</v>
+        <v>137304</v>
       </c>
       <c r="AA29" s="5">
         <f t="shared" si="9"/>
-        <v>0.98167426961632509</v>
+        <v>0.98173862060089523</v>
       </c>
       <c r="AB29" s="7">
         <v>187429</v>
@@ -5592,14 +5592,14 @@
       </c>
       <c r="AD29" s="4">
         <f t="shared" si="10"/>
-        <v>36073</v>
+        <v>36091</v>
       </c>
       <c r="AE29" s="6">
-        <v>184173</v>
+        <v>184191</v>
       </c>
       <c r="AF29" s="5">
         <f t="shared" si="11"/>
-        <v>0.98262808850284644</v>
+        <v>0.98272412486861693</v>
       </c>
       <c r="AG29" s="7">
         <v>139419</v>
@@ -5609,14 +5609,14 @@
       </c>
       <c r="AI29" s="4">
         <f t="shared" si="12"/>
-        <v>38024</v>
+        <v>38034</v>
       </c>
       <c r="AJ29" s="6">
-        <v>138019</v>
+        <v>138029</v>
       </c>
       <c r="AK29" s="5">
         <f t="shared" si="13"/>
-        <v>0.9899583270572877</v>
+        <v>0.99003005329259286</v>
       </c>
       <c r="AL29" s="7">
         <v>141276</v>
@@ -5626,14 +5626,14 @@
       </c>
       <c r="AN29" s="4">
         <f t="shared" si="14"/>
-        <v>23669</v>
+        <v>23679</v>
       </c>
       <c r="AO29" s="6">
-        <v>139175</v>
+        <v>139185</v>
       </c>
       <c r="AP29" s="5">
         <f t="shared" si="15"/>
-        <v>0.98512840114386024</v>
+        <v>0.98519918457487476</v>
       </c>
       <c r="AQ29" s="7">
         <v>188424</v>
@@ -5643,14 +5643,14 @@
       </c>
       <c r="AS29" s="4">
         <f t="shared" si="16"/>
-        <v>29811</v>
+        <v>29834</v>
       </c>
       <c r="AT29" s="6">
-        <v>186820</v>
+        <v>186843</v>
       </c>
       <c r="AU29" s="5">
         <f t="shared" si="17"/>
-        <v>0.99148728399779218</v>
+        <v>0.99160934912749965</v>
       </c>
       <c r="AV29" s="7">
         <v>141887</v>
@@ -5660,14 +5660,14 @@
       </c>
       <c r="AX29" s="4">
         <f t="shared" si="18"/>
-        <v>24987</v>
+        <v>24998</v>
       </c>
       <c r="AY29" s="6">
-        <v>140576</v>
+        <v>140587</v>
       </c>
       <c r="AZ29" s="5">
         <f t="shared" si="19"/>
-        <v>0.99076025287728964</v>
+        <v>0.99083777935963124</v>
       </c>
       <c r="BA29" s="7">
         <v>143795</v>
@@ -5677,14 +5677,14 @@
       </c>
       <c r="BC29" s="4">
         <f t="shared" si="20"/>
-        <v>25522</v>
+        <v>25538</v>
       </c>
       <c r="BD29" s="6">
-        <v>141658</v>
+        <v>141674</v>
       </c>
       <c r="BE29" s="5">
         <f t="shared" si="21"/>
-        <v>0.98513856531868282</v>
+        <v>0.98524983483431272</v>
       </c>
       <c r="BF29" s="7">
         <v>191754</v>
@@ -5694,14 +5694,14 @@
       </c>
       <c r="BH29" s="4">
         <f t="shared" si="22"/>
-        <v>43920</v>
+        <v>43956</v>
       </c>
       <c r="BI29" s="6">
-        <v>189230</v>
+        <v>189266</v>
       </c>
       <c r="BJ29" s="5">
         <f t="shared" si="23"/>
-        <v>0.98683730195980268</v>
+        <v>0.98702504250237288</v>
       </c>
     </row>
     <row r="30" spans="1:62" x14ac:dyDescent="0.3">
@@ -5719,14 +5719,14 @@
       </c>
       <c r="E30" s="4">
         <f t="shared" si="0"/>
-        <v>41587</v>
+        <v>41597</v>
       </c>
       <c r="F30" s="13">
-        <v>176260</v>
+        <v>176270</v>
       </c>
       <c r="G30" s="5">
         <f t="shared" si="1"/>
-        <v>0.98885809499231403</v>
+        <v>0.98891419723303753</v>
       </c>
       <c r="H30" s="7">
         <v>181910</v>
@@ -5736,14 +5736,14 @@
       </c>
       <c r="J30" s="4">
         <f t="shared" si="2"/>
-        <v>39136</v>
+        <v>39145</v>
       </c>
       <c r="K30" s="13">
-        <v>178405</v>
+        <v>178414</v>
       </c>
       <c r="L30" s="5">
         <f t="shared" si="3"/>
-        <v>0.98073223022373701</v>
+        <v>0.98078170523885433</v>
       </c>
       <c r="M30" s="7">
         <v>304709</v>
@@ -5753,14 +5753,14 @@
       </c>
       <c r="O30" s="4">
         <f t="shared" si="4"/>
-        <v>61674</v>
+        <v>61695</v>
       </c>
       <c r="P30" s="6">
-        <v>300945</v>
+        <v>300966</v>
       </c>
       <c r="Q30" s="5">
         <f t="shared" si="5"/>
-        <v>0.98764723063644333</v>
+        <v>0.98771614885021441</v>
       </c>
       <c r="R30" s="7">
         <v>179361</v>
@@ -5770,14 +5770,14 @@
       </c>
       <c r="T30" s="4">
         <f t="shared" si="6"/>
-        <v>37698</v>
+        <v>37709</v>
       </c>
       <c r="U30" s="13">
-        <v>178085</v>
+        <v>178096</v>
       </c>
       <c r="V30" s="5">
         <f t="shared" si="7"/>
-        <v>0.99288585589955458</v>
+        <v>0.99294718472800669</v>
       </c>
       <c r="W30" s="7">
         <v>184404</v>
@@ -5787,14 +5787,14 @@
       </c>
       <c r="Y30" s="4">
         <f t="shared" si="8"/>
-        <v>38727</v>
+        <v>38741</v>
       </c>
       <c r="Z30" s="13">
-        <v>179260</v>
+        <v>179274</v>
       </c>
       <c r="AA30" s="5">
         <f t="shared" si="9"/>
-        <v>0.97210472657859914</v>
+        <v>0.97218064684063255</v>
       </c>
       <c r="AB30" s="7">
         <v>307610</v>
@@ -5804,14 +5804,14 @@
       </c>
       <c r="AD30" s="4">
         <f t="shared" si="10"/>
-        <v>66688</v>
+        <v>66720</v>
       </c>
       <c r="AE30" s="6">
-        <v>303884</v>
+        <v>303916</v>
       </c>
       <c r="AF30" s="5">
         <f t="shared" si="11"/>
-        <v>0.98788725984200776</v>
+        <v>0.98799128766945155</v>
       </c>
       <c r="AG30" s="7">
         <v>180656</v>
@@ -5821,14 +5821,14 @@
       </c>
       <c r="AI30" s="4">
         <f t="shared" si="12"/>
-        <v>38749</v>
+        <v>38765</v>
       </c>
       <c r="AJ30" s="6">
-        <v>179075</v>
+        <v>179091</v>
       </c>
       <c r="AK30" s="5">
         <f t="shared" si="13"/>
-        <v>0.99124856080063772</v>
+        <v>0.99133712691524223</v>
       </c>
       <c r="AL30" s="7">
         <v>185185</v>
@@ -5838,14 +5838,14 @@
       </c>
       <c r="AN30" s="4">
         <f t="shared" si="14"/>
-        <v>34609</v>
+        <v>34634</v>
       </c>
       <c r="AO30" s="6">
-        <v>181830</v>
+        <v>181855</v>
       </c>
       <c r="AP30" s="5">
         <f t="shared" si="15"/>
-        <v>0.98188298188298184</v>
+        <v>0.98201798201798207</v>
       </c>
       <c r="AQ30" s="7">
         <v>311830</v>
@@ -5855,14 +5855,14 @@
       </c>
       <c r="AS30" s="4">
         <f t="shared" si="16"/>
-        <v>55991</v>
+        <v>56032</v>
       </c>
       <c r="AT30" s="6">
-        <v>308926</v>
+        <v>308967</v>
       </c>
       <c r="AU30" s="5">
         <f t="shared" si="17"/>
-        <v>0.99068723342847065</v>
+        <v>0.99081871532565824</v>
       </c>
       <c r="AV30" s="7">
         <v>184055</v>
@@ -5872,14 +5872,14 @@
       </c>
       <c r="AX30" s="4">
         <f t="shared" si="18"/>
-        <v>36866</v>
+        <v>36895</v>
       </c>
       <c r="AY30" s="6">
-        <v>182809</v>
+        <v>182838</v>
       </c>
       <c r="AZ30" s="5">
         <f t="shared" si="19"/>
-        <v>0.99323028442585093</v>
+        <v>0.9933878460242862</v>
       </c>
       <c r="BA30" s="7">
         <v>188792</v>
@@ -5889,14 +5889,14 @@
       </c>
       <c r="BC30" s="4">
         <f t="shared" si="20"/>
-        <v>37226</v>
+        <v>37264</v>
       </c>
       <c r="BD30" s="6">
-        <v>185106</v>
+        <v>185144</v>
       </c>
       <c r="BE30" s="5">
         <f t="shared" si="21"/>
-        <v>0.9804758676215094</v>
+        <v>0.9806771473367516</v>
       </c>
       <c r="BF30" s="7">
         <v>315967</v>
@@ -5906,14 +5906,14 @@
       </c>
       <c r="BH30" s="4">
         <f t="shared" si="22"/>
-        <v>79611</v>
+        <v>79688</v>
       </c>
       <c r="BI30" s="6">
-        <v>313318</v>
+        <v>313395</v>
       </c>
       <c r="BJ30" s="5">
         <f t="shared" si="23"/>
-        <v>0.99161621308554371</v>
+        <v>0.9918599094209205</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
@@ -5931,14 +5931,14 @@
       </c>
       <c r="E31" s="4">
         <f t="shared" si="0"/>
-        <v>21591</v>
+        <v>21592</v>
       </c>
       <c r="F31" s="13">
-        <v>78976</v>
+        <v>78977</v>
       </c>
       <c r="G31" s="5">
         <f t="shared" si="1"/>
-        <v>1.0039534735905422</v>
+        <v>1.0039661857242739</v>
       </c>
       <c r="H31" s="7">
         <v>80911</v>
@@ -5948,14 +5948,14 @@
       </c>
       <c r="J31" s="4">
         <f t="shared" si="2"/>
-        <v>18857</v>
+        <v>18859</v>
       </c>
       <c r="K31" s="13">
-        <v>80549</v>
+        <v>80551</v>
       </c>
       <c r="L31" s="5">
         <f t="shared" si="3"/>
-        <v>0.99552594826414209</v>
+        <v>0.99555066678201976</v>
       </c>
       <c r="M31" s="7">
         <v>142260</v>
@@ -5965,14 +5965,14 @@
       </c>
       <c r="O31" s="4">
         <f t="shared" si="4"/>
-        <v>37912</v>
+        <v>37923</v>
       </c>
       <c r="P31" s="6">
-        <v>142449</v>
+        <v>142460</v>
       </c>
       <c r="Q31" s="5">
         <f t="shared" si="5"/>
-        <v>1.0013285533530156</v>
+        <v>1.0014058765640377</v>
       </c>
       <c r="R31" s="7">
         <v>79665</v>
@@ -5982,14 +5982,14 @@
       </c>
       <c r="T31" s="4">
         <f t="shared" si="6"/>
-        <v>20842</v>
+        <v>20845</v>
       </c>
       <c r="U31" s="13">
-        <v>80188</v>
+        <v>80191</v>
       </c>
       <c r="V31" s="5">
         <f t="shared" si="7"/>
-        <v>1.0065649908993912</v>
+        <v>1.0066026485909747</v>
       </c>
       <c r="W31" s="7">
         <v>81657</v>
@@ -5999,14 +5999,14 @@
       </c>
       <c r="Y31" s="4">
         <f t="shared" si="8"/>
-        <v>20886</v>
+        <v>20890</v>
       </c>
       <c r="Z31" s="13">
-        <v>80903</v>
+        <v>80907</v>
       </c>
       <c r="AA31" s="5">
         <f t="shared" si="9"/>
-        <v>0.99076625396475504</v>
+        <v>0.99081523935486238</v>
       </c>
       <c r="AB31" s="7">
         <v>144167</v>
@@ -6016,14 +6016,14 @@
       </c>
       <c r="AD31" s="4">
         <f t="shared" si="10"/>
-        <v>39684</v>
+        <v>39696</v>
       </c>
       <c r="AE31" s="6">
-        <v>144321</v>
+        <v>144333</v>
       </c>
       <c r="AF31" s="5">
         <f t="shared" si="11"/>
-        <v>1.0010682056226459</v>
+        <v>1.0011514424244106</v>
       </c>
       <c r="AG31" s="7">
         <v>80917</v>
@@ -6033,14 +6033,14 @@
       </c>
       <c r="AI31" s="4">
         <f t="shared" si="12"/>
-        <v>21028</v>
+        <v>21032</v>
       </c>
       <c r="AJ31" s="6">
-        <v>81708</v>
+        <v>81712</v>
       </c>
       <c r="AK31" s="5">
         <f t="shared" si="13"/>
-        <v>1.0097754489167914</v>
+        <v>1.0098248822867877</v>
       </c>
       <c r="AL31" s="7">
         <v>83546</v>
@@ -6050,14 +6050,14 @@
       </c>
       <c r="AN31" s="4">
         <f t="shared" si="14"/>
-        <v>18182</v>
+        <v>18187</v>
       </c>
       <c r="AO31" s="6">
-        <v>82872</v>
+        <v>82877</v>
       </c>
       <c r="AP31" s="5">
         <f t="shared" si="15"/>
-        <v>0.9919325880353338</v>
+        <v>0.99199243530510139</v>
       </c>
       <c r="AQ31" s="7">
         <v>147023</v>
@@ -6067,14 +6067,14 @@
       </c>
       <c r="AS31" s="4">
         <f t="shared" si="16"/>
-        <v>33070</v>
+        <v>33084</v>
       </c>
       <c r="AT31" s="6">
-        <v>147025</v>
+        <v>147039</v>
       </c>
       <c r="AU31" s="5">
         <f t="shared" si="17"/>
-        <v>1.0000136033137672</v>
+        <v>1.0001088265101379</v>
       </c>
       <c r="AV31" s="7">
         <v>81694</v>
@@ -6084,14 +6084,14 @@
       </c>
       <c r="AX31" s="4">
         <f t="shared" si="18"/>
-        <v>18629</v>
+        <v>18633</v>
       </c>
       <c r="AY31" s="6">
-        <v>82604</v>
+        <v>82608</v>
       </c>
       <c r="AZ31" s="5">
         <f t="shared" si="19"/>
-        <v>1.0111391289445981</v>
+        <v>1.0111880921487502</v>
       </c>
       <c r="BA31" s="7">
         <v>83957</v>
@@ -6101,14 +6101,14 @@
       </c>
       <c r="BC31" s="4">
         <f t="shared" si="20"/>
-        <v>18471</v>
+        <v>18477</v>
       </c>
       <c r="BD31" s="6">
-        <v>83619</v>
+        <v>83625</v>
       </c>
       <c r="BE31" s="5">
         <f t="shared" si="21"/>
-        <v>0.99597412961396903</v>
+        <v>0.99604559476875065</v>
       </c>
       <c r="BF31" s="7">
         <v>148810</v>
@@ -6118,14 +6118,14 @@
       </c>
       <c r="BH31" s="4">
         <f t="shared" si="22"/>
-        <v>50267</v>
+        <v>50295</v>
       </c>
       <c r="BI31" s="6">
-        <v>149057</v>
+        <v>149085</v>
       </c>
       <c r="BJ31" s="5">
         <f t="shared" si="23"/>
-        <v>1.001659834688529</v>
+        <v>1.0018479940864189</v>
       </c>
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.3">
@@ -6143,14 +6143,14 @@
       </c>
       <c r="E32" s="4">
         <f t="shared" si="0"/>
-        <v>47084</v>
+        <v>47089</v>
       </c>
       <c r="F32" s="13">
-        <v>218148</v>
+        <v>218153</v>
       </c>
       <c r="G32" s="5">
         <f t="shared" si="1"/>
-        <v>0.99341964452418796</v>
+        <v>0.99344241392029797</v>
       </c>
       <c r="H32" s="7">
         <v>225984</v>
@@ -6160,14 +6160,14 @@
       </c>
       <c r="J32" s="4">
         <f t="shared" si="2"/>
-        <v>42408</v>
+        <v>42412</v>
       </c>
       <c r="K32" s="13">
-        <v>222629</v>
+        <v>222633</v>
       </c>
       <c r="L32" s="5">
         <f t="shared" si="3"/>
-        <v>0.98515381619937692</v>
+        <v>0.98517151656754465</v>
       </c>
       <c r="M32" s="7">
         <v>469379</v>
@@ -6177,14 +6177,14 @@
       </c>
       <c r="O32" s="4">
         <f t="shared" si="4"/>
-        <v>100148</v>
+        <v>100165</v>
       </c>
       <c r="P32" s="6">
-        <v>465875</v>
+        <v>465892</v>
       </c>
       <c r="Q32" s="5">
         <f t="shared" si="5"/>
-        <v>0.99253481727985271</v>
+        <v>0.99257103534670277</v>
       </c>
       <c r="R32" s="7">
         <v>220673</v>
@@ -6194,14 +6194,14 @@
       </c>
       <c r="T32" s="4">
         <f t="shared" si="6"/>
-        <v>47729</v>
+        <v>47735</v>
       </c>
       <c r="U32" s="13">
-        <v>219978</v>
+        <v>219984</v>
       </c>
       <c r="V32" s="5">
         <f t="shared" si="7"/>
-        <v>0.99685054356445968</v>
+        <v>0.99687773311642114</v>
       </c>
       <c r="W32" s="7">
         <v>228851</v>
@@ -6211,14 +6211,14 @@
       </c>
       <c r="Y32" s="4">
         <f t="shared" si="8"/>
-        <v>48085</v>
+        <v>48097</v>
       </c>
       <c r="Z32" s="13">
-        <v>223035</v>
+        <v>223047</v>
       </c>
       <c r="AA32" s="5">
         <f t="shared" si="9"/>
-        <v>0.97458608439552374</v>
+        <v>0.97463852025990705</v>
       </c>
       <c r="AB32" s="7">
         <v>476427</v>
@@ -6228,14 +6228,14 @@
       </c>
       <c r="AD32" s="4">
         <f t="shared" si="10"/>
-        <v>106608</v>
+        <v>106629</v>
       </c>
       <c r="AE32" s="6">
-        <v>471742</v>
+        <v>471763</v>
       </c>
       <c r="AF32" s="5">
         <f t="shared" si="11"/>
-        <v>0.99016638435688997</v>
+        <v>0.99021046246329447</v>
       </c>
       <c r="AG32" s="7">
         <v>224544</v>
@@ -6245,14 +6245,14 @@
       </c>
       <c r="AI32" s="4">
         <f t="shared" si="12"/>
-        <v>46684</v>
+        <v>46695</v>
       </c>
       <c r="AJ32" s="6">
-        <v>223768</v>
+        <v>223779</v>
       </c>
       <c r="AK32" s="5">
         <f t="shared" si="13"/>
-        <v>0.99654410716830555</v>
+        <v>0.99659309533988882</v>
       </c>
       <c r="AL32" s="7">
         <v>231787</v>
@@ -6262,14 +6262,14 @@
       </c>
       <c r="AN32" s="4">
         <f t="shared" si="14"/>
-        <v>39787</v>
+        <v>39804</v>
       </c>
       <c r="AO32" s="6">
-        <v>227513</v>
+        <v>227530</v>
       </c>
       <c r="AP32" s="5">
         <f t="shared" si="15"/>
-        <v>0.98156065698248818</v>
+        <v>0.98163400018120084</v>
       </c>
       <c r="AQ32" s="7">
         <v>484390</v>
@@ -6279,14 +6279,14 @@
       </c>
       <c r="AS32" s="4">
         <f t="shared" si="16"/>
-        <v>81068</v>
+        <v>81096</v>
       </c>
       <c r="AT32" s="6">
-        <v>480468</v>
+        <v>480496</v>
       </c>
       <c r="AU32" s="5">
         <f t="shared" si="17"/>
-        <v>0.99190321848097607</v>
+        <v>0.99196102314250911</v>
       </c>
       <c r="AV32" s="7">
         <v>227629</v>
@@ -6296,14 +6296,14 @@
       </c>
       <c r="AX32" s="4">
         <f t="shared" si="18"/>
-        <v>40939</v>
+        <v>40951</v>
       </c>
       <c r="AY32" s="6">
-        <v>227621</v>
+        <v>227633</v>
       </c>
       <c r="AZ32" s="5">
         <f t="shared" si="19"/>
-        <v>0.99996485509315591</v>
+        <v>1.0000175724534219</v>
       </c>
       <c r="BA32" s="7">
         <v>234918</v>
@@ -6313,14 +6313,14 @@
       </c>
       <c r="BC32" s="4">
         <f t="shared" si="20"/>
-        <v>43816</v>
+        <v>43834</v>
       </c>
       <c r="BD32" s="6">
-        <v>231995</v>
+        <v>232013</v>
       </c>
       <c r="BE32" s="5">
         <f t="shared" si="21"/>
-        <v>0.98755736044066444</v>
+        <v>0.98763398292170035</v>
       </c>
       <c r="BF32" s="7">
         <v>492680</v>
@@ -6330,14 +6330,14 @@
       </c>
       <c r="BH32" s="4">
         <f t="shared" si="22"/>
-        <v>132751</v>
+        <v>132809</v>
       </c>
       <c r="BI32" s="6">
-        <v>489687</v>
+        <v>489745</v>
       </c>
       <c r="BJ32" s="5">
         <f t="shared" si="23"/>
-        <v>0.99392506292116589</v>
+        <v>0.99404278639279042</v>
       </c>
     </row>
     <row r="33" spans="1:62" x14ac:dyDescent="0.3">
@@ -6355,14 +6355,14 @@
       </c>
       <c r="E33" s="20">
         <f t="shared" si="0"/>
-        <v>75783</v>
+        <v>75787</v>
       </c>
       <c r="F33" s="13">
-        <v>664232</v>
+        <v>664236</v>
       </c>
       <c r="G33" s="21">
         <f t="shared" si="1"/>
-        <v>1.0012360343195481</v>
+        <v>1.001242063755253</v>
       </c>
       <c r="H33" s="7">
         <v>674602</v>
@@ -6372,14 +6372,14 @@
       </c>
       <c r="J33" s="20">
         <f t="shared" si="2"/>
-        <v>68703</v>
+        <v>68709</v>
       </c>
       <c r="K33" s="13">
-        <v>671926</v>
+        <v>671932</v>
       </c>
       <c r="L33" s="21">
         <f t="shared" si="3"/>
-        <v>0.99603321662254185</v>
+        <v>0.99604211075567517</v>
       </c>
       <c r="M33" s="7">
         <v>1077651</v>
@@ -6389,14 +6389,14 @@
       </c>
       <c r="O33" s="20">
         <f t="shared" si="4"/>
-        <v>129433</v>
+        <v>129443</v>
       </c>
       <c r="P33" s="6">
-        <v>1076822</v>
+        <v>1076832</v>
       </c>
       <c r="Q33" s="21">
         <f t="shared" si="5"/>
-        <v>0.99923073425441078</v>
+        <v>0.99924001369645643</v>
       </c>
       <c r="R33" s="7">
         <v>670885</v>
@@ -6406,14 +6406,14 @@
       </c>
       <c r="T33" s="20">
         <f t="shared" si="6"/>
-        <v>79592</v>
+        <v>79600</v>
       </c>
       <c r="U33" s="13">
-        <v>672474</v>
+        <v>672482</v>
       </c>
       <c r="V33" s="21">
         <f t="shared" si="7"/>
-        <v>1.0023685132325213</v>
+        <v>1.0023804377799475</v>
       </c>
       <c r="W33" s="7">
         <v>679851</v>
@@ -6423,14 +6423,14 @@
       </c>
       <c r="Y33" s="20">
         <f t="shared" si="8"/>
-        <v>75694</v>
+        <v>75702</v>
       </c>
       <c r="Z33" s="13">
-        <v>678479</v>
+        <v>678487</v>
       </c>
       <c r="AA33" s="21">
         <f t="shared" si="9"/>
-        <v>0.99798191074220677</v>
+        <v>0.99799367802650873</v>
       </c>
       <c r="AB33" s="7">
         <v>1091619</v>
@@ -6440,14 +6440,14 @@
       </c>
       <c r="AD33" s="20">
         <f t="shared" si="10"/>
-        <v>137579</v>
+        <v>137592</v>
       </c>
       <c r="AE33" s="6">
-        <v>1090573</v>
+        <v>1090586</v>
       </c>
       <c r="AF33" s="21">
         <f t="shared" si="11"/>
-        <v>0.99904179022167994</v>
+        <v>0.99905369913861886</v>
       </c>
       <c r="AG33" s="7">
         <v>681949</v>
@@ -6457,14 +6457,14 @@
       </c>
       <c r="AI33" s="20">
         <f t="shared" si="12"/>
-        <v>85545</v>
+        <v>85554</v>
       </c>
       <c r="AJ33" s="6">
-        <v>683856</v>
+        <v>683865</v>
       </c>
       <c r="AK33" s="21">
         <f t="shared" si="13"/>
-        <v>1.0027963967980009</v>
+        <v>1.0028095942658468</v>
       </c>
       <c r="AL33" s="7">
         <v>691548</v>
@@ -6474,14 +6474,14 @@
       </c>
       <c r="AN33" s="20">
         <f t="shared" si="14"/>
-        <v>66486</v>
+        <v>66493</v>
       </c>
       <c r="AO33" s="6">
-        <v>689411</v>
+        <v>689418</v>
       </c>
       <c r="AP33" s="21">
         <f t="shared" si="15"/>
-        <v>0.99690983127707689</v>
+        <v>0.99691995349563589</v>
       </c>
       <c r="AQ33" s="7">
         <v>1107071</v>
@@ -6491,14 +6491,14 @@
       </c>
       <c r="AS33" s="20">
         <f t="shared" si="16"/>
-        <v>112162</v>
+        <v>112177</v>
       </c>
       <c r="AT33" s="6">
-        <v>1108805</v>
+        <v>1108820</v>
       </c>
       <c r="AU33" s="21">
         <f t="shared" si="17"/>
-        <v>1.0015662952059985</v>
+        <v>1.0015798444724864</v>
       </c>
       <c r="AV33" s="7">
         <v>697202</v>
@@ -6508,14 +6508,14 @@
       </c>
       <c r="AX33" s="20">
         <f t="shared" si="18"/>
-        <v>69913</v>
+        <v>69920</v>
       </c>
       <c r="AY33" s="6">
-        <v>700261</v>
+        <v>700268</v>
       </c>
       <c r="AZ33" s="21">
         <f t="shared" si="19"/>
-        <v>1.0043875376146367</v>
+        <v>1.004397577746478</v>
       </c>
       <c r="BA33" s="7">
         <v>707985</v>
@@ -6525,14 +6525,14 @@
       </c>
       <c r="BC33" s="20">
         <f t="shared" si="20"/>
-        <v>69593</v>
+        <v>69602</v>
       </c>
       <c r="BD33" s="6">
-        <v>709722</v>
+        <v>709731</v>
       </c>
       <c r="BE33" s="21">
         <f t="shared" si="21"/>
-        <v>1.0024534418102078</v>
+        <v>1.0024661539439395</v>
       </c>
       <c r="BF33" s="7">
         <v>1132408</v>
@@ -6542,14 +6542,14 @@
       </c>
       <c r="BH33" s="20">
         <f t="shared" si="22"/>
-        <v>174752</v>
+        <v>174787</v>
       </c>
       <c r="BI33" s="6">
-        <v>1133202</v>
+        <v>1133237</v>
       </c>
       <c r="BJ33" s="21">
         <f t="shared" si="23"/>
-        <v>1.0007011607123935</v>
+        <v>1.0007320683004712</v>
       </c>
     </row>
     <row r="34" spans="1:62" x14ac:dyDescent="0.3">
@@ -6755,14 +6755,14 @@
       </c>
       <c r="E35" s="4">
         <f t="shared" ref="E35:E48" si="24">F35-D35</f>
-        <v>2221</v>
+        <v>2222</v>
       </c>
       <c r="F35" s="13">
-        <v>11911</v>
+        <v>11912</v>
       </c>
       <c r="G35" s="5">
         <f t="shared" ref="G35:G48" si="25">F35/C35</f>
-        <v>0.99324549699799869</v>
+        <v>0.9933288859239493</v>
       </c>
       <c r="H35" s="7">
         <v>12014</v>
@@ -6772,14 +6772,14 @@
       </c>
       <c r="J35" s="4">
         <f t="shared" ref="J35:J48" si="26">K35-I35</f>
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="K35" s="13">
-        <v>11942</v>
+        <v>11943</v>
       </c>
       <c r="L35" s="5">
         <f t="shared" ref="L35:L48" si="27">K35/H35</f>
-        <v>0.99400699184285002</v>
+        <v>0.99409022806725489</v>
       </c>
       <c r="M35" s="7">
         <v>14733</v>
@@ -6789,14 +6789,14 @@
       </c>
       <c r="O35" s="4">
         <f t="shared" ref="O35:O48" si="28">P35-N35</f>
-        <v>2661</v>
+        <v>2662</v>
       </c>
       <c r="P35" s="6">
-        <v>14668</v>
+        <v>14669</v>
       </c>
       <c r="Q35" s="5">
         <f t="shared" ref="Q35:Q48" si="29">P35/M35</f>
-        <v>0.99558813547817826</v>
+        <v>0.99565601031697548</v>
       </c>
       <c r="R35" s="7">
         <v>12053</v>
@@ -6942,14 +6942,14 @@
       </c>
       <c r="BH35" s="4">
         <f t="shared" ref="BH35:BH48" si="45">BI35-BG35</f>
-        <v>3323</v>
+        <v>3324</v>
       </c>
       <c r="BI35" s="6">
-        <v>14963</v>
+        <v>14964</v>
       </c>
       <c r="BJ35" s="5">
         <f t="shared" ref="BJ35:BJ48" si="46">BI35/BF35</f>
-        <v>0.99666955305401983</v>
+        <v>0.99673616199293946</v>
       </c>
     </row>
     <row r="36" spans="1:62" x14ac:dyDescent="0.3">
@@ -6967,14 +6967,14 @@
       </c>
       <c r="E36" s="4">
         <f t="shared" si="24"/>
-        <v>186795</v>
+        <v>186813</v>
       </c>
       <c r="F36" s="13">
-        <v>888479</v>
+        <v>888497</v>
       </c>
       <c r="G36" s="5">
         <f t="shared" si="25"/>
-        <v>0.99285818051784058</v>
+        <v>0.99287829517136572</v>
       </c>
       <c r="H36" s="7">
         <v>910737</v>
@@ -6984,14 +6984,14 @@
       </c>
       <c r="J36" s="4">
         <f t="shared" si="26"/>
-        <v>161960</v>
+        <v>161978</v>
       </c>
       <c r="K36" s="13">
-        <v>898757</v>
+        <v>898775</v>
       </c>
       <c r="L36" s="5">
         <f t="shared" si="27"/>
-        <v>0.98684581827684614</v>
+        <v>0.98686558248978573</v>
       </c>
       <c r="M36" s="7">
         <v>1579599</v>
@@ -7001,14 +7001,14 @@
       </c>
       <c r="O36" s="4">
         <f t="shared" si="28"/>
-        <v>319579</v>
+        <v>319619</v>
       </c>
       <c r="P36" s="6">
-        <v>1568405</v>
+        <v>1568445</v>
       </c>
       <c r="Q36" s="5">
         <f t="shared" si="29"/>
-        <v>0.99291339131007295</v>
+        <v>0.99293871419265267</v>
       </c>
       <c r="R36" s="7">
         <v>901122</v>
@@ -7018,14 +7018,14 @@
       </c>
       <c r="T36" s="4">
         <f t="shared" si="30"/>
-        <v>174478</v>
+        <v>174504</v>
       </c>
       <c r="U36" s="13">
-        <v>898774</v>
+        <v>898800</v>
       </c>
       <c r="V36" s="5">
         <f t="shared" si="31"/>
-        <v>0.99739435947629729</v>
+        <v>0.99742321239521392</v>
       </c>
       <c r="W36" s="7">
         <v>923866</v>
@@ -7035,14 +7035,14 @@
       </c>
       <c r="Y36" s="4">
         <f t="shared" si="32"/>
-        <v>178520</v>
+        <v>178550</v>
       </c>
       <c r="Z36" s="13">
-        <v>907749</v>
+        <v>907779</v>
       </c>
       <c r="AA36" s="5">
         <f t="shared" si="33"/>
-        <v>0.98255482938001837</v>
+        <v>0.98258730162166374</v>
       </c>
       <c r="AB36" s="7">
         <v>1592928</v>
@@ -7052,14 +7052,14 @@
       </c>
       <c r="AD36" s="4">
         <f t="shared" si="34"/>
-        <v>337248</v>
+        <v>337312</v>
       </c>
       <c r="AE36" s="6">
-        <v>1585537</v>
+        <v>1585601</v>
       </c>
       <c r="AF36" s="5">
         <f t="shared" si="35"/>
-        <v>0.9953601167158842</v>
+        <v>0.99540029430080956</v>
       </c>
       <c r="AG36" s="7">
         <v>914936</v>
@@ -7069,14 +7069,14 @@
       </c>
       <c r="AI36" s="4">
         <f t="shared" si="12"/>
-        <v>305742</v>
+        <v>305786</v>
       </c>
       <c r="AJ36" s="6">
-        <v>912968</v>
+        <v>913012</v>
       </c>
       <c r="AK36" s="5">
         <f t="shared" si="36"/>
-        <v>0.99784902987749968</v>
+        <v>0.99789712067292136</v>
       </c>
       <c r="AL36" s="7">
         <v>934551</v>
@@ -7086,14 +7086,14 @@
       </c>
       <c r="AN36" s="4">
         <f t="shared" si="37"/>
-        <v>162939</v>
+        <v>162983</v>
       </c>
       <c r="AO36" s="6">
-        <v>923083</v>
+        <v>923127</v>
       </c>
       <c r="AP36" s="5">
         <f t="shared" si="38"/>
-        <v>0.98772886658941028</v>
+        <v>0.98777594802209834</v>
       </c>
       <c r="AQ36" s="7">
         <v>1610673</v>
@@ -7103,14 +7103,14 @@
       </c>
       <c r="AS36" s="4">
         <f t="shared" si="39"/>
-        <v>274982</v>
+        <v>275092</v>
       </c>
       <c r="AT36" s="6">
-        <v>1610202</v>
+        <v>1610312</v>
       </c>
       <c r="AU36" s="5">
         <f t="shared" si="40"/>
-        <v>0.9997075756531586</v>
+        <v>0.99977587008660351</v>
       </c>
       <c r="AV36" s="7">
         <v>933166</v>
@@ -7120,14 +7120,14 @@
       </c>
       <c r="AX36" s="4">
         <f t="shared" si="41"/>
-        <v>163511</v>
+        <v>163572</v>
       </c>
       <c r="AY36" s="6">
-        <v>934837</v>
+        <v>934898</v>
       </c>
       <c r="AZ36" s="5">
         <f t="shared" si="42"/>
-        <v>1.0017906781858748</v>
+        <v>1.001856047048435</v>
       </c>
       <c r="BA36" s="7">
         <v>952259</v>
@@ -7137,14 +7137,14 @@
       </c>
       <c r="BC36" s="4">
         <f t="shared" si="43"/>
-        <v>160663</v>
+        <v>160740</v>
       </c>
       <c r="BD36" s="6">
-        <v>945634</v>
+        <v>945711</v>
       </c>
       <c r="BE36" s="5">
         <f t="shared" si="44"/>
-        <v>0.99304285913811263</v>
+        <v>0.99312371949228095</v>
       </c>
       <c r="BF36" s="7">
         <v>1640364</v>
@@ -7154,14 +7154,14 @@
       </c>
       <c r="BH36" s="4">
         <f t="shared" si="45"/>
-        <v>394456</v>
+        <v>394649</v>
       </c>
       <c r="BI36" s="6">
-        <v>1638611</v>
+        <v>1638804</v>
       </c>
       <c r="BJ36" s="5">
         <f t="shared" si="46"/>
-        <v>0.99893133475253049</v>
+        <v>0.9990489915652867</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -7179,14 +7179,14 @@
       </c>
       <c r="E37" s="4">
         <f t="shared" si="24"/>
-        <v>134736</v>
+        <v>134766</v>
       </c>
       <c r="F37" s="13">
-        <v>700873</v>
+        <v>700903</v>
       </c>
       <c r="G37" s="5">
         <f t="shared" si="25"/>
-        <v>0.98743156465115234</v>
+        <v>0.98747383043530945</v>
       </c>
       <c r="H37" s="7">
         <v>717455</v>
@@ -7196,14 +7196,14 @@
       </c>
       <c r="J37" s="4">
         <f t="shared" si="26"/>
-        <v>120969</v>
+        <v>120999</v>
       </c>
       <c r="K37" s="13">
-        <v>706564</v>
+        <v>706594</v>
       </c>
       <c r="L37" s="5">
         <f t="shared" si="27"/>
-        <v>0.98481995386470234</v>
+        <v>0.98486176833390249</v>
       </c>
       <c r="M37" s="7">
         <v>885615</v>
@@ -7213,14 +7213,14 @@
       </c>
       <c r="O37" s="4">
         <f t="shared" si="28"/>
-        <v>157063</v>
+        <v>157111</v>
       </c>
       <c r="P37" s="6">
-        <v>877762</v>
+        <v>877810</v>
       </c>
       <c r="Q37" s="5">
         <f t="shared" si="29"/>
-        <v>0.99113271568345163</v>
+        <v>0.99118691530744174</v>
       </c>
       <c r="R37" s="7">
         <v>713906</v>
@@ -7230,14 +7230,14 @@
       </c>
       <c r="T37" s="4">
         <f t="shared" si="30"/>
-        <v>125339</v>
+        <v>125377</v>
       </c>
       <c r="U37" s="13">
-        <v>707647</v>
+        <v>707685</v>
       </c>
       <c r="V37" s="5">
         <f t="shared" si="31"/>
-        <v>0.99123273932422473</v>
+        <v>0.99128596762038701</v>
       </c>
       <c r="W37" s="7">
         <v>721933</v>
@@ -7247,14 +7247,14 @@
       </c>
       <c r="Y37" s="4">
         <f t="shared" si="32"/>
-        <v>128666</v>
+        <v>128707</v>
       </c>
       <c r="Z37" s="13">
-        <v>709289</v>
+        <v>709330</v>
       </c>
       <c r="AA37" s="5">
         <f t="shared" si="33"/>
-        <v>0.98248590935723956</v>
+        <v>0.98254270133100996</v>
       </c>
       <c r="AB37" s="7">
         <v>896229</v>
@@ -7264,14 +7264,14 @@
       </c>
       <c r="AD37" s="4">
         <f t="shared" si="34"/>
-        <v>180416</v>
+        <v>180475</v>
       </c>
       <c r="AE37" s="6">
-        <v>883204</v>
+        <v>883263</v>
       </c>
       <c r="AF37" s="5">
         <f t="shared" si="35"/>
-        <v>0.98546688402182925</v>
+        <v>0.98553271541090504</v>
       </c>
       <c r="AG37" s="7">
         <v>721282</v>
@@ -7281,14 +7281,14 @@
       </c>
       <c r="AI37" s="4">
         <f t="shared" si="12"/>
-        <v>136372</v>
+        <v>136424</v>
       </c>
       <c r="AJ37" s="6">
-        <v>711928</v>
+        <v>711980</v>
       </c>
       <c r="AK37" s="5">
         <f t="shared" si="36"/>
-        <v>0.98703142460230531</v>
+        <v>0.98710351845741329</v>
       </c>
       <c r="AL37" s="7">
         <v>727480</v>
@@ -7298,14 +7298,14 @@
       </c>
       <c r="AN37" s="4">
         <f t="shared" si="37"/>
-        <v>121886</v>
+        <v>121946</v>
       </c>
       <c r="AO37" s="6">
-        <v>717633</v>
+        <v>717693</v>
       </c>
       <c r="AP37" s="5">
         <f t="shared" si="38"/>
-        <v>0.98646423269368233</v>
+        <v>0.98654670918788145</v>
       </c>
       <c r="AQ37" s="7">
         <v>903787</v>
@@ -7315,14 +7315,14 @@
       </c>
       <c r="AS37" s="4">
         <f t="shared" si="39"/>
-        <v>145201</v>
+        <v>145290</v>
       </c>
       <c r="AT37" s="6">
-        <v>895620</v>
+        <v>895709</v>
       </c>
       <c r="AU37" s="5">
         <f t="shared" si="40"/>
-        <v>0.99096357880783859</v>
+        <v>0.99106205333778863</v>
       </c>
       <c r="AV37" s="7">
         <v>732294</v>
@@ -7332,14 +7332,14 @@
       </c>
       <c r="AX37" s="4">
         <f t="shared" si="41"/>
-        <v>125995</v>
+        <v>126068</v>
       </c>
       <c r="AY37" s="6">
-        <v>726205</v>
+        <v>726278</v>
       </c>
       <c r="AZ37" s="5">
         <f t="shared" si="42"/>
-        <v>0.99168503360672078</v>
+        <v>0.99178472034456111</v>
       </c>
       <c r="BA37" s="7">
         <v>740889</v>
@@ -7349,14 +7349,14 @@
       </c>
       <c r="BC37" s="4">
         <f t="shared" si="43"/>
-        <v>122882</v>
+        <v>122963</v>
       </c>
       <c r="BD37" s="6">
-        <v>731041</v>
+        <v>731122</v>
       </c>
       <c r="BE37" s="5">
         <f t="shared" si="44"/>
-        <v>0.98670786042173664</v>
+        <v>0.98681718853971379</v>
       </c>
       <c r="BF37" s="7">
         <v>918028</v>
@@ -7366,14 +7366,14 @@
       </c>
       <c r="BH37" s="4">
         <f t="shared" si="45"/>
-        <v>217233</v>
+        <v>217388</v>
       </c>
       <c r="BI37" s="6">
-        <v>908259</v>
+        <v>908414</v>
       </c>
       <c r="BJ37" s="5">
         <f t="shared" si="46"/>
-        <v>0.98935871237042883</v>
+        <v>0.98952755253652391</v>
       </c>
     </row>
     <row r="38" spans="1:62" x14ac:dyDescent="0.3">
@@ -7391,14 +7391,14 @@
       </c>
       <c r="E38" s="4">
         <f t="shared" si="24"/>
-        <v>6148</v>
+        <v>6149</v>
       </c>
       <c r="F38" s="13">
-        <v>24504</v>
+        <v>24505</v>
       </c>
       <c r="G38" s="5">
         <f t="shared" si="25"/>
-        <v>1.0061178402792035</v>
+        <v>1.0061588996099364</v>
       </c>
       <c r="H38" s="7">
         <v>24747</v>
@@ -7408,14 +7408,14 @@
       </c>
       <c r="J38" s="4">
         <f t="shared" si="26"/>
-        <v>5630</v>
+        <v>5631</v>
       </c>
       <c r="K38" s="13">
-        <v>24727</v>
+        <v>24728</v>
       </c>
       <c r="L38" s="5">
         <f t="shared" si="27"/>
-        <v>0.99919182123085626</v>
+        <v>0.99923223016931351</v>
       </c>
       <c r="M38" s="7">
         <v>37604</v>
@@ -7425,14 +7425,14 @@
       </c>
       <c r="O38" s="4">
         <f t="shared" si="28"/>
-        <v>8987</v>
+        <v>8988</v>
       </c>
       <c r="P38" s="6">
-        <v>37776</v>
+        <v>37777</v>
       </c>
       <c r="Q38" s="5">
         <f t="shared" si="29"/>
-        <v>1.0045739814913308</v>
+        <v>1.0046005744069779</v>
       </c>
       <c r="R38" s="7">
         <v>24596</v>
@@ -7442,14 +7442,14 @@
       </c>
       <c r="T38" s="4">
         <f t="shared" si="30"/>
-        <v>5847</v>
+        <v>5848</v>
       </c>
       <c r="U38" s="13">
-        <v>24825</v>
+        <v>24826</v>
       </c>
       <c r="V38" s="5">
         <f t="shared" si="31"/>
-        <v>1.0093104569848756</v>
+        <v>1.0093511140022768</v>
       </c>
       <c r="W38" s="7">
         <v>25148</v>
@@ -7459,14 +7459,14 @@
       </c>
       <c r="Y38" s="4">
         <f t="shared" si="32"/>
-        <v>6055</v>
+        <v>6056</v>
       </c>
       <c r="Z38" s="13">
-        <v>25007</v>
+        <v>25008</v>
       </c>
       <c r="AA38" s="5">
         <f t="shared" si="33"/>
-        <v>0.99439319230157464</v>
+        <v>0.99443295689518052</v>
       </c>
       <c r="AB38" s="7">
         <v>38035</v>
@@ -7476,14 +7476,14 @@
       </c>
       <c r="AD38" s="4">
         <f t="shared" si="34"/>
-        <v>9597</v>
+        <v>9602</v>
       </c>
       <c r="AE38" s="6">
-        <v>38185</v>
+        <v>38190</v>
       </c>
       <c r="AF38" s="5">
         <f t="shared" si="35"/>
-        <v>1.0039437360326016</v>
+        <v>1.0040751939003549</v>
       </c>
       <c r="AG38" s="7">
         <v>24962</v>
@@ -7493,14 +7493,14 @@
       </c>
       <c r="AI38" s="4">
         <f t="shared" si="12"/>
-        <v>6305</v>
+        <v>6308</v>
       </c>
       <c r="AJ38" s="6">
-        <v>25218</v>
+        <v>25221</v>
       </c>
       <c r="AK38" s="5">
         <f t="shared" si="36"/>
-        <v>1.0102555884945117</v>
+        <v>1.0103757711721817</v>
       </c>
       <c r="AL38" s="7">
         <v>25436</v>
@@ -7510,14 +7510,14 @@
       </c>
       <c r="AN38" s="4">
         <f t="shared" si="37"/>
-        <v>5898</v>
+        <v>5902</v>
       </c>
       <c r="AO38" s="6">
-        <v>25478</v>
+        <v>25482</v>
       </c>
       <c r="AP38" s="5">
         <f t="shared" si="38"/>
-        <v>1.0016512030193427</v>
+        <v>1.0018084604497564</v>
       </c>
       <c r="AQ38" s="7">
         <v>38569</v>
@@ -7527,14 +7527,14 @@
       </c>
       <c r="AS38" s="4">
         <f t="shared" si="39"/>
-        <v>8153</v>
+        <v>8160</v>
       </c>
       <c r="AT38" s="6">
-        <v>38889</v>
+        <v>38896</v>
       </c>
       <c r="AU38" s="5">
         <f t="shared" si="40"/>
-        <v>1.0082968186885841</v>
+        <v>1.008478311597397</v>
       </c>
       <c r="AV38" s="7">
         <v>25488</v>
@@ -7544,14 +7544,14 @@
       </c>
       <c r="AX38" s="4">
         <f t="shared" si="41"/>
-        <v>5635</v>
+        <v>5641</v>
       </c>
       <c r="AY38" s="6">
-        <v>25690</v>
+        <v>25696</v>
       </c>
       <c r="AZ38" s="5">
         <f t="shared" si="42"/>
-        <v>1.0079252981795355</v>
+        <v>1.0081607030759574</v>
       </c>
       <c r="BA38" s="7">
         <v>25933</v>
@@ -7561,14 +7561,14 @@
       </c>
       <c r="BC38" s="4">
         <f t="shared" si="43"/>
-        <v>5611</v>
+        <v>5617</v>
       </c>
       <c r="BD38" s="6">
-        <v>25959</v>
+        <v>25965</v>
       </c>
       <c r="BE38" s="5">
         <f t="shared" si="44"/>
-        <v>1.0010025835807659</v>
+        <v>1.0012339490224811</v>
       </c>
       <c r="BF38" s="7">
         <v>39379</v>
@@ -7578,14 +7578,14 @@
       </c>
       <c r="BH38" s="4">
         <f t="shared" si="45"/>
-        <v>11614</v>
+        <v>11625</v>
       </c>
       <c r="BI38" s="6">
-        <v>39517</v>
+        <v>39528</v>
       </c>
       <c r="BJ38" s="5">
         <f t="shared" si="46"/>
-        <v>1.0035044059016227</v>
+        <v>1.003783742603926</v>
       </c>
     </row>
     <row r="39" spans="1:62" x14ac:dyDescent="0.3">
@@ -7815,14 +7815,14 @@
       </c>
       <c r="E40" s="4">
         <f t="shared" si="24"/>
-        <v>64449</v>
+        <v>64470</v>
       </c>
       <c r="F40" s="13">
-        <v>289178</v>
+        <v>289199</v>
       </c>
       <c r="G40" s="5">
         <f t="shared" si="25"/>
-        <v>0.99051200898790193</v>
+        <v>0.99058393960568325</v>
       </c>
       <c r="H40" s="7">
         <v>293812</v>
@@ -7832,14 +7832,14 @@
       </c>
       <c r="J40" s="4">
         <f t="shared" si="26"/>
-        <v>59761</v>
+        <v>59785</v>
       </c>
       <c r="K40" s="13">
-        <v>290794</v>
+        <v>290818</v>
       </c>
       <c r="L40" s="5">
         <f t="shared" si="27"/>
-        <v>0.98972812546798639</v>
+        <v>0.98980981035492088</v>
       </c>
       <c r="M40" s="7">
         <v>351809</v>
@@ -7849,14 +7849,14 @@
       </c>
       <c r="O40" s="4">
         <f t="shared" si="28"/>
-        <v>72160</v>
+        <v>72192</v>
       </c>
       <c r="P40" s="6">
-        <v>349198</v>
+        <v>349230</v>
       </c>
       <c r="Q40" s="5">
         <f t="shared" si="29"/>
-        <v>0.99257835928017757</v>
+        <v>0.9926693177263799</v>
       </c>
       <c r="R40" s="7">
         <v>293831</v>
@@ -7866,14 +7866,14 @@
       </c>
       <c r="T40" s="4">
         <f t="shared" si="30"/>
-        <v>63237</v>
+        <v>63261</v>
       </c>
       <c r="U40" s="13">
-        <v>292845</v>
+        <v>292869</v>
       </c>
       <c r="V40" s="5">
         <f t="shared" si="31"/>
-        <v>0.99664432956359272</v>
+        <v>0.99672600916853571</v>
       </c>
       <c r="W40" s="7">
         <v>297227</v>
@@ -7883,14 +7883,14 @@
       </c>
       <c r="Y40" s="4">
         <f t="shared" si="32"/>
-        <v>66703</v>
+        <v>66728</v>
       </c>
       <c r="Z40" s="13">
-        <v>294248</v>
+        <v>294273</v>
       </c>
       <c r="AA40" s="5">
         <f t="shared" si="33"/>
-        <v>0.98997735737332071</v>
+        <v>0.99006146817079199</v>
       </c>
       <c r="AB40" s="7">
         <v>355500</v>
@@ -7900,14 +7900,14 @@
       </c>
       <c r="AD40" s="4">
         <f t="shared" si="34"/>
-        <v>82253</v>
+        <v>82290</v>
       </c>
       <c r="AE40" s="6">
-        <v>352804</v>
+        <v>352841</v>
       </c>
       <c r="AF40" s="5">
         <f t="shared" si="35"/>
-        <v>0.99241631504922645</v>
+        <v>0.99252039381153301</v>
       </c>
       <c r="AG40" s="7">
         <v>298328</v>
@@ -7917,14 +7917,14 @@
       </c>
       <c r="AI40" s="4">
         <f t="shared" si="12"/>
-        <v>79497</v>
+        <v>79527</v>
       </c>
       <c r="AJ40" s="6">
-        <v>295969</v>
+        <v>295999</v>
       </c>
       <c r="AK40" s="5">
         <f t="shared" si="36"/>
-        <v>0.99209259606875655</v>
+        <v>0.99219315652570328</v>
       </c>
       <c r="AL40" s="7">
         <v>299711</v>
@@ -7934,14 +7934,14 @@
       </c>
       <c r="AN40" s="4">
         <f t="shared" si="37"/>
-        <v>69557</v>
+        <v>69592</v>
       </c>
       <c r="AO40" s="6">
-        <v>297188</v>
+        <v>297223</v>
       </c>
       <c r="AP40" s="5">
         <f t="shared" si="38"/>
-        <v>0.99158189055456758</v>
+        <v>0.99169866971849552</v>
       </c>
       <c r="AQ40" s="7">
         <v>357015</v>
@@ -7951,14 +7951,14 @@
       </c>
       <c r="AS40" s="4">
         <f t="shared" si="39"/>
-        <v>76968</v>
+        <v>77018</v>
       </c>
       <c r="AT40" s="6">
-        <v>355165</v>
+        <v>355215</v>
       </c>
       <c r="AU40" s="5">
         <f t="shared" si="40"/>
-        <v>0.99481814489587272</v>
+        <v>0.9949581950338221</v>
       </c>
       <c r="AV40" s="7">
         <v>300800</v>
@@ -7968,14 +7968,14 @@
       </c>
       <c r="AX40" s="4">
         <f t="shared" si="41"/>
-        <v>66666</v>
+        <v>66714</v>
       </c>
       <c r="AY40" s="6">
-        <v>299366</v>
+        <v>299414</v>
       </c>
       <c r="AZ40" s="5">
         <f t="shared" si="42"/>
-        <v>0.99523271276595748</v>
+        <v>0.99539228723404261</v>
       </c>
       <c r="BA40" s="7">
         <v>303731</v>
@@ -7985,14 +7985,14 @@
       </c>
       <c r="BC40" s="4">
         <f t="shared" si="43"/>
-        <v>65462</v>
+        <v>65514</v>
       </c>
       <c r="BD40" s="6">
-        <v>300699</v>
+        <v>300751</v>
       </c>
       <c r="BE40" s="5">
         <f t="shared" si="44"/>
-        <v>0.99001748257504174</v>
+        <v>0.99018868669974414</v>
       </c>
       <c r="BF40" s="7">
         <v>361393</v>
@@ -8002,14 +8002,14 @@
       </c>
       <c r="BH40" s="4">
         <f t="shared" si="45"/>
-        <v>110665</v>
+        <v>110732</v>
       </c>
       <c r="BI40" s="6">
-        <v>358472</v>
+        <v>358539</v>
       </c>
       <c r="BJ40" s="5">
         <f t="shared" si="46"/>
-        <v>0.99191738633565119</v>
+        <v>0.99210278007598374</v>
       </c>
     </row>
     <row r="41" spans="1:62" x14ac:dyDescent="0.3">
@@ -8027,14 +8027,14 @@
       </c>
       <c r="E41" s="4">
         <f t="shared" si="24"/>
-        <v>153060</v>
+        <v>153102</v>
       </c>
       <c r="F41" s="13">
-        <v>944385</v>
+        <v>944427</v>
       </c>
       <c r="G41" s="5">
         <f t="shared" si="25"/>
-        <v>0.99157608923906559</v>
+        <v>0.99162018798666118</v>
       </c>
       <c r="H41" s="7">
         <v>959446</v>
@@ -8044,14 +8044,14 @@
       </c>
       <c r="J41" s="4">
         <f t="shared" si="26"/>
-        <v>141525</v>
+        <v>141566</v>
       </c>
       <c r="K41" s="13">
-        <v>948059</v>
+        <v>948100</v>
       </c>
       <c r="L41" s="5">
         <f t="shared" si="27"/>
-        <v>0.98813169266430834</v>
+        <v>0.98817442565814018</v>
       </c>
       <c r="M41" s="7">
         <v>1062442</v>
@@ -8061,14 +8061,14 @@
       </c>
       <c r="O41" s="4">
         <f t="shared" si="28"/>
-        <v>158461</v>
+        <v>158505</v>
       </c>
       <c r="P41" s="6">
-        <v>1051942</v>
+        <v>1051986</v>
       </c>
       <c r="Q41" s="5">
         <f t="shared" si="29"/>
-        <v>0.99011710756916615</v>
+        <v>0.99015852159459061</v>
       </c>
       <c r="R41" s="7">
         <v>959218</v>
@@ -8078,14 +8078,14 @@
       </c>
       <c r="T41" s="4">
         <f t="shared" si="30"/>
-        <v>144675</v>
+        <v>144720</v>
       </c>
       <c r="U41" s="13">
-        <v>951565</v>
+        <v>951610</v>
       </c>
       <c r="V41" s="5">
         <f t="shared" si="31"/>
-        <v>0.9920216259494713</v>
+        <v>0.99206853916419413</v>
       </c>
       <c r="W41" s="7">
         <v>961845</v>
@@ -8095,14 +8095,14 @@
       </c>
       <c r="Y41" s="4">
         <f t="shared" si="32"/>
-        <v>150947</v>
+        <v>150998</v>
       </c>
       <c r="Z41" s="13">
-        <v>950554</v>
+        <v>950605</v>
       </c>
       <c r="AA41" s="5">
         <f t="shared" si="33"/>
-        <v>0.98826110236056741</v>
+        <v>0.98831412545680442</v>
       </c>
       <c r="AB41" s="7">
         <v>1065577</v>
@@ -8112,14 +8112,14 @@
       </c>
       <c r="AD41" s="4">
         <f t="shared" si="34"/>
-        <v>183873</v>
+        <v>183933</v>
       </c>
       <c r="AE41" s="6">
-        <v>1055168</v>
+        <v>1055228</v>
       </c>
       <c r="AF41" s="5">
         <f t="shared" si="35"/>
-        <v>0.99023158345197015</v>
+        <v>0.99028789097362269</v>
       </c>
       <c r="AG41" s="7">
         <v>963364</v>
@@ -8129,14 +8129,14 @@
       </c>
       <c r="AI41" s="4">
         <f t="shared" si="12"/>
-        <v>171202</v>
+        <v>171259</v>
       </c>
       <c r="AJ41" s="6">
-        <v>956545</v>
+        <v>956602</v>
       </c>
       <c r="AK41" s="5">
         <f t="shared" si="36"/>
-        <v>0.99292167861784331</v>
+        <v>0.99298084628447814</v>
       </c>
       <c r="AL41" s="7">
         <v>968650</v>
@@ -8146,14 +8146,14 @@
       </c>
       <c r="AN41" s="4">
         <f t="shared" si="37"/>
-        <v>149810</v>
+        <v>149873</v>
       </c>
       <c r="AO41" s="6">
-        <v>959043</v>
+        <v>959106</v>
       </c>
       <c r="AP41" s="5">
         <f t="shared" si="38"/>
-        <v>0.99008207298817941</v>
+        <v>0.9901471119599442</v>
       </c>
       <c r="AQ41" s="7">
         <v>1071657</v>
@@ -8163,14 +8163,14 @@
       </c>
       <c r="AS41" s="4">
         <f t="shared" si="39"/>
-        <v>157037</v>
+        <v>157113</v>
       </c>
       <c r="AT41" s="6">
-        <v>1063442</v>
+        <v>1063518</v>
       </c>
       <c r="AU41" s="5">
         <f t="shared" si="40"/>
-        <v>0.9923343009936948</v>
+        <v>0.99240521920726499</v>
       </c>
       <c r="AV41" s="7">
         <v>970535</v>
@@ -8180,14 +8180,14 @@
       </c>
       <c r="AX41" s="4">
         <f t="shared" si="41"/>
-        <v>145001</v>
+        <v>145073</v>
       </c>
       <c r="AY41" s="6">
-        <v>964610</v>
+        <v>964682</v>
       </c>
       <c r="AZ41" s="5">
         <f t="shared" si="42"/>
-        <v>0.99389511970202005</v>
+        <v>0.99396930558918539</v>
       </c>
       <c r="BA41" s="7">
         <v>973311</v>
@@ -8197,14 +8197,14 @@
       </c>
       <c r="BC41" s="4">
         <f t="shared" si="43"/>
-        <v>140726</v>
+        <v>140806</v>
       </c>
       <c r="BD41" s="6">
-        <v>969298</v>
+        <v>969378</v>
       </c>
       <c r="BE41" s="5">
         <f t="shared" si="44"/>
-        <v>0.99587696019052496</v>
+        <v>0.99595915385729739</v>
       </c>
       <c r="BF41" s="7">
         <v>1078355</v>
@@ -8214,14 +8214,14 @@
       </c>
       <c r="BH41" s="4">
         <f t="shared" si="45"/>
-        <v>223372</v>
+        <v>223499</v>
       </c>
       <c r="BI41" s="6">
-        <v>1074199</v>
+        <v>1074326</v>
       </c>
       <c r="BJ41" s="5">
         <f t="shared" si="46"/>
-        <v>0.99614598161087953</v>
+        <v>0.99626375358764041</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.3">
@@ -8239,14 +8239,14 @@
       </c>
       <c r="E42" s="4">
         <f t="shared" si="24"/>
-        <v>3962</v>
+        <v>3963</v>
       </c>
       <c r="F42" s="13">
-        <v>18768</v>
+        <v>18769</v>
       </c>
       <c r="G42" s="5">
         <f t="shared" si="25"/>
-        <v>0.98706216472073205</v>
+        <v>0.98711475754707056</v>
       </c>
       <c r="H42" s="7">
         <v>19101</v>
@@ -8256,14 +8256,14 @@
       </c>
       <c r="J42" s="4">
         <f t="shared" si="26"/>
-        <v>3749</v>
+        <v>3750</v>
       </c>
       <c r="K42" s="13">
-        <v>18921</v>
+        <v>18922</v>
       </c>
       <c r="L42" s="5">
         <f t="shared" si="27"/>
-        <v>0.99057640961206217</v>
+        <v>0.9906287628919952</v>
       </c>
       <c r="M42" s="7">
         <v>21195</v>
@@ -8273,14 +8273,14 @@
       </c>
       <c r="O42" s="4">
         <f t="shared" si="28"/>
-        <v>4119</v>
+        <v>4120</v>
       </c>
       <c r="P42" s="6">
-        <v>20996</v>
+        <v>20997</v>
       </c>
       <c r="Q42" s="5">
         <f t="shared" si="29"/>
-        <v>0.99061099315876389</v>
+        <v>0.99065817409766455</v>
       </c>
       <c r="R42" s="7">
         <v>19210</v>
@@ -8290,14 +8290,14 @@
       </c>
       <c r="T42" s="4">
         <f t="shared" si="30"/>
-        <v>3888</v>
+        <v>3889</v>
       </c>
       <c r="U42" s="13">
-        <v>19071</v>
+        <v>19072</v>
       </c>
       <c r="V42" s="5">
         <f t="shared" si="31"/>
-        <v>0.99276418532014576</v>
+        <v>0.99281624154086412</v>
       </c>
       <c r="W42" s="7">
         <v>19384</v>
@@ -8307,14 +8307,14 @@
       </c>
       <c r="Y42" s="4">
         <f t="shared" si="32"/>
-        <v>4056</v>
+        <v>4057</v>
       </c>
       <c r="Z42" s="13">
-        <v>19081</v>
+        <v>19082</v>
       </c>
       <c r="AA42" s="5">
         <f t="shared" si="33"/>
-        <v>0.98436855138258361</v>
+        <v>0.98442014032191494</v>
       </c>
       <c r="AB42" s="7">
         <v>21463</v>
@@ -8324,14 +8324,14 @@
       </c>
       <c r="AD42" s="4">
         <f t="shared" si="34"/>
-        <v>4688</v>
+        <v>4690</v>
       </c>
       <c r="AE42" s="6">
-        <v>21155</v>
+        <v>21157</v>
       </c>
       <c r="AF42" s="5">
         <f t="shared" si="35"/>
-        <v>0.98564972277873553</v>
+        <v>0.98574290639705542</v>
       </c>
       <c r="AG42" s="7">
         <v>19423</v>
@@ -8341,14 +8341,14 @@
       </c>
       <c r="AI42" s="4">
         <f t="shared" si="12"/>
-        <v>4570</v>
+        <v>4572</v>
       </c>
       <c r="AJ42" s="6">
-        <v>19184</v>
+        <v>19186</v>
       </c>
       <c r="AK42" s="5">
         <f t="shared" si="36"/>
-        <v>0.98769500077228034</v>
+        <v>0.98779797147711479</v>
       </c>
       <c r="AL42" s="7">
         <v>19535</v>
@@ -8358,14 +8358,14 @@
       </c>
       <c r="AN42" s="4">
         <f t="shared" si="37"/>
-        <v>4088</v>
+        <v>4090</v>
       </c>
       <c r="AO42" s="6">
-        <v>19240</v>
+        <v>19242</v>
       </c>
       <c r="AP42" s="5">
         <f t="shared" si="38"/>
-        <v>0.98489889941131303</v>
+        <v>0.9850012797542872</v>
       </c>
       <c r="AQ42" s="7">
         <v>21570</v>
@@ -8375,14 +8375,14 @@
       </c>
       <c r="AS42" s="4">
         <f t="shared" si="39"/>
-        <v>4091</v>
+        <v>4093</v>
       </c>
       <c r="AT42" s="6">
-        <v>21289</v>
+        <v>21291</v>
       </c>
       <c r="AU42" s="5">
         <f t="shared" si="40"/>
-        <v>0.98697264719517852</v>
+        <v>0.98706536856745475</v>
       </c>
       <c r="AV42" s="7">
         <v>19570</v>
@@ -8392,14 +8392,14 @@
       </c>
       <c r="AX42" s="4">
         <f t="shared" si="41"/>
-        <v>3692</v>
+        <v>3694</v>
       </c>
       <c r="AY42" s="6">
-        <v>19324</v>
+        <v>19326</v>
       </c>
       <c r="AZ42" s="5">
         <f t="shared" si="42"/>
-        <v>0.98742973939703627</v>
+        <v>0.98753193663771077</v>
       </c>
       <c r="BA42" s="7">
         <v>19671</v>
@@ -8409,14 +8409,14 @@
       </c>
       <c r="BC42" s="4">
         <f t="shared" si="43"/>
-        <v>3590</v>
+        <v>3592</v>
       </c>
       <c r="BD42" s="6">
-        <v>19426</v>
+        <v>19428</v>
       </c>
       <c r="BE42" s="5">
         <f t="shared" si="44"/>
-        <v>0.9875451171775711</v>
+        <v>0.9876467896904072</v>
       </c>
       <c r="BF42" s="7">
         <v>21792</v>
@@ -8426,14 +8426,14 @@
       </c>
       <c r="BH42" s="4">
         <f t="shared" si="45"/>
-        <v>5297</v>
+        <v>5299</v>
       </c>
       <c r="BI42" s="6">
-        <v>21594</v>
+        <v>21596</v>
       </c>
       <c r="BJ42" s="5">
         <f t="shared" si="46"/>
-        <v>0.99091409691629961</v>
+        <v>0.99100587371512483</v>
       </c>
     </row>
     <row r="43" spans="1:62" x14ac:dyDescent="0.3">
@@ -8587,14 +8587,14 @@
       </c>
       <c r="AS43" s="4">
         <f t="shared" si="39"/>
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="AT43" s="6">
-        <v>4760</v>
+        <v>4761</v>
       </c>
       <c r="AU43" s="5">
         <f t="shared" si="40"/>
-        <v>1.0016835016835017</v>
+        <v>1.0018939393939394</v>
       </c>
       <c r="AV43" s="7">
         <v>3858</v>
@@ -8621,14 +8621,14 @@
       </c>
       <c r="BC43" s="4">
         <f t="shared" si="43"/>
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="BD43" s="6">
-        <v>3867</v>
+        <v>3868</v>
       </c>
       <c r="BE43" s="5">
         <f t="shared" si="44"/>
-        <v>0.99103024090210146</v>
+        <v>0.99128651973347004</v>
       </c>
       <c r="BF43" s="7">
         <v>4852</v>
@@ -8638,14 +8638,14 @@
       </c>
       <c r="BH43" s="4">
         <f t="shared" si="45"/>
-        <v>1879</v>
+        <v>1882</v>
       </c>
       <c r="BI43" s="6">
-        <v>4808</v>
+        <v>4811</v>
       </c>
       <c r="BJ43" s="5">
         <f t="shared" si="46"/>
-        <v>0.99093157460840886</v>
+        <v>0.99154987633965375</v>
       </c>
     </row>
     <row r="44" spans="1:62" x14ac:dyDescent="0.3">
@@ -8663,14 +8663,14 @@
       </c>
       <c r="E44" s="4">
         <f t="shared" si="24"/>
-        <v>81989</v>
+        <v>82004</v>
       </c>
       <c r="F44" s="13">
-        <v>359476</v>
+        <v>359491</v>
       </c>
       <c r="G44" s="5">
         <f t="shared" si="25"/>
-        <v>0.98833168371274605</v>
+        <v>0.98837292422742773</v>
       </c>
       <c r="H44" s="7">
         <v>368428</v>
@@ -8680,14 +8680,14 @@
       </c>
       <c r="J44" s="4">
         <f t="shared" si="26"/>
-        <v>72509</v>
+        <v>72525</v>
       </c>
       <c r="K44" s="13">
-        <v>362228</v>
+        <v>362244</v>
       </c>
       <c r="L44" s="5">
         <f t="shared" si="27"/>
-        <v>0.98317174590422007</v>
+        <v>0.98321517365672528</v>
       </c>
       <c r="M44" s="7">
         <v>437654</v>
@@ -8697,14 +8697,14 @@
       </c>
       <c r="O44" s="4">
         <f t="shared" si="28"/>
-        <v>87116</v>
+        <v>87139</v>
       </c>
       <c r="P44" s="6">
-        <v>430582</v>
+        <v>430605</v>
       </c>
       <c r="Q44" s="5">
         <f t="shared" si="29"/>
-        <v>0.9838411164984211</v>
+        <v>0.98389366942836121</v>
       </c>
       <c r="R44" s="7">
         <v>368991</v>
@@ -8714,14 +8714,14 @@
       </c>
       <c r="T44" s="4">
         <f t="shared" si="30"/>
-        <v>80923</v>
+        <v>80941</v>
       </c>
       <c r="U44" s="13">
-        <v>364673</v>
+        <v>364691</v>
       </c>
       <c r="V44" s="5">
         <f t="shared" si="31"/>
-        <v>0.9882978175619459</v>
+        <v>0.98834659923954782</v>
       </c>
       <c r="W44" s="7">
         <v>375659</v>
@@ -8731,14 +8731,14 @@
       </c>
       <c r="Y44" s="4">
         <f t="shared" si="32"/>
-        <v>79205</v>
+        <v>79230</v>
       </c>
       <c r="Z44" s="13">
-        <v>364704</v>
+        <v>364729</v>
       </c>
       <c r="AA44" s="5">
         <f t="shared" si="33"/>
-        <v>0.97083791417216148</v>
+        <v>0.97090446388879281</v>
       </c>
       <c r="AB44" s="7">
         <v>443838</v>
@@ -8748,14 +8748,14 @@
       </c>
       <c r="AD44" s="4">
         <f t="shared" si="34"/>
-        <v>99871</v>
+        <v>99906</v>
       </c>
       <c r="AE44" s="6">
-        <v>433630</v>
+        <v>433665</v>
       </c>
       <c r="AF44" s="5">
         <f t="shared" si="35"/>
-        <v>0.97700061734236365</v>
+        <v>0.97707947494356051</v>
       </c>
       <c r="AG44" s="7">
         <v>373881</v>
@@ -8765,14 +8765,14 @@
       </c>
       <c r="AI44" s="4">
         <f t="shared" si="12"/>
-        <v>83368</v>
+        <v>83396</v>
       </c>
       <c r="AJ44" s="6">
-        <v>366830</v>
+        <v>366858</v>
       </c>
       <c r="AK44" s="5">
         <f t="shared" si="36"/>
-        <v>0.98114105825115483</v>
+        <v>0.98121594838999571</v>
       </c>
       <c r="AL44" s="7">
         <v>377474</v>
@@ -8782,14 +8782,14 @@
       </c>
       <c r="AN44" s="4">
         <f t="shared" si="37"/>
-        <v>74567</v>
+        <v>74601</v>
       </c>
       <c r="AO44" s="6">
-        <v>370035</v>
+        <v>370069</v>
       </c>
       <c r="AP44" s="5">
         <f t="shared" si="38"/>
-        <v>0.9802926824099143</v>
+        <v>0.98038275483874382</v>
       </c>
       <c r="AQ44" s="7">
         <v>447335</v>
@@ -8799,14 +8799,14 @@
       </c>
       <c r="AS44" s="4">
         <f t="shared" si="39"/>
-        <v>79831</v>
+        <v>79875</v>
       </c>
       <c r="AT44" s="6">
-        <v>440442</v>
+        <v>440486</v>
       </c>
       <c r="AU44" s="5">
         <f t="shared" si="40"/>
-        <v>0.98459096650161515</v>
+        <v>0.98468932679088383</v>
       </c>
       <c r="AV44" s="7">
         <v>379419</v>
@@ -8816,14 +8816,14 @@
       </c>
       <c r="AX44" s="4">
         <f t="shared" si="41"/>
-        <v>74547</v>
+        <v>74590</v>
       </c>
       <c r="AY44" s="6">
-        <v>374385</v>
+        <v>374428</v>
       </c>
       <c r="AZ44" s="5">
         <f t="shared" si="42"/>
-        <v>0.98673234603433146</v>
+        <v>0.98684567720646565</v>
       </c>
       <c r="BA44" s="7">
         <v>384239</v>
@@ -8833,14 +8833,14 @@
       </c>
       <c r="BC44" s="4">
         <f t="shared" si="43"/>
-        <v>73226</v>
+        <v>73270</v>
       </c>
       <c r="BD44" s="6">
-        <v>377136</v>
+        <v>377180</v>
       </c>
       <c r="BE44" s="5">
         <f t="shared" si="44"/>
-        <v>0.98151410970775999</v>
+        <v>0.98162862176926335</v>
       </c>
       <c r="BF44" s="7">
         <v>454173</v>
@@ -8850,14 +8850,14 @@
       </c>
       <c r="BH44" s="4">
         <f t="shared" si="45"/>
-        <v>118469</v>
+        <v>118537</v>
       </c>
       <c r="BI44" s="6">
-        <v>447932</v>
+        <v>448000</v>
       </c>
       <c r="BJ44" s="5">
         <f t="shared" si="46"/>
-        <v>0.98625854024787907</v>
+        <v>0.98640826293064532</v>
       </c>
     </row>
     <row r="45" spans="1:62" x14ac:dyDescent="0.3">
@@ -8875,14 +8875,14 @@
       </c>
       <c r="E45" s="4">
         <f t="shared" si="24"/>
-        <v>56607</v>
+        <v>56617</v>
       </c>
       <c r="F45" s="13">
-        <v>262426</v>
+        <v>262436</v>
       </c>
       <c r="G45" s="5">
         <f t="shared" si="25"/>
-        <v>0.98426236394596089</v>
+        <v>0.98429987022826326</v>
       </c>
       <c r="H45" s="7">
         <v>269495</v>
@@ -8892,14 +8892,14 @@
       </c>
       <c r="J45" s="4">
         <f t="shared" si="26"/>
-        <v>50194</v>
+        <v>50204</v>
       </c>
       <c r="K45" s="13">
-        <v>263760</v>
+        <v>263770</v>
       </c>
       <c r="L45" s="5">
         <f t="shared" si="27"/>
-        <v>0.97871945676172101</v>
+        <v>0.97875656320154358</v>
       </c>
       <c r="M45" s="7">
         <v>320759</v>
@@ -8909,14 +8909,14 @@
       </c>
       <c r="O45" s="4">
         <f t="shared" si="28"/>
-        <v>60839</v>
+        <v>60853</v>
       </c>
       <c r="P45" s="6">
-        <v>314761</v>
+        <v>314775</v>
       </c>
       <c r="Q45" s="5">
         <f t="shared" si="29"/>
-        <v>0.98130060263312957</v>
+        <v>0.9813442491091442</v>
       </c>
       <c r="R45" s="7">
         <v>267358</v>
@@ -8926,14 +8926,14 @@
       </c>
       <c r="T45" s="4">
         <f t="shared" si="30"/>
-        <v>51921</v>
+        <v>51934</v>
       </c>
       <c r="U45" s="13">
-        <v>263973</v>
+        <v>263986</v>
       </c>
       <c r="V45" s="5">
         <f t="shared" si="31"/>
-        <v>0.9873390734520755</v>
+        <v>0.98738769739450472</v>
       </c>
       <c r="W45" s="7">
         <v>269851</v>
@@ -8943,14 +8943,14 @@
       </c>
       <c r="Y45" s="4">
         <f t="shared" si="32"/>
-        <v>56918</v>
+        <v>56929</v>
       </c>
       <c r="Z45" s="13">
-        <v>263922</v>
+        <v>263933</v>
       </c>
       <c r="AA45" s="5">
         <f t="shared" si="33"/>
-        <v>0.97802861579167766</v>
+        <v>0.97806937902768565</v>
       </c>
       <c r="AB45" s="7">
         <v>321990</v>
@@ -8960,14 +8960,14 @@
       </c>
       <c r="AD45" s="4">
         <f t="shared" si="34"/>
-        <v>71968</v>
+        <v>71984</v>
       </c>
       <c r="AE45" s="6">
-        <v>316375</v>
+        <v>316391</v>
       </c>
       <c r="AF45" s="5">
         <f t="shared" si="35"/>
-        <v>0.98256157023510049</v>
+        <v>0.98261126121929254</v>
       </c>
       <c r="AG45" s="7">
         <v>270238</v>
@@ -8977,14 +8977,14 @@
       </c>
       <c r="AI45" s="4">
         <f t="shared" si="12"/>
-        <v>57415</v>
+        <v>57429</v>
       </c>
       <c r="AJ45" s="6">
-        <v>266676</v>
+        <v>266690</v>
       </c>
       <c r="AK45" s="5">
         <f t="shared" si="36"/>
-        <v>0.98681902619172734</v>
+        <v>0.98687083237738582</v>
       </c>
       <c r="AL45" s="7">
         <v>273027</v>
@@ -8994,14 +8994,14 @@
       </c>
       <c r="AN45" s="4">
         <f t="shared" si="37"/>
-        <v>52468</v>
+        <v>52485</v>
       </c>
       <c r="AO45" s="6">
-        <v>269425</v>
+        <v>269442</v>
       </c>
       <c r="AP45" s="5">
         <f t="shared" si="38"/>
-        <v>0.98680716559168136</v>
+        <v>0.98686943049588505</v>
       </c>
       <c r="AQ45" s="7">
         <v>326184</v>
@@ -9011,14 +9011,14 @@
       </c>
       <c r="AS45" s="4">
         <f t="shared" si="39"/>
-        <v>60851</v>
+        <v>60872</v>
       </c>
       <c r="AT45" s="6">
-        <v>322988</v>
+        <v>323009</v>
       </c>
       <c r="AU45" s="5">
         <f t="shared" si="40"/>
-        <v>0.99020184926299271</v>
+        <v>0.99026623010325465</v>
       </c>
       <c r="AV45" s="7">
         <v>274208</v>
@@ -9028,14 +9028,14 @@
       </c>
       <c r="AX45" s="4">
         <f t="shared" si="41"/>
-        <v>52503</v>
+        <v>52522</v>
       </c>
       <c r="AY45" s="6">
-        <v>272441</v>
+        <v>272460</v>
       </c>
       <c r="AZ45" s="5">
         <f t="shared" si="42"/>
-        <v>0.99355598669623058</v>
+        <v>0.99362527716186255</v>
       </c>
       <c r="BA45" s="7">
         <v>277741</v>
@@ -9045,14 +9045,14 @@
       </c>
       <c r="BC45" s="4">
         <f t="shared" si="43"/>
-        <v>50376</v>
+        <v>50396</v>
       </c>
       <c r="BD45" s="6">
-        <v>274771</v>
+        <v>274791</v>
       </c>
       <c r="BE45" s="5">
         <f t="shared" si="44"/>
-        <v>0.989306584191747</v>
+        <v>0.98937859372580927</v>
       </c>
       <c r="BF45" s="7">
         <v>331328</v>
@@ -9062,14 +9062,14 @@
       </c>
       <c r="BH45" s="4">
         <f t="shared" si="45"/>
-        <v>87260</v>
+        <v>87302</v>
       </c>
       <c r="BI45" s="6">
-        <v>329139</v>
+        <v>329181</v>
       </c>
       <c r="BJ45" s="5">
         <f t="shared" si="46"/>
-        <v>0.99339325381495069</v>
+        <v>0.9935200164187753</v>
       </c>
     </row>
     <row r="46" spans="1:62" x14ac:dyDescent="0.3">
@@ -9087,14 +9087,14 @@
       </c>
       <c r="E46" s="4">
         <f t="shared" si="24"/>
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="F46" s="13">
-        <v>2478</v>
+        <v>2479</v>
       </c>
       <c r="G46" s="5">
         <f t="shared" si="25"/>
-        <v>1.023121387283237</v>
+        <v>1.023534269199009</v>
       </c>
       <c r="H46" s="7">
         <v>2553</v>
@@ -9104,14 +9104,14 @@
       </c>
       <c r="J46" s="4">
         <f t="shared" si="26"/>
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="K46" s="13">
-        <v>2555</v>
+        <v>2556</v>
       </c>
       <c r="L46" s="5">
         <f t="shared" si="27"/>
-        <v>1.0007833920877398</v>
+        <v>1.0011750881316099</v>
       </c>
       <c r="M46" s="7">
         <v>7561</v>
@@ -9121,14 +9121,14 @@
       </c>
       <c r="O46" s="4">
         <f t="shared" si="28"/>
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="P46" s="6">
-        <v>7679</v>
+        <v>7680</v>
       </c>
       <c r="Q46" s="5">
         <f t="shared" si="29"/>
-        <v>1.0156064012696733</v>
+        <v>1.0157386589075519</v>
       </c>
       <c r="R46" s="7">
         <v>2328</v>
@@ -9138,14 +9138,14 @@
       </c>
       <c r="T46" s="4">
         <f t="shared" si="30"/>
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="U46" s="13">
-        <v>2391</v>
+        <v>2392</v>
       </c>
       <c r="V46" s="5">
         <f t="shared" si="31"/>
-        <v>1.027061855670103</v>
+        <v>1.0274914089347078</v>
       </c>
       <c r="W46" s="7">
         <v>2515</v>
@@ -9155,14 +9155,14 @@
       </c>
       <c r="Y46" s="4">
         <f t="shared" si="32"/>
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="Z46" s="13">
-        <v>2475</v>
+        <v>2477</v>
       </c>
       <c r="AA46" s="5">
         <f t="shared" si="33"/>
-        <v>0.98409542743538769</v>
+        <v>0.98489065606361825</v>
       </c>
       <c r="AB46" s="7">
         <v>7764</v>
@@ -9172,14 +9172,14 @@
       </c>
       <c r="AD46" s="4">
         <f t="shared" si="34"/>
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="AE46" s="6">
-        <v>7902</v>
+        <v>7903</v>
       </c>
       <c r="AF46" s="5">
         <f t="shared" si="35"/>
-        <v>1.017774343122102</v>
+        <v>1.0179031427099434</v>
       </c>
       <c r="AG46" s="7">
         <v>2401</v>
@@ -9189,14 +9189,14 @@
       </c>
       <c r="AI46" s="4">
         <f t="shared" si="12"/>
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="AJ46" s="6">
-        <v>2471</v>
+        <v>2472</v>
       </c>
       <c r="AK46" s="5">
         <f t="shared" si="36"/>
-        <v>1.0291545189504374</v>
+        <v>1.0295710120783008</v>
       </c>
       <c r="AL46" s="7">
         <v>2561</v>
@@ -9206,14 +9206,14 @@
       </c>
       <c r="AN46" s="4">
         <f t="shared" si="37"/>
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AO46" s="6">
-        <v>2563</v>
+        <v>2564</v>
       </c>
       <c r="AP46" s="5">
         <f t="shared" si="38"/>
-        <v>1.0007809449433815</v>
+        <v>1.0011714174150723</v>
       </c>
       <c r="AQ46" s="7">
         <v>7981</v>
@@ -9223,14 +9223,14 @@
       </c>
       <c r="AS46" s="4">
         <f t="shared" si="39"/>
-        <v>1884</v>
+        <v>1885</v>
       </c>
       <c r="AT46" s="6">
-        <v>8149</v>
+        <v>8150</v>
       </c>
       <c r="AU46" s="5">
         <f t="shared" si="40"/>
-        <v>1.021049993735121</v>
+        <v>1.0211752913168777</v>
       </c>
       <c r="AV46" s="7">
         <v>2437</v>
@@ -9240,14 +9240,14 @@
       </c>
       <c r="AX46" s="4">
         <f t="shared" si="41"/>
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AY46" s="6">
-        <v>2512</v>
+        <v>2513</v>
       </c>
       <c r="AZ46" s="5">
         <f t="shared" si="42"/>
-        <v>1.030775543701272</v>
+        <v>1.0311858842839556</v>
       </c>
       <c r="BA46" s="7">
         <v>2592</v>
@@ -9257,14 +9257,14 @@
       </c>
       <c r="BC46" s="4">
         <f t="shared" si="43"/>
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="BD46" s="6">
-        <v>2576</v>
+        <v>2577</v>
       </c>
       <c r="BE46" s="5">
         <f t="shared" si="44"/>
-        <v>0.99382716049382713</v>
+        <v>0.99421296296296291</v>
       </c>
       <c r="BF46" s="7">
         <v>8179</v>
@@ -9274,14 +9274,14 @@
       </c>
       <c r="BH46" s="4">
         <f t="shared" si="45"/>
-        <v>1877</v>
+        <v>1879</v>
       </c>
       <c r="BI46" s="6">
-        <v>8326</v>
+        <v>8328</v>
       </c>
       <c r="BJ46" s="5">
         <f t="shared" si="46"/>
-        <v>1.0179728573175204</v>
+        <v>1.0182173859885071</v>
       </c>
     </row>
     <row r="47" spans="1:62" x14ac:dyDescent="0.3">
@@ -9497,10 +9497,10 @@
       </c>
     </row>
     <row r="48" spans="1:62" x14ac:dyDescent="0.3">
-      <c r="A48" s="23" t="s">
+      <c r="A48" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="B48" s="23"/>
+      <c r="B48" s="27"/>
       <c r="C48" s="9">
         <f>SUM(C10:C47)</f>
         <v>8203132</v>
@@ -9511,15 +9511,15 @@
       </c>
       <c r="E48" s="11">
         <f t="shared" si="24"/>
-        <v>1531564</v>
+        <v>1531931</v>
       </c>
       <c r="F48" s="10">
         <f>SUM(F10:F47)</f>
-        <v>8130457</v>
+        <v>8130824</v>
       </c>
       <c r="G48" s="12">
         <f t="shared" si="25"/>
-        <v>0.99114057898861074</v>
+        <v>0.99118531799805243</v>
       </c>
       <c r="H48" s="9">
         <f>SUM(H10:H47)</f>
@@ -9531,15 +9531,15 @@
       </c>
       <c r="J48" s="11">
         <f t="shared" si="26"/>
-        <v>1394075</v>
+        <v>1394484</v>
       </c>
       <c r="K48" s="10">
         <f>SUM(K10:K47)</f>
-        <v>8216994</v>
+        <v>8217403</v>
       </c>
       <c r="L48" s="12">
         <f t="shared" si="27"/>
-        <v>0.96600737819974747</v>
+        <v>0.96605546111397178</v>
       </c>
       <c r="M48" s="9">
         <f>SUM(M10:M47)</f>
@@ -9551,15 +9551,15 @@
       </c>
       <c r="O48" s="11">
         <f t="shared" si="28"/>
-        <v>2225139</v>
+        <v>2225857</v>
       </c>
       <c r="P48" s="10">
         <f>SUM(P10:P47)</f>
-        <v>12635393</v>
+        <v>12636111</v>
       </c>
       <c r="Q48" s="12">
         <f t="shared" si="29"/>
-        <v>0.99119172919177911</v>
+        <v>0.99124805317486053</v>
       </c>
       <c r="R48" s="9">
         <f>SUM(R10:R47)</f>
@@ -9571,15 +9571,15 @@
       </c>
       <c r="T48" s="11">
         <f t="shared" si="30"/>
-        <v>1484726</v>
+        <v>1485202</v>
       </c>
       <c r="U48" s="10">
         <f>SUM(U10:U47)</f>
-        <v>8215307</v>
+        <v>8215783</v>
       </c>
       <c r="V48" s="12">
         <f t="shared" si="31"/>
-        <v>0.9941858938341116</v>
+        <v>0.9942434975834864</v>
       </c>
       <c r="W48" s="9">
         <f>SUM(W10:W47)</f>
@@ -9591,15 +9591,15 @@
       </c>
       <c r="Y48" s="11">
         <f t="shared" si="32"/>
-        <v>1502920</v>
+        <v>1503456</v>
       </c>
       <c r="Z48" s="10">
         <f>SUM(Z10:Z47)</f>
-        <v>8255547</v>
+        <v>8256083</v>
       </c>
       <c r="AA48" s="12">
         <f t="shared" si="33"/>
-        <v>0.98101321552923615</v>
+        <v>0.98107690883550935</v>
       </c>
       <c r="AB48" s="9">
         <f>SUM(AB10:AB47)</f>
@@ -9611,15 +9611,15 @@
       </c>
       <c r="AD48" s="11">
         <f t="shared" si="34"/>
-        <v>2452778</v>
+        <v>2453729</v>
       </c>
       <c r="AE48" s="10">
         <f>SUM(AE10:AE47)</f>
-        <v>12733238</v>
+        <v>12734189</v>
       </c>
       <c r="AF48" s="12">
         <f t="shared" si="35"/>
-        <v>0.98943216373805509</v>
+        <v>0.98950606088721027</v>
       </c>
       <c r="AG48" s="9">
         <f>SUM(AG10:AG47)</f>
@@ -9631,15 +9631,15 @@
       </c>
       <c r="AI48" s="11">
         <f t="shared" ref="AI48" si="47">AJ48-AH48</f>
-        <v>1729931</v>
+        <v>1730557</v>
       </c>
       <c r="AJ48" s="10">
         <f>SUM(AJ10:AJ47)</f>
-        <v>8291269</v>
+        <v>8291895</v>
       </c>
       <c r="AK48" s="12">
         <f t="shared" ref="AK48" si="48">AJ48/AG48</f>
-        <v>0.99239812509747416</v>
+        <v>0.99247305225594784</v>
       </c>
       <c r="AL48" s="9">
         <f>SUM(AL10:AL47)</f>
@@ -9651,15 +9651,15 @@
       </c>
       <c r="AN48" s="11">
         <f t="shared" si="37"/>
-        <v>1399458</v>
+        <v>1400179</v>
       </c>
       <c r="AO48" s="10">
         <f>SUM(AO10:AO47)</f>
-        <v>8366944</v>
+        <v>8367665</v>
       </c>
       <c r="AP48" s="12">
         <f t="shared" si="38"/>
-        <v>0.98597611345812786</v>
+        <v>0.98606107742798388</v>
       </c>
       <c r="AQ48" s="9">
         <f>SUM(AQ10:AQ47)</f>
@@ -9671,15 +9671,15 @@
       </c>
       <c r="AS48" s="11">
         <f t="shared" si="39"/>
-        <v>2053369</v>
+        <v>2054718</v>
       </c>
       <c r="AT48" s="10">
         <f>SUM(AT10:AT47)</f>
-        <v>12912163</v>
+        <v>12913512</v>
       </c>
       <c r="AU48" s="12">
         <f t="shared" si="40"/>
-        <v>0.9935236342069439</v>
+        <v>0.9936274327248642</v>
       </c>
       <c r="AV48" s="9">
         <f>SUM(AV10:AV47)</f>
@@ -9691,15 +9691,15 @@
       </c>
       <c r="AX48" s="11">
         <f t="shared" si="41"/>
-        <v>1420368</v>
+        <v>1421237</v>
       </c>
       <c r="AY48" s="10">
         <f>SUM(AY10:AY47)</f>
-        <v>8448839</v>
+        <v>8449708</v>
       </c>
       <c r="AZ48" s="12">
         <f t="shared" si="42"/>
-        <v>0.99628858038612489</v>
+        <v>0.99639105301891573</v>
       </c>
       <c r="BA48" s="9">
         <f>SUM(BA10:BA47)</f>
@@ -9711,15 +9711,15 @@
       </c>
       <c r="BC48" s="11">
         <f t="shared" si="43"/>
-        <v>1410417</v>
+        <v>1411440</v>
       </c>
       <c r="BD48" s="10">
         <f>SUM(BD10:BD47)</f>
-        <v>8540471</v>
+        <v>8541494</v>
       </c>
       <c r="BE48" s="12">
         <f t="shared" si="44"/>
-        <v>0.98795558840847286</v>
+        <v>0.98807392831817353</v>
       </c>
       <c r="BF48" s="9">
         <f>SUM(BF10:BF47)</f>
@@ -9731,15 +9731,15 @@
       </c>
       <c r="BH48" s="11">
         <f t="shared" si="45"/>
-        <v>2969866</v>
+        <v>2972095</v>
       </c>
       <c r="BI48" s="10">
         <f>SUM(BI10:BI47)</f>
-        <v>13128484</v>
+        <v>13130713</v>
       </c>
       <c r="BJ48" s="12">
         <f t="shared" si="46"/>
-        <v>0.993927785420053</v>
+        <v>0.99409653796099384</v>
       </c>
     </row>
     <row r="49" spans="1:62" x14ac:dyDescent="0.3">
@@ -10191,10 +10191,12 @@
       <c r="BJ55" s="1"/>
     </row>
     <row r="56" spans="1:62" x14ac:dyDescent="0.3">
-      <c r="A56" s="1"/>
-      <c r="B56" s="1"/>
-      <c r="C56" s="1"/>
-      <c r="D56" s="1"/>
+      <c r="A56" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="B56" s="19"/>
+      <c r="C56" s="19"/>
+      <c r="D56" s="19"/>
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
@@ -10255,10 +10257,6 @@
       <c r="BJ56" s="1"/>
     </row>
     <row r="57" spans="1:62" x14ac:dyDescent="0.3">
-      <c r="A57" s="1"/>
-      <c r="B57" s="1"/>
-      <c r="C57" s="1"/>
-      <c r="D57" s="1"/>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
@@ -10319,12 +10317,6 @@
       <c r="BJ57" s="1"/>
     </row>
     <row r="58" spans="1:62" x14ac:dyDescent="0.3">
-      <c r="A58" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="B58" s="19"/>
-      <c r="C58" s="19"/>
-      <c r="D58" s="19"/>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
@@ -10444,128 +10436,14 @@
       <c r="BI59" s="1"/>
       <c r="BJ59" s="1"/>
     </row>
-    <row r="60" spans="1:62" x14ac:dyDescent="0.3">
-      <c r="E60" s="1"/>
-      <c r="F60" s="1"/>
-      <c r="G60" s="1"/>
-      <c r="H60" s="1"/>
-      <c r="I60" s="1"/>
-      <c r="J60" s="1"/>
-      <c r="K60" s="1"/>
-      <c r="L60" s="1"/>
-      <c r="M60" s="1"/>
-      <c r="N60" s="1"/>
-      <c r="O60" s="1"/>
-      <c r="P60" s="1"/>
-      <c r="Q60" s="1"/>
-      <c r="R60" s="1"/>
-      <c r="S60" s="1"/>
-      <c r="T60" s="1"/>
-      <c r="U60" s="1"/>
-      <c r="V60" s="1"/>
-      <c r="W60" s="1"/>
-      <c r="X60" s="1"/>
-      <c r="Y60" s="1"/>
-      <c r="Z60" s="1"/>
-      <c r="AA60" s="1"/>
-      <c r="AB60" s="1"/>
-      <c r="AC60" s="1"/>
-      <c r="AD60" s="1"/>
-      <c r="AE60" s="1"/>
-      <c r="AF60" s="1"/>
-      <c r="AG60" s="1"/>
-      <c r="AH60" s="1"/>
-      <c r="AI60" s="1"/>
-      <c r="AJ60" s="1"/>
-      <c r="AK60" s="1"/>
-      <c r="AL60" s="1"/>
-      <c r="AM60" s="1"/>
-      <c r="AN60" s="1"/>
-      <c r="AO60" s="1"/>
-      <c r="AP60" s="1"/>
-      <c r="AQ60" s="1"/>
-      <c r="AR60" s="1"/>
-      <c r="AS60" s="1"/>
-      <c r="AT60" s="1"/>
-      <c r="AU60" s="1"/>
-      <c r="AV60" s="1"/>
-      <c r="AW60" s="1"/>
-      <c r="AX60" s="1"/>
-      <c r="AY60" s="1"/>
-      <c r="AZ60" s="1"/>
-      <c r="BA60" s="1"/>
-      <c r="BB60" s="1"/>
-      <c r="BC60" s="1"/>
-      <c r="BD60" s="1"/>
-      <c r="BE60" s="1"/>
-      <c r="BF60" s="1"/>
-      <c r="BG60" s="1"/>
-      <c r="BH60" s="1"/>
-      <c r="BI60" s="1"/>
-      <c r="BJ60" s="1"/>
-    </row>
-    <row r="61" spans="1:62" x14ac:dyDescent="0.3">
-      <c r="E61" s="1"/>
-      <c r="F61" s="1"/>
-      <c r="G61" s="1"/>
-      <c r="H61" s="1"/>
-      <c r="I61" s="1"/>
-      <c r="J61" s="1"/>
-      <c r="K61" s="1"/>
-      <c r="L61" s="1"/>
-      <c r="M61" s="1"/>
-      <c r="N61" s="1"/>
-      <c r="O61" s="1"/>
-      <c r="P61" s="1"/>
-      <c r="Q61" s="1"/>
-      <c r="R61" s="1"/>
-      <c r="S61" s="1"/>
-      <c r="T61" s="1"/>
-      <c r="U61" s="1"/>
-      <c r="V61" s="1"/>
-      <c r="W61" s="1"/>
-      <c r="X61" s="1"/>
-      <c r="Y61" s="1"/>
-      <c r="Z61" s="1"/>
-      <c r="AA61" s="1"/>
-      <c r="AB61" s="1"/>
-      <c r="AC61" s="1"/>
-      <c r="AD61" s="1"/>
-      <c r="AE61" s="1"/>
-      <c r="AF61" s="1"/>
-      <c r="AG61" s="1"/>
-      <c r="AH61" s="1"/>
-      <c r="AI61" s="1"/>
-      <c r="AJ61" s="1"/>
-      <c r="AK61" s="1"/>
-      <c r="AL61" s="1"/>
-      <c r="AM61" s="1"/>
-      <c r="AN61" s="1"/>
-      <c r="AO61" s="1"/>
-      <c r="AP61" s="1"/>
-      <c r="AQ61" s="1"/>
-      <c r="AR61" s="1"/>
-      <c r="AS61" s="1"/>
-      <c r="AT61" s="1"/>
-      <c r="AU61" s="1"/>
-      <c r="AV61" s="1"/>
-      <c r="AW61" s="1"/>
-      <c r="AX61" s="1"/>
-      <c r="AY61" s="1"/>
-      <c r="AZ61" s="1"/>
-      <c r="BA61" s="1"/>
-      <c r="BB61" s="1"/>
-      <c r="BC61" s="1"/>
-      <c r="BD61" s="1"/>
-      <c r="BE61" s="1"/>
-      <c r="BF61" s="1"/>
-      <c r="BG61" s="1"/>
-      <c r="BH61" s="1"/>
-      <c r="BI61" s="1"/>
-      <c r="BJ61" s="1"/>
-    </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="R8:V8"/>
+    <mergeCell ref="M8:Q8"/>
+    <mergeCell ref="C8:G8"/>
     <mergeCell ref="BF8:BJ8"/>
     <mergeCell ref="H8:L8"/>
     <mergeCell ref="A3:B3"/>
@@ -10576,12 +10454,6 @@
     <mergeCell ref="AL8:AP8"/>
     <mergeCell ref="AG8:AK8"/>
     <mergeCell ref="AB8:AF8"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="R8:V8"/>
-    <mergeCell ref="M8:Q8"/>
-    <mergeCell ref="C8:G8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
